--- a/Students.xlsx
+++ b/Students.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$90</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1706,8 +1706,1169 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>922525106001</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>AASHIFA SAHANAJ M</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>aashifasahanaj</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/aashifasahanaj/</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>922525106002</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>AAZHIGA N</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>AAZHIGA</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/AAZHIGA/</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>922525106004</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Abirami R</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>abirami8072</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/abirami8072/</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>922525106018</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>AMIRDAVARSINI K S</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>amirda_varsini_2007</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/amirda_varsini_2007/</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>922525106022</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ANUJA S</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>anuja008</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/anuja008/</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>922525106023</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>ANUSRI R</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Anusri_2008</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Anusri_2008/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>922525106024</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ANUSYA B</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>ANUSYA_30</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/ANUSYA_30/</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>922525106046</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>BOOMIKA T</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>boomikat1206</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/boomikat1206/</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>922525106060</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>DESMA SHALINI K</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>desmashalini</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/desmashalini/</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>922525106063</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>DHANASRI R</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Dhanasri_r</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Dhanasri_r/</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>922525106064</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>DHANIKA S</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>922525106065</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>DHANUSHRI D</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>bo</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/bo/</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>922525106071</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>DHARANI V</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/c/</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>922525106092</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>ELAVARASU P</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>d</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/d/</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>922525106119</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>HAVISHMATHI S</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/e/</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>922525106136</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>JOSHITHA KS</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Joshi_666</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Joshi_666/</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>922525106138</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>JOTHISHA K S</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Jothi-</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Jothi-/</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>922525106148</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>KAVIMALAR A</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>kavimalar08</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/kavimalar08/</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>922525106155</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>KAYALVIZHI S</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>27kayalvizhi</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/27kayalvizhi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>922525106164</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>KOWSHIKA M S</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>kowshika_moorthi</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/kowshika_moorthi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>922525106171</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>LOGASRI.A</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Loga07</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Loga07/</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>922525106181</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>MADHUMITHA B</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>madhumitha-42</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/madhumitha-42/</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>922525106191</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>MANOJ KUMAR V</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>m____a____n____o____</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/m____a____n____o____/</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>922525106201</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>MONISHA V</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>MonishaV01</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/MonishaV01/</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>922525106203</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>MOULEESHWARI B</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>MouleeshwariB</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/MouleeshwariB/</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>922525106204</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>MOUSHMI P N</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Moushmi_08</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Moushmi_08/</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>922525106213</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>NIRANJANI D</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>niranjani _17</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/niranjani _17/</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>922525106219</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>NITHYASHREE P</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Nithyashree_273</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Nithyashree_273/</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>922525106220</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>NITHYASRI M</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>nithyam7809</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/nithyam7809/</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>922525106223</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>PAVITHRA S</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Pavithra145</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Pavithra145/</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>922525106230</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Pranithaashree S</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Pranithaa_shree</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Pranithaa_shree/</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>922525106237</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>PRIYADHARSHINI V</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>priyadharshiniveluchamy</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/priyadharshiniveluchamy/</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>922525106244</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>RANJANA T</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>RANJANA _2007</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/RANJANA _2007/</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>922525106250</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>RESHMI R S</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Reshmi_0826</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Reshmi_0826/</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>922525106320</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>SOBIKA R</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>_sobika_R</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/_sobika_R/</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>922525106337</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>SUGIDHARSHINI T</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Sugi_07</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Sugi_07/</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>922525106343</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>SUTHARSHANA S</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Sutharshana873</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Sutharshana873/</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>922525106345</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>SWATHI S</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>_swathi_3366</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/_swathi_3366/</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>922525106346</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>swetha E</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>swetha_20_1</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/swetha_20_1/</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>922525106348</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>THAMARAI SELVI D</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>thamarai_04</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/thamarai_04/</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>922525106351</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>THARUNIKA P</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Tharunika_12</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Tharunika_12/</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>922525106353</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>THIRISHA C</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>thirishavsb</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/thirishavsb/</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>922525106377</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>YAZHINI V</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>YAZH_RUBA</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/YAZH_RUBA/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E47"/>
+  <autoFilter ref="A1:E90"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Students.xlsx
+++ b/Students.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$140</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E90"/>
+  <dimension ref="A1:E140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2867,8 +2867,1358 @@
         </is>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>922525106253</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>RITHANYA KN</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Rithanya12-3</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Rithanya12-3/</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>922525106256</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>RITHIK P</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Rithik_78</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Rithik_78/</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>922525106257</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>RITHIKA B</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Rithika_Balakrishnan</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Rithika_Balakrishnan/</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>922525106258</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>RITHISH R</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Rithish_</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Rithish_/</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>922525106259</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>ROHITH V</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>RohithrohiV</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/RohithrohiV/</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>922525106260</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>ROOBAGAPRIYA R</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Roobagapriya</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Roobagapriya/</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>922525106261</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Roshan M</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>roshan2403</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/roshan2403/</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>922525106262</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>ROSHIKA V</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>roshikaveeramalai</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/roshikaveeramalai/</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>922525106263</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>RUBESH C</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Rubesh_7</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Rubesh_7/</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>922525106264</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>SABAREESH K</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>sabareesh_karikalan</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>922525106265</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>SABARIVASAN P</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>SabarivasanP</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/SabarivasanP/</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>922525106266</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>SAHANA.V</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Sahanavijayakumar_0033</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Sahanavijayakumar_0033/</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>922525106268</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>SAKTHI S</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Sakthisaro08</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Sakthisaro08/</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>922525106269</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Sakthivel. M</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>sakthivel23116</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/sakthivel23116/</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>922525106271</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>SANDHOSH KUMAR R</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>sandhosh_30_R</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/sandhosh_30_R/</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>922525106272</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>SANJAY D</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>itsmesanjay007</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/itsmesanjay007/</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>922525106273</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>SANJAY P</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>sanjay00675</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/sanjay00675/</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>922525106275</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>SANJAY U</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>SanjayUdayan</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/SanjayUdayan/</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>922525106278</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>SANMATHI R</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>sanmathi06</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/sanmathi06/</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>922525106279</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>SANTHIYA T</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>santhiya0202</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/santhiya0202/</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>922525106280</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>SANTHOSH D</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>santhosh7811</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/santhosh7811/</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>922525106282</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>SANTHOSH PRIYAN S</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>SANTHOSH PRIYAN S</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/SANTHOSH PRIYAN S/</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>922525106283</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>SANTHOSH S</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>SanthoshSathya260</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/SanthoshSathya260/</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>922525106284</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Santhosh S</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>santhosh2407</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/santhosh2407/</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>922525106285</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>SANTHOSH V</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>santhosh8760</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/santhosh8760/</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>922525106286</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>SARAN K</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>saran32</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/saran32/</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>922525106287</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>SARAVANAN K</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>saravanan .k</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/saravanan .k/</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>922525106288</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>SARAVANAN K</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>saravanan__k__</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/saravanan__k__/</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>922525106289</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>SARAVANAN S</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Saravanan_7525</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Saravanan_7525/</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>922525106290</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>SARIKA M P</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>sarika_5408</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/sarika_5408/</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>922525106291</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>SARVESWARAN R</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>sarvesh312008</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/sarvesh312008/</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>922525106292</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>SASHMIKA.P</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>sashmikaprabhu</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/sashmikaprabhu/</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>922525106296</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>SELVAKUMAR K</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Selvakumarsk-32</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Selvakumarsk-32/</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>922525106297</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>SELVAPRAGADEESH S</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Selvapragadeesh</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Selvapragadeesh/</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>922525106298</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>SELVA RAGAVAN</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Selvax07</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Selvax07/</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>922525106299</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>SENTHAMIZHSELVAN K</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Senthamizh08</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Senthamizh08/</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>922525106300</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Senthil.S</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Jna76WrjNd</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Jna76WrjNd/</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>922525106302</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>SHAHANA S</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>shahana_pandiraj04</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/shahana_pandiraj04/</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>922525106303</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>SHANTHINI C</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>ShanthiniChelladurai</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/ShanthiniChelladurai/</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>922525106305</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>SHARATH P</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>sharath_1010</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/sharath_1010/</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>922525106307</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>SHIVANI B</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>shivani208</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/shivani208/</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>922525106308</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>SHREE HARINI L</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Shree_Harini478</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Shree_Harini478/</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>922525106309</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>SHREE CHARAN T</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>shreecharan22</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/shreecharan22/</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>922525106310</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>SIVA MANIKANDAN K</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>9043374912</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/9043374912/</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>922525106311</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>SIVA PRAKASH M</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>sivaprakash_0406</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/sivaprakash_0406/</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>922525106312</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>SIVADHARSHINI D</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>dharshinideivsigamani</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/dharshinideivsigamani/</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>922525106313</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>SIVAGNANAM M</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>sivagnanam3344</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/sivagnanam3344/</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>922525106314</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>SIVANESH D</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>sivanesh2007</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/sivanesh2007/</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>922525106315</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>SIVANESH G</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>GSIVANESH</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/GSIVANESH/</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>922525196293</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>SASWIN D</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>saswin_88</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/saswin_88/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E90"/>
+  <autoFilter ref="A1:E140"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Students.xlsx
+++ b/Students.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$140</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$141</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E140"/>
+  <dimension ref="A1:E141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4217,8 +4217,35 @@
         </is>
       </c>
     </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>922525106301</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>SETHUPATHI G</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Sethupathi_1228</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Sethupathi_1228/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E140"/>
+  <autoFilter ref="A1:E141"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Students.xlsx
+++ b/Students.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$184</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E141"/>
+  <dimension ref="A1:E184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -575,71 +575,71 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>922525106339</t>
+          <t>922525106054</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SUJITH RAJA B</t>
+          <t>DAKSHINYA R</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>sujith45</t>
+          <t>Dakshinya555</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ECE F</t>
+          <t>ECE A</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sujith45/</t>
+          <t>https://leetcode.com/u/Dakshinya555/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>922525106054</t>
+          <t>922525106175</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DAKSHINYA R</t>
+          <t>LOHITH RAJ S</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dakshinya555</t>
+          <t>LOHITH 012008</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE C</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Dakshinya555/</t>
+          <t>https://leetcode.com/u/LOHITH 012008/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>922525106175</t>
+          <t>922525106127</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LOHITH RAJ S</t>
+          <t>JANANI A</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LOHITH 012008</t>
+          <t>janani_asohkan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -649,1671 +649,1671 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/LOHITH 012008/</t>
+          <t>https://leetcode.com/u/janani_asohkan/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>922525106319</t>
+          <t>922525106045</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SIVATHARUN C</t>
+          <t>BOOBASE R</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>sivatharun22</t>
+          <t>Boobase</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ECE F</t>
+          <t>ECE A</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivatharun22/</t>
+          <t>https://leetcode.com/u/Boobase/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>922525106359</t>
+          <t>922525106152</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>VASANTHKUMAR R</t>
+          <t>KAVIPRIYA R</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>VasanthKumar008</t>
+          <t>KAVI_RAVI</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ECE F</t>
+          <t>ECE C</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VasanthKumar008/</t>
+          <t>https://leetcode.com/u/KAVI_RAVI/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>922525106318</t>
+          <t>922525106208</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SIVASUBRAMANI A</t>
+          <t>NANDHINI D</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AK_Siva</t>
+          <t>nandhini _208</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ECE F</t>
+          <t>ECE D</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/AK_Siva/</t>
+          <t>https://leetcode.com/u/nandhini _208/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>922525106127</t>
+          <t>922525106205</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JANANI A</t>
+          <t>MYTHILI M</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>janani_asohkan</t>
+          <t>Mythili_2208</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE D</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/janani_asohkan/</t>
+          <t>https://leetcode.com/u/Mythili_2208/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>922525106045</t>
+          <t>922525106079</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BOOBASE R</t>
+          <t>DHINAKAR A</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Boobase</t>
+          <t>dhina</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE B</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Boobase/</t>
+          <t>https://leetcode.com/u/dhina/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>922525106321</t>
+          <t>922525106032</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SREE DHARANI C</t>
+          <t>ARVINSHANKARA V</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SREEDHARANI_14</t>
+          <t>Ok</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ECE F</t>
+          <t>ECE A</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SREEDHARANI_14/</t>
+          <t>https://leetcode.com/u/Ok/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>922525106152</t>
+          <t>922525106027</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>KAVIPRIYA R</t>
+          <t>ARULESH K</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>KAVI_RAVI</t>
+          <t>arul2008</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE A</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/KAVI_RAVI/</t>
+          <t>https://leetcode.com/u/arul2008/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>922525106332</t>
+          <t>922525106049</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SUBARNA V</t>
+          <t>BUVNESH N</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Subarna1017</t>
+          <t>Buvnesh_2008</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ECE F</t>
+          <t>ECE A</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Subarna1017/</t>
+          <t>https://leetcode.com/u/Buvnesh_2008/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>922525106208</t>
+          <t>922525106047</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NANDHINI D</t>
+          <t>BOSVIYA P</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>nandhini _208</t>
+          <t>BosviyaBSV</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE A</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/nandhini _208/</t>
+          <t>https://leetcode.com/u/BosviyaBSV/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>922525106205</t>
+          <t>922525106059</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MYTHILI M</t>
+          <t>DEJASRI M</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Mythili_2208</t>
+          <t>dejasri</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE A</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Mythili_2208/</t>
+          <t>https://leetcode.com/u/dejasri/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>922525106079</t>
+          <t>922525106014</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DHINAKAR A</t>
+          <t>AKASH R</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>dhina</t>
+          <t>AkashRajaram</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ECE B</t>
+          <t>ECE A</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/dhina/</t>
+          <t>https://leetcode.com/u/AkashRajaram/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>922525106341</t>
+          <t>922525106009</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SURYA PRABHU S</t>
+          <t>AISHWARYA G</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SURYA_FOUNDER</t>
+          <t>Codewithaish</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ECE F</t>
+          <t>ECE A</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SURYA_FOUNDER/</t>
+          <t>https://leetcode.com/u/Codewithaish/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>922525106032</t>
+          <t>922525106125</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ARVINSHANKARA V</t>
+          <t>JAI GANESH I</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ok</t>
+          <t>Jai_Ganesh_I</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE B</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Ok/</t>
+          <t>https://leetcode.com/u/Jai_Ganesh_I/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>922525106027</t>
+          <t>922525106186</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ARULESH K</t>
+          <t>MAHIBALAN A</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>arul2008</t>
+          <t>lakshmiprabha1984-prog</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE C</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/arul2008/</t>
+          <t>https://leetcode.com/u/lakshmiprabha1984-prog/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>922525106049</t>
+          <t>922525106160</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BUVNESH N</t>
+          <t>KOHUL V</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Buvnesh_2008</t>
+          <t>Kohul_v</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE C</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Buvnesh_2008/</t>
+          <t>https://leetcode.com/u/Kohul_v/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>922525106047</t>
+          <t>922525106144</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BOSVIYA P</t>
+          <t>KARMUKILAN J</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BosviyaBSV</t>
+          <t>karmukilan567</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE C</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/BosviyaBSV/</t>
+          <t>https://leetcode.com/u/karmukilan567/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>922525106373</t>
+          <t>922525106180</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>YASHNI S</t>
+          <t>MADHUDHARA P</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>yashnisubramaniyan</t>
+          <t>madhudhara</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ECE F</t>
+          <t>ECE C</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yashnisubramaniyan/</t>
+          <t>https://leetcode.com/u/madhudhara/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>922525106059</t>
+          <t>922525106189</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DEJASRI M</t>
+          <t>MANISHA D</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>dejasri</t>
+          <t>manishaa_20</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE C</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/dejasri/</t>
+          <t>https://leetcode.com/u/manishaa_20/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>922525106014</t>
+          <t>922525106183</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>AKASH R</t>
+          <t>MAHALAKSHMI B</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AkashRajaram</t>
+          <t>mahalakshmi182025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE C</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/AkashRajaram/</t>
+          <t>https://leetcode.com/u/mahalakshmi182025/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>922525106009</t>
+          <t>922525106184</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>AISHWARYA G</t>
+          <t>MAHALAKSHMI M</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Codewithaish</t>
+          <t>Maha ece</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE C</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Codewithaish/</t>
+          <t>https://leetcode.com/u/Maha ece/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>922525106125</t>
+          <t>922525106156</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>JAI GANESH I</t>
+          <t>KEERTHANA S</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jai_Ganesh_I</t>
+          <t>Hwfrd8kp5Y</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ECE B</t>
+          <t>ECE C</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Jai_Ganesh_I/</t>
+          <t>https://leetcode.com/u/Hwfrd8kp5Y/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>922525106186</t>
+          <t>922525106236</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MAHIBALAN A</t>
+          <t>PRITHIV S</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>lakshmiprabha1984-prog</t>
+          <t>Prithiv25</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE D</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/lakshmiprabha1984-prog/</t>
+          <t>https://leetcode.com/u/Prithiv25/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>922525106160</t>
+          <t>922525106195</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>KOHUL V</t>
+          <t>MAYUKA M</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kohul_v</t>
+          <t>Mayuka_25</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE D</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Kohul_v/</t>
+          <t>https://leetcode.com/u/Mayuka_25/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>922525106144</t>
+          <t>922525106214</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>KARMUKILAN J</t>
+          <t>NITHISH C T</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>karmukilan567</t>
+          <t>Nithish12322</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE D</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/karmukilan567/</t>
+          <t>https://leetcode.com/u/Nithish12322/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>922525106180</t>
+          <t>922525106225</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MADHUDHARA P</t>
+          <t>PIRAVEEN M</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>madhudhara</t>
+          <t>Piraveen_M</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE D</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/madhudhara/</t>
+          <t>https://leetcode.com/u/Piraveen_M/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>922525106189</t>
+          <t>922525106211</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>MANISHA D</t>
+          <t>NAVEETHA N</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>manishaa_20</t>
+          <t>Naveetha_</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE D</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/manishaa_20/</t>
+          <t>https://leetcode.com/u/Naveetha_/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>922525106183</t>
+          <t>922525106199</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MAHALAKSHMI B</t>
+          <t>MONISH S</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>mahalakshmi182025</t>
+          <t>MonishS77</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE D</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/mahalakshmi182025/</t>
+          <t>https://leetcode.com/u/MonishS77/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>922525106184</t>
+          <t>922525106232</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MAHALAKSHMI M</t>
+          <t>PRAVEEN G</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Maha ece</t>
+          <t>praveen_gobi</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE D</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Maha ece/</t>
+          <t>https://leetcode.com/u/praveen_gobi/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>922525106156</t>
+          <t>922525106001</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>KEERTHANA S</t>
+          <t>AASHIFA SAHANAJ M</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hwfrd8kp5Y</t>
+          <t>aashifasahanaj</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE A</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Hwfrd8kp5Y/</t>
+          <t>https://leetcode.com/u/aashifasahanaj/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>922525106236</t>
+          <t>922525106002</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PRITHIV S</t>
+          <t>AAZHIGA N</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Prithiv25</t>
+          <t>AAZHIGA</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE A</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Prithiv25/</t>
+          <t>https://leetcode.com/u/AAZHIGA/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>922525106195</t>
+          <t>922525106004</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MAYUKA M</t>
+          <t>Abirami R</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Mayuka_25</t>
+          <t>abirami8072</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE A</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Mayuka_25/</t>
+          <t>https://leetcode.com/u/abirami8072/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>922525106214</t>
+          <t>922525106018</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NITHISH C T</t>
+          <t>AMIRDAVARSINI K S</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Nithish12322</t>
+          <t>amirda_varsini_2007</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE A</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Nithish12322/</t>
+          <t>https://leetcode.com/u/amirda_varsini_2007/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>922525106225</t>
+          <t>922525106022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PIRAVEEN M</t>
+          <t>ANUJA S</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Piraveen_M</t>
+          <t>anuja008</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE A</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Piraveen_M/</t>
+          <t>https://leetcode.com/u/anuja008/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>922525106211</t>
+          <t>922525106023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NAVEETHA N</t>
+          <t>ANUSRI R</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Naveetha_</t>
+          <t>Anusri_2008</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE A</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Naveetha_/</t>
+          <t>https://leetcode.com/u/Anusri_2008/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>922525106199</t>
+          <t>922525106024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>MONISH S</t>
+          <t>ANUSYA B</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MonishS77</t>
+          <t>ANUSYA_30</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE A</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/MonishS77/</t>
+          <t>https://leetcode.com/u/ANUSYA_30/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>922525106232</t>
+          <t>922525106046</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PRAVEEN G</t>
+          <t>BOOMIKA T</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>praveen_gobi</t>
+          <t>boomikat1206</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE A</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/praveen_gobi/</t>
+          <t>https://leetcode.com/u/boomikat1206/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>922525106349</t>
+          <t>922525106060</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>THAMEEM FARSHITHA A</t>
+          <t>DESMA SHALINI K</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Thameem_786</t>
+          <t>desmashalini</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ECE F</t>
+          <t>ECE A</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Thameem_786/</t>
+          <t>https://leetcode.com/u/desmashalini/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>922525106342</t>
+          <t>922525106063</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SUSIDHARAN M</t>
+          <t>DHANASRI R</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>susidharan 147</t>
+          <t>Dhanasri_r</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ECE F</t>
+          <t>ECE A</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/susidharan 147/</t>
+          <t>https://leetcode.com/u/Dhanasri_r/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>922525106329</t>
+          <t>922525106064</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SRINITHE T</t>
+          <t>DHANIKA S</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>srinithe_1401</t>
+          <t>a</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ECE F</t>
+          <t>ECE B</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/srinithe_1401/</t>
+          <t>https://leetcode.com/u/a/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>922525106001</t>
+          <t>922525106065</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>AASHIFA SAHANAJ M</t>
+          <t>DHANUSHRI D</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>aashifasahanaj</t>
+          <t>bo</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE B</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/aashifasahanaj/</t>
+          <t>https://leetcode.com/u/bo/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>922525106002</t>
+          <t>922525106071</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>AAZHIGA N</t>
+          <t>DHARANI V</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AAZHIGA</t>
+          <t>c</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE B</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/AAZHIGA/</t>
+          <t>https://leetcode.com/u/c/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>922525106004</t>
+          <t>922525106092</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Abirami R</t>
+          <t>ELAVARASU P</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>abirami8072</t>
+          <t>d</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE B</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/abirami8072/</t>
+          <t>https://leetcode.com/u/d/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>922525106018</t>
+          <t>922525106119</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>AMIRDAVARSINI K S</t>
+          <t>HAVISHMATHI S</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>amirda_varsini_2007</t>
+          <t>e</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE B</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/amirda_varsini_2007/</t>
+          <t>https://leetcode.com/u/e/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>922525106022</t>
+          <t>922525106136</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ANUJA S</t>
+          <t>JOSHITHA KS</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>anuja008</t>
+          <t>Joshi_666</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE C</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/anuja008/</t>
+          <t>https://leetcode.com/u/Joshi_666/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>922525106023</t>
+          <t>922525106138</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ANUSRI R</t>
+          <t>JOTHISHA K S</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Anusri_2008</t>
+          <t>Jothi-</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE C</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Anusri_2008/</t>
+          <t>https://leetcode.com/u/Jothi-/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>922525106024</t>
+          <t>922525106148</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ANUSYA B</t>
+          <t>KAVIMALAR A</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ANUSYA_30</t>
+          <t>kavimalar08</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE C</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/ANUSYA_30/</t>
+          <t>https://leetcode.com/u/kavimalar08/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>922525106046</t>
+          <t>922525106155</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BOOMIKA T</t>
+          <t>KAYALVIZHI S</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>boomikat1206</t>
+          <t>27kayalvizhi</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE C</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/boomikat1206/</t>
+          <t>https://leetcode.com/u/27kayalvizhi/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>922525106060</t>
+          <t>922525106164</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>DESMA SHALINI K</t>
+          <t>KOWSHIKA M S</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>desmashalini</t>
+          <t>kowshika_moorthi</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE C</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/desmashalini/</t>
+          <t>https://leetcode.com/u/kowshika_moorthi/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>922525106063</t>
+          <t>922525106171</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DHANASRI R</t>
+          <t>LOGASRI.A</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Dhanasri_r</t>
+          <t>Loga07</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE C</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Dhanasri_r/</t>
+          <t>https://leetcode.com/u/Loga07/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>922525106064</t>
+          <t>922525106181</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DHANIKA S</t>
+          <t>MADHUMITHA B</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>madhumitha-42</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ECE B</t>
+          <t>ECE C</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/a/</t>
+          <t>https://leetcode.com/u/madhumitha-42/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>922525106065</t>
+          <t>922525106191</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>DHANUSHRI D</t>
+          <t>MANOJ KUMAR V</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>bo</t>
+          <t>m____a____n____o____</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ECE B</t>
+          <t>ECE D</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/bo/</t>
+          <t>https://leetcode.com/u/m____a____n____o____/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>922525106071</t>
+          <t>922525106201</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>DHARANI V</t>
+          <t>MONISHA V</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>MonishaV01</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ECE B</t>
+          <t>ECE D</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/c/</t>
+          <t>https://leetcode.com/u/MonishaV01/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>922525106092</t>
+          <t>922525106203</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ELAVARASU P</t>
+          <t>MOULEESHWARI B</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>MouleeshwariB</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ECE B</t>
+          <t>ECE D</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/d/</t>
+          <t>https://leetcode.com/u/MouleeshwariB/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>922525106119</t>
+          <t>922525106204</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>HAVISHMATHI S</t>
+          <t>MOUSHMI P N</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>Moushmi_08</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ECE B</t>
+          <t>ECE D</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/e/</t>
+          <t>https://leetcode.com/u/Moushmi_08/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>922525106136</t>
+          <t>922525106213</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>JOSHITHA KS</t>
+          <t>NIRANJANI D</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Joshi_666</t>
+          <t>niranjani _17</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE D</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Joshi_666/</t>
+          <t>https://leetcode.com/u/niranjani _17/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>922525106138</t>
+          <t>922525106219</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>JOTHISHA K S</t>
+          <t>NITHYASHREE P</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Jothi-</t>
+          <t>Nithyashree_273</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE D</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Jothi-/</t>
+          <t>https://leetcode.com/u/Nithyashree_273/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>922525106148</t>
+          <t>922525106220</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>KAVIMALAR A</t>
+          <t>NITHYASRI M</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>kavimalar08</t>
+          <t>nithyam7809</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE D</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kavimalar08/</t>
+          <t>https://leetcode.com/u/nithyam7809/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>922525106155</t>
+          <t>922525106223</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>KAYALVIZHI S</t>
+          <t>PAVITHRA S</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>27kayalvizhi</t>
+          <t>Pavithra145</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE D</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/27kayalvizhi/</t>
+          <t>https://leetcode.com/u/Pavithra145/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>922525106164</t>
+          <t>922525106230</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>KOWSHIKA M S</t>
+          <t>Pranithaashree S</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>kowshika_moorthi</t>
+          <t>Pranithaa_shree</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE D</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kowshika_moorthi/</t>
+          <t>https://leetcode.com/u/Pranithaa_shree/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>922525106171</t>
+          <t>922525106237</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>LOGASRI.A</t>
+          <t>PRIYADHARSHINI V</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Loga07</t>
+          <t>priyadharshiniveluchamy</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE D</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Loga07/</t>
+          <t>https://leetcode.com/u/priyadharshiniveluchamy/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>922525106181</t>
+          <t>922525106244</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>MADHUMITHA B</t>
+          <t>RANJANA T</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>madhumitha-42</t>
+          <t>RANJANA _2007</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE D</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/madhumitha-42/</t>
+          <t>https://leetcode.com/u/RANJANA _2007/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>922525106191</t>
+          <t>922525106250</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>MANOJ KUMAR V</t>
+          <t>RESHMI R S</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>m____a____n____o____</t>
+          <t>Reshmi_0826</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2323,564 +2323,564 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/m____a____n____o____/</t>
+          <t>https://leetcode.com/u/Reshmi_0826/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>922525106201</t>
+          <t>922525106288</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MONISHA V</t>
+          <t>SARAVANAN K</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MonishaV01</t>
+          <t>saravanan__k__</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/MonishaV01/</t>
+          <t>https://leetcode.com/u/saravanan__k__/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>922525106203</t>
+          <t>922525106253</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>MOULEESHWARI B</t>
+          <t>RITHANYA KN</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MouleeshwariB</t>
+          <t>Rithanya12-3</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/MouleeshwariB/</t>
+          <t>https://leetcode.com/u/Rithanya12-3/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>922525106204</t>
+          <t>922525106256</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>MOUSHMI P N</t>
+          <t>RITHIK P</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Moushmi_08</t>
+          <t>Rithik_78</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Moushmi_08/</t>
+          <t>https://leetcode.com/u/Rithik_78/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>922525106213</t>
+          <t>922525106257</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>NIRANJANI D</t>
+          <t>RITHIKA B</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>niranjani _17</t>
+          <t>Rithika_Balakrishnan</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/niranjani _17/</t>
+          <t>https://leetcode.com/u/Rithika_Balakrishnan/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>922525106219</t>
+          <t>922525106258</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>NITHYASHREE P</t>
+          <t>RITHISH R</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Nithyashree_273</t>
+          <t>Rithish_</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Nithyashree_273/</t>
+          <t>https://leetcode.com/u/Rithish_/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>922525106220</t>
+          <t>922525106259</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>NITHYASRI M</t>
+          <t>ROHITH V</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>nithyam7809</t>
+          <t>RohithrohiV</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/nithyam7809/</t>
+          <t>https://leetcode.com/u/RohithrohiV/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>922525106223</t>
+          <t>922525106260</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>PAVITHRA S</t>
+          <t>ROOBAGAPRIYA R</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Pavithra145</t>
+          <t>Roobagapriya</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Pavithra145/</t>
+          <t>https://leetcode.com/u/Roobagapriya/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>922525106230</t>
+          <t>922525106261</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Pranithaashree S</t>
+          <t>Roshan M</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Pranithaa_shree</t>
+          <t>roshan2403</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Pranithaa_shree/</t>
+          <t>https://leetcode.com/u/roshan2403/</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>922525106237</t>
+          <t>922525106262</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>PRIYADHARSHINI V</t>
+          <t>ROSHIKA V</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>priyadharshiniveluchamy</t>
+          <t>roshikaveeramalai</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/priyadharshiniveluchamy/</t>
+          <t>https://leetcode.com/u/roshikaveeramalai/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>922525106244</t>
+          <t>922525106263</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>RANJANA T</t>
+          <t>RUBESH C</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>RANJANA _2007</t>
+          <t>Rubesh_7</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/RANJANA _2007/</t>
+          <t>https://leetcode.com/u/Rubesh_7/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>922525106250</t>
+          <t>922525106264</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>RESHMI R S</t>
+          <t>SABAREESH K</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Reshmi_0826</t>
+          <t>sabareesh_karikalan</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Reshmi_0826/</t>
+          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>922525106320</t>
+          <t>922525106265</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SOBIKA R</t>
+          <t>SABARIVASAN P</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>_sobika_R</t>
+          <t>SabarivasanP</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>ECE F</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_sobika_R/</t>
+          <t>https://leetcode.com/u/SabarivasanP/</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>922525106337</t>
+          <t>922525106266</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SUGIDHARSHINI T</t>
+          <t>SAHANA.V</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Sugi_07</t>
+          <t>Sahanavijayakumar_0033</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>ECE F</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sugi_07/</t>
+          <t>https://leetcode.com/u/Sahanavijayakumar_0033/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>922525106343</t>
+          <t>922525106268</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SUTHARSHANA S</t>
+          <t>SAKTHI S</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Sutharshana873</t>
+          <t>Sakthisaro08</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>ECE F</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sutharshana873/</t>
+          <t>https://leetcode.com/u/Sakthisaro08/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>922525106345</t>
+          <t>922525106269</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SWATHI S</t>
+          <t>Sakthivel. M</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>_swathi_3366</t>
+          <t>sakthivel23116</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>ECE F</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_swathi_3366/</t>
+          <t>https://leetcode.com/u/sakthivel23116/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>922525106346</t>
+          <t>922525106271</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>swetha E</t>
+          <t>SANDHOSH KUMAR R</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>swetha_20_1</t>
+          <t>sandhosh_30_R</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>ECE F</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/swetha_20_1/</t>
+          <t>https://leetcode.com/u/sandhosh_30_R/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>922525106348</t>
+          <t>922525106272</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>THAMARAI SELVI D</t>
+          <t>SANJAY D</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>thamarai_04</t>
+          <t>itsmesanjay007</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>ECE F</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/thamarai_04/</t>
+          <t>https://leetcode.com/u/itsmesanjay007/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>922525106351</t>
+          <t>922525106273</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>THARUNIKA P</t>
+          <t>SANJAY P</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Tharunika_12</t>
+          <t>sanjay00675</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>ECE F</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Tharunika_12/</t>
+          <t>https://leetcode.com/u/sanjay00675/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>922525106353</t>
+          <t>922525106275</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>THIRISHA C</t>
+          <t>SANJAY U</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>thirishavsb</t>
+          <t>SanjayUdayan</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>ECE F</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/thirishavsb/</t>
+          <t>https://leetcode.com/u/SanjayUdayan/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>922525106377</t>
+          <t>922525106278</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>YAZHINI V</t>
+          <t>SANMATHI R</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>YAZH_RUBA</t>
+          <t>sanmathi06</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>ECE F</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/YAZH_RUBA/</t>
+          <t>https://leetcode.com/u/sanmathi06/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>922525106253</t>
+          <t>922525106279</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>RITHANYA KN</t>
+          <t>SANTHIYA T</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Rithanya12-3</t>
+          <t>santhiya0202</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2890,24 +2890,24 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithanya12-3/</t>
+          <t>https://leetcode.com/u/santhiya0202/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>922525106256</t>
+          <t>922525106280</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>RITHIK P</t>
+          <t>SANTHOSH D</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Rithik_78</t>
+          <t>santhosh7811</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2917,24 +2917,24 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithik_78/</t>
+          <t>https://leetcode.com/u/santhosh7811/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>922525106257</t>
+          <t>922525106282</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>RITHIKA B</t>
+          <t>SANTHOSH PRIYAN S</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Rithika_Balakrishnan</t>
+          <t>SANTHOSH PRIYAN S</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2944,24 +2944,24 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithika_Balakrishnan/</t>
+          <t>https://leetcode.com/u/SANTHOSH PRIYAN S/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>922525106258</t>
+          <t>922525106283</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>RITHISH R</t>
+          <t>SANTHOSH S</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Rithish_</t>
+          <t>SanthoshSathya260</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2971,24 +2971,24 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithish_/</t>
+          <t>https://leetcode.com/u/SanthoshSathya260/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>922525106259</t>
+          <t>922525106284</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ROHITH V</t>
+          <t>Santhosh S</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>RohithrohiV</t>
+          <t>santhosh2407</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2998,24 +2998,24 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/RohithrohiV/</t>
+          <t>https://leetcode.com/u/santhosh2407/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>922525106260</t>
+          <t>922525106285</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ROOBAGAPRIYA R</t>
+          <t>SANTHOSH V</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Roobagapriya</t>
+          <t>santhosh8760</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3025,24 +3025,24 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Roobagapriya/</t>
+          <t>https://leetcode.com/u/santhosh8760/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>922525106261</t>
+          <t>922525106286</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Roshan M</t>
+          <t>SARAN K</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>roshan2403</t>
+          <t>saran32</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3052,24 +3052,24 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/roshan2403/</t>
+          <t>https://leetcode.com/u/saran32/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>922525106262</t>
+          <t>922525106287</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ROSHIKA V</t>
+          <t>SARAVANAN K</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>roshikaveeramalai</t>
+          <t>saravanan .k</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3079,24 +3079,24 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/roshikaveeramalai/</t>
+          <t>https://leetcode.com/u/saravanan .k/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>922525106263</t>
+          <t>922525106289</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>RUBESH C</t>
+          <t>SARAVANAN S</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Rubesh_7</t>
+          <t>Saravanan_7525</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3106,24 +3106,24 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rubesh_7/</t>
+          <t>https://leetcode.com/u/Saravanan_7525/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>922525106264</t>
+          <t>922525106290</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>SABAREESH K</t>
+          <t>SARIKA M P</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>sabareesh_karikalan</t>
+          <t>sarika_5408</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3133,24 +3133,24 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
+          <t>https://leetcode.com/u/sarika_5408/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>922525106265</t>
+          <t>922525106291</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>SABARIVASAN P</t>
+          <t>SARVESWARAN R</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>SabarivasanP</t>
+          <t>sarvesh312008</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3160,24 +3160,24 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SabarivasanP/</t>
+          <t>https://leetcode.com/u/sarvesh312008/</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>922525106266</t>
+          <t>922525106292</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>SAHANA.V</t>
+          <t>SASHMIKA.P</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Sahanavijayakumar_0033</t>
+          <t>sashmikaprabhu</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3187,24 +3187,24 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sahanavijayakumar_0033/</t>
+          <t>https://leetcode.com/u/sashmikaprabhu/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>922525106268</t>
+          <t>922525106296</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>SAKTHI S</t>
+          <t>SELVAKUMAR K</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Sakthisaro08</t>
+          <t>Selvakumarsk-32</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3214,24 +3214,24 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sakthisaro08/</t>
+          <t>https://leetcode.com/u/Selvakumarsk-32/</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>922525106269</t>
+          <t>922525106297</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Sakthivel. M</t>
+          <t>SELVAPRAGADEESH S</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>sakthivel23116</t>
+          <t>Selvapragadeesh</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3241,24 +3241,24 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sakthivel23116/</t>
+          <t>https://leetcode.com/u/Selvapragadeesh/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>922525106271</t>
+          <t>922525106298</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>SANDHOSH KUMAR R</t>
+          <t>SELVA RAGAVAN</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>sandhosh_30_R</t>
+          <t>Selvax07</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3268,24 +3268,24 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sandhosh_30_R/</t>
+          <t>https://leetcode.com/u/Selvax07/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>922525106272</t>
+          <t>922525106299</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>SANJAY D</t>
+          <t>SENTHAMIZHSELVAN K</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>itsmesanjay007</t>
+          <t>Senthamizh08</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3295,24 +3295,24 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itsmesanjay007/</t>
+          <t>https://leetcode.com/u/Senthamizh08/</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>922525106273</t>
+          <t>922525106300</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SANJAY P</t>
+          <t>Senthil.S</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>sanjay00675</t>
+          <t>Jna76WrjNd</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3322,24 +3322,24 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sanjay00675/</t>
+          <t>https://leetcode.com/u/Jna76WrjNd/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>922525106275</t>
+          <t>922525106302</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>SANJAY U</t>
+          <t>SHAHANA S</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>SanjayUdayan</t>
+          <t>shahana_pandiraj04</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3349,24 +3349,24 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SanjayUdayan/</t>
+          <t>https://leetcode.com/u/shahana_pandiraj04/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>922525106278</t>
+          <t>922525106303</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SANMATHI R</t>
+          <t>SHANTHINI C</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>sanmathi06</t>
+          <t>ShanthiniChelladurai</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3376,24 +3376,24 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sanmathi06/</t>
+          <t>https://leetcode.com/u/ShanthiniChelladurai/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>922525106279</t>
+          <t>922525106305</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>SANTHIYA T</t>
+          <t>SHARATH P</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>santhiya0202</t>
+          <t>sharath_1010</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3403,24 +3403,24 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhiya0202/</t>
+          <t>https://leetcode.com/u/sharath_1010/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>922525106280</t>
+          <t>922525106307</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>SANTHOSH D</t>
+          <t>SHIVANI B</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>santhosh7811</t>
+          <t>shivani208</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3430,24 +3430,24 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh7811/</t>
+          <t>https://leetcode.com/u/shivani208/</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>922525106282</t>
+          <t>922525106308</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>SANTHOSH PRIYAN S</t>
+          <t>SHREE HARINI L</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>SANTHOSH PRIYAN S</t>
+          <t>Shree_Harini478</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -3457,24 +3457,24 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SANTHOSH PRIYAN S/</t>
+          <t>https://leetcode.com/u/Shree_Harini478/</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>922525106283</t>
+          <t>922525106309</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>SANTHOSH S</t>
+          <t>SHREE CHARAN T</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>SanthoshSathya260</t>
+          <t>shreecharan22</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3484,24 +3484,24 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SanthoshSathya260/</t>
+          <t>https://leetcode.com/u/shreecharan22/</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>922525106284</t>
+          <t>922525106310</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Santhosh S</t>
+          <t>SIVA MANIKANDAN K</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>santhosh2407</t>
+          <t>9043374912</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3511,24 +3511,24 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh2407/</t>
+          <t>https://leetcode.com/u/9043374912/</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>922525106285</t>
+          <t>922525106311</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>SANTHOSH V</t>
+          <t>SIVA PRAKASH M</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>santhosh8760</t>
+          <t>sivaprakash_0406</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -3538,24 +3538,24 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh8760/</t>
+          <t>https://leetcode.com/u/sivaprakash_0406/</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>922525106286</t>
+          <t>922525106312</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>SARAN K</t>
+          <t>SIVADHARSHINI D</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>saran32</t>
+          <t>dharshinideivsigamani</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -3565,24 +3565,24 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saran32/</t>
+          <t>https://leetcode.com/u/dharshinideivsigamani/</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>922525106287</t>
+          <t>922525106313</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>SARAVANAN K</t>
+          <t>SIVAGNANAM M</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>saravanan .k</t>
+          <t>sivagnanam3344</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3592,24 +3592,24 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saravanan .k/</t>
+          <t>https://leetcode.com/u/sivagnanam3344/</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>922525106288</t>
+          <t>922525106314</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>SARAVANAN K</t>
+          <t>SIVANESH D</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>saravanan__k__</t>
+          <t>sivanesh2007</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3619,24 +3619,24 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saravanan__k__/</t>
+          <t>https://leetcode.com/u/sivanesh2007/</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>922525106289</t>
+          <t>922525106315</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>SARAVANAN S</t>
+          <t>SIVANESH G</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Saravanan_7525</t>
+          <t>GSIVANESH</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Saravanan_7525/</t>
+          <t>https://leetcode.com/u/GSIVANESH/</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>922525106290</t>
+          <t>922525196293</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>SARIKA M P</t>
+          <t>SASWIN D</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>sarika_5408</t>
+          <t>saswin_88</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -3673,24 +3673,24 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sarika_5408/</t>
+          <t>https://leetcode.com/u/saswin_88/</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>922525106291</t>
+          <t>922525106301</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>SARVESWARAN R</t>
+          <t>SETHUPATHI G</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>sarvesh312008</t>
+          <t>Sethupathi_1228</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -3700,552 +3700,1713 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sarvesh312008/</t>
+          <t>https://leetcode.com/u/Sethupathi_1228/</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>922525106292</t>
+          <t>922525106342</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>SASHMIKA.P</t>
+          <t>SUSIDHARAN M</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>sashmikaprabhu</t>
+          <t>Susidharan147</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sashmikaprabhu/</t>
+          <t>https://leetcode.com/u/Susidharan147/</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>922525106296</t>
+          <t>922525106343</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>SELVAKUMAR K</t>
+          <t>SUTHARSHANA S</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Selvakumarsk-32</t>
+          <t>sutharshana743</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvakumarsk-32/</t>
+          <t>https://leetcode.com/u/sutharshana743/</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>922525106297</t>
+          <t>922525106344</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>SELVAPRAGADEESH S</t>
+          <t>SWATHI M</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Selvapragadeesh</t>
+          <t>Swathimanivel_1234</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvapragadeesh/</t>
+          <t>https://leetcode.com/u/Swathimanivel_1234/</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>922525106298</t>
+          <t>922525106345</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>SELVA RAGAVAN</t>
+          <t>SWATHI S</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Selvax07</t>
+          <t>swathi _3366</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvax07/</t>
+          <t>https://leetcode.com/u/swathi _3366/</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>922525106299</t>
+          <t>922525106346</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>SENTHAMIZHSELVAN K</t>
+          <t>SWETHA E</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Senthamizh08</t>
+          <t>Shwetha_20_1</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Senthamizh08/</t>
+          <t>https://leetcode.com/u/Shwetha_20_1/</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>922525106300</t>
+          <t>922525106347</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Senthil.S</t>
+          <t>TAMIL SELVAN R</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Jna76WrjNd</t>
+          <t>Kdmif0HMNm</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Jna76WrjNd/</t>
+          <t>https://leetcode.com/u/Kdmif0HMNm/</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>922525106302</t>
+          <t>922525106348</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>SHAHANA S</t>
+          <t>THAMARAI SELVI D</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>shahana_pandiraj04</t>
+          <t>thamarai_04</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shahana_pandiraj04/</t>
+          <t>https://leetcode.com/u/thamarai_04/</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>922525106303</t>
+          <t>922525106349</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>SHANTHINI C</t>
+          <t>THAMEEM FARSHITHA A</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>ShanthiniChelladurai</t>
+          <t>Thameem_786</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/ShanthiniChelladurai/</t>
+          <t>https://leetcode.com/u/Thameem_786/</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>922525106305</t>
+          <t>922525106350</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>SHARATH P</t>
+          <t>THARANISH R</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>sharath_1010</t>
+          <t>THARANISH2008</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sharath_1010/</t>
+          <t>https://leetcode.com/u/THARANISH2008/</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>922525106307</t>
+          <t>922525106351</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>SHIVANI B</t>
+          <t>THARUNIKA P</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>shivani208</t>
+          <t>Tharunika_12</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shivani208/</t>
+          <t>https://leetcode.com/u/Tharunika_12/</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>922525106308</t>
+          <t>922525106352</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>SHREE HARINI L</t>
+          <t>THIRINESH KUMAR S</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Shree_Harini478</t>
+          <t>THIRINESH KUMAR.S</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Shree_Harini478/</t>
+          <t>https://leetcode.com/u/THIRINESH KUMAR.S/</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>922525106309</t>
+          <t>922525106353</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>SHREE CHARAN T</t>
+          <t>THIRISHA C</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>shreecharan22</t>
+          <t>thirishavsb</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shreecharan22/</t>
+          <t>https://leetcode.com/u/thirishavsb/</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>922525106310</t>
+          <t>922525106354</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>SIVA MANIKANDAN K</t>
+          <t>THIRUMURUGAN S</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>9043374912</t>
+          <t>thiru0211_</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/9043374912/</t>
+          <t>https://leetcode.com/u/thiru0211_/</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>922525106311</t>
+          <t>922525106361</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>SIVA PRAKASH M</t>
+          <t>VASUKI K</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>sivaprakash_0406</t>
+          <t>vasuki</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivaprakash_0406/</t>
+          <t>https://leetcode.com/u/vasuki/</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>922525106312</t>
+          <t>922525106362</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>SIVADHARSHINI D</t>
+          <t>VELLIANGIRI R</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>dharshinideivsigamani</t>
+          <t>velliangiri_R</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/dharshinideivsigamani/</t>
+          <t>https://leetcode.com/u/velliangiri_R/</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>922525106313</t>
+          <t>922525106363</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>SIVAGNANAM M</t>
+          <t>VIGNESH M</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>sivagnanam3344</t>
+          <t>O8bYDSRUbE</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivagnanam3344/</t>
+          <t>https://leetcode.com/u/O8bYDSRUbE/</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>922525106314</t>
+          <t>922525106364</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>SIVANESH D</t>
+          <t>VIGNESH VELAN M</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>sivanesh2007</t>
+          <t>Vicky_27_Velan</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivanesh2007/</t>
+          <t>https://leetcode.com/u/Vicky_27_Velan/</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>922525106315</t>
+          <t>922525106365</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>SIVANESH G</t>
+          <t>VIGNESHWAR U</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>GSIVANESH</t>
+          <t>VIGNESHWAR0221</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/GSIVANESH/</t>
+          <t>https://leetcode.com/u/VIGNESHWAR0221/</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>922525196293</t>
+          <t>922525106366</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>SASWIN D</t>
+          <t>VIJAYARAGAVAN R</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>saswin_88</t>
+          <t>vijayaragavan1216</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saswin_88/</t>
+          <t>https://leetcode.com/u/vijayaragavan1216/</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>922525106301</t>
+          <t>922525106367</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>SETHUPATHI G</t>
+          <t>VIKRAM V</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Sethupathi_1228</t>
+          <t>vikramvicky5678</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sethupathi_1228/</t>
+          <t>https://leetcode.com/u/vikramvicky5678/</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>922525106368</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>VISHNU B</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>VISHNU_B_2008</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/VISHNU_B_2008/</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>922525106369</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>VISHNU PRIYAN S</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>itz__priyan__</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/itz__priyan__/</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>922525106370</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>VISHNUHARAN V S</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Vishnuharan082007</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Vishnuharan082007/</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>922525106371</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>VISHNUPRIYA S</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>vishnupriyamaran</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/vishnupriyamaran/</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>922525106372</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>VISHWAJETH A M</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>vishwajeth</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/vishwajeth/</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>922525106373</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>YASHNI S</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Yashnisubramaniyan</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Yashnisubramaniyan/</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>922525106374</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>YASWANTH V</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>yaswanth_2008</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/yaswanth_2008/</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>922525106375</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>YAZHINI M</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>yazhini2007</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/yazhini2007/</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>922525106376</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>YAZHINI S</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>yazhini__1234</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/yazhini__1234/</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>922525106377</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>YAZHINI V</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>VISU_YAZHU</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/VISU_YAZHU/</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>922525106378</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>YOKESWARAN S</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>syokeswaran</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/syokeswaran/</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>922525106355</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>VAISHNAVI U</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>vaish200</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/vaish200/</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>922525106356</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>VASANTH KUMAR C</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>VASANTH2007</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/VASANTH2007/</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>922525106357</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>VASANTH S</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>_vasanth_s_</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/_vasanth_s_/</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>922525106358</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>VASANTHA KUMAR D</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Vasanthakumar12232</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Vasanthakumar12232/</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>922525106359</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>VASANTHKUMAR R</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>VasanthKumar008</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/VasanthKumar008/</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>922525106316</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>SIVARANJAN M P</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>SIVARANJAN_MP</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/SIVARANJAN_MP/</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>922525106317</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>SIVASANJEEV P</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Sivasanjeev16</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Sivasanjeev16/</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>922525106318</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>SIVASUBRAMANI A</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>AK_Siva</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/AK_Siva/</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>922525106319</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>SIVATHARUN C</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>sivatharun22</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/sivatharun22/</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>922525106320</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>SOBIKA R</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>_sobika_R</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/_sobika_R/</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>922525106321</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>SREE DHARANI C</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>SREEDHARANI_14</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/SREEDHARANI_14/</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>922525106322</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>SRI  T</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Sri1540</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Sri1540/</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>922525106323</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>SRI HEERA J</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>sriheera03</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/sriheera03/</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>922525106324</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>SRI KANTH R</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>kanth2008</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/kanth2008/</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>922525106325</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>SRI SASTIKA G</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Srisastika_1401</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Srisastika_1401/</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>922525106326</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>SRI VARSHAN B P</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>srivarshan_B_P</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/srivarshan_B_P/</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>922525106327</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>SRINATH V</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>V_SRINATH</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/V_SRINATH/</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>922525106328</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>SRINIRANJAN S</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>SRINIRANJAN2008</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/SRINIRANJAN2008/</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>922525106329</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>SRINITHE T</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>srinithe_1401</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/srinithe_1401/</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>922525106330</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>SRINITHI S</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Srinithi24_</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Srinithi24_/</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>922525106331</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>SRISAMAYA R</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>mahi</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/mahi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>922525106332</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>SUBARNA V</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Subarna_17</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Subarna_17/</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>922525106333</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>SUBHA KARTHIKA R</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>subhakarthika</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/subhakarthika/</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>922525106334</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>SUBIKA T</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>subika1112</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/subika1112/</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>922525106335</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>SUDHARSAN S</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Sudharsan</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Sudharsan/</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>922525106336</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>SUGANTHAN K</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>SUGANTHKALAI</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/SUGANTHKALAI/</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>922525106360</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>VASUDEVAN G</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>GTVASU2008</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/GTVASU2008/</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>922525106337</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>SUGIDHARSHINI T</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Sugi_07</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Sugi_07/</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>922525106338</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>SUJEETH M</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>SUJEETH77</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/SUJEETH77/</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>922525106339</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>SUJITH RAJA B</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>mahi20_</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/mahi20_/</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>922525106341</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>SURYA PRABHU S</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>surya001prabhu</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/surya001prabhu/</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>922525106340</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>SUMITHRA S</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>sumithra_16</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/sumithra_16/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E141"/>
+  <autoFilter ref="A1:E184"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Students.xlsx
+++ b/Students.xlsx
@@ -2330,7 +2330,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>922525106288</t>
+          <t>922525106287</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>saravanan__k__</t>
+          <t>saravanan .k</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saravanan__k__/</t>
+          <t>https://leetcode.com/u/saravanan .k/</t>
         </is>
       </c>
     </row>
@@ -3059,7 +3059,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>922525106287</t>
+          <t>922525106288</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>saravanan .k</t>
+          <t>saravanan__k__</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saravanan .k/</t>
+          <t>https://leetcode.com/u/saravanan__k__/</t>
         </is>
       </c>
     </row>
@@ -3707,17 +3707,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>922525106342</t>
+          <t>922525106340</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>SUSIDHARAN M</t>
+          <t>SUMITHRA S</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Susidharan147</t>
+          <t>sumithra_16</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3727,24 +3727,24 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Susidharan147/</t>
+          <t>https://leetcode.com/u/sumithra_16/</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>922525106343</t>
+          <t>922525106341</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>SUTHARSHANA S</t>
+          <t>SURYA PRABHU S</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>sutharshana743</t>
+          <t>surya001prabhu</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -3754,24 +3754,24 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sutharshana743/</t>
+          <t>https://leetcode.com/u/surya001prabhu/</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>922525106344</t>
+          <t>922525106342</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>SWATHI M</t>
+          <t>SUSIDHARAN M</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Swathimanivel_1234</t>
+          <t>Susidharan147</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -3781,24 +3781,24 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Swathimanivel_1234/</t>
+          <t>https://leetcode.com/u/Susidharan147/</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>922525106345</t>
+          <t>922525106343</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>SWATHI S</t>
+          <t>SUTHARSHANA S</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>swathi _3366</t>
+          <t>sutharshana743</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -3808,24 +3808,24 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/swathi _3366/</t>
+          <t>https://leetcode.com/u/sutharshana743/</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>922525106346</t>
+          <t>922525106344</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>SWETHA E</t>
+          <t>SWATHI M</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Shwetha_20_1</t>
+          <t>Swathimanivel_1234</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -3835,7 +3835,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Shwetha_20_1/</t>
+          <t>https://leetcode.com/u/Swathimanivel_1234/</t>
         </is>
       </c>
     </row>
@@ -4544,17 +4544,17 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>922525106355</t>
+          <t>922525106346</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>VAISHNAVI U</t>
+          <t>SWETHA E</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>vaish200</t>
+          <t>Swetha_20_1</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -4564,24 +4564,24 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vaish200/</t>
+          <t>https://leetcode.com/u/Swetha_20_1/</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>922525106356</t>
+          <t>922525106355</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>VASANTH KUMAR C</t>
+          <t>VAISHNAVI U</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>VASANTH2007</t>
+          <t>vaish200</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VASANTH2007/</t>
+          <t>https://leetcode.com/u/vaish200/</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>922525106357</t>
+          <t>922525106356</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>VASANTH S</t>
+          <t>VASANTH KUMAR C</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>_vasanth_s_</t>
+          <t>VASANTH2007</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -4618,24 +4618,24 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_vasanth_s_/</t>
+          <t>https://leetcode.com/u/VASANTH2007/</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>922525106358</t>
+          <t>922525106357</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>VASANTHA KUMAR D</t>
+          <t>VASANTH S</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Vasanthakumar12232</t>
+          <t>_vasanth_s_</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -4645,24 +4645,24 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vasanthakumar12232/</t>
+          <t>https://leetcode.com/u/_vasanth_s_/</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>922525106359</t>
+          <t>922525106358</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>VASANTHKUMAR R</t>
+          <t>VASANTHA KUMAR D</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>VasanthKumar008</t>
+          <t>Vasanthakumar12232</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -4672,24 +4672,24 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VasanthKumar008/</t>
+          <t>https://leetcode.com/u/Vasanthakumar12232/</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>922525106316</t>
+          <t>922525106359</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>SIVARANJAN M P</t>
+          <t>VASANTHKUMAR R</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>SIVARANJAN_MP</t>
+          <t>VasanthKumar008</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -4699,24 +4699,24 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SIVARANJAN_MP/</t>
+          <t>https://leetcode.com/u/VasanthKumar008/</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>922525106317</t>
+          <t>922525106345</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>SIVASANJEEV P</t>
+          <t>SWATHI S</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Sivasanjeev16</t>
+          <t>_swathi _3366</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -4726,24 +4726,24 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sivasanjeev16/</t>
+          <t>https://leetcode.com/u/_swathi _3366/</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>922525106318</t>
+          <t>922525106316</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>SIVASUBRAMANI A</t>
+          <t>SIVARANJAN M P</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>AK_Siva</t>
+          <t>SIVARANJAN_MP</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -4753,24 +4753,24 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/AK_Siva/</t>
+          <t>https://leetcode.com/u/SIVARANJAN_MP/</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>922525106319</t>
+          <t>922525106317</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>SIVATHARUN C</t>
+          <t>SIVASANJEEV P</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>sivatharun22</t>
+          <t>Sivasanjeev16</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -4780,24 +4780,24 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivatharun22/</t>
+          <t>https://leetcode.com/u/Sivasanjeev16/</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>922525106320</t>
+          <t>922525106318</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>SOBIKA R</t>
+          <t>SIVASUBRAMANI A</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>_sobika_R</t>
+          <t>AK_Siva</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -4807,24 +4807,24 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_sobika_R/</t>
+          <t>https://leetcode.com/u/AK_Siva/</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>922525106321</t>
+          <t>922525106319</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>SREE DHARANI C</t>
+          <t>SIVATHARUN C</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>SREEDHARANI_14</t>
+          <t>sivatharun22</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -4834,24 +4834,24 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SREEDHARANI_14/</t>
+          <t>https://leetcode.com/u/sivatharun22/</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>922525106322</t>
+          <t>922525106320</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>SRI  T</t>
+          <t>SOBIKA R</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Sri1540</t>
+          <t>_sobika_R</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -4861,24 +4861,24 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sri1540/</t>
+          <t>https://leetcode.com/u/_sobika_R/</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>922525106323</t>
+          <t>922525106321</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>SRI HEERA J</t>
+          <t>SREE DHARANI C</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>sriheera03</t>
+          <t>SREEDHARANI_14</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -4888,24 +4888,24 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sriheera03/</t>
+          <t>https://leetcode.com/u/SREEDHARANI_14/</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>922525106324</t>
+          <t>922525106322</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>SRI KANTH R</t>
+          <t>SRI  T</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>kanth2008</t>
+          <t>Sri1540</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -4915,24 +4915,24 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kanth2008/</t>
+          <t>https://leetcode.com/u/Sri1540/</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>922525106325</t>
+          <t>922525106323</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>SRI SASTIKA G</t>
+          <t>SRI HEERA J</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Srisastika_1401</t>
+          <t>sriheera03</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -4942,24 +4942,24 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Srisastika_1401/</t>
+          <t>https://leetcode.com/u/sriheera03/</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>922525106326</t>
+          <t>922525106324</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>SRI VARSHAN B P</t>
+          <t>SRI KANTH R</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>srivarshan_B_P</t>
+          <t>kanth2008</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -4969,24 +4969,24 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/srivarshan_B_P/</t>
+          <t>https://leetcode.com/u/kanth2008/</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>922525106327</t>
+          <t>922525106325</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>SRINATH V</t>
+          <t>SRI SASTIKA G</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>V_SRINATH</t>
+          <t>Srisastika_1401</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -4996,24 +4996,24 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/V_SRINATH/</t>
+          <t>https://leetcode.com/u/Srisastika_1401/</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>922525106328</t>
+          <t>922525106326</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>SRINIRANJAN S</t>
+          <t>SRI VARSHAN B P</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>SRINIRANJAN2008</t>
+          <t>srivarshan_B_P</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -5023,24 +5023,24 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SRINIRANJAN2008/</t>
+          <t>https://leetcode.com/u/srivarshan_B_P/</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>922525106329</t>
+          <t>922525106327</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>SRINITHE T</t>
+          <t>SRINATH V</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>srinithe_1401</t>
+          <t>V_SRINATH</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -5050,24 +5050,24 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/srinithe_1401/</t>
+          <t>https://leetcode.com/u/V_SRINATH/</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>922525106330</t>
+          <t>922525106328</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>SRINITHI S</t>
+          <t>SRINIRANJAN S</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Srinithi24_</t>
+          <t>SRINIRANJAN2008</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -5077,24 +5077,24 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Srinithi24_/</t>
+          <t>https://leetcode.com/u/SRINIRANJAN2008/</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>922525106331</t>
+          <t>922525106329</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>SRISAMAYA R</t>
+          <t>SRINITHE T</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>mahi</t>
+          <t>srinithe_1401</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -5104,24 +5104,24 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/mahi/</t>
+          <t>https://leetcode.com/u/srinithe_1401/</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>922525106332</t>
+          <t>922525106330</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>SUBARNA V</t>
+          <t>SRINITHI S</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Subarna_17</t>
+          <t>Srinithi24_</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -5131,24 +5131,24 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Subarna_17/</t>
+          <t>https://leetcode.com/u/Srinithi24_/</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>922525106333</t>
+          <t>922525106331</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>SUBHA KARTHIKA R</t>
+          <t>SRISAMAYA R</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>subhakarthika</t>
+          <t>mahi</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -5158,24 +5158,24 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/subhakarthika/</t>
+          <t>https://leetcode.com/u/mahi/</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>922525106334</t>
+          <t>922525106332</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>SUBIKA T</t>
+          <t>SUBARNA V</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>subika1112</t>
+          <t>Subarna_17</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -5185,24 +5185,24 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/subika1112/</t>
+          <t>https://leetcode.com/u/Subarna_17/</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>922525106335</t>
+          <t>922525106333</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>SUDHARSAN S</t>
+          <t>SUBHA KARTHIKA R</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Sudharsan</t>
+          <t>subhakarthika</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -5212,24 +5212,24 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sudharsan/</t>
+          <t>https://leetcode.com/u/subhakarthika/</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>922525106336</t>
+          <t>922525106334</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>SUGANTHAN K</t>
+          <t>SUBIKA T</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>SUGANTHKALAI</t>
+          <t>subika1112</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SUGANTHKALAI/</t>
+          <t>https://leetcode.com/u/subika1112/</t>
         </is>
       </c>
     </row>
@@ -5273,17 +5273,17 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>922525106337</t>
+          <t>922525106335</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>SUGIDHARSHINI T</t>
+          <t>SUDHARSAN S</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Sugi_07</t>
+          <t>Sudharsan</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -5293,24 +5293,24 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sugi_07/</t>
+          <t>https://leetcode.com/u/Sudharsan/</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>922525106338</t>
+          <t>922525106336</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>SUJEETH M</t>
+          <t>SUGANTHAN K</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>SUJEETH77</t>
+          <t>SUGANTHKALAI</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -5320,24 +5320,24 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SUJEETH77/</t>
+          <t>https://leetcode.com/u/SUGANTHKALAI/</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>922525106339</t>
+          <t>922525106337</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>SUJITH RAJA B</t>
+          <t>SUGIDHARSHINI T</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>mahi20_</t>
+          <t>Sugi_07</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -5347,24 +5347,24 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/mahi20_/</t>
+          <t>https://leetcode.com/u/Sugi_07/</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>922525106341</t>
+          <t>922525106339</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>SURYA PRABHU S</t>
+          <t>SUJITH RAJA B</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>surya001prabhu</t>
+          <t>mahi20_</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -5374,24 +5374,24 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/surya001prabhu/</t>
+          <t>https://leetcode.com/u/mahi20_/</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>922525106340</t>
+          <t>922525106338</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>SUMITHRA S</t>
+          <t>SUJEETH M</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>sumithra_16</t>
+          <t>SUJEETH77</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sumithra_16/</t>
+          <t>https://leetcode.com/u/SUJEETH77/</t>
         </is>
       </c>
     </row>

--- a/Students.xlsx
+++ b/Students.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$184</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$190</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E184"/>
+  <dimension ref="A1:E190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2330,17 +2330,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>922525106287</t>
+          <t>922525106284</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SARAVANAN K</t>
+          <t>Santhosh S</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>saravanan .k</t>
+          <t>santhosh2407</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saravanan .k/</t>
+          <t>https://leetcode.com/u/santhosh2407/</t>
         </is>
       </c>
     </row>
@@ -2978,17 +2978,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>922525106284</t>
+          <t>922525106285</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Santhosh S</t>
+          <t>SANTHOSH V</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>santhosh2407</t>
+          <t>santhosh8760</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2998,24 +2998,24 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh2407/</t>
+          <t>https://leetcode.com/u/santhosh8760/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>922525106285</t>
+          <t>922525106286</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SANTHOSH V</t>
+          <t>SARAN K</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>santhosh8760</t>
+          <t>saran32</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3025,24 +3025,24 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh8760/</t>
+          <t>https://leetcode.com/u/saran32/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>922525106286</t>
+          <t>922525106287</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SARAN K</t>
+          <t>SARAVANAN K</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>saran32</t>
+          <t>saravanan .k</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saran32/</t>
+          <t>https://leetcode.com/u/saravanan .k/</t>
         </is>
       </c>
     </row>
@@ -3707,17 +3707,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>922525106340</t>
+          <t>922525106334</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>SUMITHRA S</t>
+          <t>SUBIKA T</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>sumithra_16</t>
+          <t>subika1112</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3727,24 +3727,24 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sumithra_16/</t>
+          <t>https://leetcode.com/u/subika1112/</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>922525106341</t>
+          <t>922525106335</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>SURYA PRABHU S</t>
+          <t>SUDHARSAN S</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>surya001prabhu</t>
+          <t>Sudharsan</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -3754,24 +3754,24 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/surya001prabhu/</t>
+          <t>https://leetcode.com/u/Sudharsan/</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>922525106342</t>
+          <t>922525106336</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>SUSIDHARAN M</t>
+          <t>SUGANTHAN K</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Susidharan147</t>
+          <t>SUGANTHKALAI</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -3781,24 +3781,24 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Susidharan147/</t>
+          <t>https://leetcode.com/u/SUGANTHKALAI/</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>922525106343</t>
+          <t>922525106337</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>SUTHARSHANA S</t>
+          <t>SUGIDHARSHINI T</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>sutharshana743</t>
+          <t>Sugi_07</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -3808,24 +3808,24 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sutharshana743/</t>
+          <t>https://leetcode.com/u/Sugi_07/</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>922525106344</t>
+          <t>922525106338</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>SWATHI M</t>
+          <t>SUJEETH M</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Swathimanivel_1234</t>
+          <t>SUJEETH77</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -3835,24 +3835,24 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Swathimanivel_1234/</t>
+          <t>https://leetcode.com/u/SUJEETH77/</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>922525106347</t>
+          <t>922525106339</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>TAMIL SELVAN R</t>
+          <t>SUJITH RAJA B</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Kdmif0HMNm</t>
+          <t>mahi20_</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -3862,24 +3862,24 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Kdmif0HMNm/</t>
+          <t>https://leetcode.com/u/mahi20_/</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>922525106348</t>
+          <t>922525106340</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>THAMARAI SELVI D</t>
+          <t>SUMITHRA S</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>thamarai_04</t>
+          <t>sumithra_16</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -3889,24 +3889,24 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/thamarai_04/</t>
+          <t>https://leetcode.com/u/sumithra_16/</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>922525106349</t>
+          <t>922525106341</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>THAMEEM FARSHITHA A</t>
+          <t>SURYA PRABHU S</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Thameem_786</t>
+          <t>surya001prabhu</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3916,24 +3916,24 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Thameem_786/</t>
+          <t>https://leetcode.com/u/surya001prabhu/</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>922525106350</t>
+          <t>922525106342</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>THARANISH R</t>
+          <t>SUSIDHARAN M</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>THARANISH2008</t>
+          <t>Susidharan147</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -3943,24 +3943,24 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/THARANISH2008/</t>
+          <t>https://leetcode.com/u/Susidharan147/</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>922525106351</t>
+          <t>922525106343</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>THARUNIKA P</t>
+          <t>SUTHARSHANA S</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Tharunika_12</t>
+          <t>sutharshana743</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -3970,24 +3970,24 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Tharunika_12/</t>
+          <t>https://leetcode.com/u/sutharshana743/</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>922525106352</t>
+          <t>922525106344</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>THIRINESH KUMAR S</t>
+          <t>SWATHI M</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>THIRINESH KUMAR.S</t>
+          <t>Swathimanivel_1234</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -3997,24 +3997,24 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/THIRINESH KUMAR.S/</t>
+          <t>https://leetcode.com/u/Swathimanivel_1234/</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>922525106353</t>
+          <t>922525106347</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>THIRISHA C</t>
+          <t>TAMIL SELVAN R</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>thirishavsb</t>
+          <t>Kdmif0HMNm</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -4024,24 +4024,24 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/thirishavsb/</t>
+          <t>https://leetcode.com/u/Kdmif0HMNm/</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>922525106354</t>
+          <t>922525106348</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>THIRUMURUGAN S</t>
+          <t>THAMARAI SELVI D</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>thiru0211_</t>
+          <t>thamarai_04</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -4051,24 +4051,24 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/thiru0211_/</t>
+          <t>https://leetcode.com/u/thamarai_04/</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>922525106361</t>
+          <t>922525106349</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>VASUKI K</t>
+          <t>THAMEEM FARSHITHA A</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>vasuki</t>
+          <t>Thameem_786</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -4078,24 +4078,24 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vasuki/</t>
+          <t>https://leetcode.com/u/Thameem_786/</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>922525106362</t>
+          <t>922525106350</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>VELLIANGIRI R</t>
+          <t>THARANISH R</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>velliangiri_R</t>
+          <t>THARANISH2008</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -4105,24 +4105,24 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/velliangiri_R/</t>
+          <t>https://leetcode.com/u/THARANISH2008/</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>922525106363</t>
+          <t>922525106351</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>VIGNESH M</t>
+          <t>THARUNIKA P</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>O8bYDSRUbE</t>
+          <t>Tharunika_12</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -4132,24 +4132,24 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/O8bYDSRUbE/</t>
+          <t>https://leetcode.com/u/Tharunika_12/</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>922525106364</t>
+          <t>922525106352</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>VIGNESH VELAN M</t>
+          <t>THIRINESH KUMAR S</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Vicky_27_Velan</t>
+          <t>THIRINESH KUMAR.S</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -4159,24 +4159,24 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vicky_27_Velan/</t>
+          <t>https://leetcode.com/u/THIRINESH KUMAR.S/</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>922525106365</t>
+          <t>922525106353</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>VIGNESHWAR U</t>
+          <t>THIRISHA C</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>VIGNESHWAR0221</t>
+          <t>thirishavsb</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -4186,24 +4186,24 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VIGNESHWAR0221/</t>
+          <t>https://leetcode.com/u/thirishavsb/</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>922525106366</t>
+          <t>922525106354</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>VIJAYARAGAVAN R</t>
+          <t>THIRUMURUGAN S</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>vijayaragavan1216</t>
+          <t>thiru0211_</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -4213,24 +4213,24 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vijayaragavan1216/</t>
+          <t>https://leetcode.com/u/thiru0211_/</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>922525106367</t>
+          <t>922525106361</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>VIKRAM V</t>
+          <t>VASUKI K</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>vikramvicky5678</t>
+          <t>vasuki</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -4240,24 +4240,24 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vikramvicky5678/</t>
+          <t>https://leetcode.com/u/vasuki/</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>922525106368</t>
+          <t>922525106362</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>VISHNU B</t>
+          <t>VELLIANGIRI R</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>VISHNU_B_2008</t>
+          <t>velliangiri_R</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -4267,24 +4267,24 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VISHNU_B_2008/</t>
+          <t>https://leetcode.com/u/velliangiri_R/</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>922525106369</t>
+          <t>922525106363</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>VISHNU PRIYAN S</t>
+          <t>VIGNESH M</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>itz__priyan__</t>
+          <t>O8bYDSRUbE</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -4294,24 +4294,24 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itz__priyan__/</t>
+          <t>https://leetcode.com/u/O8bYDSRUbE/</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>922525106370</t>
+          <t>922525106364</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>VISHNUHARAN V S</t>
+          <t>VIGNESH VELAN M</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Vishnuharan082007</t>
+          <t>Vicky_27_Velan</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -4321,24 +4321,24 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vishnuharan082007/</t>
+          <t>https://leetcode.com/u/Vicky_27_Velan/</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>922525106371</t>
+          <t>922525106365</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>VISHNUPRIYA S</t>
+          <t>VIGNESHWAR U</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>vishnupriyamaran</t>
+          <t>VIGNESHWAR0221</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -4348,24 +4348,24 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vishnupriyamaran/</t>
+          <t>https://leetcode.com/u/VIGNESHWAR0221/</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>922525106372</t>
+          <t>922525106366</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>VISHWAJETH A M</t>
+          <t>VIJAYARAGAVAN R</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>vishwajeth</t>
+          <t>vijayaragavan1216</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -4375,24 +4375,24 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vishwajeth/</t>
+          <t>https://leetcode.com/u/vijayaragavan1216/</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>922525106373</t>
+          <t>922525106367</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>YASHNI S</t>
+          <t>VIKRAM V</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Yashnisubramaniyan</t>
+          <t>vikramvicky5678</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -4402,24 +4402,24 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Yashnisubramaniyan/</t>
+          <t>https://leetcode.com/u/vikramvicky5678/</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>922525106374</t>
+          <t>922525106368</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>YASWANTH V</t>
+          <t>VISHNU B</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>yaswanth_2008</t>
+          <t>VISHNU_B_2008</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -4429,24 +4429,24 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yaswanth_2008/</t>
+          <t>https://leetcode.com/u/VISHNU_B_2008/</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>922525106375</t>
+          <t>922525106369</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>YAZHINI M</t>
+          <t>VISHNU PRIYAN S</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>yazhini2007</t>
+          <t>itz__priyan__</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -4456,24 +4456,24 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yazhini2007/</t>
+          <t>https://leetcode.com/u/itz__priyan__/</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>922525106376</t>
+          <t>922525106370</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>YAZHINI S</t>
+          <t>VISHNUHARAN V S</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>yazhini__1234</t>
+          <t>Vishnuharan082007</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -4483,24 +4483,24 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yazhini__1234/</t>
+          <t>https://leetcode.com/u/Vishnuharan082007/</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>922525106377</t>
+          <t>922525106371</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>YAZHINI V</t>
+          <t>VISHNUPRIYA S</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>VISU_YAZHU</t>
+          <t>vishnupriyamaran</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -4510,24 +4510,24 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VISU_YAZHU/</t>
+          <t>https://leetcode.com/u/vishnupriyamaran/</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>922525106378</t>
+          <t>922525106372</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>YOKESWARAN S</t>
+          <t>VISHWAJETH A M</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>syokeswaran</t>
+          <t>vishwajeth</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -4537,24 +4537,24 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/syokeswaran/</t>
+          <t>https://leetcode.com/u/vishwajeth/</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>922525106346</t>
+          <t>922525106373</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>SWETHA E</t>
+          <t>YASHNI S</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Swetha_20_1</t>
+          <t>Yashnisubramaniyan</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -4564,24 +4564,24 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Swetha_20_1/</t>
+          <t>https://leetcode.com/u/Yashnisubramaniyan/</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>922525106355</t>
+          <t>922525106374</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>VAISHNAVI U</t>
+          <t>YASWANTH V</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>vaish200</t>
+          <t>yaswanth_2008</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vaish200/</t>
+          <t>https://leetcode.com/u/yaswanth_2008/</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>922525106356</t>
+          <t>922525106375</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>VASANTH KUMAR C</t>
+          <t>YAZHINI M</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>VASANTH2007</t>
+          <t>yazhini2007</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -4618,24 +4618,24 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VASANTH2007/</t>
+          <t>https://leetcode.com/u/yazhini2007/</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>922525106357</t>
+          <t>922525106376</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>VASANTH S</t>
+          <t>YAZHINI S</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>_vasanth_s_</t>
+          <t>yazhini__1234</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -4645,24 +4645,24 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_vasanth_s_/</t>
+          <t>https://leetcode.com/u/yazhini__1234/</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>922525106358</t>
+          <t>922525106377</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>VASANTHA KUMAR D</t>
+          <t>YAZHINI V</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Vasanthakumar12232</t>
+          <t>VISU_YAZHU</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -4672,24 +4672,24 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vasanthakumar12232/</t>
+          <t>https://leetcode.com/u/VISU_YAZHU/</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>922525106359</t>
+          <t>922525106378</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>VASANTHKUMAR R</t>
+          <t>YOKESWARAN S</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>VasanthKumar008</t>
+          <t>syokeswaran</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -4699,24 +4699,24 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VasanthKumar008/</t>
+          <t>https://leetcode.com/u/syokeswaran/</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>922525106345</t>
+          <t>922525106346</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>SWATHI S</t>
+          <t>SWETHA E</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>_swathi _3366</t>
+          <t>Swetha_20_1</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -4726,24 +4726,24 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_swathi _3366/</t>
+          <t>https://leetcode.com/u/Swetha_20_1/</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>922525106316</t>
+          <t>922525106332</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>SIVARANJAN M P</t>
+          <t>SUBARNA V</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>SIVARANJAN_MP</t>
+          <t>Subarna_17</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -4753,24 +4753,24 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SIVARANJAN_MP/</t>
+          <t>https://leetcode.com/u/Subarna_17/</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>922525106317</t>
+          <t>922525106328</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>SIVASANJEEV P</t>
+          <t>SRINIRANJAN S</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Sivasanjeev16</t>
+          <t>SRINIRANJAN2008</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -4780,24 +4780,24 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sivasanjeev16/</t>
+          <t>https://leetcode.com/u/SRINIRANJAN2008/</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>922525106318</t>
+          <t>922525106329</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>SIVASUBRAMANI A</t>
+          <t>SRINITHE T</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>AK_Siva</t>
+          <t>srinithe_1401</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -4807,24 +4807,24 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/AK_Siva/</t>
+          <t>https://leetcode.com/u/srinithe_1401/</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>922525106319</t>
+          <t>922525106330</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>SIVATHARUN C</t>
+          <t>SRINITHI S</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>sivatharun22</t>
+          <t>Srinithi24_</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -4834,24 +4834,24 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivatharun22/</t>
+          <t>https://leetcode.com/u/Srinithi24_/</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>922525106320</t>
+          <t>922525106331</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>SOBIKA R</t>
+          <t>SRISAMAYA R</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>_sobika_R</t>
+          <t>mahi</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -4861,24 +4861,24 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_sobika_R/</t>
+          <t>https://leetcode.com/u/mahi/</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>922525106321</t>
+          <t>922525106360</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>SREE DHARANI C</t>
+          <t>VASUDEVAN G</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>SREEDHARANI_14</t>
+          <t>GTVASU2008</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -4888,24 +4888,24 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SREEDHARANI_14/</t>
+          <t>https://leetcode.com/u/GTVASU2008/</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>922525106322</t>
+          <t>922525106333</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>SRI  T</t>
+          <t>SUBHA KARTHIKA R</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Sri1540</t>
+          <t>subhakarthika</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -4915,24 +4915,24 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sri1540/</t>
+          <t>https://leetcode.com/u/subhakarthika/</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>922525106323</t>
+          <t>922525106355</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>SRI HEERA J</t>
+          <t>VAISHNAVI U</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>sriheera03</t>
+          <t>vaish200</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -4942,24 +4942,24 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sriheera03/</t>
+          <t>https://leetcode.com/u/vaish200/</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>922525106324</t>
+          <t>922525106356</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>SRI KANTH R</t>
+          <t>VASANTH KUMAR C</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>kanth2008</t>
+          <t>VASANTH2007</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -4969,24 +4969,24 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kanth2008/</t>
+          <t>https://leetcode.com/u/VASANTH2007/</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>922525106325</t>
+          <t>922525106357</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>SRI SASTIKA G</t>
+          <t>VASANTH S</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Srisastika_1401</t>
+          <t>_vasanth_s_</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -4996,24 +4996,24 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Srisastika_1401/</t>
+          <t>https://leetcode.com/u/_vasanth_s_/</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>922525106326</t>
+          <t>922525106358</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>SRI VARSHAN B P</t>
+          <t>VASANTHA KUMAR D</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>srivarshan_B_P</t>
+          <t>Vasanthakumar12232</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -5023,24 +5023,24 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/srivarshan_B_P/</t>
+          <t>https://leetcode.com/u/Vasanthakumar12232/</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>922525106327</t>
+          <t>922525106359</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>SRINATH V</t>
+          <t>VASANTHKUMAR R</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>V_SRINATH</t>
+          <t>VasanthKumar008</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -5050,24 +5050,24 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/V_SRINATH/</t>
+          <t>https://leetcode.com/u/VasanthKumar008/</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>922525106328</t>
+          <t>922525106345</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>SRINIRANJAN S</t>
+          <t>SWATHI S</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>SRINIRANJAN2008</t>
+          <t>_swathi _3366</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -5077,24 +5077,24 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SRINIRANJAN2008/</t>
+          <t>https://leetcode.com/u/_swathi _3366/</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>922525106329</t>
+          <t>922525106316</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>SRINITHE T</t>
+          <t>SIVARANJAN M P</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>srinithe_1401</t>
+          <t>SIVARANJAN_MP</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -5104,24 +5104,24 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/srinithe_1401/</t>
+          <t>https://leetcode.com/u/SIVARANJAN_MP/</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>922525106330</t>
+          <t>922525106317</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>SRINITHI S</t>
+          <t>SIVASANJEEV P</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Srinithi24_</t>
+          <t>Sivasanjeev16</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -5131,24 +5131,24 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Srinithi24_/</t>
+          <t>https://leetcode.com/u/Sivasanjeev16/</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>922525106331</t>
+          <t>922525106318</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>SRISAMAYA R</t>
+          <t>SIVASUBRAMANI A</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>mahi</t>
+          <t>AK_Siva</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -5158,24 +5158,24 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/mahi/</t>
+          <t>https://leetcode.com/u/AK_Siva/</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>922525106332</t>
+          <t>922525106319</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>SUBARNA V</t>
+          <t>SIVATHARUN C</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Subarna_17</t>
+          <t>sivatharun22</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -5185,24 +5185,24 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Subarna_17/</t>
+          <t>https://leetcode.com/u/sivatharun22/</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>922525106333</t>
+          <t>922525106320</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>SUBHA KARTHIKA R</t>
+          <t>SOBIKA R</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>subhakarthika</t>
+          <t>_sobika_R</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -5212,24 +5212,24 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/subhakarthika/</t>
+          <t>https://leetcode.com/u/_sobika_R/</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>922525106334</t>
+          <t>922525106321</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>SUBIKA T</t>
+          <t>SREE DHARANI C</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>subika1112</t>
+          <t>SREEDHARANI_14</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -5239,24 +5239,24 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/subika1112/</t>
+          <t>https://leetcode.com/u/SREEDHARANI_14/</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>922525106360</t>
+          <t>922525106322</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>VASUDEVAN G</t>
+          <t>SRI  T</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>GTVASU2008</t>
+          <t>Sri1540</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -5266,24 +5266,24 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/GTVASU2008/</t>
+          <t>https://leetcode.com/u/Sri1540/</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>922525106335</t>
+          <t>922525106323</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>SUDHARSAN S</t>
+          <t>SRI HEERA J</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Sudharsan</t>
+          <t>sriheera03</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -5293,24 +5293,24 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sudharsan/</t>
+          <t>https://leetcode.com/u/sriheera03/</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>922525106336</t>
+          <t>922525106324</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>SUGANTHAN K</t>
+          <t>SRI KANTH R</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>SUGANTHKALAI</t>
+          <t>kanth2008</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -5320,24 +5320,24 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SUGANTHKALAI/</t>
+          <t>https://leetcode.com/u/kanth2008/</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>922525106337</t>
+          <t>922525106325</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>SUGIDHARSHINI T</t>
+          <t>SRI SASTIKA G</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Sugi_07</t>
+          <t>Srisastika_1401</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -5347,24 +5347,24 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sugi_07/</t>
+          <t>https://leetcode.com/u/Srisastika_1401/</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>922525106339</t>
+          <t>922525106326</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>SUJITH RAJA B</t>
+          <t>SRI VARSHAN B P</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>mahi20_</t>
+          <t>srivarshan_B_P</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -5374,24 +5374,24 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/mahi20_/</t>
+          <t>https://leetcode.com/u/srivarshan_B_P/</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>922525106338</t>
+          <t>922525106327</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>SUJEETH M</t>
+          <t>SRINATH V</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>SUJEETH77</t>
+          <t>V_SRINATH</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -5401,12 +5401,174 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SUJEETH77/</t>
+          <t>https://leetcode.com/u/V_SRINATH/</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>922525106267</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>SAJISH R</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>SAJISH7</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/SAJISH7/</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>922525106270</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>SANDHIYA T</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>zklXTc9UAp</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/zklXTc9UAp/</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>922525106276</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>SANJAYAN</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>sanjayan31</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/sanjayan31/</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>922525106294</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>SATHANA SRI S K</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Sathana-1267</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Sathana-1267/</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>922525106304</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>SANTHOSH SHAI SIRIL</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>shandoshsai</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/shandoshsai/</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>922525106306</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>SHARUKESH</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>sharukesh2008</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/sharukesh2008/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E184"/>
+  <autoFilter ref="A1:E190"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Students.xlsx
+++ b/Students.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$190</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$121</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E190"/>
+  <dimension ref="A1:E121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -467,3095 +467,3095 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>922525106142</t>
+          <t>922525106286</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>KANITHRA R</t>
+          <t>SARAN K</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>kanithraakila</t>
+          <t>saran32</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kanithraakila/</t>
+          <t>https://leetcode.com/u/saran32/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>922525106102</t>
+          <t>922525106288</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GOWSICK S</t>
+          <t>SARAVANAN K</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>922525000000</t>
+          <t>saravanan__k__</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ECE B</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525000000/</t>
+          <t>https://leetcode.com/u/saravanan__k__/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>922525106177</t>
+          <t>922525106289</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MADELIN JENITA M</t>
+          <t>SARAVANAN S</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>jenita0206</t>
+          <t>Saravanan_7525</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/jenita0206/</t>
+          <t>https://leetcode.com/u/Saravanan_7525/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>922525106043</t>
+          <t>922525106290</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BHARGAVI K</t>
+          <t>SARIKA M P</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>bhargavi_332008</t>
+          <t>sarika_5408</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/bhargavi_332008/</t>
+          <t>https://leetcode.com/u/sarika_5408/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>922525106054</t>
+          <t>922525106291</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DAKSHINYA R</t>
+          <t>SARVESWARAN R</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dakshinya555</t>
+          <t>sarvesh312008</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Dakshinya555/</t>
+          <t>https://leetcode.com/u/sarvesh312008/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>922525106175</t>
+          <t>922525106292</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LOHITH RAJ S</t>
+          <t>SASHMIKA.P</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>LOHITH 012008</t>
+          <t>sashmikaprabhu</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/LOHITH 012008/</t>
+          <t>https://leetcode.com/u/sashmikaprabhu/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>922525106127</t>
+          <t>922525106296</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JANANI A</t>
+          <t>SELVAKUMAR K</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>janani_asohkan</t>
+          <t>Selvakumarsk-32</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/janani_asohkan/</t>
+          <t>https://leetcode.com/u/Selvakumarsk-32/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>922525106045</t>
+          <t>922525106297</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BOOBASE R</t>
+          <t>SELVAPRAGADEESH S</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Boobase</t>
+          <t>Selvapragadeesh</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Boobase/</t>
+          <t>https://leetcode.com/u/Selvapragadeesh/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>922525106152</t>
+          <t>922525106298</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>KAVIPRIYA R</t>
+          <t>SELVA RAGAVAN</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>KAVI_RAVI</t>
+          <t>Selvax07</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/KAVI_RAVI/</t>
+          <t>https://leetcode.com/u/Selvax07/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>922525106208</t>
+          <t>922525106299</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NANDHINI D</t>
+          <t>SENTHAMIZHSELVAN K</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>nandhini _208</t>
+          <t>Senthamizh08</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/nandhini _208/</t>
+          <t>https://leetcode.com/u/Senthamizh08/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>922525106205</t>
+          <t>922525106300</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MYTHILI M</t>
+          <t>Senthil.S</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mythili_2208</t>
+          <t>Jna76WrjNd</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Mythili_2208/</t>
+          <t>https://leetcode.com/u/Jna76WrjNd/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>922525106079</t>
+          <t>922525106302</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DHINAKAR A</t>
+          <t>SHAHANA S</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>dhina</t>
+          <t>shahana_pandiraj04</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ECE B</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/dhina/</t>
+          <t>https://leetcode.com/u/shahana_pandiraj04/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>922525106032</t>
+          <t>922525106303</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ARVINSHANKARA V</t>
+          <t>SHANTHINI C</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ok</t>
+          <t>ShanthiniChelladurai</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Ok/</t>
+          <t>https://leetcode.com/u/ShanthiniChelladurai/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>922525106027</t>
+          <t>922525106305</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ARULESH K</t>
+          <t>SHARATH P</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>arul2008</t>
+          <t>sharath_1010</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/arul2008/</t>
+          <t>https://leetcode.com/u/sharath_1010/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>922525106049</t>
+          <t>922525106307</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BUVNESH N</t>
+          <t>SHIVANI B</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Buvnesh_2008</t>
+          <t>shivani208</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Buvnesh_2008/</t>
+          <t>https://leetcode.com/u/shivani208/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>922525106047</t>
+          <t>922525106308</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BOSVIYA P</t>
+          <t>SHREE HARINI L</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BosviyaBSV</t>
+          <t>Shree_Harini478</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/BosviyaBSV/</t>
+          <t>https://leetcode.com/u/Shree_Harini478/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>922525106059</t>
+          <t>922525106309</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DEJASRI M</t>
+          <t>SHREE CHARAN T</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>dejasri</t>
+          <t>shreecharan22</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/dejasri/</t>
+          <t>https://leetcode.com/u/shreecharan22/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>922525106014</t>
+          <t>922525106310</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AKASH R</t>
+          <t>SIVA MANIKANDAN K</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AkashRajaram</t>
+          <t>9043374912</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/AkashRajaram/</t>
+          <t>https://leetcode.com/u/9043374912/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>922525106009</t>
+          <t>922525106311</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AISHWARYA G</t>
+          <t>SIVA PRAKASH M</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Codewithaish</t>
+          <t>sivaprakash_0406</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Codewithaish/</t>
+          <t>https://leetcode.com/u/sivaprakash_0406/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>922525106125</t>
+          <t>922525106312</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>JAI GANESH I</t>
+          <t>SIVADHARSHINI D</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jai_Ganesh_I</t>
+          <t>dharshinideivsigamani</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ECE B</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Jai_Ganesh_I/</t>
+          <t>https://leetcode.com/u/dharshinideivsigamani/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>922525106186</t>
+          <t>922525106287</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MAHIBALAN A</t>
+          <t>SARAVANAN K</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>lakshmiprabha1984-prog</t>
+          <t>saravanan .k</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/lakshmiprabha1984-prog/</t>
+          <t>https://leetcode.com/u/saravanan .k/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>922525106160</t>
+          <t>922525196293</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>KOHUL V</t>
+          <t>SASWIN D</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kohul_v</t>
+          <t>saswin_88</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Kohul_v/</t>
+          <t>https://leetcode.com/u/saswin_88/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>922525106144</t>
+          <t>922525106315</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>KARMUKILAN J</t>
+          <t>SIVANESH G</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>karmukilan567</t>
+          <t>GSIVANESH</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/karmukilan567/</t>
+          <t>https://leetcode.com/u/GSIVANESH/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>922525106180</t>
+          <t>922525106314</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MADHUDHARA P</t>
+          <t>SIVANESH D</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>madhudhara</t>
+          <t>sivanesh2007</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/madhudhara/</t>
+          <t>https://leetcode.com/u/sivanesh2007/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>922525106189</t>
+          <t>922525106313</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MANISHA D</t>
+          <t>SIVAGNANAM M</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>manishaa_20</t>
+          <t>sivagnanam3344</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/manishaa_20/</t>
+          <t>https://leetcode.com/u/sivagnanam3344/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>922525106183</t>
+          <t>922525106253</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MAHALAKSHMI B</t>
+          <t>RITHANYA KN</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>mahalakshmi182025</t>
+          <t>Rithanya12-3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/mahalakshmi182025/</t>
+          <t>https://leetcode.com/u/Rithanya12-3/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>922525106184</t>
+          <t>922525106256</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MAHALAKSHMI M</t>
+          <t>RITHIK P</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Maha ece</t>
+          <t>Rithik_78</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Maha ece/</t>
+          <t>https://leetcode.com/u/Rithik_78/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>922525106156</t>
+          <t>922525106257</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>KEERTHANA S</t>
+          <t>RITHIKA B</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Hwfrd8kp5Y</t>
+          <t>Rithika_Balakrishnan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Hwfrd8kp5Y/</t>
+          <t>https://leetcode.com/u/Rithika_Balakrishnan/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>922525106236</t>
+          <t>922525106258</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PRITHIV S</t>
+          <t>RITHISH R</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Prithiv25</t>
+          <t>Rithish_</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Prithiv25/</t>
+          <t>https://leetcode.com/u/Rithish_/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>922525106195</t>
+          <t>922525106259</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MAYUKA M</t>
+          <t>ROHITH V</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Mayuka_25</t>
+          <t>RohithrohiV</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Mayuka_25/</t>
+          <t>https://leetcode.com/u/RohithrohiV/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>922525106214</t>
+          <t>922525106260</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NITHISH C T</t>
+          <t>ROOBAGAPRIYA R</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Nithish12322</t>
+          <t>Roobagapriya</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Nithish12322/</t>
+          <t>https://leetcode.com/u/Roobagapriya/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>922525106225</t>
+          <t>922525106261</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PIRAVEEN M</t>
+          <t>Roshan M</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Piraveen_M</t>
+          <t>roshan2403</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Piraveen_M/</t>
+          <t>https://leetcode.com/u/roshan2403/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>922525106211</t>
+          <t>922525106262</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>NAVEETHA N</t>
+          <t>ROSHIKA V</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Naveetha_</t>
+          <t>roshikaveeramalai</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Naveetha_/</t>
+          <t>https://leetcode.com/u/roshikaveeramalai/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>922525106199</t>
+          <t>922525106263</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MONISH S</t>
+          <t>RUBESH C</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MonishS77</t>
+          <t>Rubesh_7</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/MonishS77/</t>
+          <t>https://leetcode.com/u/Rubesh_7/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>922525106232</t>
+          <t>922525106264</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>PRAVEEN G</t>
+          <t>SABAREESH K</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>praveen_gobi</t>
+          <t>sabareesh_karikalan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/praveen_gobi/</t>
+          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>922525106001</t>
+          <t>922525106265</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>AASHIFA SAHANAJ M</t>
+          <t>SABARIVASAN P</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>aashifasahanaj</t>
+          <t>SabarivasanP</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/aashifasahanaj/</t>
+          <t>https://leetcode.com/u/SabarivasanP/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>922525106002</t>
+          <t>922525106266</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>AAZHIGA N</t>
+          <t>SAHANA.V</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AAZHIGA</t>
+          <t>Sahanavijayakumar_0033</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/AAZHIGA/</t>
+          <t>https://leetcode.com/u/Sahanavijayakumar_0033/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>922525106004</t>
+          <t>922525106268</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Abirami R</t>
+          <t>SAKTHI S</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>abirami8072</t>
+          <t>Sakthisaro08</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/abirami8072/</t>
+          <t>https://leetcode.com/u/Sakthisaro08/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>922525106018</t>
+          <t>922525106269</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AMIRDAVARSINI K S</t>
+          <t>Sakthivel. M</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>amirda_varsini_2007</t>
+          <t>sakthivel23116</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/amirda_varsini_2007/</t>
+          <t>https://leetcode.com/u/sakthivel23116/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>922525106022</t>
+          <t>922525106271</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ANUJA S</t>
+          <t>SANDHOSH KUMAR R</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>anuja008</t>
+          <t>sandhosh_30_R</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/anuja008/</t>
+          <t>https://leetcode.com/u/sandhosh_30_R/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>922525106023</t>
+          <t>922525106272</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ANUSRI R</t>
+          <t>SANJAY D</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Anusri_2008</t>
+          <t>itsmesanjay007</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Anusri_2008/</t>
+          <t>https://leetcode.com/u/itsmesanjay007/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>922525106024</t>
+          <t>922525106273</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ANUSYA B</t>
+          <t>SANJAY P</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ANUSYA_30</t>
+          <t>sanjay00675</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/ANUSYA_30/</t>
+          <t>https://leetcode.com/u/sanjay00675/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>922525106046</t>
+          <t>922525106275</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BOOMIKA T</t>
+          <t>SANJAY U</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>boomikat1206</t>
+          <t>SanjayUdayan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/boomikat1206/</t>
+          <t>https://leetcode.com/u/SanjayUdayan/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>922525106060</t>
+          <t>922525106278</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>DESMA SHALINI K</t>
+          <t>SANMATHI R</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>desmashalini</t>
+          <t>sanmathi06</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/desmashalini/</t>
+          <t>https://leetcode.com/u/sanmathi06/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>922525106063</t>
+          <t>922525106279</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>DHANASRI R</t>
+          <t>SANTHIYA T</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Dhanasri_r</t>
+          <t>santhiya0202</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Dhanasri_r/</t>
+          <t>https://leetcode.com/u/santhiya0202/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>922525106064</t>
+          <t>922525106280</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DHANIKA S</t>
+          <t>SANTHOSH D</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>santhosh7811</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ECE B</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/a/</t>
+          <t>https://leetcode.com/u/santhosh7811/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>922525106065</t>
+          <t>922525106282</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>DHANUSHRI D</t>
+          <t>SANTHOSH PRIYAN S</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>bo</t>
+          <t>SANTHOSH PRIYAN S</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ECE B</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/bo/</t>
+          <t>https://leetcode.com/u/SANTHOSH PRIYAN S/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>922525106071</t>
+          <t>922525106283</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>DHARANI V</t>
+          <t>SANTHOSH S</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>SanthoshSathya260</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ECE B</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/c/</t>
+          <t>https://leetcode.com/u/SanthoshSathya260/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>922525106092</t>
+          <t>922525106284</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ELAVARASU P</t>
+          <t>Santhosh S</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>santhosh2407</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ECE B</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/d/</t>
+          <t>https://leetcode.com/u/santhosh2407/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>922525106119</t>
+          <t>922525106285</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>HAVISHMATHI S</t>
+          <t>SANTHOSH V</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>santhosh8760</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ECE B</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/e/</t>
+          <t>https://leetcode.com/u/santhosh8760/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>922525106136</t>
+          <t>922525106301</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>JOSHITHA KS</t>
+          <t>SETHUPATHI G</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Joshi_666</t>
+          <t>Sethupathi_1228</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Joshi_666/</t>
+          <t>https://leetcode.com/u/Sethupathi_1228/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>922525106138</t>
+          <t>922525106345</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>JOTHISHA K S</t>
+          <t>SWATHI S</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Jothi-</t>
+          <t>_swathi _3366</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Jothi-/</t>
+          <t>https://leetcode.com/u/_swathi _3366/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>922525106148</t>
+          <t>922525106361</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>KAVIMALAR A</t>
+          <t>VASUKI K</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>kavimalar08</t>
+          <t>vasuki</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kavimalar08/</t>
+          <t>https://leetcode.com/u/vasuki/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>922525106155</t>
+          <t>922525106362</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>KAYALVIZHI S</t>
+          <t>VELLIANGIRI R</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>27kayalvizhi</t>
+          <t>velliangiri_R</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/27kayalvizhi/</t>
+          <t>https://leetcode.com/u/velliangiri_R/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>922525106164</t>
+          <t>922525106363</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>KOWSHIKA M S</t>
+          <t>VIGNESH M</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>kowshika_moorthi</t>
+          <t>O8bYDSRUbE</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kowshika_moorthi/</t>
+          <t>https://leetcode.com/u/O8bYDSRUbE/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>922525106171</t>
+          <t>922525106364</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>LOGASRI.A</t>
+          <t>VIGNESH VELAN M</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Loga07</t>
+          <t>Vicky_27_Velan</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Loga07/</t>
+          <t>https://leetcode.com/u/Vicky_27_Velan/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>922525106181</t>
+          <t>922525106365</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MADHUMITHA B</t>
+          <t>VIGNESHWAR U</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>madhumitha-42</t>
+          <t>VIGNESHWAR0221</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/madhumitha-42/</t>
+          <t>https://leetcode.com/u/VIGNESHWAR0221/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>922525106191</t>
+          <t>922525106366</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MANOJ KUMAR V</t>
+          <t>VIJAYARAGAVAN R</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>m____a____n____o____</t>
+          <t>vijayaragavan1216</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/m____a____n____o____/</t>
+          <t>https://leetcode.com/u/vijayaragavan1216/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>922525106201</t>
+          <t>922525106367</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MONISHA V</t>
+          <t>VIKRAM V</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MonishaV01</t>
+          <t>vikramvicky5678</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/MonishaV01/</t>
+          <t>https://leetcode.com/u/vikramvicky5678/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>922525106203</t>
+          <t>922525106368</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MOULEESHWARI B</t>
+          <t>VISHNU B</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MouleeshwariB</t>
+          <t>VISHNU_B_2008</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/MouleeshwariB/</t>
+          <t>https://leetcode.com/u/VISHNU_B_2008/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>922525106204</t>
+          <t>922525106369</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MOUSHMI P N</t>
+          <t>VISHNU PRIYAN S</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Moushmi_08</t>
+          <t>itz__priyan__</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Moushmi_08/</t>
+          <t>https://leetcode.com/u/itz__priyan__/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>922525106213</t>
+          <t>922525106370</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>NIRANJANI D</t>
+          <t>VISHNUHARAN V S</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>niranjani _17</t>
+          <t>Vishnuharan082007</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/niranjani _17/</t>
+          <t>https://leetcode.com/u/Vishnuharan082007/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>922525106219</t>
+          <t>922525106371</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NITHYASHREE P</t>
+          <t>VISHNUPRIYA S</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Nithyashree_273</t>
+          <t>vishnupriyamaran</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Nithyashree_273/</t>
+          <t>https://leetcode.com/u/vishnupriyamaran/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>922525106220</t>
+          <t>922525106372</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NITHYASRI M</t>
+          <t>VISHWAJETH A M</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>nithyam7809</t>
+          <t>vishwajeth</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/nithyam7809/</t>
+          <t>https://leetcode.com/u/vishwajeth/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>922525106223</t>
+          <t>922525106373</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PAVITHRA S</t>
+          <t>YASHNI S</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Pavithra145</t>
+          <t>Yashnisubramaniyan</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Pavithra145/</t>
+          <t>https://leetcode.com/u/Yashnisubramaniyan/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>922525106230</t>
+          <t>922525106374</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Pranithaashree S</t>
+          <t>YASWANTH V</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Pranithaa_shree</t>
+          <t>yaswanth_2008</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Pranithaa_shree/</t>
+          <t>https://leetcode.com/u/yaswanth_2008/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>922525106237</t>
+          <t>922525106375</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PRIYADHARSHINI V</t>
+          <t>YAZHINI M</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>priyadharshiniveluchamy</t>
+          <t>yazhini2007</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/priyadharshiniveluchamy/</t>
+          <t>https://leetcode.com/u/yazhini2007/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>922525106244</t>
+          <t>922525106376</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>RANJANA T</t>
+          <t>YAZHINI S</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>RANJANA _2007</t>
+          <t>yazhini__1234</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/RANJANA _2007/</t>
+          <t>https://leetcode.com/u/yazhini__1234/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>922525106250</t>
+          <t>922525106377</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>RESHMI R S</t>
+          <t>YAZHINI V</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Reshmi_0826</t>
+          <t>VISU_YAZHU</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Reshmi_0826/</t>
+          <t>https://leetcode.com/u/VISU_YAZHU/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>922525106284</t>
+          <t>922525106378</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Santhosh S</t>
+          <t>YOKESWARAN S</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>santhosh2407</t>
+          <t>syokeswaran</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh2407/</t>
+          <t>https://leetcode.com/u/syokeswaran/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>922525106253</t>
+          <t>922525106346</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>RITHANYA KN</t>
+          <t>SWETHA E</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Rithanya12-3</t>
+          <t>Swetha_20_1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithanya12-3/</t>
+          <t>https://leetcode.com/u/Swetha_20_1/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>922525106256</t>
+          <t>922525106355</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>RITHIK P</t>
+          <t>VAISHNAVI U</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Rithik_78</t>
+          <t>vaish200</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithik_78/</t>
+          <t>https://leetcode.com/u/vaish200/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>922525106257</t>
+          <t>922525106356</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>RITHIKA B</t>
+          <t>VASANTH KUMAR C</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Rithika_Balakrishnan</t>
+          <t>VASANTH2007</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithika_Balakrishnan/</t>
+          <t>https://leetcode.com/u/VASANTH2007/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>922525106258</t>
+          <t>922525106357</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>RITHISH R</t>
+          <t>VASANTH S</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Rithish_</t>
+          <t>_vasanth_s_</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithish_/</t>
+          <t>https://leetcode.com/u/_vasanth_s_/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>922525106259</t>
+          <t>922525106358</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ROHITH V</t>
+          <t>VASANTHA KUMAR D</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>RohithrohiV</t>
+          <t>Vasanthakumar12232</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/RohithrohiV/</t>
+          <t>https://leetcode.com/u/Vasanthakumar12232/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>922525106260</t>
+          <t>922525106359</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ROOBAGAPRIYA R</t>
+          <t>VASANTHKUMAR R</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Roobagapriya</t>
+          <t>VasanthKumar008</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Roobagapriya/</t>
+          <t>https://leetcode.com/u/VasanthKumar008/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>922525106261</t>
+          <t>922525106360</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Roshan M</t>
+          <t>VASUDEVAN G</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>roshan2403</t>
+          <t>GTVASU2008</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/roshan2403/</t>
+          <t>https://leetcode.com/u/GTVASU2008/</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>922525106262</t>
+          <t>922525106316</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ROSHIKA V</t>
+          <t>SIVARANJAN M P</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>roshikaveeramalai</t>
+          <t>SIVARANJAN_MP</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/roshikaveeramalai/</t>
+          <t>https://leetcode.com/u/SIVARANJAN_MP/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>922525106263</t>
+          <t>922525106317</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>RUBESH C</t>
+          <t>SIVASANJEEV P</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Rubesh_7</t>
+          <t>Sivasanjeev16</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rubesh_7/</t>
+          <t>https://leetcode.com/u/Sivasanjeev16/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>922525106264</t>
+          <t>922525106318</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SABAREESH K</t>
+          <t>SIVASUBRAMANI A</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>sabareesh_karikalan</t>
+          <t>AK_Siva</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
+          <t>https://leetcode.com/u/AK_Siva/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>922525106265</t>
+          <t>922525106319</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SABARIVASAN P</t>
+          <t>SIVATHARUN C</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>SabarivasanP</t>
+          <t>sivatharun22</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SabarivasanP/</t>
+          <t>https://leetcode.com/u/sivatharun22/</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>922525106266</t>
+          <t>922525106320</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SAHANA.V</t>
+          <t>SOBIKA R</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Sahanavijayakumar_0033</t>
+          <t>_sobika_R</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sahanavijayakumar_0033/</t>
+          <t>https://leetcode.com/u/_sobika_R/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>922525106268</t>
+          <t>922525106321</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SAKTHI S</t>
+          <t>SREE DHARANI C</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Sakthisaro08</t>
+          <t>SREEDHARANI_14</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sakthisaro08/</t>
+          <t>https://leetcode.com/u/SREEDHARANI_14/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>922525106269</t>
+          <t>922525106322</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Sakthivel. M</t>
+          <t>SRI  T</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>sakthivel23116</t>
+          <t>Sri1540</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sakthivel23116/</t>
+          <t>https://leetcode.com/u/Sri1540/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>922525106271</t>
+          <t>922525106323</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SANDHOSH KUMAR R</t>
+          <t>SRI HEERA J</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>sandhosh_30_R</t>
+          <t>sriheera03</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sandhosh_30_R/</t>
+          <t>https://leetcode.com/u/sriheera03/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>922525106272</t>
+          <t>922525106324</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SANJAY D</t>
+          <t>SRI KANTH R</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>itsmesanjay007</t>
+          <t>kanth2008</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itsmesanjay007/</t>
+          <t>https://leetcode.com/u/kanth2008/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>922525106273</t>
+          <t>922525106325</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SANJAY P</t>
+          <t>SRI SASTIKA G</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>sanjay00675</t>
+          <t>Srisastika_1401</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sanjay00675/</t>
+          <t>https://leetcode.com/u/Srisastika_1401/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>922525106275</t>
+          <t>922525106326</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SANJAY U</t>
+          <t>SRI VARSHAN B P</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>SanjayUdayan</t>
+          <t>srivarshan_B_P</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SanjayUdayan/</t>
+          <t>https://leetcode.com/u/srivarshan_B_P/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>922525106278</t>
+          <t>922525106327</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SANMATHI R</t>
+          <t>SRINATH V</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>sanmathi06</t>
+          <t>V_SRINATH</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sanmathi06/</t>
+          <t>https://leetcode.com/u/V_SRINATH/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>922525106279</t>
+          <t>922525106328</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SANTHIYA T</t>
+          <t>SRINIRANJAN S</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>santhiya0202</t>
+          <t>SRINIRANJAN2008</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhiya0202/</t>
+          <t>https://leetcode.com/u/SRINIRANJAN2008/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>922525106280</t>
+          <t>922525106329</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SANTHOSH D</t>
+          <t>SRINITHE T</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>santhosh7811</t>
+          <t>srinithe_1401</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh7811/</t>
+          <t>https://leetcode.com/u/srinithe_1401/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>922525106282</t>
+          <t>922525106330</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>SANTHOSH PRIYAN S</t>
+          <t>SRINITHI S</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>SANTHOSH PRIYAN S</t>
+          <t>Srinithi24_</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SANTHOSH PRIYAN S/</t>
+          <t>https://leetcode.com/u/Srinithi24_/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>922525106283</t>
+          <t>922525106331</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SANTHOSH S</t>
+          <t>SRISAMAYA R</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>SanthoshSathya260</t>
+          <t>mahi</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SanthoshSathya260/</t>
+          <t>https://leetcode.com/u/mahi/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>922525106285</t>
+          <t>922525106332</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SANTHOSH V</t>
+          <t>SUBARNA V</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>santhosh8760</t>
+          <t>Subarna_17</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh8760/</t>
+          <t>https://leetcode.com/u/Subarna_17/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>922525106286</t>
+          <t>922525106333</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SARAN K</t>
+          <t>SUBHA KARTHIKA R</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>saran32</t>
+          <t>subhakarthika</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saran32/</t>
+          <t>https://leetcode.com/u/subhakarthika/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>922525106287</t>
+          <t>922525106334</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SARAVANAN K</t>
+          <t>SUBIKA T</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>saravanan .k</t>
+          <t>subika1112</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saravanan .k/</t>
+          <t>https://leetcode.com/u/subika1112/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>922525106288</t>
+          <t>922525106335</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>SARAVANAN K</t>
+          <t>SUDHARSAN S</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>saravanan__k__</t>
+          <t>Sudharsan</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saravanan__k__/</t>
+          <t>https://leetcode.com/u/Sudharsan/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>922525106289</t>
+          <t>922525106336</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>SARAVANAN S</t>
+          <t>SUGANTHAN K</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Saravanan_7525</t>
+          <t>SUGANTHKALAI</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Saravanan_7525/</t>
+          <t>https://leetcode.com/u/SUGANTHKALAI/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>922525106290</t>
+          <t>922525106337</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>SARIKA M P</t>
+          <t>SUGIDHARSHINI T</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>sarika_5408</t>
+          <t>Sugi_07</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sarika_5408/</t>
+          <t>https://leetcode.com/u/Sugi_07/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>922525106291</t>
+          <t>922525106338</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>SARVESWARAN R</t>
+          <t>SUJEETH M</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>sarvesh312008</t>
+          <t>SUJEETH77</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sarvesh312008/</t>
+          <t>https://leetcode.com/u/SUJEETH77/</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>922525106292</t>
+          <t>922525106339</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>SASHMIKA.P</t>
+          <t>SUJITH RAJA B</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>sashmikaprabhu</t>
+          <t>mahi20_</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sashmikaprabhu/</t>
+          <t>https://leetcode.com/u/mahi20_/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>922525106296</t>
+          <t>922525106340</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>SELVAKUMAR K</t>
+          <t>SUMITHRA S</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Selvakumarsk-32</t>
+          <t>sumithra_16</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvakumarsk-32/</t>
+          <t>https://leetcode.com/u/sumithra_16/</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>922525106297</t>
+          <t>922525106341</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>SELVAPRAGADEESH S</t>
+          <t>SURYA PRABHU S</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Selvapragadeesh</t>
+          <t>surya001prabhu</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvapragadeesh/</t>
+          <t>https://leetcode.com/u/surya001prabhu/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>922525106298</t>
+          <t>922525106342</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>SELVA RAGAVAN</t>
+          <t>SUSIDHARAN M</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Selvax07</t>
+          <t>Susidharan147</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvax07/</t>
+          <t>https://leetcode.com/u/Susidharan147/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>922525106299</t>
+          <t>922525106343</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>SENTHAMIZHSELVAN K</t>
+          <t>SUTHARSHANA S</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Senthamizh08</t>
+          <t>sutharshana743</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Senthamizh08/</t>
+          <t>https://leetcode.com/u/sutharshana743/</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>922525106300</t>
+          <t>922525106344</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Senthil.S</t>
+          <t>SWATHI M</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Jna76WrjNd</t>
+          <t>Swathimanivel_1234</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Jna76WrjNd/</t>
+          <t>https://leetcode.com/u/Swathimanivel_1234/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>922525106302</t>
+          <t>922525106347</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>SHAHANA S</t>
+          <t>TAMIL SELVAN R</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>shahana_pandiraj04</t>
+          <t>Kdmif0HMNm</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shahana_pandiraj04/</t>
+          <t>https://leetcode.com/u/Kdmif0HMNm/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>922525106303</t>
+          <t>922525106348</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SHANTHINI C</t>
+          <t>THAMARAI SELVI D</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>ShanthiniChelladurai</t>
+          <t>thamarai_04</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/ShanthiniChelladurai/</t>
+          <t>https://leetcode.com/u/thamarai_04/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>922525106305</t>
+          <t>922525106349</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>SHARATH P</t>
+          <t>THAMEEM FARSHITHA A</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>sharath_1010</t>
+          <t>Thameem_786</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sharath_1010/</t>
+          <t>https://leetcode.com/u/Thameem_786/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>922525106307</t>
+          <t>922525106350</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>SHIVANI B</t>
+          <t>THARANISH R</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>shivani208</t>
+          <t>THARANISH2008</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shivani208/</t>
+          <t>https://leetcode.com/u/THARANISH2008/</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>922525106308</t>
+          <t>922525106351</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>SHREE HARINI L</t>
+          <t>THARUNIKA P</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Shree_Harini478</t>
+          <t>Tharunika_12</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Shree_Harini478/</t>
+          <t>https://leetcode.com/u/Tharunika_12/</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>922525106309</t>
+          <t>922525106352</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>SHREE CHARAN T</t>
+          <t>THIRINESH KUMAR S</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>shreecharan22</t>
+          <t>THIRINESH KUMAR.S</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shreecharan22/</t>
+          <t>https://leetcode.com/u/THIRINESH KUMAR.S/</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>922525106310</t>
+          <t>922525106353</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>SIVA MANIKANDAN K</t>
+          <t>THIRISHA C</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>9043374912</t>
+          <t>thirishavsb</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/9043374912/</t>
+          <t>https://leetcode.com/u/thirishavsb/</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>922525106311</t>
+          <t>922525106354</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>SIVA PRAKASH M</t>
+          <t>THIRUMURUGAN S</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>sivaprakash_0406</t>
+          <t>thiru0211_</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivaprakash_0406/</t>
+          <t>https://leetcode.com/u/thiru0211_/</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>922525106312</t>
+          <t>922525106267</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>SIVADHARSHINI D</t>
+          <t>SAJISH R</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>dharshinideivsigamani</t>
+          <t>SAJISH7</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -3565,24 +3565,24 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/dharshinideivsigamani/</t>
+          <t>https://leetcode.com/u/SAJISH7/</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>922525106313</t>
+          <t>922525106270</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>SIVAGNANAM M</t>
+          <t>SANDHIYA T</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>sivagnanam3344</t>
+          <t>zklXTc9UAp</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3592,24 +3592,24 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivagnanam3344/</t>
+          <t>https://leetcode.com/u/zklXTc9UAp/</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>922525106314</t>
+          <t>922525106276</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>SIVANESH D</t>
+          <t>SANJAYAN</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>sivanesh2007</t>
+          <t>sanjayan31</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3619,24 +3619,24 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivanesh2007/</t>
+          <t>https://leetcode.com/u/sanjayan31/</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>922525106315</t>
+          <t>922525106294</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>SIVANESH G</t>
+          <t>SATHANA SRI S K</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>GSIVANESH</t>
+          <t>Sathana-1267</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/GSIVANESH/</t>
+          <t>https://leetcode.com/u/Sathana-1267/</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>922525196293</t>
+          <t>922525106304</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>SASWIN D</t>
+          <t>SANTHOSH SHAI SIRIL</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>saswin_88</t>
+          <t>shandoshsai</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -3673,24 +3673,24 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saswin_88/</t>
+          <t>https://leetcode.com/u/shandoshsai/</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>922525106301</t>
+          <t>922525106306</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>SETHUPATHI G</t>
+          <t>SHARUKESH</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Sethupathi_1228</t>
+          <t>sharukesh2008</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -3700,1875 +3700,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sethupathi_1228/</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>922525106334</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>SUBIKA T</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>subika1112</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/subika1112/</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>922525106335</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>SUDHARSAN S</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Sudharsan</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Sudharsan/</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>922525106336</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>SUGANTHAN K</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>SUGANTHKALAI</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/SUGANTHKALAI/</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>922525106337</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>SUGIDHARSHINI T</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Sugi_07</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Sugi_07/</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>922525106338</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>SUJEETH M</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>SUJEETH77</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/SUJEETH77/</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>922525106339</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>SUJITH RAJA B</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>mahi20_</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/mahi20_/</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>922525106340</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>SUMITHRA S</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>sumithra_16</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/sumithra_16/</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>922525106341</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>SURYA PRABHU S</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>surya001prabhu</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/surya001prabhu/</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>922525106342</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>SUSIDHARAN M</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Susidharan147</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Susidharan147/</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>922525106343</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>SUTHARSHANA S</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>sutharshana743</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/sutharshana743/</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>922525106344</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>SWATHI M</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Swathimanivel_1234</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Swathimanivel_1234/</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>922525106347</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>TAMIL SELVAN R</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Kdmif0HMNm</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Kdmif0HMNm/</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>922525106348</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>THAMARAI SELVI D</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>thamarai_04</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/thamarai_04/</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>922525106349</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>THAMEEM FARSHITHA A</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Thameem_786</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Thameem_786/</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>922525106350</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>THARANISH R</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>THARANISH2008</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/THARANISH2008/</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>922525106351</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>THARUNIKA P</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Tharunika_12</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Tharunika_12/</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>922525106352</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>THIRINESH KUMAR S</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>THIRINESH KUMAR.S</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/THIRINESH KUMAR.S/</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>922525106353</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>THIRISHA C</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>thirishavsb</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/thirishavsb/</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>922525106354</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>THIRUMURUGAN S</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>thiru0211_</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/thiru0211_/</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>922525106361</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>VASUKI K</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>vasuki</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/vasuki/</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>922525106362</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>VELLIANGIRI R</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>velliangiri_R</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/velliangiri_R/</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>922525106363</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>VIGNESH M</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>O8bYDSRUbE</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/O8bYDSRUbE/</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>922525106364</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>VIGNESH VELAN M</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Vicky_27_Velan</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Vicky_27_Velan/</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>922525106365</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>VIGNESHWAR U</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>VIGNESHWAR0221</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/VIGNESHWAR0221/</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>922525106366</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>VIJAYARAGAVAN R</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>vijayaragavan1216</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/vijayaragavan1216/</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>922525106367</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>VIKRAM V</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>vikramvicky5678</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/vikramvicky5678/</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>922525106368</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>VISHNU B</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>VISHNU_B_2008</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/VISHNU_B_2008/</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>922525106369</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>VISHNU PRIYAN S</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>itz__priyan__</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/itz__priyan__/</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>922525106370</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>VISHNUHARAN V S</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Vishnuharan082007</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Vishnuharan082007/</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>922525106371</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>VISHNUPRIYA S</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>vishnupriyamaran</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/vishnupriyamaran/</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>922525106372</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>VISHWAJETH A M</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>vishwajeth</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/vishwajeth/</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>922525106373</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>YASHNI S</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Yashnisubramaniyan</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Yashnisubramaniyan/</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>922525106374</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>YASWANTH V</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>yaswanth_2008</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/yaswanth_2008/</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>922525106375</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>YAZHINI M</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>yazhini2007</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/yazhini2007/</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>922525106376</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>YAZHINI S</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>yazhini__1234</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/yazhini__1234/</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>922525106377</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>YAZHINI V</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>VISU_YAZHU</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/VISU_YAZHU/</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>922525106378</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>YOKESWARAN S</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>syokeswaran</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/syokeswaran/</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>922525106346</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>SWETHA E</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Swetha_20_1</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Swetha_20_1/</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>922525106332</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>SUBARNA V</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Subarna_17</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Subarna_17/</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>922525106328</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>SRINIRANJAN S</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>SRINIRANJAN2008</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/SRINIRANJAN2008/</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>922525106329</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>SRINITHE T</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>srinithe_1401</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/srinithe_1401/</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>922525106330</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>SRINITHI S</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Srinithi24_</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Srinithi24_/</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>922525106331</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>SRISAMAYA R</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>mahi</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/mahi/</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>922525106360</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>VASUDEVAN G</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>GTVASU2008</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/GTVASU2008/</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>922525106333</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>SUBHA KARTHIKA R</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>subhakarthika</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/subhakarthika/</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>922525106355</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>VAISHNAVI U</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>vaish200</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/vaish200/</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>922525106356</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>VASANTH KUMAR C</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>VASANTH2007</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/VASANTH2007/</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>922525106357</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>VASANTH S</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>_vasanth_s_</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/_vasanth_s_/</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>922525106358</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>VASANTHA KUMAR D</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>Vasanthakumar12232</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Vasanthakumar12232/</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>922525106359</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>VASANTHKUMAR R</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>VasanthKumar008</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/VasanthKumar008/</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>922525106345</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>SWATHI S</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>_swathi _3366</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/_swathi _3366/</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>922525106316</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>SIVARANJAN M P</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>SIVARANJAN_MP</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/SIVARANJAN_MP/</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>922525106317</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>SIVASANJEEV P</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>Sivasanjeev16</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Sivasanjeev16/</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>922525106318</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>SIVASUBRAMANI A</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>AK_Siva</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/AK_Siva/</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>922525106319</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>SIVATHARUN C</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>sivatharun22</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/sivatharun22/</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>922525106320</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>SOBIKA R</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>_sobika_R</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/_sobika_R/</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>922525106321</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>SREE DHARANI C</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>SREEDHARANI_14</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/SREEDHARANI_14/</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>922525106322</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>SRI  T</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>Sri1540</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Sri1540/</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>922525106323</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>SRI HEERA J</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>sriheera03</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/sriheera03/</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>922525106324</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>SRI KANTH R</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>kanth2008</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/kanth2008/</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>922525106325</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>SRI SASTIKA G</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>Srisastika_1401</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Srisastika_1401/</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>922525106326</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>SRI VARSHAN B P</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>srivarshan_B_P</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/srivarshan_B_P/</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>922525106327</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>SRINATH V</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>V_SRINATH</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/V_SRINATH/</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>922525106267</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>SAJISH R</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>SAJISH7</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/SAJISH7/</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>922525106270</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>SANDHIYA T</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>zklXTc9UAp</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/zklXTc9UAp/</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>922525106276</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>SANJAYAN</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>sanjayan31</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/sanjayan31/</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>922525106294</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>SATHANA SRI S K</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>Sathana-1267</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Sathana-1267/</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>922525106304</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>SANTHOSH SHAI SIRIL</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>shandoshsai</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/shandoshsai/</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>922525106306</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>SHARUKESH</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>sharukesh2008</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/sharukesh2008/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E190"/>
+  <autoFilter ref="A1:E121"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Students.xlsx
+++ b/Students.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$121</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$360</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E121"/>
+  <dimension ref="A1:E360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -467,17 +467,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>922525106286</t>
+          <t>922525106280</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SARAN K</t>
+          <t>SANTHOSH D</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>saran32</t>
+          <t>santhosh7811</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -487,24 +487,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saran32/</t>
+          <t>https://leetcode.com/u/santhosh7811/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>922525106288</t>
+          <t>922525106253</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SARAVANAN K</t>
+          <t>RITHANYA KN</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>saravanan__k__</t>
+          <t>Rithanya12-3</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -514,24 +514,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saravanan__k__/</t>
+          <t>https://leetcode.com/u/Rithanya12-3/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>922525106289</t>
+          <t>922525106256</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SARAVANAN S</t>
+          <t>RITHIK P</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Saravanan_7525</t>
+          <t>Rithik_78</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -541,24 +541,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Saravanan_7525/</t>
+          <t>https://leetcode.com/u/Rithik_78/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>922525106290</t>
+          <t>922525106257</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SARIKA M P</t>
+          <t>RITHIKA B</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>sarika_5408</t>
+          <t>Rithika_Balakrishnan</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -568,24 +568,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sarika_5408/</t>
+          <t>https://leetcode.com/u/Rithika_Balakrishnan/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>922525106291</t>
+          <t>922525106258</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SARVESWARAN R</t>
+          <t>RITHISH R</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>sarvesh312008</t>
+          <t>Rithish_</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -595,24 +595,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sarvesh312008/</t>
+          <t>https://leetcode.com/u/Rithish_/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>922525106292</t>
+          <t>922525106259</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SASHMIKA.P</t>
+          <t>ROHITH V</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>sashmikaprabhu</t>
+          <t>RohithrohiV</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -622,24 +622,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sashmikaprabhu/</t>
+          <t>https://leetcode.com/u/RohithrohiV/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>922525106296</t>
+          <t>922525106260</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SELVAKUMAR K</t>
+          <t>ROOBAGAPRIYA R</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Selvakumarsk-32</t>
+          <t>Roobagapriya</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -649,24 +649,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvakumarsk-32/</t>
+          <t>https://leetcode.com/u/Roobagapriya/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>922525106297</t>
+          <t>922525106261</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SELVAPRAGADEESH S</t>
+          <t>Roshan M</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Selvapragadeesh</t>
+          <t>roshan2403</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -676,24 +676,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvapragadeesh/</t>
+          <t>https://leetcode.com/u/roshan2403/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>922525106298</t>
+          <t>922525106262</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SELVA RAGAVAN</t>
+          <t>ROSHIKA V</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Selvax07</t>
+          <t>roshikaveeramalai</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -703,24 +703,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvax07/</t>
+          <t>https://leetcode.com/u/roshikaveeramalai/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>922525106299</t>
+          <t>922525106263</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SENTHAMIZHSELVAN K</t>
+          <t>RUBESH C</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Senthamizh08</t>
+          <t>Rubesh_7</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -730,24 +730,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Senthamizh08/</t>
+          <t>https://leetcode.com/u/Rubesh_7/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>922525106300</t>
+          <t>922525106264</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Senthil.S</t>
+          <t>SABAREESH K</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jna76WrjNd</t>
+          <t>sabareesh_karikalan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -757,24 +757,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Jna76WrjNd/</t>
+          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>922525106302</t>
+          <t>922525106265</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SHAHANA S</t>
+          <t>SABARIVASAN P</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>shahana_pandiraj04</t>
+          <t>SabarivasanP</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -784,24 +784,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shahana_pandiraj04/</t>
+          <t>https://leetcode.com/u/SabarivasanP/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>922525106303</t>
+          <t>922525106266</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SHANTHINI C</t>
+          <t>SAHANA.V</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ShanthiniChelladurai</t>
+          <t>Sahanavijayakumar_0033</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/ShanthiniChelladurai/</t>
+          <t>https://leetcode.com/u/Sahanavijayakumar_0033/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>922525106305</t>
+          <t>922525106268</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SHARATH P</t>
+          <t>SAKTHI S</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>sharath_1010</t>
+          <t>Sakthisaro08</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -838,24 +838,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sharath_1010/</t>
+          <t>https://leetcode.com/u/Sakthisaro08/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>922525106307</t>
+          <t>922525106269</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SHIVANI B</t>
+          <t>Sakthivel. M</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>shivani208</t>
+          <t>sakthivel23116</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -865,24 +865,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shivani208/</t>
+          <t>https://leetcode.com/u/sakthivel23116/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>922525106308</t>
+          <t>922525106271</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SHREE HARINI L</t>
+          <t>SANDHOSH KUMAR R</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Shree_Harini478</t>
+          <t>sandhosh_30_R</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -892,24 +892,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Shree_Harini478/</t>
+          <t>https://leetcode.com/u/sandhosh_30_R/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>922525106309</t>
+          <t>922525106272</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SHREE CHARAN T</t>
+          <t>SANJAY D</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>shreecharan22</t>
+          <t>itsmesanjay007</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -919,24 +919,24 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shreecharan22/</t>
+          <t>https://leetcode.com/u/itsmesanjay007/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>922525106310</t>
+          <t>922525106273</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SIVA MANIKANDAN K</t>
+          <t>SANJAY P</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>9043374912</t>
+          <t>sanjay00675</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -946,24 +946,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/9043374912/</t>
+          <t>https://leetcode.com/u/sanjay00675/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>922525106311</t>
+          <t>922525106275</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SIVA PRAKASH M</t>
+          <t>SANJAY U</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>sivaprakash_0406</t>
+          <t>SanjayUdayan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -973,24 +973,24 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivaprakash_0406/</t>
+          <t>https://leetcode.com/u/SanjayUdayan/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>922525106312</t>
+          <t>922525106278</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SIVADHARSHINI D</t>
+          <t>SANMATHI R</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>dharshinideivsigamani</t>
+          <t>sanmathi06</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1000,24 +1000,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/dharshinideivsigamani/</t>
+          <t>https://leetcode.com/u/sanmathi06/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>922525106287</t>
+          <t>922525106279</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SARAVANAN K</t>
+          <t>SANTHIYA T</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>saravanan .k</t>
+          <t>santhiya0202</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1027,24 +1027,24 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saravanan .k/</t>
+          <t>https://leetcode.com/u/santhiya0202/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>922525196293</t>
+          <t>922525106282</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SASWIN D</t>
+          <t>SANTHOSH PRIYAN S</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>saswin_88</t>
+          <t>SANTHOSH PRIYAN S</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1054,24 +1054,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saswin_88/</t>
+          <t>https://leetcode.com/u/SANTHOSH PRIYAN S/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>922525106315</t>
+          <t>922525106283</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SIVANESH G</t>
+          <t>SANTHOSH S</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>GSIVANESH</t>
+          <t>SanthoshSathya260</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1081,24 +1081,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/GSIVANESH/</t>
+          <t>https://leetcode.com/u/SanthoshSathya260/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>922525106314</t>
+          <t>922525106284</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SIVANESH D</t>
+          <t>Santhosh S</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>sivanesh2007</t>
+          <t>santhosh2407</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1108,24 +1108,24 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivanesh2007/</t>
+          <t>https://leetcode.com/u/santhosh2407/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>922525106313</t>
+          <t>922525106285</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SIVAGNANAM M</t>
+          <t>SANTHOSH V</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>sivagnanam3344</t>
+          <t>santhosh8760</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1135,24 +1135,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivagnanam3344/</t>
+          <t>https://leetcode.com/u/santhosh8760/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>922525106253</t>
+          <t>922525106286</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>RITHANYA KN</t>
+          <t>SARAN K</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Rithanya12-3</t>
+          <t>saran32</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1162,24 +1162,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithanya12-3/</t>
+          <t>https://leetcode.com/u/saran32/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>922525106256</t>
+          <t>922525106287</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>RITHIK P</t>
+          <t>SARAVANAN K</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Rithik_78</t>
+          <t>saravanan .k</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1189,24 +1189,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithik_78/</t>
+          <t>https://leetcode.com/u/saravanan .k/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>922525106257</t>
+          <t>922525106288</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>RITHIKA B</t>
+          <t>SARAVANAN K</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Rithika_Balakrishnan</t>
+          <t>saravanan__k__</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1216,24 +1216,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithika_Balakrishnan/</t>
+          <t>https://leetcode.com/u/saravanan__k__/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>922525106258</t>
+          <t>922525106289</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>RITHISH R</t>
+          <t>SARAVANAN S</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Rithish_</t>
+          <t>Saravanan_7525</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1243,24 +1243,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithish_/</t>
+          <t>https://leetcode.com/u/Saravanan_7525/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>922525106259</t>
+          <t>922525106290</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ROHITH V</t>
+          <t>SARIKA M P</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>RohithrohiV</t>
+          <t>sarika_5408</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1270,24 +1270,24 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/RohithrohiV/</t>
+          <t>https://leetcode.com/u/sarika_5408/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>922525106260</t>
+          <t>922525106291</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ROOBAGAPRIYA R</t>
+          <t>SARVESWARAN R</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Roobagapriya</t>
+          <t>sarvesh312008</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1297,24 +1297,24 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Roobagapriya/</t>
+          <t>https://leetcode.com/u/sarvesh312008/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>922525106261</t>
+          <t>922525106292</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Roshan M</t>
+          <t>SASHMIKA.P</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>roshan2403</t>
+          <t>sashmikaprabhu</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1324,24 +1324,24 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/roshan2403/</t>
+          <t>https://leetcode.com/u/sashmikaprabhu/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>922525106262</t>
+          <t>922525106296</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ROSHIKA V</t>
+          <t>SELVAKUMAR K</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>roshikaveeramalai</t>
+          <t>Selvakumarsk-32</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1351,24 +1351,24 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/roshikaveeramalai/</t>
+          <t>https://leetcode.com/u/Selvakumarsk-32/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>922525106263</t>
+          <t>922525106297</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>RUBESH C</t>
+          <t>SELVAPRAGADEESH S</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Rubesh_7</t>
+          <t>Selvapragadeesh</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1378,24 +1378,24 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rubesh_7/</t>
+          <t>https://leetcode.com/u/Selvapragadeesh/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>922525106264</t>
+          <t>922525106298</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SABAREESH K</t>
+          <t>SELVA RAGAVAN</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>sabareesh_karikalan</t>
+          <t>Selvax07</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1405,24 +1405,24 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
+          <t>https://leetcode.com/u/Selvax07/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>922525106265</t>
+          <t>922525106299</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SABARIVASAN P</t>
+          <t>SENTHAMIZHSELVAN K</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SabarivasanP</t>
+          <t>Senthamizh08</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1432,24 +1432,24 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SabarivasanP/</t>
+          <t>https://leetcode.com/u/Senthamizh08/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>922525106266</t>
+          <t>922525106300</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SAHANA.V</t>
+          <t>Senthil.S</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sahanavijayakumar_0033</t>
+          <t>Jna76WrjNd</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1459,24 +1459,24 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sahanavijayakumar_0033/</t>
+          <t>https://leetcode.com/u/Jna76WrjNd/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>922525106268</t>
+          <t>922525106302</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SAKTHI S</t>
+          <t>SHAHANA S</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sakthisaro08</t>
+          <t>shahana_pandiraj04</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1486,24 +1486,24 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sakthisaro08/</t>
+          <t>https://leetcode.com/u/shahana_pandiraj04/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>922525106269</t>
+          <t>922525106303</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Sakthivel. M</t>
+          <t>SHANTHINI C</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>sakthivel23116</t>
+          <t>ShanthiniChelladurai</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1513,24 +1513,24 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sakthivel23116/</t>
+          <t>https://leetcode.com/u/ShanthiniChelladurai/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>922525106271</t>
+          <t>922525106305</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SANDHOSH KUMAR R</t>
+          <t>SHARATH P</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>sandhosh_30_R</t>
+          <t>sharath_1010</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1540,24 +1540,24 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sandhosh_30_R/</t>
+          <t>https://leetcode.com/u/sharath_1010/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>922525106272</t>
+          <t>922525106307</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SANJAY D</t>
+          <t>SHIVANI B</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>itsmesanjay007</t>
+          <t>shivani208</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1567,24 +1567,24 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itsmesanjay007/</t>
+          <t>https://leetcode.com/u/shivani208/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>922525106273</t>
+          <t>922525106308</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SANJAY P</t>
+          <t>SHREE HARINI L</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>sanjay00675</t>
+          <t>Shree_Harini478</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1594,24 +1594,24 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sanjay00675/</t>
+          <t>https://leetcode.com/u/Shree_Harini478/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>922525106275</t>
+          <t>922525106309</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SANJAY U</t>
+          <t>SHREE CHARAN T</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SanjayUdayan</t>
+          <t>shreecharan22</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1621,24 +1621,24 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SanjayUdayan/</t>
+          <t>https://leetcode.com/u/shreecharan22/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>922525106278</t>
+          <t>922525106310</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SANMATHI R</t>
+          <t>SIVA MANIKANDAN K</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>sanmathi06</t>
+          <t>9043374912</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1648,24 +1648,24 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sanmathi06/</t>
+          <t>https://leetcode.com/u/9043374912/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>922525106279</t>
+          <t>922525106311</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SANTHIYA T</t>
+          <t>SIVA PRAKASH M</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>santhiya0202</t>
+          <t>sivaprakash_0406</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1675,24 +1675,24 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhiya0202/</t>
+          <t>https://leetcode.com/u/sivaprakash_0406/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>922525106280</t>
+          <t>922525106312</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SANTHOSH D</t>
+          <t>SIVADHARSHINI D</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>santhosh7811</t>
+          <t>dharshinideivsigamani</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1702,24 +1702,24 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh7811/</t>
+          <t>https://leetcode.com/u/dharshinideivsigamani/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>922525106282</t>
+          <t>922525106313</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SANTHOSH PRIYAN S</t>
+          <t>SIVAGNANAM M</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SANTHOSH PRIYAN S</t>
+          <t>sivagnanam3344</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1729,24 +1729,24 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SANTHOSH PRIYAN S/</t>
+          <t>https://leetcode.com/u/sivagnanam3344/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>922525106283</t>
+          <t>922525106314</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SANTHOSH S</t>
+          <t>SIVANESH D</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SanthoshSathya260</t>
+          <t>sivanesh2007</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SanthoshSathya260/</t>
+          <t>https://leetcode.com/u/sivanesh2007/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>922525106284</t>
+          <t>922525106315</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Santhosh S</t>
+          <t>SIVANESH G</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>santhosh2407</t>
+          <t>GSIVANESH</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1783,24 +1783,24 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh2407/</t>
+          <t>https://leetcode.com/u/GSIVANESH/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>922525106285</t>
+          <t>922525196293</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SANTHOSH V</t>
+          <t>SASWIN D</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>santhosh8760</t>
+          <t>saswin_88</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh8760/</t>
+          <t>https://leetcode.com/u/saswin_88/</t>
         </is>
       </c>
     </row>
@@ -1844,17 +1844,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>922525106345</t>
+          <t>922525106361</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SWATHI S</t>
+          <t>VASUKI K</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>_swathi _3366</t>
+          <t>vasuki</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1864,24 +1864,24 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_swathi _3366/</t>
+          <t>https://leetcode.com/u/vasuki/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>922525106361</t>
+          <t>922525106362</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>VASUKI K</t>
+          <t>VELLIANGIRI R</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>vasuki</t>
+          <t>velliangiri_R</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1891,24 +1891,24 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vasuki/</t>
+          <t>https://leetcode.com/u/velliangiri_R/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>922525106362</t>
+          <t>922525106363</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>VELLIANGIRI R</t>
+          <t>VIGNESH M</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>velliangiri_R</t>
+          <t>O8bYDSRUbE</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1918,24 +1918,24 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/velliangiri_R/</t>
+          <t>https://leetcode.com/u/O8bYDSRUbE/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>922525106363</t>
+          <t>922525106364</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>VIGNESH M</t>
+          <t>VIGNESH VELAN M</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>O8bYDSRUbE</t>
+          <t>Vicky_27_Velan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1945,24 +1945,24 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/O8bYDSRUbE/</t>
+          <t>https://leetcode.com/u/Vicky_27_Velan/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>922525106364</t>
+          <t>922525106365</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>VIGNESH VELAN M</t>
+          <t>VIGNESHWAR U</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Vicky_27_Velan</t>
+          <t>VIGNESHWAR0221</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1972,24 +1972,24 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vicky_27_Velan/</t>
+          <t>https://leetcode.com/u/VIGNESHWAR0221/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>922525106365</t>
+          <t>922525106366</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>VIGNESHWAR U</t>
+          <t>VIJAYARAGAVAN R</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>VIGNESHWAR0221</t>
+          <t>vijayaragavan1216</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1999,24 +1999,24 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VIGNESHWAR0221/</t>
+          <t>https://leetcode.com/u/vijayaragavan1216/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>922525106366</t>
+          <t>922525106367</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>VIJAYARAGAVAN R</t>
+          <t>VIKRAM V</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>vijayaragavan1216</t>
+          <t>vikramvicky5678</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2026,24 +2026,24 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vijayaragavan1216/</t>
+          <t>https://leetcode.com/u/vikramvicky5678/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>922525106367</t>
+          <t>922525106368</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>VIKRAM V</t>
+          <t>VISHNU B</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>vikramvicky5678</t>
+          <t>VISHNU_B_2008</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2053,24 +2053,24 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vikramvicky5678/</t>
+          <t>https://leetcode.com/u/VISHNU_B_2008/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>922525106368</t>
+          <t>922525106369</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>VISHNU B</t>
+          <t>VISHNU PRIYAN S</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>VISHNU_B_2008</t>
+          <t>itz__priyan__</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2080,24 +2080,24 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VISHNU_B_2008/</t>
+          <t>https://leetcode.com/u/itz__priyan__/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>922525106369</t>
+          <t>922525106316</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>VISHNU PRIYAN S</t>
+          <t>SIVARANJAN M P</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>itz__priyan__</t>
+          <t>SIVARANJAN_MP</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2107,24 +2107,24 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itz__priyan__/</t>
+          <t>https://leetcode.com/u/SIVARANJAN_MP/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>922525106370</t>
+          <t>922525106317</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>VISHNUHARAN V S</t>
+          <t>SIVASANJEEV P</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Vishnuharan082007</t>
+          <t>Sivasanjeev16</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2134,24 +2134,24 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vishnuharan082007/</t>
+          <t>https://leetcode.com/u/Sivasanjeev16/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>922525106371</t>
+          <t>922525106318</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>VISHNUPRIYA S</t>
+          <t>SIVASUBRAMANI A</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>vishnupriyamaran</t>
+          <t>AK_Siva</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2161,24 +2161,24 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vishnupriyamaran/</t>
+          <t>https://leetcode.com/u/AK_Siva/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>922525106372</t>
+          <t>922525106319</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>VISHWAJETH A M</t>
+          <t>SIVATHARUN C</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>vishwajeth</t>
+          <t>sivatharun22</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2188,24 +2188,24 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vishwajeth/</t>
+          <t>https://leetcode.com/u/sivatharun22/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>922525106373</t>
+          <t>922525106320</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>YASHNI S</t>
+          <t>SOBIKA R</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Yashnisubramaniyan</t>
+          <t>_sobika_R</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2215,24 +2215,24 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Yashnisubramaniyan/</t>
+          <t>https://leetcode.com/u/_sobika_R/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>922525106374</t>
+          <t>922525106321</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>YASWANTH V</t>
+          <t>SREE DHARANI C</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>yaswanth_2008</t>
+          <t>SREEDHARANI_14</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2242,24 +2242,24 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yaswanth_2008/</t>
+          <t>https://leetcode.com/u/SREEDHARANI_14/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>922525106375</t>
+          <t>922525106322</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>YAZHINI M</t>
+          <t>SRI  T</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>yazhini2007</t>
+          <t>Sri1540</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2269,24 +2269,24 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yazhini2007/</t>
+          <t>https://leetcode.com/u/Sri1540/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>922525106376</t>
+          <t>922525106323</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>YAZHINI S</t>
+          <t>SRI HEERA J</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>yazhini__1234</t>
+          <t>sriheera03</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2296,24 +2296,24 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yazhini__1234/</t>
+          <t>https://leetcode.com/u/sriheera03/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>922525106377</t>
+          <t>922525106324</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>YAZHINI V</t>
+          <t>SRI KANTH R</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>VISU_YAZHU</t>
+          <t>kanth2008</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2323,24 +2323,24 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VISU_YAZHU/</t>
+          <t>https://leetcode.com/u/kanth2008/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>922525106378</t>
+          <t>922525106371</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>YOKESWARAN S</t>
+          <t>VISHNUPRIYA S</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>syokeswaran</t>
+          <t>vishnupriyamaran</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2350,24 +2350,24 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/syokeswaran/</t>
+          <t>https://leetcode.com/u/vishnupriyamaran/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>922525106346</t>
+          <t>922525106372</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SWETHA E</t>
+          <t>VISHWAJETH A M</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Swetha_20_1</t>
+          <t>vishwajeth</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2377,24 +2377,24 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Swetha_20_1/</t>
+          <t>https://leetcode.com/u/vishwajeth/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>922525106355</t>
+          <t>922525106373</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>VAISHNAVI U</t>
+          <t>YASHNI S</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>vaish200</t>
+          <t>Yashnisubramaniyan</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2404,24 +2404,24 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vaish200/</t>
+          <t>https://leetcode.com/u/Yashnisubramaniyan/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>922525106356</t>
+          <t>922525106374</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>VASANTH KUMAR C</t>
+          <t>YASWANTH V</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>VASANTH2007</t>
+          <t>yaswanth_2008</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2431,24 +2431,24 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VASANTH2007/</t>
+          <t>https://leetcode.com/u/yaswanth_2008/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>922525106357</t>
+          <t>922525106375</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>VASANTH S</t>
+          <t>YAZHINI M</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>_vasanth_s_</t>
+          <t>yazhini2007</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2458,24 +2458,24 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_vasanth_s_/</t>
+          <t>https://leetcode.com/u/yazhini2007/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>922525106358</t>
+          <t>922525106376</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>VASANTHA KUMAR D</t>
+          <t>YAZHINI S</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Vasanthakumar12232</t>
+          <t>yazhini__1234</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2485,24 +2485,24 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vasanthakumar12232/</t>
+          <t>https://leetcode.com/u/yazhini__1234/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>922525106359</t>
+          <t>922525106377</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>VASANTHKUMAR R</t>
+          <t>YAZHINI V</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>VasanthKumar008</t>
+          <t>VISU_YAZHU</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2512,24 +2512,24 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VasanthKumar008/</t>
+          <t>https://leetcode.com/u/VISU_YAZHU/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>922525106360</t>
+          <t>922525106378</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>VASUDEVAN G</t>
+          <t>YOKESWARAN S</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>GTVASU2008</t>
+          <t>syokeswaran</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2539,24 +2539,24 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/GTVASU2008/</t>
+          <t>https://leetcode.com/u/syokeswaran/</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>922525106316</t>
+          <t>922525106346</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SIVARANJAN M P</t>
+          <t>SWETHA E</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>SIVARANJAN_MP</t>
+          <t>Swetha_20_1</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2566,24 +2566,24 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SIVARANJAN_MP/</t>
+          <t>https://leetcode.com/u/Swetha_20_1/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>922525106317</t>
+          <t>922525106325</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SIVASANJEEV P</t>
+          <t>SRI SASTIKA G</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Sivasanjeev16</t>
+          <t>Srisastika_1401</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2593,24 +2593,24 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sivasanjeev16/</t>
+          <t>https://leetcode.com/u/Srisastika_1401/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>922525106318</t>
+          <t>922525106326</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SIVASUBRAMANI A</t>
+          <t>SRI VARSHAN B P</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AK_Siva</t>
+          <t>srivarshan_B_P</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2620,24 +2620,24 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/AK_Siva/</t>
+          <t>https://leetcode.com/u/srivarshan_B_P/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>922525106319</t>
+          <t>922525106327</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SIVATHARUN C</t>
+          <t>SRINATH V</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>sivatharun22</t>
+          <t>V_SRINATH</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2647,24 +2647,24 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivatharun22/</t>
+          <t>https://leetcode.com/u/V_SRINATH/</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>922525106320</t>
+          <t>922525106328</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SOBIKA R</t>
+          <t>SRINIRANJAN S</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>_sobika_R</t>
+          <t>SRINIRANJAN2008</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2674,24 +2674,24 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_sobika_R/</t>
+          <t>https://leetcode.com/u/SRINIRANJAN2008/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>922525106321</t>
+          <t>922525106329</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SREE DHARANI C</t>
+          <t>SRINITHE T</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>SREEDHARANI_14</t>
+          <t>srinithe_1401</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SREEDHARANI_14/</t>
+          <t>https://leetcode.com/u/srinithe_1401/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>922525106322</t>
+          <t>922525106330</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SRI  T</t>
+          <t>SRINITHI S</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Sri1540</t>
+          <t>Srinithi24_</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2728,24 +2728,24 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sri1540/</t>
+          <t>https://leetcode.com/u/Srinithi24_/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>922525106323</t>
+          <t>922525106331</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SRI HEERA J</t>
+          <t>SRISAMAYA R</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>sriheera03</t>
+          <t>mahi</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2755,24 +2755,24 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sriheera03/</t>
+          <t>https://leetcode.com/u/mahi/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>922525106324</t>
+          <t>922525106332</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SRI KANTH R</t>
+          <t>SUBARNA V</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>kanth2008</t>
+          <t>Subarna_17</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2782,24 +2782,24 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kanth2008/</t>
+          <t>https://leetcode.com/u/Subarna_17/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>922525106325</t>
+          <t>922525106333</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SRI SASTIKA G</t>
+          <t>SUBHA KARTHIKA R</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Srisastika_1401</t>
+          <t>subhakarthika</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2809,24 +2809,24 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Srisastika_1401/</t>
+          <t>https://leetcode.com/u/subhakarthika/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>922525106326</t>
+          <t>922525106334</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SRI VARSHAN B P</t>
+          <t>SUBIKA T</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>srivarshan_B_P</t>
+          <t>subika1112</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2836,24 +2836,24 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/srivarshan_B_P/</t>
+          <t>https://leetcode.com/u/subika1112/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>922525106327</t>
+          <t>922525106335</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SRINATH V</t>
+          <t>SUDHARSAN S</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>V_SRINATH</t>
+          <t>Sudharsan</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2863,24 +2863,24 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/V_SRINATH/</t>
+          <t>https://leetcode.com/u/Sudharsan/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>922525106328</t>
+          <t>922525106336</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SRINIRANJAN S</t>
+          <t>SUGANTHAN K</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>SRINIRANJAN2008</t>
+          <t>SUGANTHKALAI</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2890,24 +2890,24 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SRINIRANJAN2008/</t>
+          <t>https://leetcode.com/u/SUGANTHKALAI/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>922525106329</t>
+          <t>922525106337</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SRINITHE T</t>
+          <t>SUGIDHARSHINI T</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>srinithe_1401</t>
+          <t>Sugi_07</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2917,24 +2917,24 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/srinithe_1401/</t>
+          <t>https://leetcode.com/u/Sugi_07/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>922525106330</t>
+          <t>922525106338</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>SRINITHI S</t>
+          <t>SUJEETH M</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Srinithi24_</t>
+          <t>SUJEETH77</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2944,24 +2944,24 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Srinithi24_/</t>
+          <t>https://leetcode.com/u/SUJEETH77/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>922525106331</t>
+          <t>922525106339</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SRISAMAYA R</t>
+          <t>SUJITH RAJA B</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>mahi</t>
+          <t>mahi20_</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2971,24 +2971,24 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/mahi/</t>
+          <t>https://leetcode.com/u/mahi20_/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>922525106332</t>
+          <t>922525106340</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SUBARNA V</t>
+          <t>SUMITHRA S</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Subarna_17</t>
+          <t>sumithra_16</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2998,24 +2998,24 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Subarna_17/</t>
+          <t>https://leetcode.com/u/sumithra_16/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>922525106333</t>
+          <t>922525106341</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SUBHA KARTHIKA R</t>
+          <t>SURYA PRABHU S</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>subhakarthika</t>
+          <t>surya001prabhu</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3025,24 +3025,24 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/subhakarthika/</t>
+          <t>https://leetcode.com/u/surya001prabhu/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>922525106334</t>
+          <t>922525106342</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SUBIKA T</t>
+          <t>SUSIDHARAN M</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>subika1112</t>
+          <t>Susidharan147</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3052,24 +3052,24 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/subika1112/</t>
+          <t>https://leetcode.com/u/Susidharan147/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>922525106335</t>
+          <t>922525106343</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>SUDHARSAN S</t>
+          <t>SUTHARSHANA S</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Sudharsan</t>
+          <t>sutharshana743</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3079,24 +3079,24 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sudharsan/</t>
+          <t>https://leetcode.com/u/sutharshana743/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>922525106336</t>
+          <t>922525106344</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>SUGANTHAN K</t>
+          <t>SWATHI M</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>SUGANTHKALAI</t>
+          <t>Swathimanivel_1234</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3106,24 +3106,24 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SUGANTHKALAI/</t>
+          <t>https://leetcode.com/u/Swathimanivel_1234/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>922525106337</t>
+          <t>922525106370</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>SUGIDHARSHINI T</t>
+          <t>VISHNUHARAN V S</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Sugi_07</t>
+          <t>Vishnuharan082007</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3133,24 +3133,24 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sugi_07/</t>
+          <t>https://leetcode.com/u/Vishnuharan082007/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>922525106338</t>
+          <t>922525106349</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>SUJEETH M</t>
+          <t>THAMEEM FARSHITHA A</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>SUJEETH77</t>
+          <t>Thameem_786</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3160,24 +3160,24 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SUJEETH77/</t>
+          <t>https://leetcode.com/u/Thameem_786/</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>922525106339</t>
+          <t>922525106355</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>SUJITH RAJA B</t>
+          <t>VAISHNAVI U</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>mahi20_</t>
+          <t>vaish200</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3187,24 +3187,24 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/mahi20_/</t>
+          <t>https://leetcode.com/u/vaish200/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>922525106340</t>
+          <t>922525106356</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>SUMITHRA S</t>
+          <t>VASANTH KUMAR C</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>sumithra_16</t>
+          <t>VASANTH2007</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3214,24 +3214,24 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sumithra_16/</t>
+          <t>https://leetcode.com/u/VASANTH2007/</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>922525106341</t>
+          <t>922525106357</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>SURYA PRABHU S</t>
+          <t>VASANTH S</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>surya001prabhu</t>
+          <t>_vasanth_s_</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3241,24 +3241,24 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/surya001prabhu/</t>
+          <t>https://leetcode.com/u/_vasanth_s_/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>922525106342</t>
+          <t>922525106358</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>SUSIDHARAN M</t>
+          <t>VASANTHA KUMAR D</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Susidharan147</t>
+          <t>Vasanthakumar12232</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3268,24 +3268,24 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Susidharan147/</t>
+          <t>https://leetcode.com/u/Vasanthakumar12232/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>922525106343</t>
+          <t>922525106359</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>SUTHARSHANA S</t>
+          <t>VASANTHKUMAR R</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>sutharshana743</t>
+          <t>VasanthKumar008</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3295,24 +3295,24 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sutharshana743/</t>
+          <t>https://leetcode.com/u/VasanthKumar008/</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>922525106344</t>
+          <t>922525106345</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SWATHI M</t>
+          <t>SWATHI S</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Swathimanivel_1234</t>
+          <t>_swathi _3366</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Swathimanivel_1234/</t>
+          <t>https://leetcode.com/u/_swathi _3366/</t>
         </is>
       </c>
     </row>
@@ -3383,17 +3383,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>922525106349</t>
+          <t>922525106360</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>THAMEEM FARSHITHA A</t>
+          <t>VASUDEVAN G</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Thameem_786</t>
+          <t>GTVASU2008</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Thameem_786/</t>
+          <t>https://leetcode.com/u/GTVASU2008/</t>
         </is>
       </c>
     </row>
@@ -3704,8 +3704,6461 @@
         </is>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>922525106095</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>GOMATHI R</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>gomathi_0709</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/gomathi_0709/</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>922525106099</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>GOVARTHAN K S</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>GOVARTHANKS</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/GOVARTHANKS/</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>922525106105</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>GOWTHAM S</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Gowtham_080</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Gowtham_080/</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>922525106107</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>GUNA SHREE V</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Gunashree20</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Gunashree20/</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>922525106119</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>HAVISHMATHI S</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>HAVISHMATHIS</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/HAVISHMATHIS/</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>922525106040</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>BHARANIDHARAN S</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Idvdnnsh577q</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Idvdnnsh577q/</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>922525106200</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>MONISHA R</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>itsmoni</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/itsmoni/</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>922525106167</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>LAKSHETHA V</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>itz_lakshe</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/itz_lakshe/</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>922525106234</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>PRAVEENKUMAR R</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>itz_praveen_</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/itz_praveen_/</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>922525106154</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>KAVYA A</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>itzz__kavya02</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/itzz__kavya02/</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>922525106025</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>ARSATHA BEGAM M S</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>jakabesj</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/jakabesj/</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>922525106127</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>JANANI A</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>janani_asohkan</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/janani_asohkan/</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>922525106128</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>JASHVANTH J S</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>jashvanth2007</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/jashvanth2007/</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>922525106129</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>JASVANTHRAM SP</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>jasvanthram</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/jasvanthram/</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>922525106130</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>JAYASAKTHI V</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>jayasakthi_25</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/jayasakthi_25/</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>922525106134</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>JEEVANAA S</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>jeevanaa_174_</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/jeevanaa_174_/</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>922525106132</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Jeevan bala G</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>jeevanbala142008</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/jeevanbala142008/</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>922525106177</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>MADELIN JENITA M</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>jenita0206</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/jenita0206/</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>922525106135</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>JERSHITH J S</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Jerry2008</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Jerry2008/</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>922525106136</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>JOSHITHA KANNAN SUDHA</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Joshi_666</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Joshi_666/</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>922525106138</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>JOTHISHA K S</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Jothi-</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Jothi-/</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>922525106137</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Jothi harshan D K</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Jothiharshan16</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Jothiharshan16/</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>922525106142</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>KANITHRA R</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>kanithraakila</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/kanithraakila/</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>922525106143</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>KARISHMA M</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Karishma_m_08</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Karishma_m_08/</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>922525106144</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>KARMUKILAN J</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>karmukilan567</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/karmukilan567/</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>922525106145</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>KARSHANA SRI V</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>karshana_234</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/karshana_234/</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>922525106146</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>KARTHIKA K</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Karthi270827</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Karthi270827/</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>922525106147</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>KATHIR E</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>kathir__21</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/kathir__21/</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>922525106152</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>KAVIPRIYA R</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>KAVI_RAVI</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/KAVI_RAVI/</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>922525106153</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>KAVIYARASU K</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>kavi12d</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/kavi12d/</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>922525106148</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>KAVIMALAR A</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>kavimalar08</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/kavimalar08/</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>922525106149</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>KAVIN KUMAR S</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>KAVIN__26</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/KAVIN__26/</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>922525106150</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>KAVINKUMAR M</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>kavinleet</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/kavinleet/</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>922525106156</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>KEERTHANA S</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>keerthana_19selvam</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/keerthana_19selvam/</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>922525106157</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>KESAVINI M</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>KESAVINI892</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/KESAVINI892/</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>922525106158</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>KIRUTHIKA S</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>kiruthika_selvanathan05092007</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/kiruthika_selvanathan05092007/</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>922525106160</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>KOHUL V</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>kohul_v</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/kohul_v/</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>922525106162</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>KOWSHIK R</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>kowshik_rk_</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/kowshik_rk_/</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>922525106164</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>KOWSHIKA M S</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>kowshika_moorthi</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/kowshika_moorthi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>922525106163</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>KOWSHIKA B</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Kowshika08</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Kowshika08/</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>922525106165</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>KOWSHIKAN P</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>KOWSHIKAN-PALANISAMY</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/KOWSHIKAN-PALANISAMY/</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>922525106161</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>KOWSHIK M</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>kowshikm23</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/kowshikm23/</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>922525106166</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>KRISH R</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>krish-2007</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/krish-2007/</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>922525106168</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>LAVANYA V</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>lavilavanya</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/lavilavanya/</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>922525106169</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>LINGESHWARAN K</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>LING2007</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/LING2007/</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>922525106210</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>NAVANEETHAN L</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>lnavaneethan08</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/lnavaneethan08/</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>922525106171</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>LOGASRI.A</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Loga07</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Loga07/</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>922525106172</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>LOGAVARDHAN M</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>loga16</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/loga16/</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>922525106170</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>LOGADHARSHINI T</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>LogadharshiniT</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/LogadharshiniT/</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>922525106173</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>LOGESH H</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>logesh2008</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/logesh2008/</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>922525106174</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>LOGESHWARAN K</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>LOGESHWARAN2008</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/LOGESHWARAN2008/</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>922525106175</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>LOHITH RAJ S</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>LOHITH012008</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/LOHITH012008/</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>922525106176</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>LOKRAJI R</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>LOKRAJI6793</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/LOKRAJI6793/</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>922525106191</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Manoj Kumar V</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>m____a____n____o____</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/m____a____n____o____/</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>922525106179</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>MADHANKUMAR S</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Madhankumar861053</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Madhankumar861053/</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>922525106180</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>MADHUDHARA P</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>madhudhara</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/madhudhara/</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>922525106181</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>MADHUMITHA B</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Madhumitha42</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Madhumitha42/</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>922525106182</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Madhup Kishor G S</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Madhupkishor_20</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Madhupkishor_20/</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>922525106185</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>MAHALAKSHMI P</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>maha_lakh_20</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/maha_lakh_20/</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>922525106183</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>MAHALAKSHMI B</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>mahalakshmi182025</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/mahalakshmi182025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>922525106186</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>MAHIBALAN .A</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>mahi2</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/mahi2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>922525106187</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>MAHIN ABHISHEK VH</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Mahinabhishek0411</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Mahinabhishek0411/</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>922525106189</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Manisha D</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>manishaa_20</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/manishaa_20/</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>922525106190</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>MANOJ A</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Manoj_1319</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Manoj_1319/</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>922525106193</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>MATHESHKUMAR S</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>mathesh25</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/mathesh25/</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>922525106194</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>MAYAKANNAN K</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Mayakannan129</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Mayakannan129/</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>922525106195</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>MAYUKA M</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Mayuka_M</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Mayuka_M/</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>922525106196</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Milan D</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>milan190308</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/milan190308/</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>922525106201</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>MONISHA V</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Monishav2007</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Monishav2007/</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>922525106202</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Morrish D</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>morrishd</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/morrishd/</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>922525106203</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>MOULEESHWARI B</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Mouleeshwari2008</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Mouleeshwari2008/</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>922525106204</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>MOUSHMI P N</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Moushmi_20</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Moushmi_20/</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>922525106205</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>MYTHILI M</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>mythilimurugesan</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/mythilimurugesan/</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>922525106206</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>NAFREEN J M</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>NafreenJohnbasha</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/NafreenJohnbasha/</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>922525106208</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>NANDHINI D</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>nandhini546</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/nandhini546/</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>922525106211</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Naveetha N</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>NAVEETHAN</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/NAVEETHAN/</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>922525106213</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>NIRANJANI D</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>niranjani_123</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/niranjani_123/</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>922525106215</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>NITHISH P</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Nithish_P_CS</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Nithish_P_CS/</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>922525106214</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>NITHISH C T</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Nithishct123</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Nithishct123/</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>922525106216</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Nithish R</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>nithishramalingam007</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/nithishramalingam007/</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>922525106217</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>NITHISHWARAN D</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>nithishwaran25</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/nithishwaran25/</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>922525106219</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>NITHYASHREE P</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Nithyashree273</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Nithyashree273/</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>922525106218</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>NITHYASHREE G</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>NithyashreeG10</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/NithyashreeG10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>922525106220</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>NITHYASRI M</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Nithyasri2008</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Nithyasri2008/</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>922525106222</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>PAARGAVI R</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>paargavi2007</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/paargavi2007/</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>922525106223</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>PAVITHRA S</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>pavithra145</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/pavithra145/</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>922525106224</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>PAVITHRAN S</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Pavithran_S_</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Pavithran_S_/</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>922525106225</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>PIRAVEEN M</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Piraveen2025</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Piraveen2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>922525106227</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>PRADHOSH T</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>pradhosh</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/pradhosh/</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>922525106228</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>PRAGALATHAN T</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>pragalathan070108</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/pragalathan070108/</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>922525106229</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>PRANESH Y</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Pranesh-Y</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Pranesh-Y/</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>922525106230</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>PRANITHASREE SAMINATHAN</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>pranithaashree</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/pranithaashree/</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>922525106232</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>PRAVEEN G</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>praveen_3208</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/praveen_3208/</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>922525106231</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>PRAVEEN D</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>praveen1247</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/praveen1247/</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>922525106233</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>PRAVEEN G</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>PRAVEENGANESAN</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/PRAVEENGANESAN/</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>922525106235</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>PREETHY M S</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>preethy2007</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/preethy2007/</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>922525106086</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>DIVYA V</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>princess-nk</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/princess-nk/</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>922525106236</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>PRITHIV S</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>prithiv16</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/prithiv16/</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>922525106237</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>PRIYADHARSHINI V</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>priyadharshini1551</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/priyadharshini1551/</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>922525106238</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>PRIYANKA A</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Priyankaashok1201</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Priyankaashok1201/</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>922525106239</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>PRIYANKA K R</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>priyankadhanush23</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/priyankadhanush23/</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>922525106240</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>RAGADHARSHINI S</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Ragadharshini_2181</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Ragadharshini_2181/</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>922525106241</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>RAGUNATH M</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>ragunath24</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/ragunath24/</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>922525106242</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>RAHULKAJAN M</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>rahulkajan</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/rahulkajan/</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>922525106243</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>RAJAPRAGADEESWARAN R</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>rajaprahadeeswaran</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/rajaprahadeeswaran/</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>922525106244</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>RANJANA T</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>RANJANA_2007</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/RANJANA_2007/</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>922525106246</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>RASIKA S</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>RASIKA_2008</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/RASIKA_2008/</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>922525106247</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>RATHISH R</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Rathish2025</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Rathish2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>922525106248</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>RAVIKUMAR S</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Ravikumar_14</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Ravikumar_14/</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>922525106249</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>RENOFIYA HASIN A</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Renofiya-2007</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Renofiya-2007/</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>922525106250</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>RESMHI S</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>reshmi2008</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/reshmi2008/</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>922525106251</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>RETHANYA S</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>rethanya38</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/rethanya38/</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>922525106252</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>RETHISH</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Rethish_R</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Rethish_R/</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>922525106026</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>ARUL S.T.</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>S_T_Arul</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/S_T_Arul/</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>922525106199</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>MONISH S</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>smonish777</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/smonish777/</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>922525106198</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>MOHAMMED ABUTHARIK S</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>tharik25</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/tharik25/</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>922525106010</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>AJAIRAJAN SR</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>UJw4zUNnJJ</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/UJw4zUNnJJ/</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>922525106034</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Asmitha E</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/1/</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>922525106076</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>DHARSINI V S</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>vsdharsini</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/vsdharsini/</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>922525106043</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>BHARGAVI K</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>922525106036</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>BALARITHISH S</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/3/</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>922525106035</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>BALAJI C</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/4/</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>922525106058</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>DEEKSHA K</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/5/</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>922525106106</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>GOWTHAMAN N</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>92252510610</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/92252510610/</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>922525106101</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>GOWRISANKAR S</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>922524106101</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922524106101/</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>922525106011</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>AJAYKRISHNA R</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>922525106011</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106011/</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>922525106049</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>BUVNESH N</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>922525106049</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106049/</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>922525106052</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>CHINMAYASRI K</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>922525106052</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106052/</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>922525106055</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>DARSHAN C</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>922525106055</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106055/</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>922525106064</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>DHANIKA S</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>922525106064</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106064/</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>922525106065</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>DHANUSHRI D</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>922525106065</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106065/</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>922525106066</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>DHANYA K</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>922525106066</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106066/</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>922525106067</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>DHARAN.K</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>922525106067</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106067/</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>922525106069</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>DHARANESH S</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>922525106069</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106069/</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>922525106070</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>DHARANI M</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>922525106070</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106070/</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>922525106071</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>DHARANI V</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>922525106071</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106071/</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>922525106072</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>DAHARANESH R</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>922525106072</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106072/</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>922525106073</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>DHARMENDRA M P</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>922525106073</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106073/</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>922525106075</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>DHARSHINI S</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>922525106075</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106075/</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>922525106077</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>DHARUN T</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>922525106077</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106077/</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>922525106078</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>DHILIP P</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>922525106078</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106078/</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>922525106079</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>DHINAKAR A</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>922525106079</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106079/</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>922525106081</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>DILIPKUMAR K</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>922525106081</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106081/</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>922525106083</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>DINESHKUMAR P</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>922525106083</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106083/</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>922525106084</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>DINESHKUMAR V</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>922525106084</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106084/</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>922525106085</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>DIVYA ROJA R</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>922525106085</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106085/</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>922525106087</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>DIVYADHARSHINI G</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>922525106087</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106087/</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>922525106088</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>DIVYADHARSHINI S</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>922525106088</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106088/</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>922525106089</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>DURAIMURUGAN K</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>922525106089</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106089/</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>922525106090</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>ELAKKIYA N</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>922525106090</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106090/</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>922525106091</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>ELAVARASAN R</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>922525106091</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106091/</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>922525106092</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>ELAVARASU P</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>922525106092</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106092/</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>922525106093</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>GIRIVASH P</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>922525106093</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106093/</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>922525106096</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>GOPALA KRISHNAN C</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>922525106096</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106096/</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>922525106097</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>GOPINATH R</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>922525106097</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106097/</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>922525106098</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>GOUTHAM R J</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>922525106098</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106098/</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>922525106100</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>GOWRIKA K P</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>922525106100</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106100/</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>922525106103</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>GOWTHAM M</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>922525106103</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106103/</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>922525106104</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>GOWTHAM R</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>922525106104</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106104/</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>922525106102</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>GOWSICK S</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>922525106106</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106106/</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>922525106108</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>GURUSARAN R</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>922525106108</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106108/</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>922525106109</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>HANSHIKAVARSA K S</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>922525106109</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106109/</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>922525106110</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>HARI HARAN R</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>922525106110</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106110/</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>922525106111</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>HARIS S</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>922525106111</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106111/</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>922525106112</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>HARINI S</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>922525106112</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106112/</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>922525106113</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>HARIS M</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>922525106113</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106113/</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>922525106114</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>HARIS RAGAVENDAR A</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>922525106114</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106114/</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>922525106115</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>HARISH D</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>922525106115</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106115/</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>922525106116</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>HARISH M S</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>922525106116</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106116/</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>922525106117</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>HARISH P</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>922525106117</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106117/</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>922525106118</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>HARISHANKAR R</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>922525106118</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106118/</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>922525106120</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>HEMAA SRI A</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>922525106120</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106120/</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>922525106121</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>HEMAVARSHINI S</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>922525106121</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106121/</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>922525106122</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>HIRESH K</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>922525106122</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106122/</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>922525106123</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>INBNATHAN S</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>922525106123</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106123/</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>922525106124</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>INDHIRAJITH K</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>922525106124</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106124/</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>922525106125</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>JAI GANESH I</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>922525106125</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106125/</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>922525106126</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>JANA S</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>922525106126</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525106126/</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>922525106226</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>PRABHAKARAN D</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>_d_Prabhakaran_</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/_d_Prabhakaran_/</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>922525106139</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>KAMALINI G</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>_kamalini_</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/_kamalini_/</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>922525106151</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>KAVIPRIYA J</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>_kavipriya_16</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/_kavipriya_16/</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>922525106056</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>DARSHAN MANISH A</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>2007darshan</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/2007darshan/</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>922525106140</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>KANISHKA A R</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>26kanishka</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/26kanishka/</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>922525106155</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>KAYALVIZHI S</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>27kayalvizhi</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/27kayalvizhi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>922525106005</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>ADHITHMITHRAN P</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/A/</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>922525106001</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>AASHIFA SAHANAJ M</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>aashifasahanaj</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/aashifasahanaj/</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>922525106002</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>AAZHIGA N</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>AAZHIGA</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/AAZHIGA/</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>922525106003</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>ABINAYA N</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Abinaya7095</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Abinaya7095/</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>922525106004</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Abirami R</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>abirami8072</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/abirami8072/</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>922525106006</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>AFTON AJ</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>afton_2008</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/afton_2008/</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>922525106007</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>AGATHEESWARAN K</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>agatheeswarank</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/agatheeswarank/</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>922525106028</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>ARUN C</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>AGmXRQ1yTe</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/AGmXRQ1yTe/</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>922525106012</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>AJAYKUMAR A L</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>AjaykumarAL</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/AjaykumarAL/</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>922525106013</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>AJITH KUMAR M</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>ajit_kumar_23</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/ajit_kumar_23/</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>922525106014</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Akash.R</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>AkashRajaram</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/AkashRajaram/</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>922525106015</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Akshara KR</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Akshara015</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Akshara015/</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>922525106017</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>ALAGESHWARAN J</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Alageshwaran2008</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Alageshwaran2008/</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>922525106018</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Amirdavarsini K S</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>amirda_varsini_2007</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/amirda_varsini_2007/</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>922525106019</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>ANBARASU S</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Anbarasu28122007</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Anbarasu28122007/</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>922525106020</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>ANJITHAA N</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Anjithaa2006</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Anjithaa2006/</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>922525106021</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>ANOOP C</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>anoop_appuz</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/anoop_appuz/</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>922525106022</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>ANUJA S</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>anuja008</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/anuja008/</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>922525106023</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>ANUSRI R</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Anusri_2008</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Anusri_2008/</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>922525106024</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>ANUSYA B</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>ANUSYA_30</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/ANUSYA_30/</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>922525106027</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Arulesh K</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>arul2008</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/arul2008/</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>922525106030</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>ARUNKUMAR K</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Arunkumar2008</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Arunkumar2008/</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>922525106031</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>ARUNPRASANTH T</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>arunprasanth6435</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/arunprasanth6435/</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>922525106029</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>R ARUN PRASATH</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Arunravi1810</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Arunravi1810/</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>922525106032</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>ARVIN SHANKARA</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Arvin</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Arvin/</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>922525106033</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>ASHOK KUMAR P</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>ASHOKKUMAR18</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/ASHOKKUMAR18/</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>922525106008</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>AHELESH G S</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/B/</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>922525106037</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>BARANITHARAN V</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>barani_7</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/barani_7/</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>922525106039</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>BENOV NAVIN V</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Benov_18</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Benov_18/</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>922525106042</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>BHARATHWAJ S</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>BharathwajX</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/BharathwajX/</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>922525106044</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Bhavan bala N</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>BhavanBala</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/BhavanBala/</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>922525106041</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>BHARATH KUMAR E</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>BK5226221</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/BK5226221/</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>922525106045</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>BOOBASE R</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Boobase</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Boobase/</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>922525106046</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>BOOMIKA T</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>boomikat123</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/boomikat123/</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>922525106047</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>BOSVIYA P</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>BosviyaBSV</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/BosviyaBSV/</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>922525106048</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>BRINDHA S</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Brindha_S</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Brindha_S/</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>922525106050</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>CHARUDESNA S</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>charu120108</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/charu120108/</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>922525106051</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>CHARUNETHRA S</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>charunethra07</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/charunethra07/</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>922525106053</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>CHINNAPPAN S</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>chinnappanrajniselvi</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/chinnappanrajniselvi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>922525106009</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>AISHWARYA G</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>codewithaish</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/codewithaish/</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>922525106038</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>BAVITHA T</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>codewithakshaya</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/codewithakshaya/</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>922525106016</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>AKSHAYA S</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>codewithakshaya78</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/codewithakshaya78/</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>922525106054</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>DAKSHINYA R</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Dakshinya555</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Dakshinya555/</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>922525106057</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>DARSHAN V V</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Darshan_mainsh008</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Darshan_mainsh008/</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>922525106059</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>DEJASRI M</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>dejasri</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/dejasri/</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>922525106060</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>DESMA SHALINI K</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>desmashalini</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/desmashalini/</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>922525106061</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>DEVA V</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Devaece</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Devaece/</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>922525106062</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>DHAKSESH PRANAV P</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Dhaksesh_Pranav_P</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Dhaksesh_Pranav_P/</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>922525106063</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>DHANASRI R</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Dhanasri_r</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Dhanasri_r/</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>922525106068</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>DHARANEESH K</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>dharaneeshk</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/dharaneeshk/</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>922525106133</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>JEEVADHARSHAN R R</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>dharshanjeeva</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/dharshanjeeva/</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>922525106074</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>DHARSHINI P</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Dharshini_74</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Dharshini_74/</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>922525106080</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>DHIVAKAR R</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>DhivakarR</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/DhivakarR/</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>922525106082</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>DINESH P</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Dinesh_106082</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Dinesh_106082/</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>922525106094</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>GOKUL D</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Gokul_tamilan_india</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Gokul_tamilan_india/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E121"/>
+  <autoFilter ref="A1:E360"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Students.xlsx
+++ b/Students.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$360</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$359</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E360"/>
+  <dimension ref="A1:E359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -467,17 +467,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>922525106280</t>
+          <t>922525106309</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SANTHOSH D</t>
+          <t>SHREE CHARAN T</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>santhosh7811</t>
+          <t>shreecharan22</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -487,24 +487,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh7811/</t>
+          <t>https://leetcode.com/u/shreecharan22/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>922525106253</t>
+          <t>922525196293</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>RITHANYA KN</t>
+          <t>SASWIN D</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Rithanya12-3</t>
+          <t>saswin_88</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -514,24 +514,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithanya12-3/</t>
+          <t>https://leetcode.com/u/saswin_88/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>922525106256</t>
+          <t>922525106315</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RITHIK P</t>
+          <t>SIVANESH G</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Rithik_78</t>
+          <t>GSIVANESH</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -541,24 +541,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithik_78/</t>
+          <t>https://leetcode.com/u/GSIVANESH/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>922525106257</t>
+          <t>922525106314</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RITHIKA B</t>
+          <t>SIVANESH D</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Rithika_Balakrishnan</t>
+          <t>sivanesh2007</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -568,24 +568,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithika_Balakrishnan/</t>
+          <t>https://leetcode.com/u/sivanesh2007/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>922525106258</t>
+          <t>922525106313</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>RITHISH R</t>
+          <t>SIVAGNANAM M</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Rithish_</t>
+          <t>sivagnanam3344</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -595,24 +595,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithish_/</t>
+          <t>https://leetcode.com/u/sivagnanam3344/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>922525106259</t>
+          <t>922525106312</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ROHITH V</t>
+          <t>SIVADHARSHINI D</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RohithrohiV</t>
+          <t>dharshinideivsigamani</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -622,24 +622,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/RohithrohiV/</t>
+          <t>https://leetcode.com/u/dharshinideivsigamani/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>922525106260</t>
+          <t>922525106311</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ROOBAGAPRIYA R</t>
+          <t>SIVA PRAKASH M</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Roobagapriya</t>
+          <t>sivaprakash_0406</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -649,24 +649,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Roobagapriya/</t>
+          <t>https://leetcode.com/u/sivaprakash_0406/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>922525106261</t>
+          <t>922525106310</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Roshan M</t>
+          <t>SIVA MANIKANDAN K</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>roshan2403</t>
+          <t>9043374912</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -676,24 +676,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/roshan2403/</t>
+          <t>https://leetcode.com/u/9043374912/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>922525106262</t>
+          <t>922525106253</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ROSHIKA V</t>
+          <t>RITHANYA KN</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>roshikaveeramalai</t>
+          <t>Rithanya12-3</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -703,24 +703,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/roshikaveeramalai/</t>
+          <t>https://leetcode.com/u/Rithanya12-3/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>922525106263</t>
+          <t>922525106256</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>RUBESH C</t>
+          <t>RITHIK P</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Rubesh_7</t>
+          <t>Rithik_78</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -730,24 +730,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rubesh_7/</t>
+          <t>https://leetcode.com/u/Rithik_78/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>922525106264</t>
+          <t>922525106257</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SABAREESH K</t>
+          <t>RITHIKA B</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>sabareesh_karikalan</t>
+          <t>Rithika_Balakrishnan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -757,24 +757,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
+          <t>https://leetcode.com/u/Rithika_Balakrishnan/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>922525106265</t>
+          <t>922525106258</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SABARIVASAN P</t>
+          <t>RITHISH R</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SabarivasanP</t>
+          <t>Rithish_</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -784,24 +784,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SabarivasanP/</t>
+          <t>https://leetcode.com/u/Rithish_/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>922525106266</t>
+          <t>922525106259</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SAHANA.V</t>
+          <t>ROHITH V</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sahanavijayakumar_0033</t>
+          <t>RohithrohiV</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sahanavijayakumar_0033/</t>
+          <t>https://leetcode.com/u/RohithrohiV/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>922525106268</t>
+          <t>922525106260</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SAKTHI S</t>
+          <t>ROOBAGAPRIYA R</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sakthisaro08</t>
+          <t>Roobagapriya</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -838,24 +838,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sakthisaro08/</t>
+          <t>https://leetcode.com/u/Roobagapriya/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>922525106269</t>
+          <t>922525106261</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sakthivel. M</t>
+          <t>Roshan M</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>sakthivel23116</t>
+          <t>roshan2403</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -865,24 +865,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sakthivel23116/</t>
+          <t>https://leetcode.com/u/roshan2403/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>922525106271</t>
+          <t>922525106262</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SANDHOSH KUMAR R</t>
+          <t>ROSHIKA V</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>sandhosh_30_R</t>
+          <t>roshikaveeramalai</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -892,24 +892,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sandhosh_30_R/</t>
+          <t>https://leetcode.com/u/roshikaveeramalai/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>922525106272</t>
+          <t>922525106263</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SANJAY D</t>
+          <t>RUBESH C</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>itsmesanjay007</t>
+          <t>Rubesh_7</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -919,24 +919,24 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itsmesanjay007/</t>
+          <t>https://leetcode.com/u/Rubesh_7/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>922525106273</t>
+          <t>922525106264</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SANJAY P</t>
+          <t>SABAREESH K</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>sanjay00675</t>
+          <t>sabareesh_karikalan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -946,24 +946,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sanjay00675/</t>
+          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>922525106275</t>
+          <t>922525106265</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SANJAY U</t>
+          <t>SABARIVASAN P</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SanjayUdayan</t>
+          <t>SabarivasanP</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -973,24 +973,24 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SanjayUdayan/</t>
+          <t>https://leetcode.com/u/SabarivasanP/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>922525106278</t>
+          <t>922525106266</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SANMATHI R</t>
+          <t>SAHANA.V</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>sanmathi06</t>
+          <t>Sahanavijayakumar_0033</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1000,24 +1000,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sanmathi06/</t>
+          <t>https://leetcode.com/u/Sahanavijayakumar_0033/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>922525106279</t>
+          <t>922525106268</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SANTHIYA T</t>
+          <t>SAKTHI S</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>santhiya0202</t>
+          <t>Sakthisaro08</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1027,24 +1027,24 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhiya0202/</t>
+          <t>https://leetcode.com/u/Sakthisaro08/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>922525106282</t>
+          <t>922525106269</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SANTHOSH PRIYAN S</t>
+          <t>Sakthivel. M</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SANTHOSH PRIYAN S</t>
+          <t>sakthivel23116</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1054,24 +1054,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SANTHOSH PRIYAN S/</t>
+          <t>https://leetcode.com/u/sakthivel23116/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>922525106283</t>
+          <t>922525106271</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SANTHOSH S</t>
+          <t>SANDHOSH KUMAR R</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SanthoshSathya260</t>
+          <t>sandhosh_30_R</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1081,24 +1081,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SanthoshSathya260/</t>
+          <t>https://leetcode.com/u/sandhosh_30_R/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>922525106284</t>
+          <t>922525106272</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Santhosh S</t>
+          <t>SANJAY D</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>santhosh2407</t>
+          <t>itsmesanjay007</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1108,24 +1108,24 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh2407/</t>
+          <t>https://leetcode.com/u/itsmesanjay007/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>922525106285</t>
+          <t>922525106273</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SANTHOSH V</t>
+          <t>SANJAY P</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>santhosh8760</t>
+          <t>sanjay00675</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1135,24 +1135,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh8760/</t>
+          <t>https://leetcode.com/u/sanjay00675/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>922525106286</t>
+          <t>922525106275</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SARAN K</t>
+          <t>SANJAY U</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>saran32</t>
+          <t>SanjayUdayan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1162,24 +1162,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saran32/</t>
+          <t>https://leetcode.com/u/SanjayUdayan/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>922525106287</t>
+          <t>922525106278</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SARAVANAN K</t>
+          <t>SANMATHI R</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>saravanan .k</t>
+          <t>sanmathi06</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1189,24 +1189,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saravanan .k/</t>
+          <t>https://leetcode.com/u/sanmathi06/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>922525106288</t>
+          <t>922525106279</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SARAVANAN K</t>
+          <t>SANTHIYA T</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>saravanan__k__</t>
+          <t>santhiya0202</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1216,24 +1216,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saravanan__k__/</t>
+          <t>https://leetcode.com/u/santhiya0202/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>922525106289</t>
+          <t>922525106280</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SARAVANAN S</t>
+          <t>SANTHOSH D</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Saravanan_7525</t>
+          <t>santhosh7811</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1243,24 +1243,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Saravanan_7525/</t>
+          <t>https://leetcode.com/u/santhosh7811/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>922525106290</t>
+          <t>922525106282</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SARIKA M P</t>
+          <t>SANTHOSH PRIYAN S</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>sarika_5408</t>
+          <t>SANTHOSH PRIYAN S</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1270,24 +1270,24 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sarika_5408/</t>
+          <t>https://leetcode.com/u/SANTHOSH PRIYAN S/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>922525106291</t>
+          <t>922525106283</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SARVESWARAN R</t>
+          <t>SANTHOSH S</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>sarvesh312008</t>
+          <t>SanthoshSathya260</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1297,24 +1297,24 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sarvesh312008/</t>
+          <t>https://leetcode.com/u/SanthoshSathya260/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>922525106292</t>
+          <t>922525106284</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SASHMIKA.P</t>
+          <t>Santhosh S</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>sashmikaprabhu</t>
+          <t>santhosh2407</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1324,24 +1324,24 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sashmikaprabhu/</t>
+          <t>https://leetcode.com/u/santhosh2407/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>922525106296</t>
+          <t>922525106285</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SELVAKUMAR K</t>
+          <t>SANTHOSH V</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Selvakumarsk-32</t>
+          <t>santhosh8760</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1351,24 +1351,24 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvakumarsk-32/</t>
+          <t>https://leetcode.com/u/santhosh8760/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>922525106297</t>
+          <t>922525106286</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SELVAPRAGADEESH S</t>
+          <t>SARAN K</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Selvapragadeesh</t>
+          <t>saran32</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1378,24 +1378,24 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvapragadeesh/</t>
+          <t>https://leetcode.com/u/saran32/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>922525106298</t>
+          <t>922525106287</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SELVA RAGAVAN</t>
+          <t>SARAVANAN K</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Selvax07</t>
+          <t>saravanan .k</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1405,24 +1405,24 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvax07/</t>
+          <t>https://leetcode.com/u/saravanan .k/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>922525106299</t>
+          <t>922525106288</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SENTHAMIZHSELVAN K</t>
+          <t>SARAVANAN K</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Senthamizh08</t>
+          <t>saravanan__k__</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1432,24 +1432,24 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Senthamizh08/</t>
+          <t>https://leetcode.com/u/saravanan__k__/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>922525106300</t>
+          <t>922525106289</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Senthil.S</t>
+          <t>SARAVANAN S</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Jna76WrjNd</t>
+          <t>Saravanan_7525</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1459,24 +1459,24 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Jna76WrjNd/</t>
+          <t>https://leetcode.com/u/Saravanan_7525/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>922525106302</t>
+          <t>922525106290</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SHAHANA S</t>
+          <t>SARIKA M P</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>shahana_pandiraj04</t>
+          <t>sarika_5408</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1486,24 +1486,24 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shahana_pandiraj04/</t>
+          <t>https://leetcode.com/u/sarika_5408/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>922525106303</t>
+          <t>922525106291</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SHANTHINI C</t>
+          <t>SARVESWARAN R</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ShanthiniChelladurai</t>
+          <t>sarvesh312008</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1513,24 +1513,24 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/ShanthiniChelladurai/</t>
+          <t>https://leetcode.com/u/sarvesh312008/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>922525106305</t>
+          <t>922525106292</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SHARATH P</t>
+          <t>SASHMIKA.P</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>sharath_1010</t>
+          <t>sashmikaprabhu</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1540,24 +1540,24 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sharath_1010/</t>
+          <t>https://leetcode.com/u/sashmikaprabhu/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>922525106307</t>
+          <t>922525106296</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SHIVANI B</t>
+          <t>SELVAKUMAR K</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>shivani208</t>
+          <t>Selvakumarsk-32</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1567,24 +1567,24 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shivani208/</t>
+          <t>https://leetcode.com/u/Selvakumarsk-32/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>922525106308</t>
+          <t>922525106297</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SHREE HARINI L</t>
+          <t>SELVAPRAGADEESH S</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Shree_Harini478</t>
+          <t>Selvapragadeesh</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1594,24 +1594,24 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Shree_Harini478/</t>
+          <t>https://leetcode.com/u/Selvapragadeesh/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>922525106309</t>
+          <t>922525106298</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SHREE CHARAN T</t>
+          <t>SELVA RAGAVAN</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>shreecharan22</t>
+          <t>Selvax07</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1621,24 +1621,24 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shreecharan22/</t>
+          <t>https://leetcode.com/u/Selvax07/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>922525106310</t>
+          <t>922525106299</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SIVA MANIKANDAN K</t>
+          <t>SENTHAMIZHSELVAN K</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>9043374912</t>
+          <t>Senthamizh08</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1648,24 +1648,24 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/9043374912/</t>
+          <t>https://leetcode.com/u/Senthamizh08/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>922525106311</t>
+          <t>922525106300</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SIVA PRAKASH M</t>
+          <t>Senthil.S</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>sivaprakash_0406</t>
+          <t>Jna76WrjNd</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1675,24 +1675,24 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivaprakash_0406/</t>
+          <t>https://leetcode.com/u/Jna76WrjNd/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>922525106312</t>
+          <t>922525106302</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SIVADHARSHINI D</t>
+          <t>SHAHANA S</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>dharshinideivsigamani</t>
+          <t>shahana_pandiraj04</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1702,24 +1702,24 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/dharshinideivsigamani/</t>
+          <t>https://leetcode.com/u/shahana_pandiraj04/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>922525106313</t>
+          <t>922525106303</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SIVAGNANAM M</t>
+          <t>SHANTHINI C</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>sivagnanam3344</t>
+          <t>ShanthiniChelladurai</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1729,24 +1729,24 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivagnanam3344/</t>
+          <t>https://leetcode.com/u/ShanthiniChelladurai/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>922525106314</t>
+          <t>922525106305</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SIVANESH D</t>
+          <t>SHARATH P</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>sivanesh2007</t>
+          <t>sharath_1010</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivanesh2007/</t>
+          <t>https://leetcode.com/u/sharath_1010/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>922525106315</t>
+          <t>922525106307</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SIVANESH G</t>
+          <t>SHIVANI B</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>GSIVANESH</t>
+          <t>shivani208</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1783,24 +1783,24 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/GSIVANESH/</t>
+          <t>https://leetcode.com/u/shivani208/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>922525196293</t>
+          <t>922525106308</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SASWIN D</t>
+          <t>SHREE HARINI L</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>saswin_88</t>
+          <t>Shree_Harini478</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saswin_88/</t>
+          <t>https://leetcode.com/u/Shree_Harini478/</t>
         </is>
       </c>
     </row>
@@ -1844,17 +1844,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>922525106361</t>
+          <t>922525106370</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>VASUKI K</t>
+          <t>VISHNUHARAN V S</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>vasuki</t>
+          <t>Vishnuharan082007</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1864,24 +1864,24 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vasuki/</t>
+          <t>https://leetcode.com/u/Vishnuharan082007/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>922525106362</t>
+          <t>922525106378</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>VELLIANGIRI R</t>
+          <t>YOKESWARAN S</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>velliangiri_R</t>
+          <t>syokeswaran</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1891,24 +1891,24 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/velliangiri_R/</t>
+          <t>https://leetcode.com/u/syokeswaran/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>922525106363</t>
+          <t>922525106377</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>VIGNESH M</t>
+          <t>YAZHINI V</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>O8bYDSRUbE</t>
+          <t>VISU_YAZHU</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1918,24 +1918,24 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/O8bYDSRUbE/</t>
+          <t>https://leetcode.com/u/VISU_YAZHU/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>922525106364</t>
+          <t>922525106376</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>VIGNESH VELAN M</t>
+          <t>YAZHINI S</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Vicky_27_Velan</t>
+          <t>yazhini__1234</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1945,24 +1945,24 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vicky_27_Velan/</t>
+          <t>https://leetcode.com/u/yazhini__1234/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>922525106365</t>
+          <t>922525106375</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>VIGNESHWAR U</t>
+          <t>YAZHINI M</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>VIGNESHWAR0221</t>
+          <t>yazhini2007</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1972,24 +1972,24 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VIGNESHWAR0221/</t>
+          <t>https://leetcode.com/u/yazhini2007/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>922525106366</t>
+          <t>922525106374</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>VIJAYARAGAVAN R</t>
+          <t>YASWANTH V</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>vijayaragavan1216</t>
+          <t>yaswanth_2008</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1999,24 +1999,24 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vijayaragavan1216/</t>
+          <t>https://leetcode.com/u/yaswanth_2008/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>922525106367</t>
+          <t>922525106373</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>VIKRAM V</t>
+          <t>YASHNI S</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>vikramvicky5678</t>
+          <t>Yashnisubramaniyan</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2026,24 +2026,24 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vikramvicky5678/</t>
+          <t>https://leetcode.com/u/Yashnisubramaniyan/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>922525106368</t>
+          <t>922525106372</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>VISHNU B</t>
+          <t>VISHWAJETH A M</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>VISHNU_B_2008</t>
+          <t>vishwajeth</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2053,24 +2053,24 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VISHNU_B_2008/</t>
+          <t>https://leetcode.com/u/vishwajeth/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>922525106369</t>
+          <t>922525106371</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>VISHNU PRIYAN S</t>
+          <t>VISHNUPRIYA S</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>itz__priyan__</t>
+          <t>vishnupriyamaran</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itz__priyan__/</t>
+          <t>https://leetcode.com/u/vishnupriyamaran/</t>
         </is>
       </c>
     </row>
@@ -2330,17 +2330,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>922525106371</t>
+          <t>922525106325</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>VISHNUPRIYA S</t>
+          <t>SRI SASTIKA G</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>vishnupriyamaran</t>
+          <t>Srisastika_1401</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2350,24 +2350,24 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vishnupriyamaran/</t>
+          <t>https://leetcode.com/u/Srisastika_1401/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>922525106372</t>
+          <t>922525106326</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>VISHWAJETH A M</t>
+          <t>SRI VARSHAN B P</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>vishwajeth</t>
+          <t>srivarshan_B_P</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2377,24 +2377,24 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vishwajeth/</t>
+          <t>https://leetcode.com/u/srivarshan_B_P/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>922525106373</t>
+          <t>922525106327</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>YASHNI S</t>
+          <t>SRINATH V</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Yashnisubramaniyan</t>
+          <t>V_SRINATH</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2404,24 +2404,24 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Yashnisubramaniyan/</t>
+          <t>https://leetcode.com/u/V_SRINATH/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>922525106374</t>
+          <t>922525106328</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>YASWANTH V</t>
+          <t>SRINIRANJAN S</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>yaswanth_2008</t>
+          <t>SRINIRANJAN2008</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2431,24 +2431,24 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yaswanth_2008/</t>
+          <t>https://leetcode.com/u/SRINIRANJAN2008/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>922525106375</t>
+          <t>922525106329</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>YAZHINI M</t>
+          <t>SRINITHE T</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>yazhini2007</t>
+          <t>srinithe_1401</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2458,24 +2458,24 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yazhini2007/</t>
+          <t>https://leetcode.com/u/srinithe_1401/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>922525106376</t>
+          <t>922525106330</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>YAZHINI S</t>
+          <t>SRINITHI S</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>yazhini__1234</t>
+          <t>Srinithi24_</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2485,24 +2485,24 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yazhini__1234/</t>
+          <t>https://leetcode.com/u/Srinithi24_/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>922525106377</t>
+          <t>922525106331</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>YAZHINI V</t>
+          <t>SRISAMAYA R</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>VISU_YAZHU</t>
+          <t>mahi</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2512,24 +2512,24 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VISU_YAZHU/</t>
+          <t>https://leetcode.com/u/mahi/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>922525106378</t>
+          <t>922525106332</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>YOKESWARAN S</t>
+          <t>SUBARNA V</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>syokeswaran</t>
+          <t>Subarna_17</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2539,24 +2539,24 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/syokeswaran/</t>
+          <t>https://leetcode.com/u/Subarna_17/</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>922525106346</t>
+          <t>922525106334</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SWETHA E</t>
+          <t>SUBIKA T</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Swetha_20_1</t>
+          <t>subika1112</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2566,24 +2566,24 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Swetha_20_1/</t>
+          <t>https://leetcode.com/u/subika1112/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>922525106325</t>
+          <t>922525106335</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SRI SASTIKA G</t>
+          <t>SUDHARSAN S</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Srisastika_1401</t>
+          <t>Sudharsan</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2593,24 +2593,24 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Srisastika_1401/</t>
+          <t>https://leetcode.com/u/Sudharsan/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>922525106326</t>
+          <t>922525106336</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SRI VARSHAN B P</t>
+          <t>SUGANTHAN K</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>srivarshan_B_P</t>
+          <t>SUGANTHKALAI</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2620,24 +2620,24 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/srivarshan_B_P/</t>
+          <t>https://leetcode.com/u/SUGANTHKALAI/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>922525106327</t>
+          <t>922525106337</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SRINATH V</t>
+          <t>SUGIDHARSHINI T</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>V_SRINATH</t>
+          <t>Sugi_07</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2647,24 +2647,24 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/V_SRINATH/</t>
+          <t>https://leetcode.com/u/Sugi_07/</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>922525106328</t>
+          <t>922525106338</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SRINIRANJAN S</t>
+          <t>SUJEETH M</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>SRINIRANJAN2008</t>
+          <t>SUJEETH77</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2674,24 +2674,24 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SRINIRANJAN2008/</t>
+          <t>https://leetcode.com/u/SUJEETH77/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>922525106329</t>
+          <t>922525106339</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SRINITHE T</t>
+          <t>SUJITH RAJA B</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>srinithe_1401</t>
+          <t>mahi20_</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/srinithe_1401/</t>
+          <t>https://leetcode.com/u/mahi20_/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>922525106330</t>
+          <t>922525106340</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SRINITHI S</t>
+          <t>SUMITHRA S</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Srinithi24_</t>
+          <t>sumithra_16</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2728,24 +2728,24 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Srinithi24_/</t>
+          <t>https://leetcode.com/u/sumithra_16/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>922525106331</t>
+          <t>922525106341</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SRISAMAYA R</t>
+          <t>SURYA PRABHU S</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>mahi</t>
+          <t>surya001prabhu</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2755,24 +2755,24 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/mahi/</t>
+          <t>https://leetcode.com/u/surya001prabhu/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>922525106332</t>
+          <t>922525106342</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SUBARNA V</t>
+          <t>SUSIDHARAN M</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Subarna_17</t>
+          <t>Susidharan147</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2782,24 +2782,24 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Subarna_17/</t>
+          <t>https://leetcode.com/u/Susidharan147/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>922525106333</t>
+          <t>922525106343</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SUBHA KARTHIKA R</t>
+          <t>SUTHARSHANA S</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>subhakarthika</t>
+          <t>sutharshana743</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2809,24 +2809,24 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/subhakarthika/</t>
+          <t>https://leetcode.com/u/sutharshana743/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>922525106334</t>
+          <t>922525106344</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SUBIKA T</t>
+          <t>SWATHI M</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>subika1112</t>
+          <t>Swathimanivel_1234</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2836,24 +2836,24 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/subika1112/</t>
+          <t>https://leetcode.com/u/Swathimanivel_1234/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>922525106335</t>
+          <t>922525106365</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SUDHARSAN S</t>
+          <t>VIGNESHWAR U</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Sudharsan</t>
+          <t>VIGNESHWAR0221</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2863,24 +2863,24 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sudharsan/</t>
+          <t>https://leetcode.com/u/VIGNESHWAR0221/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>922525106336</t>
+          <t>922525106366</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SUGANTHAN K</t>
+          <t>VIJAYARAGAVAN R</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>SUGANTHKALAI</t>
+          <t>vijayaragavan1216</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2890,24 +2890,24 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SUGANTHKALAI/</t>
+          <t>https://leetcode.com/u/vijayaragavan1216/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>922525106337</t>
+          <t>922525106367</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SUGIDHARSHINI T</t>
+          <t>VIKRAM V</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Sugi_07</t>
+          <t>vikramvicky5678</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2917,24 +2917,24 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sugi_07/</t>
+          <t>https://leetcode.com/u/vikramvicky5678/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>922525106338</t>
+          <t>922525106368</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>SUJEETH M</t>
+          <t>VISHNU B</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>SUJEETH77</t>
+          <t>VISHNU_B_2008</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2944,24 +2944,24 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SUJEETH77/</t>
+          <t>https://leetcode.com/u/VISHNU_B_2008/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>922525106339</t>
+          <t>922525106369</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SUJITH RAJA B</t>
+          <t>VISHNU PRIYAN S</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>mahi20_</t>
+          <t>itz__priyan__</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2971,24 +2971,24 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/mahi20_/</t>
+          <t>https://leetcode.com/u/itz__priyan__/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>922525106340</t>
+          <t>922525106346</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SUMITHRA S</t>
+          <t>SWETHA E</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>sumithra_16</t>
+          <t>Swetha_20_1</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2998,24 +2998,24 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sumithra_16/</t>
+          <t>https://leetcode.com/u/Swetha_20_1/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>922525106341</t>
+          <t>922525106347</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SURYA PRABHU S</t>
+          <t>TAMIL SELVAN R</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>surya001prabhu</t>
+          <t>Kdmif0HMNm</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3025,24 +3025,24 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/surya001prabhu/</t>
+          <t>https://leetcode.com/u/Kdmif0HMNm/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>922525106342</t>
+          <t>922525106348</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SUSIDHARAN M</t>
+          <t>THAMARAI SELVI D</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Susidharan147</t>
+          <t>thamarai_04</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3052,24 +3052,24 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Susidharan147/</t>
+          <t>https://leetcode.com/u/thamarai_04/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>922525106343</t>
+          <t>922525106349</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>SUTHARSHANA S</t>
+          <t>THAMEEM FARSHITHA A</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>sutharshana743</t>
+          <t>Thameem_786</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3079,24 +3079,24 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sutharshana743/</t>
+          <t>https://leetcode.com/u/Thameem_786/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>922525106344</t>
+          <t>922525106350</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>SWATHI M</t>
+          <t>THARANISH R</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Swathimanivel_1234</t>
+          <t>THARANISH2008</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3106,24 +3106,24 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Swathimanivel_1234/</t>
+          <t>https://leetcode.com/u/THARANISH2008/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>922525106370</t>
+          <t>922525106351</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>VISHNUHARAN V S</t>
+          <t>THARUNIKA P</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Vishnuharan082007</t>
+          <t>Tharunika_12</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3133,24 +3133,24 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vishnuharan082007/</t>
+          <t>https://leetcode.com/u/Tharunika_12/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>922525106349</t>
+          <t>922525106352</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>THAMEEM FARSHITHA A</t>
+          <t>THIRINESH KUMAR S</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Thameem_786</t>
+          <t>THIRINESH KUMAR.S</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3160,24 +3160,24 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Thameem_786/</t>
+          <t>https://leetcode.com/u/THIRINESH KUMAR.S/</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>922525106355</t>
+          <t>922525106353</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>VAISHNAVI U</t>
+          <t>THIRISHA C</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>vaish200</t>
+          <t>thirishavsb</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3187,24 +3187,24 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vaish200/</t>
+          <t>https://leetcode.com/u/thirishavsb/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>922525106356</t>
+          <t>922525106354</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>VASANTH KUMAR C</t>
+          <t>THIRUMURUGAN S</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>VASANTH2007</t>
+          <t>thiru0211_</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3214,24 +3214,24 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VASANTH2007/</t>
+          <t>https://leetcode.com/u/thiru0211_/</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>922525106357</t>
+          <t>922525106355</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>VASANTH S</t>
+          <t>VAISHNAVI U</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>_vasanth_s_</t>
+          <t>vaish200</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3241,24 +3241,24 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_vasanth_s_/</t>
+          <t>https://leetcode.com/u/vaish200/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>922525106358</t>
+          <t>922525106356</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>VASANTHA KUMAR D</t>
+          <t>VASANTH KUMAR C</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Vasanthakumar12232</t>
+          <t>VASANTH2007</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3268,24 +3268,24 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vasanthakumar12232/</t>
+          <t>https://leetcode.com/u/VASANTH2007/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>922525106359</t>
+          <t>922525106357</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>VASANTHKUMAR R</t>
+          <t>VASANTH S</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>VasanthKumar008</t>
+          <t>_vasanth_s_</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3295,24 +3295,24 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VasanthKumar008/</t>
+          <t>https://leetcode.com/u/_vasanth_s_/</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>922525106345</t>
+          <t>922525106358</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SWATHI S</t>
+          <t>VASANTHA KUMAR D</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>_swathi _3366</t>
+          <t>Vasanthakumar12232</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3322,24 +3322,24 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_swathi _3366/</t>
+          <t>https://leetcode.com/u/Vasanthakumar12232/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>922525106347</t>
+          <t>922525106359</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>TAMIL SELVAN R</t>
+          <t>VASANTHKUMAR R</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Kdmif0HMNm</t>
+          <t>VasanthKumar008</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3349,24 +3349,24 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Kdmif0HMNm/</t>
+          <t>https://leetcode.com/u/VasanthKumar008/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>922525106348</t>
+          <t>922525106345</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>THAMARAI SELVI D</t>
+          <t>SWATHI S</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>thamarai_04</t>
+          <t>_swathi _3366</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/thamarai_04/</t>
+          <t>https://leetcode.com/u/_swathi _3366/</t>
         </is>
       </c>
     </row>
@@ -3410,17 +3410,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>922525106350</t>
+          <t>922525106361</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>THARANISH R</t>
+          <t>VASUKI K</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>THARANISH2008</t>
+          <t>vasuki</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3430,24 +3430,24 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/THARANISH2008/</t>
+          <t>https://leetcode.com/u/vasuki/</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>922525106351</t>
+          <t>922525106362</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>THARUNIKA P</t>
+          <t>VELLIANGIRI R</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Tharunika_12</t>
+          <t>velliangiri_R</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -3457,24 +3457,24 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Tharunika_12/</t>
+          <t>https://leetcode.com/u/velliangiri_R/</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>922525106352</t>
+          <t>922525106363</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>THIRINESH KUMAR S</t>
+          <t>VIGNESH M</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>THIRINESH KUMAR.S</t>
+          <t>O8bYDSRUbE</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3484,24 +3484,24 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/THIRINESH KUMAR.S/</t>
+          <t>https://leetcode.com/u/O8bYDSRUbE/</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>922525106353</t>
+          <t>922525106364</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>THIRISHA C</t>
+          <t>VIGNESH VELAN M</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>thirishavsb</t>
+          <t>Vicky_27_Velan</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3511,51 +3511,51 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/thirishavsb/</t>
+          <t>https://leetcode.com/u/Vicky_27_Velan/</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>922525106354</t>
+          <t>922525106267</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>THIRUMURUGAN S</t>
+          <t>SAJISH R</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>thiru0211_</t>
+          <t>SAJISH7</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>ECE F</t>
+          <t>ECE E</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/thiru0211_/</t>
+          <t>https://leetcode.com/u/SAJISH7/</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>922525106267</t>
+          <t>922525106270</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>SAJISH R</t>
+          <t>SANDHIYA T</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>SAJISH7</t>
+          <t>zklXTc9UAp</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -3565,24 +3565,24 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SAJISH7/</t>
+          <t>https://leetcode.com/u/zklXTc9UAp/</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>922525106270</t>
+          <t>922525106276</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>SANDHIYA T</t>
+          <t>SANJAYAN</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>zklXTc9UAp</t>
+          <t>sanjayan31</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3592,24 +3592,24 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/zklXTc9UAp/</t>
+          <t>https://leetcode.com/u/sanjayan31/</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>922525106276</t>
+          <t>922525106294</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>SANJAYAN</t>
+          <t>SATHANA SRI S K</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>sanjayan31</t>
+          <t>Sathana-1267</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3619,24 +3619,24 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sanjayan31/</t>
+          <t>https://leetcode.com/u/Sathana-1267/</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>922525106294</t>
+          <t>922525106304</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>SATHANA SRI S K</t>
+          <t>SANTHOSH SHAI SIRIL</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Sathana-1267</t>
+          <t>shandoshsai</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sathana-1267/</t>
+          <t>https://leetcode.com/u/shandoshsai/</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>922525106304</t>
+          <t>922525106306</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>SANTHOSH SHAI SIRIL</t>
+          <t>SHARUKESH</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>shandoshsai</t>
+          <t>sharukesh2008</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -3673,34 +3673,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shandoshsai/</t>
+          <t>https://leetcode.com/u/sharukesh2008/</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>922525106306</t>
+          <t>922525106094</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>SHARUKESH</t>
+          <t>GOKUL D</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>sharukesh2008</t>
+          <t>Gokul_tamilan_india</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>ECE E</t>
+          <t>ECE B</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sharukesh2008/</t>
+          <t>https://leetcode.com/u/Gokul_tamilan_india/</t>
         </is>
       </c>
     </row>
@@ -10130,35 +10130,8 @@
         </is>
       </c>
     </row>
-    <row r="360">
-      <c r="A360" t="inlineStr">
-        <is>
-          <t>922525106094</t>
-        </is>
-      </c>
-      <c r="B360" t="inlineStr">
-        <is>
-          <t>GOKUL D</t>
-        </is>
-      </c>
-      <c r="C360" t="inlineStr">
-        <is>
-          <t>Gokul_tamilan_india</t>
-        </is>
-      </c>
-      <c r="D360" t="inlineStr">
-        <is>
-          <t>ECE B</t>
-        </is>
-      </c>
-      <c r="E360" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Gokul_tamilan_india/</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E360"/>
+  <autoFilter ref="A1:E359"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Students.xlsx
+++ b/Students.xlsx
@@ -467,17 +467,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>922525106309</t>
+          <t>922525106310</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SHREE CHARAN T</t>
+          <t>SIVA MANIKANDAN K</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>shreecharan22</t>
+          <t>9043374912</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -487,24 +487,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shreecharan22/</t>
+          <t>https://leetcode.com/u/9043374912/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>922525196293</t>
+          <t>922525106312</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SASWIN D</t>
+          <t>SIVADHARSHINI D</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>saswin_88</t>
+          <t>dharshinideivsigamani</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -514,24 +514,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saswin_88/</t>
+          <t>https://leetcode.com/u/dharshinideivsigamani/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>922525106315</t>
+          <t>922525106313</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SIVANESH G</t>
+          <t>SIVAGNANAM M</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GSIVANESH</t>
+          <t>sivagnanam3344</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/GSIVANESH/</t>
+          <t>https://leetcode.com/u/sivagnanam3344/</t>
         </is>
       </c>
     </row>
@@ -575,17 +575,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>922525106313</t>
+          <t>922525106315</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SIVAGNANAM M</t>
+          <t>SIVANESH G</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>sivagnanam3344</t>
+          <t>GSIVANESH</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -595,24 +595,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivagnanam3344/</t>
+          <t>https://leetcode.com/u/GSIVANESH/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>922525106312</t>
+          <t>922525196293</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SIVADHARSHINI D</t>
+          <t>SASWIN D</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>dharshinideivsigamani</t>
+          <t>saswin_88</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/dharshinideivsigamani/</t>
+          <t>https://leetcode.com/u/saswin_88/</t>
         </is>
       </c>
     </row>
@@ -656,17 +656,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>922525106310</t>
+          <t>922525106253</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SIVA MANIKANDAN K</t>
+          <t>RITHANYA KN</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>9043374912</t>
+          <t>Rithanya12-3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -676,24 +676,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/9043374912/</t>
+          <t>https://leetcode.com/u/Rithanya12-3/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>922525106253</t>
+          <t>922525106256</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RITHANYA KN</t>
+          <t>RITHIK P</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rithanya12-3</t>
+          <t>Rithik_78</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -703,24 +703,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithanya12-3/</t>
+          <t>https://leetcode.com/u/Rithik_78/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>922525106256</t>
+          <t>922525106257</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>RITHIK P</t>
+          <t>RITHIKA B</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Rithik_78</t>
+          <t>Rithika_Balakrishnan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -730,24 +730,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithik_78/</t>
+          <t>https://leetcode.com/u/Rithika_Balakrishnan/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>922525106257</t>
+          <t>922525106258</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RITHIKA B</t>
+          <t>RITHISH R</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Rithika_Balakrishnan</t>
+          <t>Rithish_</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -757,24 +757,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithika_Balakrishnan/</t>
+          <t>https://leetcode.com/u/Rithish_/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>922525106258</t>
+          <t>922525106259</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>RITHISH R</t>
+          <t>ROHITH V</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Rithish_</t>
+          <t>RohithrohiV</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -784,24 +784,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithish_/</t>
+          <t>https://leetcode.com/u/RohithrohiV/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>922525106259</t>
+          <t>922525106260</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ROHITH V</t>
+          <t>ROOBAGAPRIYA R</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>RohithrohiV</t>
+          <t>Roobagapriya</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/RohithrohiV/</t>
+          <t>https://leetcode.com/u/Roobagapriya/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>922525106260</t>
+          <t>922525106261</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ROOBAGAPRIYA R</t>
+          <t>Roshan M</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Roobagapriya</t>
+          <t>roshan2403</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -838,24 +838,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Roobagapriya/</t>
+          <t>https://leetcode.com/u/roshan2403/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>922525106261</t>
+          <t>922525106262</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Roshan M</t>
+          <t>ROSHIKA V</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>roshan2403</t>
+          <t>roshikaveeramalai</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -865,24 +865,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/roshan2403/</t>
+          <t>https://leetcode.com/u/roshikaveeramalai/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>922525106262</t>
+          <t>922525106263</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ROSHIKA V</t>
+          <t>RUBESH C</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>roshikaveeramalai</t>
+          <t>Rubesh_7</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -892,24 +892,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/roshikaveeramalai/</t>
+          <t>https://leetcode.com/u/Rubesh_7/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>922525106263</t>
+          <t>922525106264</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>RUBESH C</t>
+          <t>SABAREESH K</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Rubesh_7</t>
+          <t>sabareesh_karikalan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -919,24 +919,24 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rubesh_7/</t>
+          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>922525106264</t>
+          <t>922525106265</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SABAREESH K</t>
+          <t>SABARIVASAN P</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>sabareesh_karikalan</t>
+          <t>SabarivasanP</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -946,24 +946,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
+          <t>https://leetcode.com/u/SabarivasanP/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>922525106265</t>
+          <t>922525106266</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SABARIVASAN P</t>
+          <t>SAHANA.V</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SabarivasanP</t>
+          <t>Sahanavijayakumar_0033</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -973,24 +973,24 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SabarivasanP/</t>
+          <t>https://leetcode.com/u/Sahanavijayakumar_0033/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>922525106266</t>
+          <t>922525106268</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SAHANA.V</t>
+          <t>SAKTHI S</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sahanavijayakumar_0033</t>
+          <t>Sakthisaro08</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1000,24 +1000,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sahanavijayakumar_0033/</t>
+          <t>https://leetcode.com/u/Sakthisaro08/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>922525106268</t>
+          <t>922525106269</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SAKTHI S</t>
+          <t>Sakthivel. M</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sakthisaro08</t>
+          <t>sakthivel23116</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1027,24 +1027,24 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sakthisaro08/</t>
+          <t>https://leetcode.com/u/sakthivel23116/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>922525106269</t>
+          <t>922525106271</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Sakthivel. M</t>
+          <t>SANDHOSH KUMAR R</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>sakthivel23116</t>
+          <t>sandhosh_30_R</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1054,24 +1054,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sakthivel23116/</t>
+          <t>https://leetcode.com/u/sandhosh_30_R/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>922525106271</t>
+          <t>922525106272</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SANDHOSH KUMAR R</t>
+          <t>SANJAY D</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>sandhosh_30_R</t>
+          <t>itsmesanjay007</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1081,24 +1081,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sandhosh_30_R/</t>
+          <t>https://leetcode.com/u/itsmesanjay007/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>922525106272</t>
+          <t>922525106273</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SANJAY D</t>
+          <t>SANJAY P</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>itsmesanjay007</t>
+          <t>sanjay00675</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1108,24 +1108,24 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itsmesanjay007/</t>
+          <t>https://leetcode.com/u/sanjay00675/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>922525106273</t>
+          <t>922525106275</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SANJAY P</t>
+          <t>SANJAY U</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>sanjay00675</t>
+          <t>SanjayUdayan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1135,24 +1135,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sanjay00675/</t>
+          <t>https://leetcode.com/u/SanjayUdayan/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>922525106275</t>
+          <t>922525106278</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SANJAY U</t>
+          <t>SANMATHI R</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SanjayUdayan</t>
+          <t>sanmathi06</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1162,24 +1162,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SanjayUdayan/</t>
+          <t>https://leetcode.com/u/sanmathi06/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>922525106278</t>
+          <t>922525106279</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SANMATHI R</t>
+          <t>SANTHIYA T</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>sanmathi06</t>
+          <t>santhiya0202</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1189,24 +1189,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sanmathi06/</t>
+          <t>https://leetcode.com/u/santhiya0202/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>922525106279</t>
+          <t>922525106280</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SANTHIYA T</t>
+          <t>SANTHOSH D</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>santhiya0202</t>
+          <t>santhosh7811</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1216,24 +1216,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhiya0202/</t>
+          <t>https://leetcode.com/u/santhosh7811/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>922525106280</t>
+          <t>922525106282</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SANTHOSH D</t>
+          <t>SANTHOSH PRIYAN S</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>santhosh7811</t>
+          <t>SANTHOSH PRIYAN S</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1243,24 +1243,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh7811/</t>
+          <t>https://leetcode.com/u/SANTHOSH PRIYAN S/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>922525106282</t>
+          <t>922525106283</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SANTHOSH PRIYAN S</t>
+          <t>SANTHOSH S</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SANTHOSH PRIYAN S</t>
+          <t>SanthoshSathya260</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1270,24 +1270,24 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SANTHOSH PRIYAN S/</t>
+          <t>https://leetcode.com/u/SanthoshSathya260/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>922525106283</t>
+          <t>922525106284</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SANTHOSH S</t>
+          <t>Santhosh S</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SanthoshSathya260</t>
+          <t>santhosh2407</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1297,24 +1297,24 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SanthoshSathya260/</t>
+          <t>https://leetcode.com/u/santhosh2407/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>922525106284</t>
+          <t>922525106285</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Santhosh S</t>
+          <t>SANTHOSH V</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>santhosh2407</t>
+          <t>santhosh8760</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1324,24 +1324,24 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh2407/</t>
+          <t>https://leetcode.com/u/santhosh8760/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>922525106285</t>
+          <t>922525106286</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SANTHOSH V</t>
+          <t>SARAN K</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>santhosh8760</t>
+          <t>saran32</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1351,24 +1351,24 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh8760/</t>
+          <t>https://leetcode.com/u/saran32/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>922525106286</t>
+          <t>922525106287</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SARAN K</t>
+          <t>SARAVANAN K</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>saran32</t>
+          <t>saravanan .k</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1378,14 +1378,14 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saran32/</t>
+          <t>https://leetcode.com/u/saravanan .k/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>922525106287</t>
+          <t>922525106288</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>saravanan .k</t>
+          <t>saravanan__k__</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1405,24 +1405,24 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saravanan .k/</t>
+          <t>https://leetcode.com/u/saravanan__k__/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>922525106288</t>
+          <t>922525106289</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SARAVANAN K</t>
+          <t>SARAVANAN S</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>saravanan__k__</t>
+          <t>Saravanan_7525</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1432,24 +1432,24 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saravanan__k__/</t>
+          <t>https://leetcode.com/u/Saravanan_7525/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>922525106289</t>
+          <t>922525106290</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SARAVANAN S</t>
+          <t>SARIKA M P</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Saravanan_7525</t>
+          <t>sarika_5408</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1459,24 +1459,24 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Saravanan_7525/</t>
+          <t>https://leetcode.com/u/sarika_5408/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>922525106290</t>
+          <t>922525106291</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SARIKA M P</t>
+          <t>SARVESWARAN R</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>sarika_5408</t>
+          <t>sarvesh312008</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1486,24 +1486,24 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sarika_5408/</t>
+          <t>https://leetcode.com/u/sarvesh312008/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>922525106291</t>
+          <t>922525106292</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SARVESWARAN R</t>
+          <t>SASHMIKA.P</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>sarvesh312008</t>
+          <t>sashmikaprabhu</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1513,24 +1513,24 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sarvesh312008/</t>
+          <t>https://leetcode.com/u/sashmikaprabhu/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>922525106292</t>
+          <t>922525106296</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SASHMIKA.P</t>
+          <t>SELVAKUMAR K</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>sashmikaprabhu</t>
+          <t>Selvakumarsk-32</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1540,24 +1540,24 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sashmikaprabhu/</t>
+          <t>https://leetcode.com/u/Selvakumarsk-32/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>922525106296</t>
+          <t>922525106297</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SELVAKUMAR K</t>
+          <t>SELVAPRAGADEESH S</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Selvakumarsk-32</t>
+          <t>Selvapragadeesh</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1567,24 +1567,24 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvakumarsk-32/</t>
+          <t>https://leetcode.com/u/Selvapragadeesh/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>922525106297</t>
+          <t>922525106298</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SELVAPRAGADEESH S</t>
+          <t>SELVA RAGAVAN</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Selvapragadeesh</t>
+          <t>Selvax07</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1594,24 +1594,24 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvapragadeesh/</t>
+          <t>https://leetcode.com/u/Selvax07/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>922525106298</t>
+          <t>922525106299</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SELVA RAGAVAN</t>
+          <t>SENTHAMIZHSELVAN K</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Selvax07</t>
+          <t>Senthamizh08</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1621,24 +1621,24 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvax07/</t>
+          <t>https://leetcode.com/u/Senthamizh08/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>922525106299</t>
+          <t>922525106300</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SENTHAMIZHSELVAN K</t>
+          <t>Senthil.S</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Senthamizh08</t>
+          <t>Jna76WrjNd</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1648,24 +1648,24 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Senthamizh08/</t>
+          <t>https://leetcode.com/u/Jna76WrjNd/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>922525106300</t>
+          <t>922525106302</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Senthil.S</t>
+          <t>SHAHANA S</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Jna76WrjNd</t>
+          <t>shahana_pandiraj04</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1675,24 +1675,24 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Jna76WrjNd/</t>
+          <t>https://leetcode.com/u/shahana_pandiraj04/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>922525106302</t>
+          <t>922525106303</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SHAHANA S</t>
+          <t>SHANTHINI C</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>shahana_pandiraj04</t>
+          <t>ShanthiniChelladurai</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1702,24 +1702,24 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shahana_pandiraj04/</t>
+          <t>https://leetcode.com/u/ShanthiniChelladurai/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>922525106303</t>
+          <t>922525106305</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SHANTHINI C</t>
+          <t>SHARATH P</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ShanthiniChelladurai</t>
+          <t>sharath_1010</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1729,24 +1729,24 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/ShanthiniChelladurai/</t>
+          <t>https://leetcode.com/u/sharath_1010/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>922525106305</t>
+          <t>922525106307</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SHARATH P</t>
+          <t>SHIVANI B</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>sharath_1010</t>
+          <t>shivani208</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sharath_1010/</t>
+          <t>https://leetcode.com/u/shivani208/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>922525106307</t>
+          <t>922525106308</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SHIVANI B</t>
+          <t>SHREE HARINI L</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>shivani208</t>
+          <t>Shree_Harini478</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1783,24 +1783,24 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shivani208/</t>
+          <t>https://leetcode.com/u/Shree_Harini478/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>922525106308</t>
+          <t>922525106309</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SHREE HARINI L</t>
+          <t>SHREE CHARAN T</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Shree_Harini478</t>
+          <t>shreecharan22</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Shree_Harini478/</t>
+          <t>https://leetcode.com/u/shreecharan22/</t>
         </is>
       </c>
     </row>
@@ -1844,17 +1844,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>922525106370</t>
+          <t>922525106347</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>VISHNUHARAN V S</t>
+          <t>TAMIL SELVAN R</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Vishnuharan082007</t>
+          <t>Kdmif0HMNm</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1864,24 +1864,24 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vishnuharan082007/</t>
+          <t>https://leetcode.com/u/Kdmif0HMNm/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>922525106378</t>
+          <t>922525106373</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>YOKESWARAN S</t>
+          <t>YASHNI S</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>syokeswaran</t>
+          <t>Yashnisubramaniyan</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1891,24 +1891,24 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/syokeswaran/</t>
+          <t>https://leetcode.com/u/Yashnisubramaniyan/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>922525106377</t>
+          <t>922525106374</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>YAZHINI V</t>
+          <t>YASWANTH V</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>VISU_YAZHU</t>
+          <t>yaswanth_2008</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1918,24 +1918,24 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VISU_YAZHU/</t>
+          <t>https://leetcode.com/u/yaswanth_2008/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>922525106376</t>
+          <t>922525106375</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>YAZHINI S</t>
+          <t>YAZHINI M</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>yazhini__1234</t>
+          <t>yazhini2007</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1945,24 +1945,24 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yazhini__1234/</t>
+          <t>https://leetcode.com/u/yazhini2007/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>922525106375</t>
+          <t>922525106376</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>YAZHINI M</t>
+          <t>YAZHINI S</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>yazhini2007</t>
+          <t>yazhini__1234</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1972,24 +1972,24 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yazhini2007/</t>
+          <t>https://leetcode.com/u/yazhini__1234/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>922525106374</t>
+          <t>922525106377</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>YASWANTH V</t>
+          <t>YAZHINI V</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>yaswanth_2008</t>
+          <t>VISU_YAZHU</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1999,24 +1999,24 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yaswanth_2008/</t>
+          <t>https://leetcode.com/u/VISU_YAZHU/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>922525106373</t>
+          <t>922525106378</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>YASHNI S</t>
+          <t>YOKESWARAN S</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Yashnisubramaniyan</t>
+          <t>syokeswaran</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2026,24 +2026,24 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Yashnisubramaniyan/</t>
+          <t>https://leetcode.com/u/syokeswaran/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>922525106372</t>
+          <t>922525106346</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>VISHWAJETH A M</t>
+          <t>SWETHA E</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>vishwajeth</t>
+          <t>Swetha_20_1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2053,24 +2053,24 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vishwajeth/</t>
+          <t>https://leetcode.com/u/Swetha_20_1/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>922525106371</t>
+          <t>922525106316</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>VISHNUPRIYA S</t>
+          <t>SIVARANJAN M P</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>vishnupriyamaran</t>
+          <t>SIVARANJAN_MP</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2080,24 +2080,24 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vishnupriyamaran/</t>
+          <t>https://leetcode.com/u/SIVARANJAN_MP/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>922525106316</t>
+          <t>922525106317</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SIVARANJAN M P</t>
+          <t>SIVASANJEEV P</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SIVARANJAN_MP</t>
+          <t>Sivasanjeev16</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2107,24 +2107,24 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SIVARANJAN_MP/</t>
+          <t>https://leetcode.com/u/Sivasanjeev16/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>922525106317</t>
+          <t>922525106318</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SIVASANJEEV P</t>
+          <t>SIVASUBRAMANI A</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Sivasanjeev16</t>
+          <t>AK_Siva</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2134,24 +2134,24 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sivasanjeev16/</t>
+          <t>https://leetcode.com/u/AK_Siva/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>922525106318</t>
+          <t>922525106319</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SIVASUBRAMANI A</t>
+          <t>SIVATHARUN C</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AK_Siva</t>
+          <t>sivatharun22</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2161,24 +2161,24 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/AK_Siva/</t>
+          <t>https://leetcode.com/u/sivatharun22/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>922525106319</t>
+          <t>922525106320</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SIVATHARUN C</t>
+          <t>SOBIKA R</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>sivatharun22</t>
+          <t>_sobika_R</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2188,24 +2188,24 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivatharun22/</t>
+          <t>https://leetcode.com/u/_sobika_R/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>922525106320</t>
+          <t>922525106321</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SOBIKA R</t>
+          <t>SREE DHARANI C</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>_sobika_R</t>
+          <t>SREEDHARANI_14</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2215,24 +2215,24 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_sobika_R/</t>
+          <t>https://leetcode.com/u/SREEDHARANI_14/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>922525106321</t>
+          <t>922525106322</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SREE DHARANI C</t>
+          <t>SRI  T</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>SREEDHARANI_14</t>
+          <t>Sri1540</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2242,24 +2242,24 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SREEDHARANI_14/</t>
+          <t>https://leetcode.com/u/Sri1540/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>922525106322</t>
+          <t>922525106323</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SRI  T</t>
+          <t>SRI HEERA J</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Sri1540</t>
+          <t>sriheera03</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2269,24 +2269,24 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sri1540/</t>
+          <t>https://leetcode.com/u/sriheera03/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>922525106323</t>
+          <t>922525106324</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SRI HEERA J</t>
+          <t>SRI KANTH R</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>sriheera03</t>
+          <t>kanth2008</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2296,24 +2296,24 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sriheera03/</t>
+          <t>https://leetcode.com/u/kanth2008/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>922525106324</t>
+          <t>922525106325</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SRI KANTH R</t>
+          <t>SRI SASTIKA G</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>kanth2008</t>
+          <t>Srisastika_1401</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2323,24 +2323,24 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kanth2008/</t>
+          <t>https://leetcode.com/u/Srisastika_1401/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>922525106325</t>
+          <t>922525106326</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SRI SASTIKA G</t>
+          <t>SRI VARSHAN B P</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Srisastika_1401</t>
+          <t>srivarshan_B_P</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2350,24 +2350,24 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Srisastika_1401/</t>
+          <t>https://leetcode.com/u/srivarshan_B_P/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>922525106326</t>
+          <t>922525106327</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SRI VARSHAN B P</t>
+          <t>SRINATH V</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>srivarshan_B_P</t>
+          <t>V_SRINATH</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2377,24 +2377,24 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/srivarshan_B_P/</t>
+          <t>https://leetcode.com/u/V_SRINATH/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>922525106327</t>
+          <t>922525106328</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SRINATH V</t>
+          <t>SRINIRANJAN S</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>V_SRINATH</t>
+          <t>SRINIRANJAN2008</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2404,24 +2404,24 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/V_SRINATH/</t>
+          <t>https://leetcode.com/u/SRINIRANJAN2008/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>922525106328</t>
+          <t>922525106329</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SRINIRANJAN S</t>
+          <t>SRINITHE T</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>SRINIRANJAN2008</t>
+          <t>srinithe_1401</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2431,24 +2431,24 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SRINIRANJAN2008/</t>
+          <t>https://leetcode.com/u/srinithe_1401/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>922525106329</t>
+          <t>922525106330</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SRINITHE T</t>
+          <t>SRINITHI S</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>srinithe_1401</t>
+          <t>Srinithi24_</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2458,24 +2458,24 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/srinithe_1401/</t>
+          <t>https://leetcode.com/u/Srinithi24_/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>922525106330</t>
+          <t>922525106331</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SRINITHI S</t>
+          <t>SRISAMAYA R</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Srinithi24_</t>
+          <t>mahi</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2485,24 +2485,24 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Srinithi24_/</t>
+          <t>https://leetcode.com/u/mahi/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>922525106331</t>
+          <t>922525106332</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SRISAMAYA R</t>
+          <t>SUBARNA V</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>mahi</t>
+          <t>Subarna_17</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2512,24 +2512,24 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/mahi/</t>
+          <t>https://leetcode.com/u/Subarna_17/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>922525106332</t>
+          <t>922525106334</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SUBARNA V</t>
+          <t>SUBIKA T</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Subarna_17</t>
+          <t>subika1112</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2539,24 +2539,24 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Subarna_17/</t>
+          <t>https://leetcode.com/u/subika1112/</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>922525106334</t>
+          <t>922525106335</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SUBIKA T</t>
+          <t>SUDHARSAN S</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>subika1112</t>
+          <t>Sudharsan</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2566,24 +2566,24 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/subika1112/</t>
+          <t>https://leetcode.com/u/Sudharsan/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>922525106335</t>
+          <t>922525106336</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SUDHARSAN S</t>
+          <t>SUGANTHAN K</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Sudharsan</t>
+          <t>SUGANTHKALAI</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2593,24 +2593,24 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sudharsan/</t>
+          <t>https://leetcode.com/u/SUGANTHKALAI/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>922525106336</t>
+          <t>922525106337</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SUGANTHAN K</t>
+          <t>SUGIDHARSHINI T</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>SUGANTHKALAI</t>
+          <t>Sugi_07</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2620,24 +2620,24 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SUGANTHKALAI/</t>
+          <t>https://leetcode.com/u/Sugi_07/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>922525106337</t>
+          <t>922525106338</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SUGIDHARSHINI T</t>
+          <t>SUJEETH M</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Sugi_07</t>
+          <t>SUJEETH77</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2647,24 +2647,24 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sugi_07/</t>
+          <t>https://leetcode.com/u/SUJEETH77/</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>922525106338</t>
+          <t>922525106339</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SUJEETH M</t>
+          <t>SUJITH RAJA B</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>SUJEETH77</t>
+          <t>mahi20_</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2674,24 +2674,24 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SUJEETH77/</t>
+          <t>https://leetcode.com/u/mahi20_/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>922525106339</t>
+          <t>922525106340</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SUJITH RAJA B</t>
+          <t>SUMITHRA S</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>mahi20_</t>
+          <t>sumithra_16</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/mahi20_/</t>
+          <t>https://leetcode.com/u/sumithra_16/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>922525106340</t>
+          <t>922525106341</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SUMITHRA S</t>
+          <t>SURYA PRABHU S</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>sumithra_16</t>
+          <t>surya001prabhu</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2728,24 +2728,24 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sumithra_16/</t>
+          <t>https://leetcode.com/u/surya001prabhu/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>922525106341</t>
+          <t>922525106342</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SURYA PRABHU S</t>
+          <t>SUSIDHARAN M</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>surya001prabhu</t>
+          <t>Susidharan147</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2755,24 +2755,24 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/surya001prabhu/</t>
+          <t>https://leetcode.com/u/Susidharan147/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>922525106342</t>
+          <t>922525106343</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SUSIDHARAN M</t>
+          <t>SUTHARSHANA S</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Susidharan147</t>
+          <t>sutharshana743</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2782,24 +2782,24 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Susidharan147/</t>
+          <t>https://leetcode.com/u/sutharshana743/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>922525106343</t>
+          <t>922525106344</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SUTHARSHANA S</t>
+          <t>SWATHI M</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>sutharshana743</t>
+          <t>Swathimanivel_1234</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2809,24 +2809,24 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sutharshana743/</t>
+          <t>https://leetcode.com/u/Swathimanivel_1234/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>922525106344</t>
+          <t>922525106366</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SWATHI M</t>
+          <t>VIJAYARAGAVAN R</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Swathimanivel_1234</t>
+          <t>vijayaragavan1216</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2836,24 +2836,24 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Swathimanivel_1234/</t>
+          <t>https://leetcode.com/u/vijayaragavan1216/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>922525106365</t>
+          <t>922525106367</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>VIGNESHWAR U</t>
+          <t>VIKRAM V</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>VIGNESHWAR0221</t>
+          <t>vikramvicky5678</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2863,24 +2863,24 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VIGNESHWAR0221/</t>
+          <t>https://leetcode.com/u/vikramvicky5678/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>922525106366</t>
+          <t>922525106368</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>VIJAYARAGAVAN R</t>
+          <t>VISHNU B</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>vijayaragavan1216</t>
+          <t>VISHNU_B_2008</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2890,24 +2890,24 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vijayaragavan1216/</t>
+          <t>https://leetcode.com/u/VISHNU_B_2008/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>922525106367</t>
+          <t>922525106369</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>VIKRAM V</t>
+          <t>VISHNU PRIYAN S</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>vikramvicky5678</t>
+          <t>itz__priyan__</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2917,24 +2917,24 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vikramvicky5678/</t>
+          <t>https://leetcode.com/u/itz__priyan__/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>922525106368</t>
+          <t>922525106370</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>VISHNU B</t>
+          <t>VISHNUHARAN V S</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>VISHNU_B_2008</t>
+          <t>Vishnuharan082007</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2944,24 +2944,24 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VISHNU_B_2008/</t>
+          <t>https://leetcode.com/u/Vishnuharan082007/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>922525106369</t>
+          <t>922525106371</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>VISHNU PRIYAN S</t>
+          <t>VISHNUPRIYA S</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>itz__priyan__</t>
+          <t>vishnupriyamaran</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2971,24 +2971,24 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itz__priyan__/</t>
+          <t>https://leetcode.com/u/vishnupriyamaran/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>922525106346</t>
+          <t>922525106372</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SWETHA E</t>
+          <t>VISHWAJETH A M</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Swetha_20_1</t>
+          <t>vishwajeth</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2998,24 +2998,24 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Swetha_20_1/</t>
+          <t>https://leetcode.com/u/vishwajeth/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>922525106347</t>
+          <t>922525106348</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>TAMIL SELVAN R</t>
+          <t>THAMARAI SELVI D</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Kdmif0HMNm</t>
+          <t>thamarai_04</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3025,24 +3025,24 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Kdmif0HMNm/</t>
+          <t>https://leetcode.com/u/thamarai_04/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>922525106348</t>
+          <t>922525106349</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>THAMARAI SELVI D</t>
+          <t>THAMEEM FARSHITHA A</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>thamarai_04</t>
+          <t>Thameem_786</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3052,24 +3052,24 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/thamarai_04/</t>
+          <t>https://leetcode.com/u/Thameem_786/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>922525106349</t>
+          <t>922525106350</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>THAMEEM FARSHITHA A</t>
+          <t>THARANISH R</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Thameem_786</t>
+          <t>THARANISH2008</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3079,24 +3079,24 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Thameem_786/</t>
+          <t>https://leetcode.com/u/THARANISH2008/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>922525106350</t>
+          <t>922525106351</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>THARANISH R</t>
+          <t>THARUNIKA P</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>THARANISH2008</t>
+          <t>Tharunika_12</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3106,24 +3106,24 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/THARANISH2008/</t>
+          <t>https://leetcode.com/u/Tharunika_12/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>922525106351</t>
+          <t>922525106352</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>THARUNIKA P</t>
+          <t>THIRINESH KUMAR S</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Tharunika_12</t>
+          <t>THIRINESH KUMAR.S</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3133,24 +3133,24 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Tharunika_12/</t>
+          <t>https://leetcode.com/u/THIRINESH KUMAR.S/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>922525106352</t>
+          <t>922525106353</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>THIRINESH KUMAR S</t>
+          <t>THIRISHA C</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>THIRINESH KUMAR.S</t>
+          <t>thirishavsb</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3160,24 +3160,24 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/THIRINESH KUMAR.S/</t>
+          <t>https://leetcode.com/u/thirishavsb/</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>922525106353</t>
+          <t>922525106354</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>THIRISHA C</t>
+          <t>THIRUMURUGAN S</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>thirishavsb</t>
+          <t>thiru0211_</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3187,24 +3187,24 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/thirishavsb/</t>
+          <t>https://leetcode.com/u/thiru0211_/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>922525106354</t>
+          <t>922525106355</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>THIRUMURUGAN S</t>
+          <t>VAISHNAVI U</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>thiru0211_</t>
+          <t>vaish200</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3214,24 +3214,24 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/thiru0211_/</t>
+          <t>https://leetcode.com/u/vaish200/</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>922525106355</t>
+          <t>922525106356</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>VAISHNAVI U</t>
+          <t>VASANTH KUMAR C</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>vaish200</t>
+          <t>VASANTH2007</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3241,24 +3241,24 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vaish200/</t>
+          <t>https://leetcode.com/u/VASANTH2007/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>922525106356</t>
+          <t>922525106357</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>VASANTH KUMAR C</t>
+          <t>VASANTH S</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>VASANTH2007</t>
+          <t>_vasanth_s_</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3268,24 +3268,24 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VASANTH2007/</t>
+          <t>https://leetcode.com/u/_vasanth_s_/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>922525106357</t>
+          <t>922525106358</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>VASANTH S</t>
+          <t>VASANTHA KUMAR D</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>_vasanth_s_</t>
+          <t>Vasanthakumar12232</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3295,24 +3295,24 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_vasanth_s_/</t>
+          <t>https://leetcode.com/u/Vasanthakumar12232/</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>922525106358</t>
+          <t>922525106359</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>VASANTHA KUMAR D</t>
+          <t>VASANTHKUMAR R</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Vasanthakumar12232</t>
+          <t>VasanthKumar008</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3322,24 +3322,24 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vasanthakumar12232/</t>
+          <t>https://leetcode.com/u/VasanthKumar008/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>922525106359</t>
+          <t>922525106345</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>VASANTHKUMAR R</t>
+          <t>SWATHI S</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>VasanthKumar008</t>
+          <t>_swathi _3366</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3349,24 +3349,24 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VasanthKumar008/</t>
+          <t>https://leetcode.com/u/_swathi _3366/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>922525106345</t>
+          <t>922525106360</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SWATHI S</t>
+          <t>VASUDEVAN G</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>_swathi _3366</t>
+          <t>GTVASU2008</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3376,24 +3376,24 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_swathi _3366/</t>
+          <t>https://leetcode.com/u/GTVASU2008/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>922525106360</t>
+          <t>922525106361</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>VASUDEVAN G</t>
+          <t>VASUKI K</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>GTVASU2008</t>
+          <t>vasuki</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3403,24 +3403,24 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/GTVASU2008/</t>
+          <t>https://leetcode.com/u/vasuki/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>922525106361</t>
+          <t>922525106362</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>VASUKI K</t>
+          <t>VELLIANGIRI R</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>vasuki</t>
+          <t>velliangiri_R</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3430,24 +3430,24 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vasuki/</t>
+          <t>https://leetcode.com/u/velliangiri_R/</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>922525106362</t>
+          <t>922525106363</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>VELLIANGIRI R</t>
+          <t>VIGNESH M</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>velliangiri_R</t>
+          <t>O8bYDSRUbE</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -3457,24 +3457,24 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/velliangiri_R/</t>
+          <t>https://leetcode.com/u/O8bYDSRUbE/</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>922525106363</t>
+          <t>922525106364</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>VIGNESH M</t>
+          <t>VIGNESH VELAN M</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>O8bYDSRUbE</t>
+          <t>Vicky_27_Velan</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3484,24 +3484,24 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/O8bYDSRUbE/</t>
+          <t>https://leetcode.com/u/Vicky_27_Velan/</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>922525106364</t>
+          <t>922525106365</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>VIGNESH VELAN M</t>
+          <t>VIGNESHWAR U</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Vicky_27_Velan</t>
+          <t>VIGNESHWAR0221</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vicky_27_Velan/</t>
+          <t>https://leetcode.com/u/VIGNESHWAR0221/</t>
         </is>
       </c>
     </row>
@@ -3680,17 +3680,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>922525106094</t>
+          <t>922525106095</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>GOKUL D</t>
+          <t>GOMATHI R</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Gokul_tamilan_india</t>
+          <t>gomathi_0709</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -3700,24 +3700,24 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Gokul_tamilan_india/</t>
+          <t>https://leetcode.com/u/gomathi_0709/</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>922525106095</t>
+          <t>922525106099</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>GOMATHI R</t>
+          <t>GOVARTHAN K S</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>gomathi_0709</t>
+          <t>GOVARTHANKS</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3727,24 +3727,24 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/gomathi_0709/</t>
+          <t>https://leetcode.com/u/GOVARTHANKS/</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>922525106099</t>
+          <t>922525106105</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>GOVARTHAN K S</t>
+          <t>GOWTHAM S</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>GOVARTHANKS</t>
+          <t>Gowtham_080</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -3754,24 +3754,24 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/GOVARTHANKS/</t>
+          <t>https://leetcode.com/u/Gowtham_080/</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>922525106105</t>
+          <t>922525106107</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>GOWTHAM S</t>
+          <t>GUNA SHREE V</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Gowtham_080</t>
+          <t>Gunashree20</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -3781,24 +3781,24 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Gowtham_080/</t>
+          <t>https://leetcode.com/u/Gunashree20/</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>922525106107</t>
+          <t>922525106119</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>GUNA SHREE V</t>
+          <t>HAVISHMATHI S</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Gunashree20</t>
+          <t>HAVISHMATHIS</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -3808,213 +3808,213 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Gunashree20/</t>
+          <t>https://leetcode.com/u/HAVISHMATHIS/</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>922525106119</t>
+          <t>922525106040</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>HAVISHMATHI S</t>
+          <t>BHARANIDHARAN S</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>HAVISHMATHIS</t>
+          <t>Idvdnnsh577q</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>ECE B</t>
+          <t>ECE A</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/HAVISHMATHIS/</t>
+          <t>https://leetcode.com/u/Idvdnnsh577q/</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>922525106040</t>
+          <t>922525106200</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>BHARANIDHARAN S</t>
+          <t>MONISHA R</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Idvdnnsh577q</t>
+          <t>itsmoni</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE D</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Idvdnnsh577q/</t>
+          <t>https://leetcode.com/u/itsmoni/</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>922525106200</t>
+          <t>922525106167</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>MONISHA R</t>
+          <t>LAKSHETHA V</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>itsmoni</t>
+          <t>itz_lakshe</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE C</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itsmoni/</t>
+          <t>https://leetcode.com/u/itz_lakshe/</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>922525106167</t>
+          <t>922525106234</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>LAKSHETHA V</t>
+          <t>PRAVEENKUMAR R</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>itz_lakshe</t>
+          <t>itz_praveen_</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE D</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itz_lakshe/</t>
+          <t>https://leetcode.com/u/itz_praveen_/</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>922525106234</t>
+          <t>922525106154</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PRAVEENKUMAR R</t>
+          <t>KAVYA A</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>itz_praveen_</t>
+          <t>itzz__kavya02</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE C</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itz_praveen_/</t>
+          <t>https://leetcode.com/u/itzz__kavya02/</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>922525106154</t>
+          <t>922525106025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>KAVYA A</t>
+          <t>ARSATHA BEGAM M S</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>itzz__kavya02</t>
+          <t>jakabesj</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE A</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itzz__kavya02/</t>
+          <t>https://leetcode.com/u/jakabesj/</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>922525106025</t>
+          <t>922525106127</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>ARSATHA BEGAM M S</t>
+          <t>JANANI A</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>jakabesj</t>
+          <t>janani_asohkan</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE C</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/jakabesj/</t>
+          <t>https://leetcode.com/u/janani_asohkan/</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>922525106127</t>
+          <t>922525106128</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>JANANI A</t>
+          <t>JASHVANTH J S</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>janani_asohkan</t>
+          <t>jashvanth2007</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -4024,24 +4024,24 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/janani_asohkan/</t>
+          <t>https://leetcode.com/u/jashvanth2007/</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>922525106128</t>
+          <t>922525106129</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>JASHVANTH J S</t>
+          <t>JASVANTHRAM SP</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>jashvanth2007</t>
+          <t>jasvanthram</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -4051,24 +4051,24 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/jashvanth2007/</t>
+          <t>https://leetcode.com/u/jasvanthram/</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>922525106129</t>
+          <t>922525106130</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>JASVANTHRAM SP</t>
+          <t>JAYASAKTHI V</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>jasvanthram</t>
+          <t>jayasakthi_25</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -4078,24 +4078,24 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/jasvanthram/</t>
+          <t>https://leetcode.com/u/jayasakthi_25/</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>922525106130</t>
+          <t>922525106134</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>JAYASAKTHI V</t>
+          <t>JEEVANAA S</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>jayasakthi_25</t>
+          <t>jeevanaa_174_</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -4105,24 +4105,24 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/jayasakthi_25/</t>
+          <t>https://leetcode.com/u/jeevanaa_174_/</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>922525106134</t>
+          <t>922525106132</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>JEEVANAA S</t>
+          <t>Jeevan bala G</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>jeevanaa_174_</t>
+          <t>jeevanbala142008</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -4132,24 +4132,24 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/jeevanaa_174_/</t>
+          <t>https://leetcode.com/u/jeevanbala142008/</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>922525106132</t>
+          <t>922525106177</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Jeevan bala G</t>
+          <t>MADELIN JENITA M</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>jeevanbala142008</t>
+          <t>jenita0206</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -4159,24 +4159,24 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/jeevanbala142008/</t>
+          <t>https://leetcode.com/u/jenita0206/</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>922525106177</t>
+          <t>922525106135</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>MADELIN JENITA M</t>
+          <t>JERSHITH J S</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>jenita0206</t>
+          <t>Jerry2008</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -4186,24 +4186,24 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/jenita0206/</t>
+          <t>https://leetcode.com/u/Jerry2008/</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>922525106135</t>
+          <t>922525106136</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>JERSHITH J S</t>
+          <t>JOSHITHA KANNAN SUDHA</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Jerry2008</t>
+          <t>Joshi_666</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -4213,24 +4213,24 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Jerry2008/</t>
+          <t>https://leetcode.com/u/Joshi_666/</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>922525106136</t>
+          <t>922525106138</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>JOSHITHA KANNAN SUDHA</t>
+          <t>JOTHISHA K S</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Joshi_666</t>
+          <t>Jothi-</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -4240,24 +4240,24 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Joshi_666/</t>
+          <t>https://leetcode.com/u/Jothi-/</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>922525106138</t>
+          <t>922525106137</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>JOTHISHA K S</t>
+          <t>Jothi harshan D K</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Jothi-</t>
+          <t>Jothiharshan16</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -4267,24 +4267,24 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Jothi-/</t>
+          <t>https://leetcode.com/u/Jothiharshan16/</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>922525106137</t>
+          <t>922525106142</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Jothi harshan D K</t>
+          <t>KANITHRA R</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Jothiharshan16</t>
+          <t>kanithraakila</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -4294,24 +4294,24 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Jothiharshan16/</t>
+          <t>https://leetcode.com/u/kanithraakila/</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>922525106142</t>
+          <t>922525106143</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>KANITHRA R</t>
+          <t>KARISHMA M</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>kanithraakila</t>
+          <t>Karishma_m_08</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -4321,24 +4321,24 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kanithraakila/</t>
+          <t>https://leetcode.com/u/Karishma_m_08/</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>922525106143</t>
+          <t>922525106144</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>KARISHMA M</t>
+          <t>KARMUKILAN J</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Karishma_m_08</t>
+          <t>karmukilan567</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -4348,24 +4348,24 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Karishma_m_08/</t>
+          <t>https://leetcode.com/u/karmukilan567/</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>922525106144</t>
+          <t>922525106145</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>KARMUKILAN J</t>
+          <t>KARSHANA SRI V</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>karmukilan567</t>
+          <t>karshana_234</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -4375,24 +4375,24 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/karmukilan567/</t>
+          <t>https://leetcode.com/u/karshana_234/</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>922525106145</t>
+          <t>922525106146</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>KARSHANA SRI V</t>
+          <t>KARTHIKA K</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>karshana_234</t>
+          <t>Karthi270827</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -4402,24 +4402,24 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/karshana_234/</t>
+          <t>https://leetcode.com/u/Karthi270827/</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>922525106146</t>
+          <t>922525106147</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>KARTHIKA K</t>
+          <t>KATHIR E</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Karthi270827</t>
+          <t>kathir__21</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -4429,24 +4429,24 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Karthi270827/</t>
+          <t>https://leetcode.com/u/kathir__21/</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>922525106147</t>
+          <t>922525106152</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>KATHIR E</t>
+          <t>KAVIPRIYA R</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>kathir__21</t>
+          <t>KAVI_RAVI</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -4456,24 +4456,24 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kathir__21/</t>
+          <t>https://leetcode.com/u/KAVI_RAVI/</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>922525106152</t>
+          <t>922525106153</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>KAVIPRIYA R</t>
+          <t>KAVIYARASU K</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>KAVI_RAVI</t>
+          <t>kavi12d</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -4483,24 +4483,24 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/KAVI_RAVI/</t>
+          <t>https://leetcode.com/u/kavi12d/</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>922525106153</t>
+          <t>922525106148</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>KAVIYARASU K</t>
+          <t>KAVIMALAR A</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>kavi12d</t>
+          <t>kavimalar08</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -4510,24 +4510,24 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kavi12d/</t>
+          <t>https://leetcode.com/u/kavimalar08/</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>922525106148</t>
+          <t>922525106149</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>KAVIMALAR A</t>
+          <t>KAVIN KUMAR S</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>kavimalar08</t>
+          <t>KAVIN__26</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -4537,24 +4537,24 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kavimalar08/</t>
+          <t>https://leetcode.com/u/KAVIN__26/</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>922525106149</t>
+          <t>922525106150</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>KAVIN KUMAR S</t>
+          <t>KAVINKUMAR M</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>KAVIN__26</t>
+          <t>kavinleet</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -4564,24 +4564,24 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/KAVIN__26/</t>
+          <t>https://leetcode.com/u/kavinleet/</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>922525106150</t>
+          <t>922525106156</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>KAVINKUMAR M</t>
+          <t>KEERTHANA S</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>kavinleet</t>
+          <t>keerthana_19selvam</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kavinleet/</t>
+          <t>https://leetcode.com/u/keerthana_19selvam/</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>922525106156</t>
+          <t>922525106157</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>KEERTHANA S</t>
+          <t>KESAVINI M</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>keerthana_19selvam</t>
+          <t>KESAVINI892</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -4618,24 +4618,24 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/keerthana_19selvam/</t>
+          <t>https://leetcode.com/u/KESAVINI892/</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>922525106157</t>
+          <t>922525106158</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>KESAVINI M</t>
+          <t>KIRUTHIKA S</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>KESAVINI892</t>
+          <t>kiruthika_selvanathan05092007</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -4645,24 +4645,24 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/KESAVINI892/</t>
+          <t>https://leetcode.com/u/kiruthika_selvanathan05092007/</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>922525106158</t>
+          <t>922525106160</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>KIRUTHIKA S</t>
+          <t>KOHUL V</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>kiruthika_selvanathan05092007</t>
+          <t>kohul_v</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -4672,24 +4672,24 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kiruthika_selvanathan05092007/</t>
+          <t>https://leetcode.com/u/kohul_v/</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>922525106160</t>
+          <t>922525106162</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>KOHUL V</t>
+          <t>KOWSHIK R</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>kohul_v</t>
+          <t>kowshik_rk_</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -4699,24 +4699,24 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kohul_v/</t>
+          <t>https://leetcode.com/u/kowshik_rk_/</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>922525106162</t>
+          <t>922525106164</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>KOWSHIK R</t>
+          <t>KOWSHIKA M S</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>kowshik_rk_</t>
+          <t>kowshika_moorthi</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -4726,24 +4726,24 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kowshik_rk_/</t>
+          <t>https://leetcode.com/u/kowshika_moorthi/</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>922525106164</t>
+          <t>922525106163</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>KOWSHIKA M S</t>
+          <t>KOWSHIKA B</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>kowshika_moorthi</t>
+          <t>Kowshika08</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -4753,24 +4753,24 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kowshika_moorthi/</t>
+          <t>https://leetcode.com/u/Kowshika08/</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>922525106163</t>
+          <t>922525106165</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>KOWSHIKA B</t>
+          <t>KOWSHIKAN P</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Kowshika08</t>
+          <t>KOWSHIKAN-PALANISAMY</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -4780,24 +4780,24 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Kowshika08/</t>
+          <t>https://leetcode.com/u/KOWSHIKAN-PALANISAMY/</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>922525106165</t>
+          <t>922525106161</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>KOWSHIKAN P</t>
+          <t>KOWSHIK M</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>KOWSHIKAN-PALANISAMY</t>
+          <t>kowshikm23</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -4807,24 +4807,24 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/KOWSHIKAN-PALANISAMY/</t>
+          <t>https://leetcode.com/u/kowshikm23/</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>922525106161</t>
+          <t>922525106166</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>KOWSHIK M</t>
+          <t>KRISH R</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>kowshikm23</t>
+          <t>krish-2007</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -4834,24 +4834,24 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kowshikm23/</t>
+          <t>https://leetcode.com/u/krish-2007/</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>922525106166</t>
+          <t>922525106168</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>KRISH R</t>
+          <t>LAVANYA V</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>krish-2007</t>
+          <t>lavilavanya</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -4861,24 +4861,24 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/krish-2007/</t>
+          <t>https://leetcode.com/u/lavilavanya/</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>922525106168</t>
+          <t>922525106169</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>LAVANYA V</t>
+          <t>LINGESHWARAN K</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>lavilavanya</t>
+          <t>LING2007</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -4888,78 +4888,78 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/lavilavanya/</t>
+          <t>https://leetcode.com/u/LING2007/</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>922525106169</t>
+          <t>922525106210</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>LINGESHWARAN K</t>
+          <t>NAVANEETHAN L</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>LING2007</t>
+          <t>lnavaneethan08</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE D</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/LING2007/</t>
+          <t>https://leetcode.com/u/lnavaneethan08/</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>922525106210</t>
+          <t>922525106171</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>NAVANEETHAN L</t>
+          <t>LOGASRI.A</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>lnavaneethan08</t>
+          <t>Loga07</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE C</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/lnavaneethan08/</t>
+          <t>https://leetcode.com/u/Loga07/</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>922525106171</t>
+          <t>922525106172</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>LOGASRI.A</t>
+          <t>LOGAVARDHAN M</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Loga07</t>
+          <t>loga16</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -4969,24 +4969,24 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Loga07/</t>
+          <t>https://leetcode.com/u/loga16/</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>922525106172</t>
+          <t>922525106170</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>LOGAVARDHAN M</t>
+          <t>LOGADHARSHINI T</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>loga16</t>
+          <t>LogadharshiniT</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -4996,24 +4996,24 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/loga16/</t>
+          <t>https://leetcode.com/u/LogadharshiniT/</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>922525106170</t>
+          <t>922525106173</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>LOGADHARSHINI T</t>
+          <t>LOGESH H</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>LogadharshiniT</t>
+          <t>logesh2008</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -5023,24 +5023,24 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/LogadharshiniT/</t>
+          <t>https://leetcode.com/u/logesh2008/</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>922525106173</t>
+          <t>922525106174</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>LOGESH H</t>
+          <t>LOGESHWARAN K</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>logesh2008</t>
+          <t>LOGESHWARAN2008</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -5050,24 +5050,24 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/logesh2008/</t>
+          <t>https://leetcode.com/u/LOGESHWARAN2008/</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>922525106174</t>
+          <t>922525106175</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>LOGESHWARAN K</t>
+          <t>LOHITH RAJ S</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>LOGESHWARAN2008</t>
+          <t>LOHITH012008</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -5077,24 +5077,24 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/LOGESHWARAN2008/</t>
+          <t>https://leetcode.com/u/LOHITH012008/</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>922525106175</t>
+          <t>922525106176</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>LOHITH RAJ S</t>
+          <t>LOKRAJI R</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>LOHITH012008</t>
+          <t>LOKRAJI6793</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -5104,78 +5104,78 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/LOHITH012008/</t>
+          <t>https://leetcode.com/u/LOKRAJI6793/</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>922525106176</t>
+          <t>922525106191</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>LOKRAJI R</t>
+          <t>Manoj Kumar V</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>LOKRAJI6793</t>
+          <t>m____a____n____o____</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE D</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/LOKRAJI6793/</t>
+          <t>https://leetcode.com/u/m____a____n____o____/</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>922525106191</t>
+          <t>922525106179</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Manoj Kumar V</t>
+          <t>MADHANKUMAR S</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>m____a____n____o____</t>
+          <t>Madhankumar861053</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE C</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/m____a____n____o____/</t>
+          <t>https://leetcode.com/u/Madhankumar861053/</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>922525106179</t>
+          <t>922525106180</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>MADHANKUMAR S</t>
+          <t>MADHUDHARA P</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Madhankumar861053</t>
+          <t>madhudhara</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -5185,24 +5185,24 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Madhankumar861053/</t>
+          <t>https://leetcode.com/u/madhudhara/</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>922525106180</t>
+          <t>922525106181</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>MADHUDHARA P</t>
+          <t>MADHUMITHA B</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>madhudhara</t>
+          <t>Madhumitha42</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -5212,24 +5212,24 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/madhudhara/</t>
+          <t>https://leetcode.com/u/Madhumitha42/</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>922525106181</t>
+          <t>922525106182</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>MADHUMITHA B</t>
+          <t>Madhup Kishor G S</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Madhumitha42</t>
+          <t>Madhupkishor_20</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -5239,24 +5239,24 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Madhumitha42/</t>
+          <t>https://leetcode.com/u/Madhupkishor_20/</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>922525106182</t>
+          <t>922525106185</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Madhup Kishor G S</t>
+          <t>MAHALAKSHMI P</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Madhupkishor_20</t>
+          <t>maha_lakh_20</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -5266,24 +5266,24 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Madhupkishor_20/</t>
+          <t>https://leetcode.com/u/maha_lakh_20/</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>922525106185</t>
+          <t>922525106183</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>MAHALAKSHMI P</t>
+          <t>MAHALAKSHMI B</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>maha_lakh_20</t>
+          <t>mahalakshmi182025</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -5293,24 +5293,24 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/maha_lakh_20/</t>
+          <t>https://leetcode.com/u/mahalakshmi182025/</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>922525106183</t>
+          <t>922525106186</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>MAHALAKSHMI B</t>
+          <t>MAHIBALAN .A</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>mahalakshmi182025</t>
+          <t>mahi2</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -5320,24 +5320,24 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/mahalakshmi182025/</t>
+          <t>https://leetcode.com/u/mahi2/</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>922525106186</t>
+          <t>922525106187</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>MAHIBALAN .A</t>
+          <t>MAHIN ABHISHEK VH</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>mahi2</t>
+          <t>Mahinabhishek0411</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -5347,24 +5347,24 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/mahi2/</t>
+          <t>https://leetcode.com/u/Mahinabhishek0411/</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>922525106187</t>
+          <t>922525106189</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>MAHIN ABHISHEK VH</t>
+          <t>Manisha D</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Mahinabhishek0411</t>
+          <t>manishaa_20</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -5374,51 +5374,51 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Mahinabhishek0411/</t>
+          <t>https://leetcode.com/u/manishaa_20/</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>922525106189</t>
+          <t>922525106190</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Manisha D</t>
+          <t>MANOJ A</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>manishaa_20</t>
+          <t>Manoj_1319</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE D</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/manishaa_20/</t>
+          <t>https://leetcode.com/u/Manoj_1319/</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>922525106190</t>
+          <t>922525106193</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>MANOJ A</t>
+          <t>MATHESHKUMAR S</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Manoj_1319</t>
+          <t>mathesh25</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -5428,24 +5428,24 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Manoj_1319/</t>
+          <t>https://leetcode.com/u/mathesh25/</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>922525106193</t>
+          <t>922525106194</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>MATHESHKUMAR S</t>
+          <t>MAYAKANNAN K</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>mathesh25</t>
+          <t>Mayakannan129</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -5455,24 +5455,24 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/mathesh25/</t>
+          <t>https://leetcode.com/u/Mayakannan129/</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>922525106194</t>
+          <t>922525106195</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>MAYAKANNAN K</t>
+          <t>MAYUKA M</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Mayakannan129</t>
+          <t>Mayuka_M</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -5482,24 +5482,24 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Mayakannan129/</t>
+          <t>https://leetcode.com/u/Mayuka_M/</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>922525106195</t>
+          <t>922525106196</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>MAYUKA M</t>
+          <t>Milan D</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Mayuka_M</t>
+          <t>milan190308</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -5509,24 +5509,24 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Mayuka_M/</t>
+          <t>https://leetcode.com/u/milan190308/</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>922525106196</t>
+          <t>922525106201</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Milan D</t>
+          <t>MONISHA V</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>milan190308</t>
+          <t>Monishav2007</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/milan190308/</t>
+          <t>https://leetcode.com/u/Monishav2007/</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>922525106201</t>
+          <t>922525106202</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>MONISHA V</t>
+          <t>Morrish D</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Monishav2007</t>
+          <t>morrishd</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -5563,24 +5563,24 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Monishav2007/</t>
+          <t>https://leetcode.com/u/morrishd/</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>922525106202</t>
+          <t>922525106203</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Morrish D</t>
+          <t>MOULEESHWARI B</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>morrishd</t>
+          <t>Mouleeshwari2008</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -5590,24 +5590,24 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/morrishd/</t>
+          <t>https://leetcode.com/u/Mouleeshwari2008/</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>922525106203</t>
+          <t>922525106204</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>MOULEESHWARI B</t>
+          <t>MOUSHMI P N</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Mouleeshwari2008</t>
+          <t>Moushmi_20</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -5617,24 +5617,24 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Mouleeshwari2008/</t>
+          <t>https://leetcode.com/u/Moushmi_20/</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>922525106204</t>
+          <t>922525106205</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>MOUSHMI P N</t>
+          <t>MYTHILI M</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Moushmi_20</t>
+          <t>mythilimurugesan</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -5644,24 +5644,24 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Moushmi_20/</t>
+          <t>https://leetcode.com/u/mythilimurugesan/</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>922525106205</t>
+          <t>922525106206</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>MYTHILI M</t>
+          <t>NAFREEN J M</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>mythilimurugesan</t>
+          <t>NafreenJohnbasha</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -5671,24 +5671,24 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/mythilimurugesan/</t>
+          <t>https://leetcode.com/u/NafreenJohnbasha/</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>922525106206</t>
+          <t>922525106208</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>NAFREEN J M</t>
+          <t>NANDHINI D</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>NafreenJohnbasha</t>
+          <t>nandhini546</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -5698,24 +5698,24 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/NafreenJohnbasha/</t>
+          <t>https://leetcode.com/u/nandhini546/</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>922525106208</t>
+          <t>922525106211</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>NANDHINI D</t>
+          <t>Naveetha N</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>nandhini546</t>
+          <t>NAVEETHAN</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -5725,24 +5725,24 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/nandhini546/</t>
+          <t>https://leetcode.com/u/NAVEETHAN/</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>922525106211</t>
+          <t>922525106213</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Naveetha N</t>
+          <t>NIRANJANI D</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>NAVEETHAN</t>
+          <t>niranjani_123</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -5752,24 +5752,24 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/NAVEETHAN/</t>
+          <t>https://leetcode.com/u/niranjani_123/</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>922525106213</t>
+          <t>922525106215</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>NIRANJANI D</t>
+          <t>NITHISH P</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>niranjani_123</t>
+          <t>Nithish_P_CS</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -5779,24 +5779,24 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/niranjani_123/</t>
+          <t>https://leetcode.com/u/Nithish_P_CS/</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>922525106215</t>
+          <t>922525106214</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>NITHISH P</t>
+          <t>NITHISH C T</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Nithish_P_CS</t>
+          <t>Nithishct123</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -5806,24 +5806,24 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Nithish_P_CS/</t>
+          <t>https://leetcode.com/u/Nithishct123/</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>922525106214</t>
+          <t>922525106216</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>NITHISH C T</t>
+          <t>Nithish R</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Nithishct123</t>
+          <t>nithishramalingam007</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -5833,24 +5833,24 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Nithishct123/</t>
+          <t>https://leetcode.com/u/nithishramalingam007/</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>922525106216</t>
+          <t>922525106217</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Nithish R</t>
+          <t>NITHISHWARAN D</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>nithishramalingam007</t>
+          <t>nithishwaran25</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -5860,24 +5860,24 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/nithishramalingam007/</t>
+          <t>https://leetcode.com/u/nithishwaran25/</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>922525106217</t>
+          <t>922525106219</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>NITHISHWARAN D</t>
+          <t>NITHYASHREE P</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>nithishwaran25</t>
+          <t>Nithyashree273</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -5887,24 +5887,24 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/nithishwaran25/</t>
+          <t>https://leetcode.com/u/Nithyashree273/</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>922525106219</t>
+          <t>922525106218</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>NITHYASHREE P</t>
+          <t>NITHYASHREE G</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Nithyashree273</t>
+          <t>NithyashreeG10</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -5914,24 +5914,24 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Nithyashree273/</t>
+          <t>https://leetcode.com/u/NithyashreeG10/</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>922525106218</t>
+          <t>922525106220</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>NITHYASHREE G</t>
+          <t>NITHYASRI M</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>NithyashreeG10</t>
+          <t>Nithyasri2008</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -5941,24 +5941,24 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/NithyashreeG10/</t>
+          <t>https://leetcode.com/u/Nithyasri2008/</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>922525106220</t>
+          <t>922525106222</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>NITHYASRI M</t>
+          <t>PAARGAVI R</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Nithyasri2008</t>
+          <t>paargavi2007</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -5968,24 +5968,24 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Nithyasri2008/</t>
+          <t>https://leetcode.com/u/paargavi2007/</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>922525106222</t>
+          <t>922525106223</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>PAARGAVI R</t>
+          <t>PAVITHRA S</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>paargavi2007</t>
+          <t>pavithra145</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -5995,24 +5995,24 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/paargavi2007/</t>
+          <t>https://leetcode.com/u/pavithra145/</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>922525106223</t>
+          <t>922525106224</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>PAVITHRA S</t>
+          <t>PAVITHRAN S</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>pavithra145</t>
+          <t>Pavithran_S_</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -6022,24 +6022,24 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/pavithra145/</t>
+          <t>https://leetcode.com/u/Pavithran_S_/</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>922525106224</t>
+          <t>922525106225</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>PAVITHRAN S</t>
+          <t>PIRAVEEN M</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Pavithran_S_</t>
+          <t>Piraveen2025</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -6049,24 +6049,24 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Pavithran_S_/</t>
+          <t>https://leetcode.com/u/Piraveen2025/</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>922525106225</t>
+          <t>922525106227</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>PIRAVEEN M</t>
+          <t>PRADHOSH T</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Piraveen2025</t>
+          <t>pradhosh</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -6076,24 +6076,24 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Piraveen2025/</t>
+          <t>https://leetcode.com/u/pradhosh/</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>922525106227</t>
+          <t>922525106228</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>PRADHOSH T</t>
+          <t>PRAGALATHAN T</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>pradhosh</t>
+          <t>pragalathan070108</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -6103,24 +6103,24 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/pradhosh/</t>
+          <t>https://leetcode.com/u/pragalathan070108/</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>922525106228</t>
+          <t>922525106229</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>PRAGALATHAN T</t>
+          <t>PRANESH Y</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>pragalathan070108</t>
+          <t>Pranesh-Y</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -6130,24 +6130,24 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/pragalathan070108/</t>
+          <t>https://leetcode.com/u/Pranesh-Y/</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>922525106229</t>
+          <t>922525106230</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>PRANESH Y</t>
+          <t>PRANITHASREE SAMINATHAN</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Pranesh-Y</t>
+          <t>pranithaashree</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -6157,24 +6157,24 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Pranesh-Y/</t>
+          <t>https://leetcode.com/u/pranithaashree/</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>922525106230</t>
+          <t>922525106232</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>PRANITHASREE SAMINATHAN</t>
+          <t>PRAVEEN G</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>pranithaashree</t>
+          <t>praveen_3208</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -6184,24 +6184,24 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/pranithaashree/</t>
+          <t>https://leetcode.com/u/praveen_3208/</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>922525106232</t>
+          <t>922525106231</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>PRAVEEN G</t>
+          <t>PRAVEEN D</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>praveen_3208</t>
+          <t>praveen1247</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -6211,24 +6211,24 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/praveen_3208/</t>
+          <t>https://leetcode.com/u/praveen1247/</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>922525106231</t>
+          <t>922525106233</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>PRAVEEN D</t>
+          <t>PRAVEEN G</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>praveen1247</t>
+          <t>PRAVEENGANESAN</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -6238,24 +6238,24 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/praveen1247/</t>
+          <t>https://leetcode.com/u/PRAVEENGANESAN/</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>922525106233</t>
+          <t>922525106235</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>PRAVEEN G</t>
+          <t>PREETHY M S</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>PRAVEENGANESAN</t>
+          <t>preethy2007</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -6265,78 +6265,78 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/PRAVEENGANESAN/</t>
+          <t>https://leetcode.com/u/preethy2007/</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>922525106235</t>
+          <t>922525106086</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>PREETHY M S</t>
+          <t>DIVYA V</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>preethy2007</t>
+          <t>princess-nk</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE B</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/preethy2007/</t>
+          <t>https://leetcode.com/u/princess-nk/</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>922525106086</t>
+          <t>922525106236</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>DIVYA V</t>
+          <t>PRITHIV S</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>princess-nk</t>
+          <t>prithiv16</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>ECE B</t>
+          <t>ECE D</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/princess-nk/</t>
+          <t>https://leetcode.com/u/prithiv16/</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>922525106236</t>
+          <t>922525106237</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>PRITHIV S</t>
+          <t>PRIYADHARSHINI V</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>prithiv16</t>
+          <t>priyadharshini1551</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -6346,24 +6346,24 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/prithiv16/</t>
+          <t>https://leetcode.com/u/priyadharshini1551/</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>922525106237</t>
+          <t>922525106238</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>PRIYADHARSHINI V</t>
+          <t>PRIYANKA A</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>priyadharshini1551</t>
+          <t>Priyankaashok1201</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -6373,24 +6373,24 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/priyadharshini1551/</t>
+          <t>https://leetcode.com/u/Priyankaashok1201/</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>922525106238</t>
+          <t>922525106239</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>PRIYANKA A</t>
+          <t>PRIYANKA K R</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Priyankaashok1201</t>
+          <t>priyankadhanush23</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -6400,24 +6400,24 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Priyankaashok1201/</t>
+          <t>https://leetcode.com/u/priyankadhanush23/</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>922525106239</t>
+          <t>922525106240</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>PRIYANKA K R</t>
+          <t>RAGADHARSHINI S</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>priyankadhanush23</t>
+          <t>Ragadharshini_2181</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -6427,24 +6427,24 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/priyankadhanush23/</t>
+          <t>https://leetcode.com/u/Ragadharshini_2181/</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>922525106240</t>
+          <t>922525106241</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>RAGADHARSHINI S</t>
+          <t>RAGUNATH M</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Ragadharshini_2181</t>
+          <t>ragunath24</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -6454,24 +6454,24 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Ragadharshini_2181/</t>
+          <t>https://leetcode.com/u/ragunath24/</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>922525106241</t>
+          <t>922525106242</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>RAGUNATH M</t>
+          <t>RAHULKAJAN M</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>ragunath24</t>
+          <t>rahulkajan</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -6481,24 +6481,24 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/ragunath24/</t>
+          <t>https://leetcode.com/u/rahulkajan/</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>922525106242</t>
+          <t>922525106243</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>RAHULKAJAN M</t>
+          <t>RAJAPRAGADEESWARAN R</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>rahulkajan</t>
+          <t>rajaprahadeeswaran</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -6508,24 +6508,24 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/rahulkajan/</t>
+          <t>https://leetcode.com/u/rajaprahadeeswaran/</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>922525106243</t>
+          <t>922525106244</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>RAJAPRAGADEESWARAN R</t>
+          <t>RANJANA T</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>rajaprahadeeswaran</t>
+          <t>RANJANA_2007</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -6535,24 +6535,24 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/rajaprahadeeswaran/</t>
+          <t>https://leetcode.com/u/RANJANA_2007/</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>922525106244</t>
+          <t>922525106246</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>RANJANA T</t>
+          <t>RASIKA S</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>RANJANA_2007</t>
+          <t>RASIKA_2008</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -6562,24 +6562,24 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/RANJANA_2007/</t>
+          <t>https://leetcode.com/u/RASIKA_2008/</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>922525106246</t>
+          <t>922525106247</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>RASIKA S</t>
+          <t>RATHISH R</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>RASIKA_2008</t>
+          <t>Rathish2025</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -6589,24 +6589,24 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/RASIKA_2008/</t>
+          <t>https://leetcode.com/u/Rathish2025/</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>922525106247</t>
+          <t>922525106248</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>RATHISH R</t>
+          <t>RAVIKUMAR S</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Rathish2025</t>
+          <t>Ravikumar_14</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -6616,24 +6616,24 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rathish2025/</t>
+          <t>https://leetcode.com/u/Ravikumar_14/</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>922525106248</t>
+          <t>922525106249</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>RAVIKUMAR S</t>
+          <t>RENOFIYA HASIN A</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Ravikumar_14</t>
+          <t>Renofiya-2007</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -6643,24 +6643,24 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Ravikumar_14/</t>
+          <t>https://leetcode.com/u/Renofiya-2007/</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>922525106249</t>
+          <t>922525106250</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>RENOFIYA HASIN A</t>
+          <t>RESMHI S</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Renofiya-2007</t>
+          <t>reshmi2008</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -6670,24 +6670,24 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Renofiya-2007/</t>
+          <t>https://leetcode.com/u/reshmi2008/</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>922525106250</t>
+          <t>922525106251</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>RESMHI S</t>
+          <t>RETHANYA S</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>reshmi2008</t>
+          <t>rethanya38</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -6697,24 +6697,24 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/reshmi2008/</t>
+          <t>https://leetcode.com/u/rethanya38/</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>922525106251</t>
+          <t>922525106252</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>RETHANYA S</t>
+          <t>RETHISH</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>rethanya38</t>
+          <t>Rethish_R</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -6724,78 +6724,78 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/rethanya38/</t>
+          <t>https://leetcode.com/u/Rethish_R/</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>922525106252</t>
+          <t>922525106026</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>RETHISH</t>
+          <t>ARUL S.T.</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Rethish_R</t>
+          <t>S_T_Arul</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE A</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rethish_R/</t>
+          <t>https://leetcode.com/u/S_T_Arul/</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>922525106026</t>
+          <t>922525106199</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>ARUL S.T.</t>
+          <t>MONISH S</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>S_T_Arul</t>
+          <t>smonish777</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE D</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/S_T_Arul/</t>
+          <t>https://leetcode.com/u/smonish777/</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>922525106199</t>
+          <t>922525106198</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>MONISH S</t>
+          <t>MOHAMMED ABUTHARIK S</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>smonish777</t>
+          <t>tharik25</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -6805,61 +6805,61 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/smonish777/</t>
+          <t>https://leetcode.com/u/tharik25/</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>922525106198</t>
+          <t>922525106010</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>MOHAMMED ABUTHARIK S</t>
+          <t>AJAIRAJAN SR</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>tharik25</t>
+          <t>UJw4zUNnJJ</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE A</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/tharik25/</t>
+          <t>https://leetcode.com/u/UJw4zUNnJJ/</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>922525106010</t>
+          <t>922525106076</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>AJAIRAJAN SR</t>
+          <t>DHARSINI V S</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>UJw4zUNnJJ</t>
+          <t>vsdharsini</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE B</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/UJw4zUNnJJ/</t>
+          <t>https://leetcode.com/u/vsdharsini/</t>
         </is>
       </c>
     </row>
@@ -6893,27 +6893,27 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>922525106076</t>
+          <t>922525106005</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>DHARSINI V S</t>
+          <t>ADHITHMITHRAN P</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>vsdharsini</t>
+          <t>ADHITHMITHRAN</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>ECE B</t>
+          <t>ECE A</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vsdharsini/</t>
+          <t>https://leetcode.com/u/ADHITHMITHRAN/</t>
         </is>
       </c>
     </row>
@@ -8675,17 +8675,17 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>922525106005</t>
+          <t>922525106001</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>ADHITHMITHRAN P</t>
+          <t>AASHIFA SAHANAJ M</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>aashifasahanaj</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -8695,24 +8695,24 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/A/</t>
+          <t>https://leetcode.com/u/aashifasahanaj/</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>922525106001</t>
+          <t>922525106002</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>AASHIFA SAHANAJ M</t>
+          <t>AAZHIGA N</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>aashifasahanaj</t>
+          <t>AAZHIGA</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -8722,24 +8722,24 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/aashifasahanaj/</t>
+          <t>https://leetcode.com/u/AAZHIGA/</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>922525106002</t>
+          <t>922525106003</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>AAZHIGA N</t>
+          <t>ABINAYA N</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>AAZHIGA</t>
+          <t>Abinaya7095</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -8749,24 +8749,24 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/AAZHIGA/</t>
+          <t>https://leetcode.com/u/Abinaya7095/</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>922525106003</t>
+          <t>922525106004</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>ABINAYA N</t>
+          <t>Abirami R</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Abinaya7095</t>
+          <t>abirami8072</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -8776,24 +8776,24 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Abinaya7095/</t>
+          <t>https://leetcode.com/u/abirami8072/</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>922525106004</t>
+          <t>922525106006</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Abirami R</t>
+          <t>AFTON AJ</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>abirami8072</t>
+          <t>afton_2008</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -8803,24 +8803,24 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/abirami8072/</t>
+          <t>https://leetcode.com/u/afton_2008/</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>922525106006</t>
+          <t>922525106007</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>AFTON AJ</t>
+          <t>AGATHEESWARAN K</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>afton_2008</t>
+          <t>agatheeswarank</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -8830,24 +8830,24 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/afton_2008/</t>
+          <t>https://leetcode.com/u/agatheeswarank/</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>922525106007</t>
+          <t>922525106028</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>AGATHEESWARAN K</t>
+          <t>ARUN C</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>agatheeswarank</t>
+          <t>AGmXRQ1yTe</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -8857,24 +8857,24 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/agatheeswarank/</t>
+          <t>https://leetcode.com/u/AGmXRQ1yTe/</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>922525106028</t>
+          <t>922525106012</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>ARUN C</t>
+          <t>AJAYKUMAR A L</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>AGmXRQ1yTe</t>
+          <t>AjaykumarAL</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -8884,24 +8884,24 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/AGmXRQ1yTe/</t>
+          <t>https://leetcode.com/u/AjaykumarAL/</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>922525106012</t>
+          <t>922525106013</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>AJAYKUMAR A L</t>
+          <t>AJITH KUMAR M</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>AjaykumarAL</t>
+          <t>ajit_kumar_23</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -8911,24 +8911,24 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/AjaykumarAL/</t>
+          <t>https://leetcode.com/u/ajit_kumar_23/</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>922525106013</t>
+          <t>922525106014</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>AJITH KUMAR M</t>
+          <t>Akash.R</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>ajit_kumar_23</t>
+          <t>AkashRajaram</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -8938,24 +8938,24 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/ajit_kumar_23/</t>
+          <t>https://leetcode.com/u/AkashRajaram/</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>922525106014</t>
+          <t>922525106015</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Akash.R</t>
+          <t>Akshara KR</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>AkashRajaram</t>
+          <t>Akshara015</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -8965,24 +8965,24 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/AkashRajaram/</t>
+          <t>https://leetcode.com/u/Akshara015/</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>922525106015</t>
+          <t>922525106017</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Akshara KR</t>
+          <t>ALAGESHWARAN J</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Akshara015</t>
+          <t>Alageshwaran2008</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -8992,24 +8992,24 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Akshara015/</t>
+          <t>https://leetcode.com/u/Alageshwaran2008/</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>922525106017</t>
+          <t>922525106018</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>ALAGESHWARAN J</t>
+          <t>Amirdavarsini K S</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Alageshwaran2008</t>
+          <t>amirda_varsini_2007</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -9019,24 +9019,24 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Alageshwaran2008/</t>
+          <t>https://leetcode.com/u/amirda_varsini_2007/</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>922525106018</t>
+          <t>922525106019</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Amirdavarsini K S</t>
+          <t>ANBARASU S</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>amirda_varsini_2007</t>
+          <t>Anbarasu28122007</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -9046,24 +9046,24 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/amirda_varsini_2007/</t>
+          <t>https://leetcode.com/u/Anbarasu28122007/</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>922525106019</t>
+          <t>922525106020</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>ANBARASU S</t>
+          <t>ANJITHAA N</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Anbarasu28122007</t>
+          <t>Anjithaa2006</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -9073,24 +9073,24 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Anbarasu28122007/</t>
+          <t>https://leetcode.com/u/Anjithaa2006/</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>922525106020</t>
+          <t>922525106021</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>ANJITHAA N</t>
+          <t>ANOOP C</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Anjithaa2006</t>
+          <t>anoop_appuz</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -9100,24 +9100,24 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Anjithaa2006/</t>
+          <t>https://leetcode.com/u/anoop_appuz/</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>922525106021</t>
+          <t>922525106022</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>ANOOP C</t>
+          <t>ANUJA S</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>anoop_appuz</t>
+          <t>anuja008</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -9127,24 +9127,24 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/anoop_appuz/</t>
+          <t>https://leetcode.com/u/anuja008/</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>922525106022</t>
+          <t>922525106023</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>ANUJA S</t>
+          <t>ANUSRI R</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>anuja008</t>
+          <t>Anusri_2008</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -9154,24 +9154,24 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/anuja008/</t>
+          <t>https://leetcode.com/u/Anusri_2008/</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>922525106023</t>
+          <t>922525106024</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>ANUSRI R</t>
+          <t>ANUSYA B</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Anusri_2008</t>
+          <t>ANUSYA_30</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -9181,24 +9181,24 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Anusri_2008/</t>
+          <t>https://leetcode.com/u/ANUSYA_30/</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>922525106024</t>
+          <t>922525106027</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>ANUSYA B</t>
+          <t>Arulesh K</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>ANUSYA_30</t>
+          <t>arul2008</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -9208,24 +9208,24 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/ANUSYA_30/</t>
+          <t>https://leetcode.com/u/arul2008/</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>922525106027</t>
+          <t>922525106030</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Arulesh K</t>
+          <t>ARUNKUMAR K</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>arul2008</t>
+          <t>Arunkumar2008</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -9235,24 +9235,24 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/arul2008/</t>
+          <t>https://leetcode.com/u/Arunkumar2008/</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>922525106030</t>
+          <t>922525106031</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>ARUNKUMAR K</t>
+          <t>ARUNPRASANTH T</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Arunkumar2008</t>
+          <t>arunprasanth6435</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -9262,24 +9262,24 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Arunkumar2008/</t>
+          <t>https://leetcode.com/u/arunprasanth6435/</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>922525106031</t>
+          <t>922525106029</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>ARUNPRASANTH T</t>
+          <t>R ARUN PRASATH</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>arunprasanth6435</t>
+          <t>Arunravi1810</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -9289,24 +9289,24 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/arunprasanth6435/</t>
+          <t>https://leetcode.com/u/Arunravi1810/</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>922525106029</t>
+          <t>922525106032</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>R ARUN PRASATH</t>
+          <t>ARVIN SHANKARA</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Arunravi1810</t>
+          <t>Arvin</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -9316,24 +9316,24 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Arunravi1810/</t>
+          <t>https://leetcode.com/u/Arvin/</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>922525106032</t>
+          <t>922525106033</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>ARVIN SHANKARA</t>
+          <t>ASHOK KUMAR P</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Arvin</t>
+          <t>ASHOKKUMAR18</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -9343,24 +9343,24 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Arvin/</t>
+          <t>https://leetcode.com/u/ASHOKKUMAR18/</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>922525106033</t>
+          <t>922525106008</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>ASHOK KUMAR P</t>
+          <t>AHELESH G S</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>ASHOKKUMAR18</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -9370,24 +9370,24 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/ASHOKKUMAR18/</t>
+          <t>https://leetcode.com/u/B/</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>922525106008</t>
+          <t>922525106037</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>AHELESH G S</t>
+          <t>BARANITHARAN V</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>barani_7</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -9397,24 +9397,24 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/B/</t>
+          <t>https://leetcode.com/u/barani_7/</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>922525106037</t>
+          <t>922525106039</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>BARANITHARAN V</t>
+          <t>BENOV NAVIN V</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>barani_7</t>
+          <t>Benov_18</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -9424,24 +9424,24 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/barani_7/</t>
+          <t>https://leetcode.com/u/Benov_18/</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>922525106039</t>
+          <t>922525106042</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>BENOV NAVIN V</t>
+          <t>BHARATHWAJ S</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Benov_18</t>
+          <t>BharathwajX</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -9451,24 +9451,24 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Benov_18/</t>
+          <t>https://leetcode.com/u/BharathwajX/</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>922525106042</t>
+          <t>922525106044</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>BHARATHWAJ S</t>
+          <t>Bhavan bala N</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>BharathwajX</t>
+          <t>BhavanBala</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -9478,24 +9478,24 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/BharathwajX/</t>
+          <t>https://leetcode.com/u/BhavanBala/</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>922525106044</t>
+          <t>922525106041</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Bhavan bala N</t>
+          <t>BHARATH KUMAR E</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>BhavanBala</t>
+          <t>BK5226221</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -9505,24 +9505,24 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/BhavanBala/</t>
+          <t>https://leetcode.com/u/BK5226221/</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>922525106041</t>
+          <t>922525106045</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>BHARATH KUMAR E</t>
+          <t>BOOBASE R</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>BK5226221</t>
+          <t>Boobase</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -9532,24 +9532,24 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/BK5226221/</t>
+          <t>https://leetcode.com/u/Boobase/</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>922525106045</t>
+          <t>922525106046</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>BOOBASE R</t>
+          <t>BOOMIKA T</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Boobase</t>
+          <t>boomikat123</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -9559,24 +9559,24 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Boobase/</t>
+          <t>https://leetcode.com/u/boomikat123/</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>922525106046</t>
+          <t>922525106047</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>BOOMIKA T</t>
+          <t>BOSVIYA P</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>boomikat123</t>
+          <t>BosviyaBSV</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -9586,24 +9586,24 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/boomikat123/</t>
+          <t>https://leetcode.com/u/BosviyaBSV/</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>922525106047</t>
+          <t>922525106048</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>BOSVIYA P</t>
+          <t>BRINDHA S</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>BosviyaBSV</t>
+          <t>Brindha_S</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -9613,24 +9613,24 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/BosviyaBSV/</t>
+          <t>https://leetcode.com/u/Brindha_S/</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>922525106048</t>
+          <t>922525106050</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>BRINDHA S</t>
+          <t>CHARUDESNA S</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Brindha_S</t>
+          <t>charu120108</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -9640,24 +9640,24 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Brindha_S/</t>
+          <t>https://leetcode.com/u/charu120108/</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>922525106050</t>
+          <t>922525106051</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>CHARUDESNA S</t>
+          <t>CHARUNETHRA S</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>charu120108</t>
+          <t>charunethra07</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -9667,24 +9667,24 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/charu120108/</t>
+          <t>https://leetcode.com/u/charunethra07/</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>922525106051</t>
+          <t>922525106053</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>CHARUNETHRA S</t>
+          <t>CHINNAPPAN S</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>charunethra07</t>
+          <t>chinnappanrajniselvi</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -9694,24 +9694,24 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/charunethra07/</t>
+          <t>https://leetcode.com/u/chinnappanrajniselvi/</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>922525106053</t>
+          <t>922525106009</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>CHINNAPPAN S</t>
+          <t>AISHWARYA G</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>chinnappanrajniselvi</t>
+          <t>codewithaish</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -9721,24 +9721,24 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/chinnappanrajniselvi/</t>
+          <t>https://leetcode.com/u/codewithaish/</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>922525106009</t>
+          <t>922525106038</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>AISHWARYA G</t>
+          <t>BAVITHA T</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>codewithaish</t>
+          <t>codewithakshaya</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -9748,24 +9748,24 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/codewithaish/</t>
+          <t>https://leetcode.com/u/codewithakshaya/</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>922525106038</t>
+          <t>922525106016</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>BAVITHA T</t>
+          <t>AKSHAYA S</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>codewithakshaya</t>
+          <t>codewithakshaya78</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -9775,24 +9775,24 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/codewithakshaya/</t>
+          <t>https://leetcode.com/u/codewithakshaya78/</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>922525106016</t>
+          <t>922525106054</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>AKSHAYA S</t>
+          <t>DAKSHINYA R</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>codewithakshaya78</t>
+          <t>Dakshinya555</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -9802,24 +9802,24 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/codewithakshaya78/</t>
+          <t>https://leetcode.com/u/Dakshinya555/</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>922525106054</t>
+          <t>922525106057</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>DAKSHINYA R</t>
+          <t>DARSHAN V V</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Dakshinya555</t>
+          <t>Darshan_mainsh008</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -9829,24 +9829,24 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Dakshinya555/</t>
+          <t>https://leetcode.com/u/Darshan_mainsh008/</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>922525106057</t>
+          <t>922525106059</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>DARSHAN V V</t>
+          <t>DEJASRI M</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Darshan_mainsh008</t>
+          <t>dejasri</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -9856,24 +9856,24 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Darshan_mainsh008/</t>
+          <t>https://leetcode.com/u/dejasri/</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>922525106059</t>
+          <t>922525106060</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>DEJASRI M</t>
+          <t>DESMA SHALINI K</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>dejasri</t>
+          <t>desmashalini</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -9883,24 +9883,24 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/dejasri/</t>
+          <t>https://leetcode.com/u/desmashalini/</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>922525106060</t>
+          <t>922525106061</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>DESMA SHALINI K</t>
+          <t>DEVA V</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>desmashalini</t>
+          <t>Devaece</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -9910,24 +9910,24 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/desmashalini/</t>
+          <t>https://leetcode.com/u/Devaece/</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>922525106061</t>
+          <t>922525106062</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>DEVA V</t>
+          <t>DHAKSESH PRANAV P</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Devaece</t>
+          <t>Dhaksesh_Pranav_P</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -9937,24 +9937,24 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Devaece/</t>
+          <t>https://leetcode.com/u/Dhaksesh_Pranav_P/</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>922525106062</t>
+          <t>922525106063</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>DHAKSESH PRANAV P</t>
+          <t>DHANASRI R</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Dhaksesh_Pranav_P</t>
+          <t>Dhanasri_r</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -9964,105 +9964,105 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Dhaksesh_Pranav_P/</t>
+          <t>https://leetcode.com/u/Dhanasri_r/</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>922525106063</t>
+          <t>922525106068</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>DHANASRI R</t>
+          <t>DHARANEESH K</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Dhanasri_r</t>
+          <t>dharaneeshk</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE B</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Dhanasri_r/</t>
+          <t>https://leetcode.com/u/dharaneeshk/</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>922525106068</t>
+          <t>922525106133</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>DHARANEESH K</t>
+          <t>JEEVADHARSHAN R R</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>dharaneeshk</t>
+          <t>dharshanjeeva</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>ECE B</t>
+          <t>ECE C</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/dharaneeshk/</t>
+          <t>https://leetcode.com/u/dharshanjeeva/</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>922525106133</t>
+          <t>922525106074</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>JEEVADHARSHAN R R</t>
+          <t>DHARSHINI P</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>dharshanjeeva</t>
+          <t>Dharshini_74</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE B</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/dharshanjeeva/</t>
+          <t>https://leetcode.com/u/Dharshini_74/</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>922525106074</t>
+          <t>922525106080</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>DHARSHINI P</t>
+          <t>DHIVAKAR R</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Dharshini_74</t>
+          <t>DhivakarR</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -10072,24 +10072,24 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Dharshini_74/</t>
+          <t>https://leetcode.com/u/DhivakarR/</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>922525106080</t>
+          <t>922525106082</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>DHIVAKAR R</t>
+          <t>DINESH P</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>DhivakarR</t>
+          <t>Dinesh_106082</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -10099,24 +10099,24 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/DhivakarR/</t>
+          <t>https://leetcode.com/u/Dinesh_106082/</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>922525106082</t>
+          <t>922525106094</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>DINESH P</t>
+          <t>GOKUL D</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Dinesh_106082</t>
+          <t>Gokul_tamilan_india</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Dinesh_106082/</t>
+          <t>https://leetcode.com/u/Gokul_tamilan_india/</t>
         </is>
       </c>
     </row>

--- a/Students.xlsx
+++ b/Students.xlsx
@@ -494,17 +494,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>922525106292</t>
+          <t>922525106291</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SASHMIKA.P</t>
+          <t>SARVESWARAN R</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>sashmikaprabhu</t>
+          <t>sarvesh312008</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -514,24 +514,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sashmikaprabhu/</t>
+          <t>https://leetcode.com/u/sarvesh312008/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>922525106307</t>
+          <t>922525106292</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SHIVANI B</t>
+          <t>SASHMIKA.P</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>shivani208</t>
+          <t>sashmikaprabhu</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -541,24 +541,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shivani208/</t>
+          <t>https://leetcode.com/u/sashmikaprabhu/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>922525106272</t>
+          <t>922525106307</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SANJAY D</t>
+          <t>SHIVANI B</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>itsmesanjay007</t>
+          <t>shivani208</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -568,24 +568,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itsmesanjay007/</t>
+          <t>https://leetcode.com/u/shivani208/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>922525106309</t>
+          <t>922525106272</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SHREE CHARAN T</t>
+          <t>SANJAY D</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>shreecharan22</t>
+          <t>itsmesanjay007</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -595,24 +595,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shreecharan22/</t>
+          <t>https://leetcode.com/u/itsmesanjay007/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>922525106314</t>
+          <t>922525106309</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SIVANESH D</t>
+          <t>SHREE CHARAN T</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>sivanesh2007</t>
+          <t>shreecharan22</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -622,24 +622,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivanesh2007/</t>
+          <t>https://leetcode.com/u/shreecharan22/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>922525196293</t>
+          <t>922525106314</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SASWIN D</t>
+          <t>SIVANESH D</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>saswin_88</t>
+          <t>sivanesh2007</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -649,24 +649,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saswin_88/</t>
+          <t>https://leetcode.com/u/sivanesh2007/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>922525106253</t>
+          <t>922525196293</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>RITHANYA KN</t>
+          <t>SASWIN D</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Rithanya12-3</t>
+          <t>saswin_88</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -676,24 +676,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithanya12-3/</t>
+          <t>https://leetcode.com/u/saswin_88/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>922525106257</t>
+          <t>922525106253</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RITHIKA B</t>
+          <t>RITHANYA KN</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rithika_Balakrishnan</t>
+          <t>Rithanya12-3</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -703,24 +703,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithika_Balakrishnan/</t>
+          <t>https://leetcode.com/u/Rithanya12-3/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>922525106259</t>
+          <t>922525106257</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ROHITH V</t>
+          <t>RITHIKA B</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>RohithrohiV</t>
+          <t>Rithika_Balakrishnan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -730,24 +730,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/RohithrohiV/</t>
+          <t>https://leetcode.com/u/Rithika_Balakrishnan/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>922525106260</t>
+          <t>922525106259</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ROOBAGAPRIYA R</t>
+          <t>ROHITH V</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Roobagapriya</t>
+          <t>RohithrohiV</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -757,24 +757,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Roobagapriya/</t>
+          <t>https://leetcode.com/u/RohithrohiV/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>922525106264</t>
+          <t>922525106260</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SABAREESH K</t>
+          <t>ROOBAGAPRIYA R</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>sabareesh_karikalan</t>
+          <t>Roobagapriya</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -784,24 +784,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
+          <t>https://leetcode.com/u/Roobagapriya/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>922525106256</t>
+          <t>922525106264</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>RITHIK P</t>
+          <t>SABAREESH K</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Rithik_78</t>
+          <t>sabareesh_karikalan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithik_78/</t>
+          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>922525106258</t>
+          <t>922525106256</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RITHISH R</t>
+          <t>RITHIK P</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Rithish_</t>
+          <t>Rithik_78</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -838,24 +838,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithish_/</t>
+          <t>https://leetcode.com/u/Rithik_78/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>922525106266</t>
+          <t>922525106258</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SAHANA.V</t>
+          <t>RITHISH R</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sahanavijayakumar_0033</t>
+          <t>Rithish_</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -865,24 +865,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sahanavijayakumar_0033/</t>
+          <t>https://leetcode.com/u/Rithish_/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>922525106269</t>
+          <t>922525106266</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sakthivel. M</t>
+          <t>SAHANA.V</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>sakthivel23116</t>
+          <t>Sahanavijayakumar_0033</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -892,24 +892,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sakthivel23116/</t>
+          <t>https://leetcode.com/u/Sahanavijayakumar_0033/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>922525106275</t>
+          <t>922525106269</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SANJAY U</t>
+          <t>Sakthivel. M</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SanjayUdayan</t>
+          <t>sakthivel23116</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -919,24 +919,24 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SanjayUdayan/</t>
+          <t>https://leetcode.com/u/sakthivel23116/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>922525106283</t>
+          <t>922525106275</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SANTHOSH S</t>
+          <t>SANJAY U</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SanthoshSathya260</t>
+          <t>SanjayUdayan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SanthoshSathya260/</t>
+          <t>https://leetcode.com/u/SanjayUdayan/</t>
         </is>
       </c>
     </row>
@@ -1034,17 +1034,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>922525106291</t>
+          <t>922525106283</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SARVESWARAN R</t>
+          <t>SANTHOSH S</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>sarvesh312008</t>
+          <t>SanthoshSathya260</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sarvesh312008/</t>
+          <t>https://leetcode.com/u/SanthoshSathya260/</t>
         </is>
       </c>
     </row>
@@ -2627,17 +2627,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>922525106377</t>
+          <t>922525106329</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>YAZHINI V</t>
+          <t>SRINITHE T</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>VISU_YAZHU</t>
+          <t>srinithe_1401</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2647,24 +2647,24 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VISU_YAZHU/</t>
+          <t>https://leetcode.com/u/srinithe_1401/</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>922525106346</t>
+          <t>922525106377</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SWETHA E</t>
+          <t>YAZHINI V</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Swetha_20_1</t>
+          <t>VISU_YAZHU</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2674,24 +2674,24 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Swetha_20_1/</t>
+          <t>https://leetcode.com/u/VISU_YAZHU/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>922525106329</t>
+          <t>922525106346</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SRINITHE T</t>
+          <t>SWETHA E</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>srinithe_1401</t>
+          <t>Swetha_20_1</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/srinithe_1401/</t>
+          <t>https://leetcode.com/u/Swetha_20_1/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>922525106339</t>
+          <t>922525106330</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SUJITH RAJA B</t>
+          <t>SRINITHI S</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>mahi20_</t>
+          <t>Srinithi24_</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2728,24 +2728,24 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/mahi20_/</t>
+          <t>https://leetcode.com/u/Srinithi24_/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>922525106330</t>
+          <t>922525106339</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SRINITHI S</t>
+          <t>SUJITH RAJA B</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Srinithi24_</t>
+          <t>mahi20_</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2755,24 +2755,24 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Srinithi24_/</t>
+          <t>https://leetcode.com/u/mahi20_/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>922525106331</t>
+          <t>922525106353</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SRISAMAYA R</t>
+          <t>THIRISHA C</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>mahi</t>
+          <t>thirishavsb</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2782,24 +2782,24 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/mahi/</t>
+          <t>https://leetcode.com/u/thirishavsb/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>922525106332</t>
+          <t>922525106331</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SUBARNA V</t>
+          <t>SRISAMAYA R</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Subarna_17</t>
+          <t>mahi</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2809,24 +2809,24 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Subarna_17/</t>
+          <t>https://leetcode.com/u/mahi/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>922525106334</t>
+          <t>922525106332</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SUBIKA T</t>
+          <t>SUBARNA V</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>subika1112</t>
+          <t>Subarna_17</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2836,24 +2836,24 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/subika1112/</t>
+          <t>https://leetcode.com/u/Subarna_17/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>922525106353</t>
+          <t>922525106334</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>THIRISHA C</t>
+          <t>SUBIKA T</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>thirishavsb</t>
+          <t>subika1112</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/thirishavsb/</t>
+          <t>https://leetcode.com/u/subika1112/</t>
         </is>
       </c>
     </row>
@@ -2951,17 +2951,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>922525106364</t>
+          <t>922525106338</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>VIGNESH VELAN M</t>
+          <t>SUJEETH M</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Vicky_27_Velan</t>
+          <t>SUJEETH77</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2971,24 +2971,24 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vicky_27_Velan/</t>
+          <t>https://leetcode.com/u/SUJEETH77/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>922525106338</t>
+          <t>922525106364</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SUJEETH M</t>
+          <t>VIGNESH VELAN M</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>SUJEETH77</t>
+          <t>Vicky_27_Velan</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SUJEETH77/</t>
+          <t>https://leetcode.com/u/Vicky_27_Velan/</t>
         </is>
       </c>
     </row>
@@ -3680,17 +3680,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>922525106170</t>
+          <t>922525106169</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>LOGADHARSHINI T</t>
+          <t>LINGESHWARAN K</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>LogadharshiniT</t>
+          <t>LING2007</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -3700,24 +3700,24 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/LogadharshiniT/</t>
+          <t>https://leetcode.com/u/LING2007/</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>922525106171</t>
+          <t>922525106170</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>LOGASRI.A</t>
+          <t>LOGADHARSHINI T</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Loga07</t>
+          <t>LogadharshiniT</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3727,24 +3727,24 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Loga07/</t>
+          <t>https://leetcode.com/u/LogadharshiniT/</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>922525106172</t>
+          <t>922525106171</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>LOGAVARDHAN M</t>
+          <t>LOGASRI.A</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>loga16</t>
+          <t>Loga07</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -3754,24 +3754,24 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/loga16/</t>
+          <t>https://leetcode.com/u/Loga07/</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>922525106174</t>
+          <t>922525106172</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>LOGESHWARAN K</t>
+          <t>LOGAVARDHAN M</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>LOGESHWARAN2008</t>
+          <t>loga16</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -3781,24 +3781,24 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/LOGESHWARAN2008/</t>
+          <t>https://leetcode.com/u/loga16/</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>922525106175</t>
+          <t>922525106174</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>LOHITH RAJ S</t>
+          <t>LOGESHWARAN K</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>LOHITH012008</t>
+          <t>LOGESHWARAN2008</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -3808,24 +3808,24 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/LOHITH012008/</t>
+          <t>https://leetcode.com/u/LOGESHWARAN2008/</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>922525106176</t>
+          <t>922525106175</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>LOKRAJI R</t>
+          <t>LOHITH RAJ S</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>LOKRAJI6793</t>
+          <t>LOHITH012008</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -3835,24 +3835,24 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/LOKRAJI6793/</t>
+          <t>https://leetcode.com/u/LOHITH012008/</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>922525106177</t>
+          <t>922525106176</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>MADELIN JENITA M</t>
+          <t>LOKRAJI R</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>jenita0206</t>
+          <t>LOKRAJI6793</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -3862,24 +3862,24 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/jenita0206/</t>
+          <t>https://leetcode.com/u/LOKRAJI6793/</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>922525106179</t>
+          <t>922525106177</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>MADHANKUMAR S</t>
+          <t>MADELIN JENITA M</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Madhankumar861053</t>
+          <t>jenita0206</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -3889,24 +3889,24 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Madhankumar861053/</t>
+          <t>https://leetcode.com/u/jenita0206/</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>922525106180</t>
+          <t>922525106179</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>MADHUDHARA P</t>
+          <t>MADHANKUMAR S</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>madhudhara</t>
+          <t>Madhankumar861053</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3916,24 +3916,24 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/madhudhara/</t>
+          <t>https://leetcode.com/u/Madhankumar861053/</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>922525106181</t>
+          <t>922525106180</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>MADHUMITHA B</t>
+          <t>MADHUDHARA P</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Madhumitha42</t>
+          <t>madhudhara</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -3943,24 +3943,24 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Madhumitha42/</t>
+          <t>https://leetcode.com/u/madhudhara/</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>922525106182</t>
+          <t>922525106181</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Madhup Kishor G S</t>
+          <t>MADHUMITHA B</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Madhupkishor_20</t>
+          <t>Madhumitha42</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -3970,24 +3970,24 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Madhupkishor_20/</t>
+          <t>https://leetcode.com/u/Madhumitha42/</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>922525106183</t>
+          <t>922525106182</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>MAHALAKSHMI B</t>
+          <t>Madhup Kishor G S</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>mahalakshmi182025</t>
+          <t>Madhupkishor_20</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -3997,24 +3997,24 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/mahalakshmi182025/</t>
+          <t>https://leetcode.com/u/Madhupkishor_20/</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>922525106185</t>
+          <t>922525106183</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>MAHALAKSHMI P</t>
+          <t>MAHALAKSHMI B</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>maha_lakh_20</t>
+          <t>mahalakshmi182025</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -4024,24 +4024,24 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/maha_lakh_20/</t>
+          <t>https://leetcode.com/u/mahalakshmi182025/</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>922525106186</t>
+          <t>922525106185</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>MAHIBALAN .A</t>
+          <t>MAHALAKSHMI P</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>mahi2</t>
+          <t>maha_lakh_20</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -4051,24 +4051,24 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/mahi2/</t>
+          <t>https://leetcode.com/u/maha_lakh_20/</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>922525106187</t>
+          <t>922525106186</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>MAHIN ABHISHEK VH</t>
+          <t>MAHIBALAN .A</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Mahinabhishek0411</t>
+          <t>mahi2</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -4078,24 +4078,24 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Mahinabhishek0411/</t>
+          <t>https://leetcode.com/u/mahi2/</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>922525106189</t>
+          <t>922525106187</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Manisha D</t>
+          <t>MAHIN ABHISHEK VH</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>manishaa_20</t>
+          <t>Mahinabhishek0411</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -4105,51 +4105,51 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/manishaa_20/</t>
+          <t>https://leetcode.com/u/Mahinabhishek0411/</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>922525106190</t>
+          <t>922525106189</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>MANOJ A</t>
+          <t>Manisha D</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Manoj_1319</t>
+          <t>manishaa_20</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE C</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Manoj_1319/</t>
+          <t>https://leetcode.com/u/manishaa_20/</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>922525106191</t>
+          <t>922525106190</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Manoj Kumar V</t>
+          <t>MANOJ A</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>m____a____n____o____</t>
+          <t>Manoj_1319</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -4159,24 +4159,24 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/m____a____n____o____/</t>
+          <t>https://leetcode.com/u/Manoj_1319/</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>922525106193</t>
+          <t>922525106191</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>MATHESHKUMAR S</t>
+          <t>Manoj Kumar V</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>mathesh25</t>
+          <t>m____a____n____o____</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -4186,24 +4186,24 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/mathesh25/</t>
+          <t>https://leetcode.com/u/m____a____n____o____/</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>922525106194</t>
+          <t>922525106193</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>MAYAKANNAN K</t>
+          <t>MATHESHKUMAR S</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Mayakannan129</t>
+          <t>mathesh25</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -4213,24 +4213,24 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Mayakannan129/</t>
+          <t>https://leetcode.com/u/mathesh25/</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>922525106195</t>
+          <t>922525106194</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>MAYUKA M</t>
+          <t>MAYAKANNAN K</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Mayuka_M</t>
+          <t>Mayakannan129</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -4240,24 +4240,24 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Mayuka_M/</t>
+          <t>https://leetcode.com/u/Mayakannan129/</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>922525106196</t>
+          <t>922525106195</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Milan D</t>
+          <t>MAYUKA M</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>milan190308</t>
+          <t>Mayuka_M</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -4267,24 +4267,24 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/milan190308/</t>
+          <t>https://leetcode.com/u/Mayuka_M/</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>922525106200</t>
+          <t>922525106196</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MONISHA R</t>
+          <t>Milan D</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>itsmoni</t>
+          <t>milan190308</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -4294,24 +4294,24 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itsmoni/</t>
+          <t>https://leetcode.com/u/milan190308/</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>922525106201</t>
+          <t>922525106200</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MONISHA V</t>
+          <t>MONISHA R</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Monishav2007</t>
+          <t>itsmoni</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -4321,24 +4321,24 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Monishav2007/</t>
+          <t>https://leetcode.com/u/itsmoni/</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>922525106202</t>
+          <t>922525106201</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Morrish D</t>
+          <t>MONISHA V</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>morrishd</t>
+          <t>Monishav2007</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -4348,24 +4348,24 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/morrishd/</t>
+          <t>https://leetcode.com/u/Monishav2007/</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>922525106203</t>
+          <t>922525106202</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MOULEESHWARI B</t>
+          <t>Morrish D</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Mouleeshwari2008</t>
+          <t>morrishd</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -4375,24 +4375,24 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Mouleeshwari2008/</t>
+          <t>https://leetcode.com/u/morrishd/</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>922525106204</t>
+          <t>922525106203</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MOUSHMI P N</t>
+          <t>MOULEESHWARI B</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Moushmi_20</t>
+          <t>Mouleeshwari2008</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -4402,78 +4402,78 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Moushmi_20/</t>
+          <t>https://leetcode.com/u/Mouleeshwari2008/</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>922525106106</t>
+          <t>922525106204</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>GOWTHAMAN N</t>
+          <t>MOUSHMI P N</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>92252510610</t>
+          <t>Moushmi_20</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>ECE B</t>
+          <t>ECE D</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/92252510610/</t>
+          <t>https://leetcode.com/u/Moushmi_20/</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>922525106205</t>
+          <t>922525106106</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>MYTHILI M</t>
+          <t>GOWTHAMAN N</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>mythilimurugesan</t>
+          <t>92252510610</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE B</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/mythilimurugesan/</t>
+          <t>https://leetcode.com/u/92252510610/</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>922525106206</t>
+          <t>922525106205</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>NAFREEN J M</t>
+          <t>MYTHILI M</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>NafreenJohnbasha</t>
+          <t>mythilimurugesan</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -4483,24 +4483,24 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/NafreenJohnbasha/</t>
+          <t>https://leetcode.com/u/mythilimurugesan/</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>922525106208</t>
+          <t>922525106206</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>NANDHINI D</t>
+          <t>NAFREEN J M</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>nandhini546</t>
+          <t>NafreenJohnbasha</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -4510,24 +4510,24 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/nandhini546/</t>
+          <t>https://leetcode.com/u/NafreenJohnbasha/</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>922525106210</t>
+          <t>922525106208</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>NAVANEETHAN L</t>
+          <t>NANDHINI D</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>lnavaneethan08</t>
+          <t>nandhini546</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -4537,24 +4537,24 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/lnavaneethan08/</t>
+          <t>https://leetcode.com/u/nandhini546/</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>922525106211</t>
+          <t>922525106210</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Naveetha N</t>
+          <t>NAVANEETHAN L</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>NAVEETHAN</t>
+          <t>lnavaneethan08</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -4564,24 +4564,24 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/NAVEETHAN/</t>
+          <t>https://leetcode.com/u/lnavaneethan08/</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>922525106213</t>
+          <t>922525106211</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>NIRANJANI D</t>
+          <t>Naveetha N</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>niranjani_123</t>
+          <t>NAVEETHAN</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/niranjani_123/</t>
+          <t>https://leetcode.com/u/NAVEETHAN/</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>922525106214</t>
+          <t>922525106213</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>NITHISH C T</t>
+          <t>NIRANJANI D</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Nithishct123</t>
+          <t>niranjani_123</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -4618,24 +4618,24 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Nithishct123/</t>
+          <t>https://leetcode.com/u/niranjani_123/</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>922525106215</t>
+          <t>922525106214</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>NITHISH P</t>
+          <t>NITHISH C T</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Nithish_P_CS</t>
+          <t>Nithishct123</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -4645,24 +4645,24 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Nithish_P_CS/</t>
+          <t>https://leetcode.com/u/Nithishct123/</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>922525106216</t>
+          <t>922525106215</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Nithish R</t>
+          <t>NITHISH P</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>nithishramalingam007</t>
+          <t>Nithish_P_CS</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -4672,24 +4672,24 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/nithishramalingam007/</t>
+          <t>https://leetcode.com/u/Nithish_P_CS/</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>922525106217</t>
+          <t>922525106216</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>NITHISHWARAN D</t>
+          <t>Nithish R</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>nithishwaran25</t>
+          <t>nithishramalingam007</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -4699,24 +4699,24 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/nithishwaran25/</t>
+          <t>https://leetcode.com/u/nithishramalingam007/</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>922525106218</t>
+          <t>922525106217</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>NITHYASHREE G</t>
+          <t>NITHISHWARAN D</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>NithyashreeG10</t>
+          <t>nithishwaran25</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -4726,24 +4726,24 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/NithyashreeG10/</t>
+          <t>https://leetcode.com/u/nithishwaran25/</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>922525106219</t>
+          <t>922525106218</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>NITHYASHREE P</t>
+          <t>NITHYASHREE G</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Nithyashree273</t>
+          <t>NithyashreeG10</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -4753,24 +4753,24 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Nithyashree273/</t>
+          <t>https://leetcode.com/u/NithyashreeG10/</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>922525106220</t>
+          <t>922525106219</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>NITHYASRI M</t>
+          <t>NITHYASHREE P</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Nithyasri2008</t>
+          <t>Nithyashree273</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -4780,24 +4780,24 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Nithyasri2008/</t>
+          <t>https://leetcode.com/u/Nithyashree273/</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>922525106222</t>
+          <t>922525106220</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>PAARGAVI R</t>
+          <t>NITHYASRI M</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>paargavi2007</t>
+          <t>Nithyasri2008</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -4807,24 +4807,24 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/paargavi2007/</t>
+          <t>https://leetcode.com/u/Nithyasri2008/</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>922525106223</t>
+          <t>922525106222</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>PAVITHRA S</t>
+          <t>PAARGAVI R</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>pavithra145</t>
+          <t>paargavi2007</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -4834,24 +4834,24 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/pavithra145/</t>
+          <t>https://leetcode.com/u/paargavi2007/</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>922525106224</t>
+          <t>922525106223</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>PAVITHRAN S</t>
+          <t>PAVITHRA S</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Pavithran_S_</t>
+          <t>pavithra145</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -4861,24 +4861,24 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Pavithran_S_/</t>
+          <t>https://leetcode.com/u/pavithra145/</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>922525106225</t>
+          <t>922525106224</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>PIRAVEEN M</t>
+          <t>PAVITHRAN S</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Piraveen2025</t>
+          <t>Pavithran_S_</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -4888,24 +4888,24 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Piraveen2025/</t>
+          <t>https://leetcode.com/u/Pavithran_S_/</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>922525106226</t>
+          <t>922525106225</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>PRABHAKARAN D</t>
+          <t>PIRAVEEN M</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>_d_Prabhakaran_</t>
+          <t>Piraveen2025</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -4915,24 +4915,24 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_d_Prabhakaran_/</t>
+          <t>https://leetcode.com/u/Piraveen2025/</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>922525106227</t>
+          <t>922525106226</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>PRADHOSH T</t>
+          <t>PRABHAKARAN D</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>pradhosh</t>
+          <t>_d_Prabhakaran_</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -4942,24 +4942,24 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/pradhosh/</t>
+          <t>https://leetcode.com/u/_d_Prabhakaran_/</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>922525106228</t>
+          <t>922525106227</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>PRAGALATHAN T</t>
+          <t>PRADHOSH T</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>pragalathan070108</t>
+          <t>pradhosh</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -4969,24 +4969,24 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/pragalathan070108/</t>
+          <t>https://leetcode.com/u/pradhosh/</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>922525106229</t>
+          <t>922525106228</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>PRANESH Y</t>
+          <t>PRAGALATHAN T</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Pranesh-Y</t>
+          <t>pragalathan070108</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -4996,24 +4996,24 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Pranesh-Y/</t>
+          <t>https://leetcode.com/u/pragalathan070108/</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>922525106230</t>
+          <t>922525106229</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>PRANITHASREE SAMINATHAN</t>
+          <t>PRANESH Y</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>pranithaashree</t>
+          <t>Pranesh-Y</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -5023,24 +5023,24 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/pranithaashree/</t>
+          <t>https://leetcode.com/u/Pranesh-Y/</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>922525106231</t>
+          <t>922525106230</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>PRAVEEN D</t>
+          <t>PRANITHASREE SAMINATHAN</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>praveen1247</t>
+          <t>pranithaashree</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -5050,24 +5050,24 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/praveen1247/</t>
+          <t>https://leetcode.com/u/pranithaashree/</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>922525106232</t>
+          <t>922525106231</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>PRAVEEN G</t>
+          <t>PRAVEEN D</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>praveen_3208</t>
+          <t>praveen1247</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -5077,14 +5077,14 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/praveen_3208/</t>
+          <t>https://leetcode.com/u/praveen1247/</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>922525106233</t>
+          <t>922525106232</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>PRAVEENGANESAN</t>
+          <t>praveen_3208</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -5104,24 +5104,24 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/PRAVEENGANESAN/</t>
+          <t>https://leetcode.com/u/praveen_3208/</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>922525106234</t>
+          <t>922525106233</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>PRAVEENKUMAR R</t>
+          <t>PRAVEEN G</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>itz_praveen_</t>
+          <t>PRAVEENGANESAN</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -5131,24 +5131,24 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itz_praveen_/</t>
+          <t>https://leetcode.com/u/PRAVEENGANESAN/</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>922525106235</t>
+          <t>922525106234</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>PREETHY M S</t>
+          <t>PRAVEENKUMAR R</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>preethy2007</t>
+          <t>itz_praveen_</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -5158,24 +5158,24 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/preethy2007/</t>
+          <t>https://leetcode.com/u/itz_praveen_/</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>922525106236</t>
+          <t>922525106235</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>PRITHIV S</t>
+          <t>PREETHY M S</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>prithiv16</t>
+          <t>preethy2007</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -5185,24 +5185,24 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/prithiv16/</t>
+          <t>https://leetcode.com/u/preethy2007/</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>922525106237</t>
+          <t>922525106236</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>PRIYADHARSHINI V</t>
+          <t>PRITHIV S</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>priyadharshini1551</t>
+          <t>prithiv16</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -5212,24 +5212,24 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/priyadharshini1551/</t>
+          <t>https://leetcode.com/u/prithiv16/</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>922525106238</t>
+          <t>922525106237</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>PRIYANKA A</t>
+          <t>PRIYADHARSHINI V</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Priyankaashok1201</t>
+          <t>priyadharshini1551</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -5239,24 +5239,24 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Priyankaashok1201/</t>
+          <t>https://leetcode.com/u/priyadharshini1551/</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>922525106239</t>
+          <t>922525106238</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>PRIYANKA K R</t>
+          <t>PRIYANKA A</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>priyankadhanush23</t>
+          <t>Priyankaashok1201</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -5266,24 +5266,24 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/priyankadhanush23/</t>
+          <t>https://leetcode.com/u/Priyankaashok1201/</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>922525106240</t>
+          <t>922525106239</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>RAGADHARSHINI S</t>
+          <t>PRIYANKA K R</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Ragadharshini_2181</t>
+          <t>priyankadhanush23</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -5293,24 +5293,24 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Ragadharshini_2181/</t>
+          <t>https://leetcode.com/u/priyankadhanush23/</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>922525106241</t>
+          <t>922525106240</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>RAGUNATH M</t>
+          <t>RAGADHARSHINI S</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>ragunath24</t>
+          <t>Ragadharshini_2181</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -5320,24 +5320,24 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/ragunath24/</t>
+          <t>https://leetcode.com/u/Ragadharshini_2181/</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>922525106242</t>
+          <t>922525106241</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>RAHULKAJAN M</t>
+          <t>RAGUNATH M</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>rahulkajan</t>
+          <t>ragunath24</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -5347,24 +5347,24 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/rahulkajan/</t>
+          <t>https://leetcode.com/u/ragunath24/</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>922525106243</t>
+          <t>922525106242</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>RAJAPRAGADEESWARAN R</t>
+          <t>RAHULKAJAN M</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>rajaprahadeeswaran</t>
+          <t>rahulkajan</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -5374,24 +5374,24 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/rajaprahadeeswaran/</t>
+          <t>https://leetcode.com/u/rahulkajan/</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>922525106244</t>
+          <t>922525106243</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>RANJANA T</t>
+          <t>RAJAPRAGADEESWARAN R</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>RANJANA_2007</t>
+          <t>rajaprahadeeswaran</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -5401,24 +5401,24 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/RANJANA_2007/</t>
+          <t>https://leetcode.com/u/rajaprahadeeswaran/</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>922525106246</t>
+          <t>922525106244</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>RASIKA S</t>
+          <t>RANJANA T</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>RASIKA_2008</t>
+          <t>RANJANA_2007</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -5428,24 +5428,24 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/RASIKA_2008/</t>
+          <t>https://leetcode.com/u/RANJANA_2007/</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>922525106247</t>
+          <t>922525106246</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>RATHISH R</t>
+          <t>RASIKA S</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Rathish2025</t>
+          <t>RASIKA_2008</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -5455,24 +5455,24 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rathish2025/</t>
+          <t>https://leetcode.com/u/RASIKA_2008/</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>922525106248</t>
+          <t>922525106247</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>RAVIKUMAR S</t>
+          <t>RATHISH R</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Ravikumar_14</t>
+          <t>Rathish2025</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -5482,78 +5482,78 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Ravikumar_14/</t>
+          <t>https://leetcode.com/u/Rathish2025/</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>922525106005</t>
+          <t>922525106248</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>ADHITHMITHRAN P</t>
+          <t>RAVIKUMAR S</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>ADHITHMITHRAN</t>
+          <t>Ravikumar_14</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE D</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/ADHITHMITHRAN/</t>
+          <t>https://leetcode.com/u/Ravikumar_14/</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>922525106043</t>
+          <t>922525106173</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>BHARGAVI K</t>
+          <t>LOGESH H</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>logesh2008</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE C</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/2/</t>
+          <t>https://leetcode.com/u/logesh2008/</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>922525106036</t>
+          <t>922525106005</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>BALARITHISH S</t>
+          <t>ADHITHMITHRAN P</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>ADHITHMITHRAN</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -5563,24 +5563,24 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/3/</t>
+          <t>https://leetcode.com/u/ADHITHMITHRAN/</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>922525106035</t>
+          <t>922525106043</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>BALAJI C</t>
+          <t>BHARGAVI K</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -5590,24 +5590,24 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/4/</t>
+          <t>https://leetcode.com/u/2/</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>922525106058</t>
+          <t>922525106036</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>DEEKSHA K</t>
+          <t>BALARITHISH S</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -5617,24 +5617,24 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/5/</t>
+          <t>https://leetcode.com/u/3/</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>922525106011</t>
+          <t>922525106035</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>AJAYKRISHNA R</t>
+          <t>BALAJI C</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>922525106011</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -5644,24 +5644,24 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106011/</t>
+          <t>https://leetcode.com/u/4/</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>922525106049</t>
+          <t>922525106058</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>BUVNESH N</t>
+          <t>DEEKSHA K</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>922525106049</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -5671,24 +5671,24 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106049/</t>
+          <t>https://leetcode.com/u/5/</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>922525106052</t>
+          <t>922525106011</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>CHINMAYASRI K</t>
+          <t>AJAYKRISHNA R</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>922525106052</t>
+          <t>922525106011</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -5698,24 +5698,24 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106052/</t>
+          <t>https://leetcode.com/u/922525106011/</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>922525106055</t>
+          <t>922525106049</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>DARSHAN C</t>
+          <t>BUVNESH N</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>922525106055</t>
+          <t>922525106049</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -5725,78 +5725,78 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106055/</t>
+          <t>https://leetcode.com/u/922525106049/</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>922525106093</t>
+          <t>922525106052</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>GIRIVASH P</t>
+          <t>CHINMAYASRI K</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>922525106093</t>
+          <t>922525106052</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>ECE B</t>
+          <t>ECE A</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106093/</t>
+          <t>https://leetcode.com/u/922525106052/</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>922525106096</t>
+          <t>922525106055</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>GOPALA KRISHNAN C</t>
+          <t>DARSHAN C</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>922525106096</t>
+          <t>922525106055</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>ECE B</t>
+          <t>ECE A</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106096/</t>
+          <t>https://leetcode.com/u/922525106055/</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>922525106097</t>
+          <t>922525106093</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>GOPINATH R</t>
+          <t>GIRIVASH P</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>922525106097</t>
+          <t>922525106093</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -5806,78 +5806,78 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106097/</t>
+          <t>https://leetcode.com/u/922525106093/</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>922525106056</t>
+          <t>922525106096</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>DARSHAN MANISH A</t>
+          <t>GOPALA KRISHNAN C</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>2007darshan</t>
+          <t>922525106096</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE B</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/2007darshan/</t>
+          <t>https://leetcode.com/u/922525106096/</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>922525106006</t>
+          <t>922525106097</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>AFTON AJ</t>
+          <t>GOPINATH R</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>afton_2008</t>
+          <t>922525106097</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE B</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/afton_2008/</t>
+          <t>https://leetcode.com/u/922525106097/</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>922525106028</t>
+          <t>922525106056</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>ARUN C</t>
+          <t>DARSHAN MANISH A</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>AGmXRQ1yTe</t>
+          <t>2007darshan</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -5887,24 +5887,24 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/AGmXRQ1yTe/</t>
+          <t>https://leetcode.com/u/2007darshan/</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>922525106012</t>
+          <t>922525106006</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>AJAYKUMAR A L</t>
+          <t>AFTON AJ</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>AjaykumarAL</t>
+          <t>afton_2008</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -5914,24 +5914,24 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/AjaykumarAL/</t>
+          <t>https://leetcode.com/u/afton_2008/</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>922525106013</t>
+          <t>922525106028</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>AJITH KUMAR M</t>
+          <t>ARUN C</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>ajit_kumar_23</t>
+          <t>AGmXRQ1yTe</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -5941,24 +5941,24 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/ajit_kumar_23/</t>
+          <t>https://leetcode.com/u/AGmXRQ1yTe/</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>922525106019</t>
+          <t>922525106013</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>ANBARASU S</t>
+          <t>AJITH KUMAR M</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Anbarasu28122007</t>
+          <t>ajit_kumar_23</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -5968,24 +5968,24 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Anbarasu28122007/</t>
+          <t>https://leetcode.com/u/ajit_kumar_23/</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>922525106020</t>
+          <t>922525106019</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>ANJITHAA N</t>
+          <t>ANBARASU S</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Anjithaa2006</t>
+          <t>Anbarasu28122007</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -5995,24 +5995,24 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Anjithaa2006/</t>
+          <t>https://leetcode.com/u/Anbarasu28122007/</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>922525106021</t>
+          <t>922525106020</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>ANOOP C</t>
+          <t>ANJITHAA N</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>anoop_appuz</t>
+          <t>Anjithaa2006</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -6022,24 +6022,24 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/anoop_appuz/</t>
+          <t>https://leetcode.com/u/Anjithaa2006/</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>922525106022</t>
+          <t>922525106021</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>ANUJA S</t>
+          <t>ANOOP C</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>anuja008</t>
+          <t>anoop_appuz</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -6049,24 +6049,24 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/anuja008/</t>
+          <t>https://leetcode.com/u/anoop_appuz/</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>922525106027</t>
+          <t>922525106022</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Arulesh K</t>
+          <t>ANUJA S</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>arul2008</t>
+          <t>anuja008</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -6076,7 +6076,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/arul2008/</t>
+          <t>https://leetcode.com/u/anuja008/</t>
         </is>
       </c>
     </row>
@@ -6110,17 +6110,17 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>922525106037</t>
+          <t>922525106008</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>BARANITHARAN V</t>
+          <t>AHELESH G S</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>barani_7</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -6130,24 +6130,24 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/barani_7/</t>
+          <t>https://leetcode.com/u/B/</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>922525106039</t>
+          <t>922525106037</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>BENOV NAVIN V</t>
+          <t>BARANITHARAN V</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Benov_18</t>
+          <t>barani_7</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -6157,24 +6157,24 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Benov_18/</t>
+          <t>https://leetcode.com/u/barani_7/</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>922525106044</t>
+          <t>922525106039</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Bhavan bala N</t>
+          <t>BENOV NAVIN V</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>BhavanBala</t>
+          <t>Benov_18</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -6184,24 +6184,24 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/BhavanBala/</t>
+          <t>https://leetcode.com/u/Benov_18/</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>922525106041</t>
+          <t>922525106044</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>BHARATH KUMAR E</t>
+          <t>Bhavan bala N</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>BK5226221</t>
+          <t>BhavanBala</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -6211,24 +6211,24 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/BK5226221/</t>
+          <t>https://leetcode.com/u/BhavanBala/</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>922525106045</t>
+          <t>922525106041</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>BOOBASE R</t>
+          <t>BHARATH KUMAR E</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Boobase</t>
+          <t>BK5226221</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -6238,24 +6238,24 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Boobase/</t>
+          <t>https://leetcode.com/u/BK5226221/</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>922525106046</t>
+          <t>922525106045</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>BOOMIKA T</t>
+          <t>BOOBASE R</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>boomikat123</t>
+          <t>Boobase</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -6265,24 +6265,24 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/boomikat123/</t>
+          <t>https://leetcode.com/u/Boobase/</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>922525106047</t>
+          <t>922525106046</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>BOSVIYA P</t>
+          <t>BOOMIKA T</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>BosviyaBSV</t>
+          <t>boomikat123</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -6292,24 +6292,24 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/BosviyaBSV/</t>
+          <t>https://leetcode.com/u/boomikat123/</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>922525106048</t>
+          <t>922525106047</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>BRINDHA S</t>
+          <t>BOSVIYA P</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Brindha_S</t>
+          <t>BosviyaBSV</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -6319,24 +6319,24 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Brindha_S/</t>
+          <t>https://leetcode.com/u/BosviyaBSV/</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>922525106014</t>
+          <t>922525106048</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Akash.R</t>
+          <t>BRINDHA S</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>AkashRajaram</t>
+          <t>Brindha_S</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -6346,24 +6346,24 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/AkashRajaram/</t>
+          <t>https://leetcode.com/u/Brindha_S/</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>922525106050</t>
+          <t>922525106014</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>CHARUDESNA S</t>
+          <t>Akash.R</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>charu120108</t>
+          <t>AkashRajaram</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -6373,24 +6373,24 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/charu120108/</t>
+          <t>https://leetcode.com/u/AkashRajaram/</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>922525106051</t>
+          <t>922525106050</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>CHARUNETHRA S</t>
+          <t>CHARUDESNA S</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>charunethra07</t>
+          <t>charu120108</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -6400,24 +6400,24 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/charunethra07/</t>
+          <t>https://leetcode.com/u/charu120108/</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>922525106038</t>
+          <t>922525106051</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>BAVITHA T</t>
+          <t>CHARUNETHRA S</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>codewithakshaya</t>
+          <t>charunethra07</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -6427,24 +6427,24 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/codewithakshaya/</t>
+          <t>https://leetcode.com/u/charunethra07/</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>922525106016</t>
+          <t>922525106038</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>AKSHAYA S</t>
+          <t>BAVITHA T</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>codewithakshaya78</t>
+          <t>codewithakshaya</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -6454,24 +6454,24 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/codewithakshaya78/</t>
+          <t>https://leetcode.com/u/codewithakshaya/</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>922525106054</t>
+          <t>922525106016</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>DAKSHINYA R</t>
+          <t>AKSHAYA S</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Dakshinya555</t>
+          <t>codewithakshaya78</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -6481,24 +6481,24 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Dakshinya555/</t>
+          <t>https://leetcode.com/u/codewithakshaya78/</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>922525106057</t>
+          <t>922525106054</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>DARSHAN V V</t>
+          <t>DAKSHINYA R</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Darshan_mainsh008</t>
+          <t>Dakshinya555</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -6508,24 +6508,24 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Darshan_mainsh008/</t>
+          <t>https://leetcode.com/u/Dakshinya555/</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>922525106059</t>
+          <t>922525106057</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>DEJASRI M</t>
+          <t>DARSHAN V V</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>dejasri</t>
+          <t>Darshan_mainsh008</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -6535,24 +6535,24 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/dejasri/</t>
+          <t>https://leetcode.com/u/Darshan_mainsh008/</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>922525106040</t>
+          <t>922525106059</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>BHARANIDHARAN S</t>
+          <t>DEJASRI M</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Idvdnnsh577q</t>
+          <t>dejasri</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -6562,24 +6562,24 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Idvdnnsh577q/</t>
+          <t>https://leetcode.com/u/dejasri/</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>922525106025</t>
+          <t>922525106040</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>ARSATHA BEGAM M S</t>
+          <t>BHARANIDHARAN S</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>jakabesj</t>
+          <t>Idvdnnsh577q</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -6589,51 +6589,51 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/jakabesj/</t>
+          <t>https://leetcode.com/u/Idvdnnsh577q/</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>922525106129</t>
+          <t>922525106025</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>JASVANTHRAM SP</t>
+          <t>ARSATHA BEGAM M S</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>jasvanthram</t>
+          <t>jakabesj</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE A</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/jasvanthram/</t>
+          <t>https://leetcode.com/u/jakabesj/</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>922525106173</t>
+          <t>922525106129</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>LOGESH H</t>
+          <t>JASVANTHRAM SP</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>logesh2008</t>
+          <t>jasvanthram</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -6643,7 +6643,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/logesh2008/</t>
+          <t>https://leetcode.com/u/jasvanthram/</t>
         </is>
       </c>
     </row>
@@ -6893,17 +6893,17 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>922525106008</t>
+          <t>922525106027</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>AHELESH G S</t>
+          <t>Arulesh K</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>arul2008</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -6913,7 +6913,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/B/</t>
+          <t>https://leetcode.com/u/arul2008/</t>
         </is>
       </c>
     </row>
@@ -7919,44 +7919,44 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>922525106080</t>
+          <t>922525106147</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>DHIVAKAR R</t>
+          <t>KATHIR E</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>DhivakarR</t>
+          <t>kathir__21</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>ECE B</t>
+          <t>ECE C</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/DhivakarR/</t>
+          <t>https://leetcode.com/u/kathir__21/</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>922525106081</t>
+          <t>922525106080</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>DILIPKUMAR K</t>
+          <t>DHIVAKAR R</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>922525106081</t>
+          <t>DhivakarR</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -7966,24 +7966,24 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106081/</t>
+          <t>https://leetcode.com/u/DhivakarR/</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>922525106082</t>
+          <t>922525106081</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>DINESH P</t>
+          <t>DILIPKUMAR K</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Dinesh_106082</t>
+          <t>922525106081</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -7993,24 +7993,24 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Dinesh_106082/</t>
+          <t>https://leetcode.com/u/922525106081/</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>922525106083</t>
+          <t>922525106082</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>DINESHKUMAR P</t>
+          <t>DINESH P</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>922525106083</t>
+          <t>Dinesh_106082</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -8020,24 +8020,24 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106083/</t>
+          <t>https://leetcode.com/u/Dinesh_106082/</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>922525106084</t>
+          <t>922525106083</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>DINESHKUMAR V</t>
+          <t>DINESHKUMAR P</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>922525106084</t>
+          <t>922525106083</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -8047,24 +8047,24 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106084/</t>
+          <t>https://leetcode.com/u/922525106083/</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>922525106085</t>
+          <t>922525106084</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>DIVYA ROJA R</t>
+          <t>DINESHKUMAR V</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>922525106085</t>
+          <t>922525106084</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -8074,24 +8074,24 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106085/</t>
+          <t>https://leetcode.com/u/922525106084/</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>922525106086</t>
+          <t>922525106085</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>DIVYA V</t>
+          <t>DIVYA ROJA R</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>princess-nk</t>
+          <t>922525106085</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -8101,24 +8101,24 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/princess-nk/</t>
+          <t>https://leetcode.com/u/922525106085/</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>922525106087</t>
+          <t>922525106086</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>DIVYADHARSHINI G</t>
+          <t>DIVYA V</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>922525106087</t>
+          <t>princess-nk</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -8128,24 +8128,24 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106087/</t>
+          <t>https://leetcode.com/u/princess-nk/</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>922525106088</t>
+          <t>922525106087</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>DIVYADHARSHINI S</t>
+          <t>DIVYADHARSHINI G</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>922525106088</t>
+          <t>922525106087</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -8155,24 +8155,24 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106088/</t>
+          <t>https://leetcode.com/u/922525106087/</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>922525106089</t>
+          <t>922525106088</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>DURAIMURUGAN K</t>
+          <t>DIVYADHARSHINI S</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>922525106089</t>
+          <t>922525106088</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -8182,24 +8182,24 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106089/</t>
+          <t>https://leetcode.com/u/922525106088/</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>922525106090</t>
+          <t>922525106089</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>ELAKKIYA N</t>
+          <t>DURAIMURUGAN K</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>922525106090</t>
+          <t>922525106089</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -8209,24 +8209,24 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106090/</t>
+          <t>https://leetcode.com/u/922525106089/</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>922525106091</t>
+          <t>922525106090</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>ELAVARASAN R</t>
+          <t>ELAKKIYA N</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>922525106091</t>
+          <t>922525106090</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -8236,24 +8236,24 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106091/</t>
+          <t>https://leetcode.com/u/922525106090/</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>922525106092</t>
+          <t>922525106091</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>ELAVARASU P</t>
+          <t>ELAVARASAN R</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>922525106092</t>
+          <t>922525106091</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -8263,24 +8263,24 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106092/</t>
+          <t>https://leetcode.com/u/922525106091/</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>922525106094</t>
+          <t>922525106092</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>GOKUL D</t>
+          <t>ELAVARASU P</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Gokul_tamilan_india</t>
+          <t>922525106092</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -8290,24 +8290,24 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Gokul_tamilan_india/</t>
+          <t>https://leetcode.com/u/922525106092/</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>922525106095</t>
+          <t>922525106094</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>GOMATHI R</t>
+          <t>GOKUL D</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>gomathi_0709</t>
+          <t>Gokul_tamilan_india</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -8317,24 +8317,24 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/gomathi_0709/</t>
+          <t>https://leetcode.com/u/Gokul_tamilan_india/</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>922525106098</t>
+          <t>922525106095</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>GOUTHAM R J</t>
+          <t>GOMATHI R</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>922525106098</t>
+          <t>gomathi_0709</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -8344,24 +8344,24 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106098/</t>
+          <t>https://leetcode.com/u/gomathi_0709/</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>922525106099</t>
+          <t>922525106098</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>GOVARTHAN K S</t>
+          <t>GOUTHAM R J</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>GOVARTHANKS</t>
+          <t>922525106098</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -8371,24 +8371,24 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/GOVARTHANKS/</t>
+          <t>https://leetcode.com/u/922525106098/</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>922525106100</t>
+          <t>922525106099</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>GOWRIKA K P</t>
+          <t>GOVARTHAN K S</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>922525106100</t>
+          <t>GOVARTHANKS</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -8398,24 +8398,24 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106100/</t>
+          <t>https://leetcode.com/u/GOVARTHANKS/</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>922525106101</t>
+          <t>922525106100</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>GOWRISANKAR S</t>
+          <t>GOWRIKA K P</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>922524106101</t>
+          <t>922525106100</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -8425,24 +8425,24 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922524106101/</t>
+          <t>https://leetcode.com/u/922525106100/</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>922525106102</t>
+          <t>922525106101</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>GOWSICK S</t>
+          <t>GOWRISANKAR S</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>922525106106</t>
+          <t>922524106101</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -8452,24 +8452,24 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106106/</t>
+          <t>https://leetcode.com/u/922524106101/</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>922525106103</t>
+          <t>922525106102</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>GOWTHAM M</t>
+          <t>GOWSICK S</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>922525106103</t>
+          <t>922525106106</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -8479,24 +8479,24 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106103/</t>
+          <t>https://leetcode.com/u/922525106106/</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>922525106104</t>
+          <t>922525106103</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>GOWTHAM R</t>
+          <t>GOWTHAM M</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>922525106104</t>
+          <t>922525106103</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -8506,24 +8506,24 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106104/</t>
+          <t>https://leetcode.com/u/922525106103/</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>922525106105</t>
+          <t>922525106104</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>GOWTHAM S</t>
+          <t>GOWTHAM R</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Gowtham_080</t>
+          <t>922525106104</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -8533,24 +8533,24 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Gowtham_080/</t>
+          <t>https://leetcode.com/u/922525106104/</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>922525106107</t>
+          <t>922525106105</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>GUNA SHREE V</t>
+          <t>GOWTHAM S</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Gunashree20</t>
+          <t>Gowtham_080</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -8560,24 +8560,24 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Gunashree20/</t>
+          <t>https://leetcode.com/u/Gowtham_080/</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>922525106108</t>
+          <t>922525106107</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>GURUSARAN R</t>
+          <t>GUNA SHREE V</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>922525106108</t>
+          <t>Gunashree20</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -8587,24 +8587,24 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106108/</t>
+          <t>https://leetcode.com/u/Gunashree20/</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>922525106109</t>
+          <t>922525106108</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>HANSHIKAVARSA K S</t>
+          <t>GURUSARAN R</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>922525106109</t>
+          <t>922525106108</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -8614,24 +8614,24 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106109/</t>
+          <t>https://leetcode.com/u/922525106108/</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>922525106110</t>
+          <t>922525106109</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>HARI HARAN R</t>
+          <t>HANSHIKAVARSA K S</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>922525106110</t>
+          <t>922525106109</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -8641,24 +8641,24 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106110/</t>
+          <t>https://leetcode.com/u/922525106109/</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>922525106111</t>
+          <t>922525106110</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>HARIS S</t>
+          <t>HARI HARAN R</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>922525106111</t>
+          <t>922525106110</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -8668,24 +8668,24 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106111/</t>
+          <t>https://leetcode.com/u/922525106110/</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>922525106112</t>
+          <t>922525106111</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>HARINI S</t>
+          <t>HARIS S</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>922525106112</t>
+          <t>922525106111</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -8695,24 +8695,24 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106112/</t>
+          <t>https://leetcode.com/u/922525106111/</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>922525106113</t>
+          <t>922525106112</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>HARIS M</t>
+          <t>HARINI S</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>922525106113</t>
+          <t>922525106112</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -8722,24 +8722,24 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106113/</t>
+          <t>https://leetcode.com/u/922525106112/</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>922525106114</t>
+          <t>922525106113</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>HARIS RAGAVENDAR A</t>
+          <t>HARIS M</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>922525106114</t>
+          <t>922525106113</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -8749,24 +8749,24 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106114/</t>
+          <t>https://leetcode.com/u/922525106113/</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>922525106115</t>
+          <t>922525106114</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>HARISH D</t>
+          <t>HARIS RAGAVENDAR A</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>922525106115</t>
+          <t>922525106114</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -8776,24 +8776,24 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106115/</t>
+          <t>https://leetcode.com/u/922525106114/</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>922525106116</t>
+          <t>922525106115</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>HARISH M S</t>
+          <t>HARISH D</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>922525106116</t>
+          <t>922525106115</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -8803,24 +8803,24 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106116/</t>
+          <t>https://leetcode.com/u/922525106115/</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>922525106117</t>
+          <t>922525106116</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>HARISH P</t>
+          <t>HARISH M S</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>922525106117</t>
+          <t>922525106116</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -8830,24 +8830,24 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106117/</t>
+          <t>https://leetcode.com/u/922525106116/</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>922525106118</t>
+          <t>922525106117</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>HARISHANKAR R</t>
+          <t>HARISH P</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>922525106118</t>
+          <t>922525106117</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -8857,24 +8857,24 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106118/</t>
+          <t>https://leetcode.com/u/922525106117/</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>922525106119</t>
+          <t>922525106118</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>HAVISHMATHI S</t>
+          <t>HARISHANKAR R</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>HAVISHMATHIS</t>
+          <t>922525106118</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -8884,24 +8884,24 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/HAVISHMATHIS/</t>
+          <t>https://leetcode.com/u/922525106118/</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>922525106120</t>
+          <t>922525106119</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>HEMAA SRI A</t>
+          <t>HAVISHMATHI S</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>922525106120</t>
+          <t>HAVISHMATHIS</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -8911,24 +8911,24 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106120/</t>
+          <t>https://leetcode.com/u/HAVISHMATHIS/</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>922525106121</t>
+          <t>922525106120</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>HEMAVARSHINI S</t>
+          <t>HEMAA SRI A</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>922525106121</t>
+          <t>922525106120</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -8938,24 +8938,24 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106121/</t>
+          <t>https://leetcode.com/u/922525106120/</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>922525106122</t>
+          <t>922525106121</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>HIRESH K</t>
+          <t>HEMAVARSHINI S</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>922525106122</t>
+          <t>922525106121</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -8965,24 +8965,24 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106122/</t>
+          <t>https://leetcode.com/u/922525106121/</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>922525106123</t>
+          <t>922525106122</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>INBNATHAN S</t>
+          <t>HIRESH K</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>922525106123</t>
+          <t>922525106122</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -8992,24 +8992,24 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106123/</t>
+          <t>https://leetcode.com/u/922525106122/</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>922525106124</t>
+          <t>922525106123</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>INDHIRAJITH K</t>
+          <t>INBNATHAN S</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>922525106124</t>
+          <t>922525106123</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -9019,24 +9019,24 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106124/</t>
+          <t>https://leetcode.com/u/922525106123/</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>922525106125</t>
+          <t>922525106124</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>JAI GANESH I</t>
+          <t>INDHIRAJITH K</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>922525106125</t>
+          <t>922525106124</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -9046,24 +9046,24 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106125/</t>
+          <t>https://leetcode.com/u/922525106124/</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>922525106126</t>
+          <t>922525106125</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>JANA S</t>
+          <t>JAI GANESH I</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>922525106126</t>
+          <t>922525106125</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -9073,51 +9073,51 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106126/</t>
+          <t>https://leetcode.com/u/922525106125/</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>922525106127</t>
+          <t>922525106126</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>JANANI A</t>
+          <t>JANA S</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>janani_asohkan</t>
+          <t>922525106126</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE B</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/janani_asohkan/</t>
+          <t>https://leetcode.com/u/922525106126/</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>922525106128</t>
+          <t>922525106127</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>JASHVANTH J S</t>
+          <t>JANANI A</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>jashvanth2007</t>
+          <t>janani_asohkan</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -9127,24 +9127,24 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/jashvanth2007/</t>
+          <t>https://leetcode.com/u/janani_asohkan/</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>922525106130</t>
+          <t>922525106128</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>JAYASAKTHI V</t>
+          <t>JASHVANTH J S</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>jayasakthi_25</t>
+          <t>jashvanth2007</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -9154,24 +9154,24 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/jayasakthi_25/</t>
+          <t>https://leetcode.com/u/jashvanth2007/</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>922525106132</t>
+          <t>922525106130</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Jeevan bala G</t>
+          <t>JAYASAKTHI V</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>jeevanbala142008</t>
+          <t>jayasakthi_25</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -9181,24 +9181,24 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/jeevanbala142008/</t>
+          <t>https://leetcode.com/u/jayasakthi_25/</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>922525106133</t>
+          <t>922525106132</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>JEEVADHARSHAN R R</t>
+          <t>Jeevan bala G</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>dharshanjeeva</t>
+          <t>jeevanbala142008</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -9208,24 +9208,24 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/dharshanjeeva/</t>
+          <t>https://leetcode.com/u/jeevanbala142008/</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>922525106134</t>
+          <t>922525106133</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>JEEVANAA S</t>
+          <t>JEEVADHARSHAN R R</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>jeevanaa_174_</t>
+          <t>dharshanjeeva</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -9235,24 +9235,24 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/jeevanaa_174_/</t>
+          <t>https://leetcode.com/u/dharshanjeeva/</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>922525106135</t>
+          <t>922525106134</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>JERSHITH J S</t>
+          <t>JEEVANAA S</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Jerry2008</t>
+          <t>jeevanaa_174_</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -9262,24 +9262,24 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Jerry2008/</t>
+          <t>https://leetcode.com/u/jeevanaa_174_/</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>922525106136</t>
+          <t>922525106135</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>JOSHITHA KANNAN SUDHA</t>
+          <t>JERSHITH J S</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Joshi_666</t>
+          <t>Jerry2008</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -9289,24 +9289,24 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Joshi_666/</t>
+          <t>https://leetcode.com/u/Jerry2008/</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>922525106137</t>
+          <t>922525106136</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Jothi harshan D K</t>
+          <t>JOSHITHA KANNAN SUDHA</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Jothiharshan16</t>
+          <t>Joshi_666</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -9316,24 +9316,24 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Jothiharshan16/</t>
+          <t>https://leetcode.com/u/Joshi_666/</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>922525106138</t>
+          <t>922525106137</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>JOTHISHA K S</t>
+          <t>Jothi harshan D K</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Jothi-</t>
+          <t>Jothiharshan16</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -9343,24 +9343,24 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Jothi-/</t>
+          <t>https://leetcode.com/u/Jothiharshan16/</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>922525106139</t>
+          <t>922525106138</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>KAMALINI G</t>
+          <t>JOTHISHA K S</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>_kamalini_</t>
+          <t>Jothi-</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -9370,24 +9370,24 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_kamalini_/</t>
+          <t>https://leetcode.com/u/Jothi-/</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>922525106140</t>
+          <t>922525106139</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>KANISHKA A R</t>
+          <t>KAMALINI G</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>26kanishka</t>
+          <t>_kamalini_</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -9397,24 +9397,24 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/26kanishka/</t>
+          <t>https://leetcode.com/u/_kamalini_/</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>922525106142</t>
+          <t>922525106140</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>KANITHRA R</t>
+          <t>KANISHKA A R</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>kanithraakila</t>
+          <t>26kanishka</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -9424,24 +9424,24 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kanithraakila/</t>
+          <t>https://leetcode.com/u/26kanishka/</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>922525106143</t>
+          <t>922525106142</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>KARISHMA M</t>
+          <t>KANITHRA R</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Karishma_m_08</t>
+          <t>kanithraakila</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -9451,24 +9451,24 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Karishma_m_08/</t>
+          <t>https://leetcode.com/u/kanithraakila/</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>922525106144</t>
+          <t>922525106143</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>KARMUKILAN J</t>
+          <t>KARISHMA M</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>karmukilan567</t>
+          <t>Karishma_m_08</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -9478,24 +9478,24 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/karmukilan567/</t>
+          <t>https://leetcode.com/u/Karishma_m_08/</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>922525106145</t>
+          <t>922525106144</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>KARSHANA SRI V</t>
+          <t>KARMUKILAN J</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>karshana_234</t>
+          <t>karmukilan567</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -9505,24 +9505,24 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/karshana_234/</t>
+          <t>https://leetcode.com/u/karmukilan567/</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>922525106146</t>
+          <t>922525106145</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>KARTHIKA K</t>
+          <t>KARSHANA SRI V</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Karthi270827</t>
+          <t>karshana_234</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -9532,24 +9532,24 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Karthi270827/</t>
+          <t>https://leetcode.com/u/karshana_234/</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>922525106147</t>
+          <t>922525106146</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>KATHIR E</t>
+          <t>KARTHIKA K</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>kathir__21</t>
+          <t>Karthi270827</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -9559,7 +9559,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kathir__21/</t>
+          <t>https://leetcode.com/u/Karthi270827/</t>
         </is>
       </c>
     </row>
@@ -9620,44 +9620,44 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>922525106150</t>
+          <t>922525106012</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>KAVINKUMAR M</t>
+          <t>AJAYKUMAR A L</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>kavinleet</t>
+          <t>AjaykumarAL</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE A</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kavinleet/</t>
+          <t>https://leetcode.com/u/AjaykumarAL/</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>922525106151</t>
+          <t>922525106150</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>KAVIPRIYA J</t>
+          <t>KAVINKUMAR M</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>_kavipriya_16</t>
+          <t>kavinleet</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -9667,24 +9667,24 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_kavipriya_16/</t>
+          <t>https://leetcode.com/u/kavinleet/</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>922525106152</t>
+          <t>922525106151</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>KAVIPRIYA R</t>
+          <t>KAVIPRIYA J</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>KAVI_RAVI</t>
+          <t>_kavipriya_16</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -9694,24 +9694,24 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/KAVI_RAVI/</t>
+          <t>https://leetcode.com/u/_kavipriya_16/</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>922525106153</t>
+          <t>922525106152</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>KAVIYARASU K</t>
+          <t>KAVIPRIYA R</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>kavi12d</t>
+          <t>KAVI_RAVI</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -9721,24 +9721,24 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kavi12d/</t>
+          <t>https://leetcode.com/u/KAVI_RAVI/</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>922525106154</t>
+          <t>922525106153</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>KAVYA A</t>
+          <t>KAVIYARASU K</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>itzz__kavya02</t>
+          <t>kavi12d</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -9748,24 +9748,24 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itzz__kavya02/</t>
+          <t>https://leetcode.com/u/kavi12d/</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>922525106155</t>
+          <t>922525106154</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>KAYALVIZHI S</t>
+          <t>KAVYA A</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>27kayalvizhi</t>
+          <t>itzz__kavya02</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -9775,24 +9775,24 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/27kayalvizhi/</t>
+          <t>https://leetcode.com/u/itzz__kavya02/</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>922525106156</t>
+          <t>922525106155</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>KEERTHANA S</t>
+          <t>KAYALVIZHI S</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>keerthana_19selvam</t>
+          <t>27kayalvizhi</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -9802,24 +9802,24 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/keerthana_19selvam/</t>
+          <t>https://leetcode.com/u/27kayalvizhi/</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>922525106157</t>
+          <t>922525106156</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>KESAVINI M</t>
+          <t>KEERTHANA S</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>KESAVINI892</t>
+          <t>keerthana_19selvam</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -9829,24 +9829,24 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/KESAVINI892/</t>
+          <t>https://leetcode.com/u/keerthana_19selvam/</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>922525106158</t>
+          <t>922525106157</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>KIRUTHIKA S</t>
+          <t>KESAVINI M</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>kiruthika_selvanathan05092007</t>
+          <t>KESAVINI892</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -9856,24 +9856,24 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kiruthika_selvanathan05092007/</t>
+          <t>https://leetcode.com/u/KESAVINI892/</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>922525106160</t>
+          <t>922525106158</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>KOHUL V</t>
+          <t>KIRUTHIKA S</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>kohul_v</t>
+          <t>kiruthika_selvanathan05092007</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -9883,24 +9883,24 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kohul_v/</t>
+          <t>https://leetcode.com/u/kiruthika_selvanathan05092007/</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>922525106161</t>
+          <t>922525106160</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>KOWSHIK M</t>
+          <t>KOHUL V</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>kowshikm23</t>
+          <t>kohul_v</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -9910,24 +9910,24 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kowshikm23/</t>
+          <t>https://leetcode.com/u/kohul_v/</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>922525106162</t>
+          <t>922525106161</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>KOWSHIK R</t>
+          <t>KOWSHIK M</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>kowshik_rk_</t>
+          <t>kowshikm23</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -9937,24 +9937,24 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kowshik_rk_/</t>
+          <t>https://leetcode.com/u/kowshikm23/</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>922525106163</t>
+          <t>922525106162</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>KOWSHIKA B</t>
+          <t>KOWSHIK R</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Kowshika08</t>
+          <t>kowshik_rk_</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -9964,24 +9964,24 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Kowshika08/</t>
+          <t>https://leetcode.com/u/kowshik_rk_/</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>922525106164</t>
+          <t>922525106163</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>KOWSHIKA M S</t>
+          <t>KOWSHIKA B</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>kowshika_moorthi</t>
+          <t>Kowshika08</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -9991,24 +9991,24 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kowshika_moorthi/</t>
+          <t>https://leetcode.com/u/Kowshika08/</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>922525106165</t>
+          <t>922525106164</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>KOWSHIKAN P</t>
+          <t>KOWSHIKA M S</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>KOWSHIKAN-PALANISAMY</t>
+          <t>kowshika_moorthi</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -10018,24 +10018,24 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/KOWSHIKAN-PALANISAMY/</t>
+          <t>https://leetcode.com/u/kowshika_moorthi/</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>922525106166</t>
+          <t>922525106165</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>KRISH R</t>
+          <t>KOWSHIKAN P</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>krish-2007</t>
+          <t>KOWSHIKAN-PALANISAMY</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -10045,24 +10045,24 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/krish-2007/</t>
+          <t>https://leetcode.com/u/KOWSHIKAN-PALANISAMY/</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>922525106167</t>
+          <t>922525106166</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>LAKSHETHA V</t>
+          <t>KRISH R</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>itz_lakshe</t>
+          <t>krish-2007</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -10072,24 +10072,24 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itz_lakshe/</t>
+          <t>https://leetcode.com/u/krish-2007/</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>922525106168</t>
+          <t>922525106167</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>LAVANYA V</t>
+          <t>LAKSHETHA V</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>lavilavanya</t>
+          <t>itz_lakshe</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -10099,24 +10099,24 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/lavilavanya/</t>
+          <t>https://leetcode.com/u/itz_lakshe/</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>922525106169</t>
+          <t>922525106168</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>LINGESHWARAN K</t>
+          <t>LAVANYA V</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>LING2007</t>
+          <t>lavilavanya</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/LING2007/</t>
+          <t>https://leetcode.com/u/lavilavanya/</t>
         </is>
       </c>
     </row>

--- a/Students.xlsx
+++ b/Students.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$359</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$360</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E359"/>
+  <dimension ref="A1:E360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -467,17 +467,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>922525106265</t>
+          <t>922525106263</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SABARIVASAN P</t>
+          <t>RUBESH C</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SabarivasanP</t>
+          <t>Rubesh_7</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -487,24 +487,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SabarivasanP/</t>
+          <t>https://leetcode.com/u/Rubesh_7/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>922525106291</t>
+          <t>922525106283</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SARVESWARAN R</t>
+          <t>SANTHOSH S</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>sarvesh312008</t>
+          <t>SanthoshSathya260</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -514,24 +514,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sarvesh312008/</t>
+          <t>https://leetcode.com/u/SanthoshSathya260/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>922525106292</t>
+          <t>922525106291</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SASHMIKA.P</t>
+          <t>SARVESWARAN R</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>sashmikaprabhu</t>
+          <t>sarvesh312008</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -541,24 +541,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sashmikaprabhu/</t>
+          <t>https://leetcode.com/u/sarvesh312008/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>922525106307</t>
+          <t>922525106292</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SHIVANI B</t>
+          <t>SASHMIKA.P</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>shivani208</t>
+          <t>sashmikaprabhu</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -568,24 +568,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shivani208/</t>
+          <t>https://leetcode.com/u/sashmikaprabhu/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>922525106272</t>
+          <t>922525106307</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SANJAY D</t>
+          <t>SHIVANI B</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>itsmesanjay007</t>
+          <t>shivani208</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -595,24 +595,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itsmesanjay007/</t>
+          <t>https://leetcode.com/u/shivani208/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>922525106309</t>
+          <t>922525106272</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SHREE CHARAN T</t>
+          <t>SANJAY D</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>shreecharan22</t>
+          <t>itsmesanjay007</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -622,24 +622,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shreecharan22/</t>
+          <t>https://leetcode.com/u/itsmesanjay007/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>922525106314</t>
+          <t>922525106309</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SIVANESH D</t>
+          <t>SHREE CHARAN T</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>sivanesh2007</t>
+          <t>shreecharan22</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -649,24 +649,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivanesh2007/</t>
+          <t>https://leetcode.com/u/shreecharan22/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>922525196293</t>
+          <t>922525106314</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SASWIN D</t>
+          <t>SIVANESH D</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>saswin_88</t>
+          <t>sivanesh2007</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -676,24 +676,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saswin_88/</t>
+          <t>https://leetcode.com/u/sivanesh2007/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>922525106253</t>
+          <t>922525196293</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RITHANYA KN</t>
+          <t>SASWIN D</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rithanya12-3</t>
+          <t>saswin_88</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -703,24 +703,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithanya12-3/</t>
+          <t>https://leetcode.com/u/saswin_88/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>922525106257</t>
+          <t>922525106253</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>RITHIKA B</t>
+          <t>RITHANYA KN</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Rithika_Balakrishnan</t>
+          <t>Rithanya12-3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -730,24 +730,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithika_Balakrishnan/</t>
+          <t>https://leetcode.com/u/Rithanya12-3/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>922525106259</t>
+          <t>922525106257</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ROHITH V</t>
+          <t>RITHIKA B</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>RohithrohiV</t>
+          <t>Rithika_Balakrishnan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -757,24 +757,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/RohithrohiV/</t>
+          <t>https://leetcode.com/u/Rithika_Balakrishnan/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>922525106260</t>
+          <t>922525106259</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ROOBAGAPRIYA R</t>
+          <t>ROHITH V</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Roobagapriya</t>
+          <t>RohithrohiV</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -784,24 +784,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Roobagapriya/</t>
+          <t>https://leetcode.com/u/RohithrohiV/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>922525106264</t>
+          <t>922525106260</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SABAREESH K</t>
+          <t>ROOBAGAPRIYA R</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>sabareesh_karikalan</t>
+          <t>Roobagapriya</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
+          <t>https://leetcode.com/u/Roobagapriya/</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>922525106266</t>
+          <t>922525106264</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SAHANA.V</t>
+          <t>SABAREESH K</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sahanavijayakumar_0033</t>
+          <t>sabareesh_karikalan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -892,24 +892,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sahanavijayakumar_0033/</t>
+          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>922525106269</t>
+          <t>922525106266</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sakthivel. M</t>
+          <t>SAHANA.V</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>sakthivel23116</t>
+          <t>Sahanavijayakumar_0033</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -919,24 +919,24 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sakthivel23116/</t>
+          <t>https://leetcode.com/u/Sahanavijayakumar_0033/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>922525106275</t>
+          <t>922525106269</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SANJAY U</t>
+          <t>Sakthivel. M</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SanjayUdayan</t>
+          <t>sakthivel23116</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SanjayUdayan/</t>
+          <t>https://leetcode.com/u/sakthivel23116/</t>
         </is>
       </c>
     </row>
@@ -1007,17 +1007,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>922525106263</t>
+          <t>922525106275</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>RUBESH C</t>
+          <t>SANJAY U</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Rubesh_7</t>
+          <t>SanjayUdayan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1027,24 +1027,24 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rubesh_7/</t>
+          <t>https://leetcode.com/u/SanjayUdayan/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>922525106283</t>
+          <t>922525106265</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SANTHOSH S</t>
+          <t>SABARIVASAN P</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SanthoshSathya260</t>
+          <t>SabarivasanP</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SanthoshSathya260/</t>
+          <t>https://leetcode.com/u/SabarivasanP/</t>
         </is>
       </c>
     </row>
@@ -1844,17 +1844,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>922525106369</t>
+          <t>922525106367</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>VISHNU PRIYAN S</t>
+          <t>VIKRAM V</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>itz__priyan__</t>
+          <t>vikramvicky5678</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1864,24 +1864,24 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itz__priyan__/</t>
+          <t>https://leetcode.com/u/vikramvicky5678/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>922525106370</t>
+          <t>922525106368</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>VISHNUHARAN V S</t>
+          <t>VISHNU B</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Vishnuharan082007</t>
+          <t>VISHNU_B_2008</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1891,24 +1891,24 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vishnuharan082007/</t>
+          <t>https://leetcode.com/u/VISHNU_B_2008/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>922525106371</t>
+          <t>922525106369</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>VISHNUPRIYA S</t>
+          <t>VISHNU PRIYAN S</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>vishnupriyamaran</t>
+          <t>itz__priyan__</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1918,24 +1918,24 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vishnupriyamaran/</t>
+          <t>https://leetcode.com/u/itz__priyan__/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>922525106367</t>
+          <t>922525106370</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>VIKRAM V</t>
+          <t>VISHNUHARAN V S</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>vikramvicky5678</t>
+          <t>Vishnuharan082007</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1945,24 +1945,24 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vikramvicky5678/</t>
+          <t>https://leetcode.com/u/Vishnuharan082007/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>922525106361</t>
+          <t>922525106365</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>VASUKI K</t>
+          <t>VIGNESHWAR U</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>vasuki</t>
+          <t>VIGNESHWAR0221</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1972,24 +1972,24 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vasuki/</t>
+          <t>https://leetcode.com/u/VIGNESHWAR0221/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>922525106362</t>
+          <t>922525106359</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>VELLIANGIRI R</t>
+          <t>VASANTHKUMAR R</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>velliangiri_R</t>
+          <t>VasanthKumar008</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1999,24 +1999,24 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/velliangiri_R/</t>
+          <t>https://leetcode.com/u/VasanthKumar008/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>922525106363</t>
+          <t>922525106360</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>VIGNESH M</t>
+          <t>VASUDEVAN G</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>O8bYDSRUbE</t>
+          <t>GTVASU2008</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2026,24 +2026,24 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/O8bYDSRUbE/</t>
+          <t>https://leetcode.com/u/GTVASU2008/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>922525106365</t>
+          <t>922525106361</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>VIGNESHWAR U</t>
+          <t>VASUKI K</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>VIGNESHWAR0221</t>
+          <t>vasuki</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2053,24 +2053,24 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VIGNESHWAR0221/</t>
+          <t>https://leetcode.com/u/vasuki/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>922525106366</t>
+          <t>922525106362</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>VIJAYARAGAVAN R</t>
+          <t>VELLIANGIRI R</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>vijayaragavan1216</t>
+          <t>velliangiri_R</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2080,24 +2080,24 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vijayaragavan1216/</t>
+          <t>https://leetcode.com/u/velliangiri_R/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>922525106368</t>
+          <t>922525106363</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>VISHNU B</t>
+          <t>VIGNESH M</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>VISHNU_B_2008</t>
+          <t>O8bYDSRUbE</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2107,24 +2107,24 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VISHNU_B_2008/</t>
+          <t>https://leetcode.com/u/O8bYDSRUbE/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>922525106372</t>
+          <t>922525106366</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>VISHWAJETH A M</t>
+          <t>VIJAYARAGAVAN R</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>vishwajeth</t>
+          <t>vijayaragavan1216</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2134,24 +2134,24 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vishwajeth/</t>
+          <t>https://leetcode.com/u/vijayaragavan1216/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>922525106373</t>
+          <t>922525106371</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>YASHNI S</t>
+          <t>VISHNUPRIYA S</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Yashnisubramaniyan</t>
+          <t>vishnupriyamaran</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2161,24 +2161,24 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Yashnisubramaniyan/</t>
+          <t>https://leetcode.com/u/vishnupriyamaran/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>922525106374</t>
+          <t>922525106372</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>YASWANTH V</t>
+          <t>VISHWAJETH A M</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>yaswanth_2008</t>
+          <t>vishwajeth</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2188,24 +2188,24 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yaswanth_2008/</t>
+          <t>https://leetcode.com/u/vishwajeth/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>922525106375</t>
+          <t>922525106373</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>YAZHINI M</t>
+          <t>YASHNI S</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>yazhini2007</t>
+          <t>Yashnisubramaniyan</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2215,24 +2215,24 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yazhini2007/</t>
+          <t>https://leetcode.com/u/Yashnisubramaniyan/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>922525106376</t>
+          <t>922525106374</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>YAZHINI S</t>
+          <t>YASWANTH V</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>yazhini__1234</t>
+          <t>yaswanth_2008</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2242,24 +2242,24 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yazhini__1234/</t>
+          <t>https://leetcode.com/u/yaswanth_2008/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>922525106378</t>
+          <t>922525106375</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>YOKESWARAN S</t>
+          <t>YAZHINI M</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>syokeswaran</t>
+          <t>yazhini2007</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2269,24 +2269,24 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/syokeswaran/</t>
+          <t>https://leetcode.com/u/yazhini2007/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>922525106316</t>
+          <t>922525106376</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SIVARANJAN M P</t>
+          <t>YAZHINI S</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SIVARANJAN_MP</t>
+          <t>yazhini__1234</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2296,24 +2296,24 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SIVARANJAN_MP/</t>
+          <t>https://leetcode.com/u/yazhini__1234/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>922525106317</t>
+          <t>922525106316</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SIVASANJEEV P</t>
+          <t>SIVARANJAN M P</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Sivasanjeev16</t>
+          <t>SIVARANJAN_MP</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2323,24 +2323,24 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sivasanjeev16/</t>
+          <t>https://leetcode.com/u/SIVARANJAN_MP/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>922525106318</t>
+          <t>922525106317</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SIVASUBRAMANI A</t>
+          <t>SIVASANJEEV P</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>AK_Siva</t>
+          <t>Sivasanjeev16</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2350,24 +2350,24 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/AK_Siva/</t>
+          <t>https://leetcode.com/u/Sivasanjeev16/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>922525106319</t>
+          <t>922525106318</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SIVATHARUN C</t>
+          <t>SIVASUBRAMANI A</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>sivatharun22</t>
+          <t>AK_Siva</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2377,24 +2377,24 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivatharun22/</t>
+          <t>https://leetcode.com/u/AK_Siva/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>922525106320</t>
+          <t>922525106319</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SOBIKA R</t>
+          <t>SIVATHARUN C</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>_sobika_R</t>
+          <t>sivatharun22</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2404,24 +2404,24 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_sobika_R/</t>
+          <t>https://leetcode.com/u/sivatharun22/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>922525106321</t>
+          <t>922525106320</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SREE DHARANI C</t>
+          <t>SOBIKA R</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>SREEDHARANI_14</t>
+          <t>_sobika_R</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2431,24 +2431,24 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SREEDHARANI_14/</t>
+          <t>https://leetcode.com/u/_sobika_R/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>922525106322</t>
+          <t>922525106321</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SRI  T</t>
+          <t>SREE DHARANI C</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Sri1540</t>
+          <t>SREEDHARANI_14</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2458,24 +2458,24 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sri1540/</t>
+          <t>https://leetcode.com/u/SREEDHARANI_14/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>922525106323</t>
+          <t>922525106322</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SRI HEERA J</t>
+          <t>SRI  T</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>sriheera03</t>
+          <t>Sri1540</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2485,24 +2485,24 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sriheera03/</t>
+          <t>https://leetcode.com/u/Sri1540/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>922525106324</t>
+          <t>922525106323</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SRI KANTH R</t>
+          <t>SRI HEERA J</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>kanth2008</t>
+          <t>sriheera03</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2512,24 +2512,24 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kanth2008/</t>
+          <t>https://leetcode.com/u/sriheera03/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>922525106325</t>
+          <t>922525106324</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SRI SASTIKA G</t>
+          <t>SRI KANTH R</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Srisastika_1401</t>
+          <t>kanth2008</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2539,24 +2539,24 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Srisastika_1401/</t>
+          <t>https://leetcode.com/u/kanth2008/</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>922525106326</t>
+          <t>922525106325</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SRI VARSHAN B P</t>
+          <t>SRI SASTIKA G</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>srivarshan_B_P</t>
+          <t>Srisastika_1401</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2566,24 +2566,24 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/srivarshan_B_P/</t>
+          <t>https://leetcode.com/u/Srisastika_1401/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>922525106327</t>
+          <t>922525106326</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SRINATH V</t>
+          <t>SRI VARSHAN B P</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>V_SRINATH</t>
+          <t>srivarshan_B_P</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2593,24 +2593,24 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/V_SRINATH/</t>
+          <t>https://leetcode.com/u/srivarshan_B_P/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>922525106328</t>
+          <t>922525106327</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SRINIRANJAN S</t>
+          <t>SRINATH V</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>SRINIRANJAN2008</t>
+          <t>V_SRINATH</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2620,24 +2620,24 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SRINIRANJAN2008/</t>
+          <t>https://leetcode.com/u/V_SRINATH/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>922525106329</t>
+          <t>922525106328</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SRINITHE T</t>
+          <t>SRINIRANJAN S</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>srinithe_1401</t>
+          <t>SRINIRANJAN2008</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2647,24 +2647,24 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/srinithe_1401/</t>
+          <t>https://leetcode.com/u/SRINIRANJAN2008/</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>922525106377</t>
+          <t>922525106329</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>YAZHINI V</t>
+          <t>SRINITHE T</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>VISU_YAZHU</t>
+          <t>srinithe_1401</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2674,24 +2674,24 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VISU_YAZHU/</t>
+          <t>https://leetcode.com/u/srinithe_1401/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>922525106346</t>
+          <t>922525106364</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SWETHA E</t>
+          <t>VIGNESH VELAN M</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Swetha_20_1</t>
+          <t>Vicky_27_Velan</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Swetha_20_1/</t>
+          <t>https://leetcode.com/u/Vicky_27_Velan/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>922525106330</t>
+          <t>922525106377</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SRINITHI S</t>
+          <t>YAZHINI V</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Srinithi24_</t>
+          <t>VISU_YAZHU</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2728,24 +2728,24 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Srinithi24_/</t>
+          <t>https://leetcode.com/u/VISU_YAZHU/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>922525106339</t>
+          <t>922525106346</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SUJITH RAJA B</t>
+          <t>SWETHA E</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>mahi20_</t>
+          <t>Swetha_20_1</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2755,24 +2755,24 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/mahi20_/</t>
+          <t>https://leetcode.com/u/Swetha_20_1/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>922525106353</t>
+          <t>922525106378</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>THIRISHA C</t>
+          <t>YOKESWARAN S</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>thirishavsb</t>
+          <t>syokeswaran</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2782,24 +2782,24 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/thirishavsb/</t>
+          <t>https://leetcode.com/u/syokeswaran/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>922525106331</t>
+          <t>922525106330</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SRISAMAYA R</t>
+          <t>SRINITHI S</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>mahi</t>
+          <t>Srinithi24_</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2809,24 +2809,24 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/mahi/</t>
+          <t>https://leetcode.com/u/Srinithi24_/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>922525106332</t>
+          <t>922525106339</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SUBARNA V</t>
+          <t>SUJITH RAJA B</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Subarna_17</t>
+          <t>mahi20_</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2836,24 +2836,24 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Subarna_17/</t>
+          <t>https://leetcode.com/u/mahi20_/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>922525106334</t>
+          <t>922525106353</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SUBIKA T</t>
+          <t>THIRISHA C</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>subika1112</t>
+          <t>thirishavsb</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2863,24 +2863,24 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/subika1112/</t>
+          <t>https://leetcode.com/u/thirishavsb/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>922525106335</t>
+          <t>922525106331</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SUDHARSAN S</t>
+          <t>SRISAMAYA R</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Sudharsan</t>
+          <t>mahi</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2890,24 +2890,24 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sudharsan/</t>
+          <t>https://leetcode.com/u/mahi/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>922525106336</t>
+          <t>922525106332</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SUGANTHAN K</t>
+          <t>SUBARNA V</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>SUGANTHKALAI</t>
+          <t>Subarna_17</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2917,24 +2917,24 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SUGANTHKALAI/</t>
+          <t>https://leetcode.com/u/Subarna_17/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>922525106337</t>
+          <t>922525106334</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>SUGIDHARSHINI T</t>
+          <t>SUBIKA T</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Sugi_07</t>
+          <t>subika1112</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2944,24 +2944,24 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sugi_07/</t>
+          <t>https://leetcode.com/u/subika1112/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>922525106338</t>
+          <t>922525106335</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SUJEETH M</t>
+          <t>SUDHARSAN S</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>SUJEETH77</t>
+          <t>Sudharsan</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2971,24 +2971,24 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SUJEETH77/</t>
+          <t>https://leetcode.com/u/Sudharsan/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>922525106364</t>
+          <t>922525106336</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>VIGNESH VELAN M</t>
+          <t>SUGANTHAN K</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Vicky_27_Velan</t>
+          <t>SUGANTHKALAI</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2998,24 +2998,24 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vicky_27_Velan/</t>
+          <t>https://leetcode.com/u/SUGANTHKALAI/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>922525106340</t>
+          <t>922525106337</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SUMITHRA S</t>
+          <t>SUGIDHARSHINI T</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>sumithra_16</t>
+          <t>Sugi_07</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3025,24 +3025,24 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sumithra_16/</t>
+          <t>https://leetcode.com/u/Sugi_07/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>922525106341</t>
+          <t>922525106338</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SURYA PRABHU S</t>
+          <t>SUJEETH M</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>surya001prabhu</t>
+          <t>SUJEETH77</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3052,24 +3052,24 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/surya001prabhu/</t>
+          <t>https://leetcode.com/u/SUJEETH77/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>922525106342</t>
+          <t>922525106340</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>SUSIDHARAN M</t>
+          <t>SUMITHRA S</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Susidharan147</t>
+          <t>sumithra_16</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3079,24 +3079,24 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Susidharan147/</t>
+          <t>https://leetcode.com/u/sumithra_16/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>922525106343</t>
+          <t>922525106341</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>SUTHARSHANA S</t>
+          <t>SURYA PRABHU S</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>sutharshana743</t>
+          <t>surya001prabhu</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3106,24 +3106,24 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sutharshana743/</t>
+          <t>https://leetcode.com/u/surya001prabhu/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>922525106344</t>
+          <t>922525106342</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>SWATHI M</t>
+          <t>SUSIDHARAN M</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Swathimanivel_1234</t>
+          <t>Susidharan147</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3133,24 +3133,24 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Swathimanivel_1234/</t>
+          <t>https://leetcode.com/u/Susidharan147/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>922525106345</t>
+          <t>922525106343</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>SWATHI S</t>
+          <t>SUTHARSHANA S</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>_swathi _3366</t>
+          <t>sutharshana743</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3160,24 +3160,24 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_swathi _3366/</t>
+          <t>https://leetcode.com/u/sutharshana743/</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>922525106347</t>
+          <t>922525106344</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>TAMIL SELVAN R</t>
+          <t>SWATHI M</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Kdmif0HMNm</t>
+          <t>Swathimanivel_1234</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3187,24 +3187,24 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Kdmif0HMNm/</t>
+          <t>https://leetcode.com/u/Swathimanivel_1234/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>922525106348</t>
+          <t>922525106345</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>THAMARAI SELVI D</t>
+          <t>SWATHI S</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>thamarai_04</t>
+          <t>_swathi _3366</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3214,24 +3214,24 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/thamarai_04/</t>
+          <t>https://leetcode.com/u/_swathi _3366/</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>922525106349</t>
+          <t>922525106347</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>THAMEEM FARSHITHA A</t>
+          <t>TAMIL SELVAN R</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Thameem_786</t>
+          <t>Kdmif0HMNm</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3241,24 +3241,24 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Thameem_786/</t>
+          <t>https://leetcode.com/u/Kdmif0HMNm/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>922525106350</t>
+          <t>922525106348</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>THARANISH R</t>
+          <t>THAMARAI SELVI D</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>THARANISH2008</t>
+          <t>thamarai_04</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3268,24 +3268,24 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/THARANISH2008/</t>
+          <t>https://leetcode.com/u/thamarai_04/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>922525106351</t>
+          <t>922525106349</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>THARUNIKA P</t>
+          <t>THAMEEM FARSHITHA A</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Tharunika_12</t>
+          <t>Thameem_786</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3295,24 +3295,24 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Tharunika_12/</t>
+          <t>https://leetcode.com/u/Thameem_786/</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>922525106352</t>
+          <t>922525106350</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>THIRINESH KUMAR S</t>
+          <t>THARANISH R</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>THIRINESH KUMAR.S</t>
+          <t>THARANISH2008</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3322,24 +3322,24 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/THIRINESH KUMAR.S/</t>
+          <t>https://leetcode.com/u/THARANISH2008/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>922525106354</t>
+          <t>922525106351</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>THIRUMURUGAN S</t>
+          <t>THARUNIKA P</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>thiru0211_</t>
+          <t>Tharunika_12</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3349,24 +3349,24 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/thiru0211_/</t>
+          <t>https://leetcode.com/u/Tharunika_12/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>922525106355</t>
+          <t>922525106352</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>VAISHNAVI U</t>
+          <t>THIRINESH KUMAR S</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>vaish200</t>
+          <t>THIRINESH KUMAR.S</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3376,24 +3376,24 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vaish200/</t>
+          <t>https://leetcode.com/u/THIRINESH KUMAR.S/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>922525106356</t>
+          <t>922525106354</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>VASANTH KUMAR C</t>
+          <t>THIRUMURUGAN S</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>VASANTH2007</t>
+          <t>thiru0211_</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3403,24 +3403,24 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VASANTH2007/</t>
+          <t>https://leetcode.com/u/thiru0211_/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>922525106357</t>
+          <t>922525106355</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>VASANTH S</t>
+          <t>VAISHNAVI U</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>_vasanth_s_</t>
+          <t>vaish200</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3430,24 +3430,24 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_vasanth_s_/</t>
+          <t>https://leetcode.com/u/vaish200/</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>922525106358</t>
+          <t>922525106356</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>VASANTHA KUMAR D</t>
+          <t>VASANTH KUMAR C</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Vasanthakumar12232</t>
+          <t>VASANTH2007</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -3457,24 +3457,24 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vasanthakumar12232/</t>
+          <t>https://leetcode.com/u/VASANTH2007/</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>922525106359</t>
+          <t>922525106357</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>VASANTHKUMAR R</t>
+          <t>VASANTH S</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>VasanthKumar008</t>
+          <t>_vasanth_s_</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3484,24 +3484,24 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VasanthKumar008/</t>
+          <t>https://leetcode.com/u/_vasanth_s_/</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>922525106360</t>
+          <t>922525106358</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>VASUDEVAN G</t>
+          <t>VASANTHA KUMAR D</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>GTVASU2008</t>
+          <t>Vasanthakumar12232</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/GTVASU2008/</t>
+          <t>https://leetcode.com/u/Vasanthakumar12232/</t>
         </is>
       </c>
     </row>
@@ -3680,17 +3680,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>922525106169</t>
+          <t>922525106168</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>LINGESHWARAN K</t>
+          <t>LAVANYA V</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>LING2007</t>
+          <t>lavilavanya</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -3700,24 +3700,24 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/LING2007/</t>
+          <t>https://leetcode.com/u/lavilavanya/</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>922525106170</t>
+          <t>922525106169</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>LOGADHARSHINI T</t>
+          <t>LINGESHWARAN K</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>LogadharshiniT</t>
+          <t>LING2007</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3727,24 +3727,24 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/LogadharshiniT/</t>
+          <t>https://leetcode.com/u/LING2007/</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>922525106171</t>
+          <t>922525106170</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>LOGASRI.A</t>
+          <t>LOGADHARSHINI T</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Loga07</t>
+          <t>LogadharshiniT</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -3754,24 +3754,24 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Loga07/</t>
+          <t>https://leetcode.com/u/LogadharshiniT/</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>922525106172</t>
+          <t>922525106171</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>LOGAVARDHAN M</t>
+          <t>LOGASRI.A</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>loga16</t>
+          <t>Loga07</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -3781,24 +3781,24 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/loga16/</t>
+          <t>https://leetcode.com/u/Loga07/</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>922525106174</t>
+          <t>922525106172</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>LOGESHWARAN K</t>
+          <t>LOGAVARDHAN M</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>LOGESHWARAN2008</t>
+          <t>loga16</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -3808,24 +3808,24 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/LOGESHWARAN2008/</t>
+          <t>https://leetcode.com/u/loga16/</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>922525106175</t>
+          <t>922525106174</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>LOHITH RAJ S</t>
+          <t>LOGESHWARAN K</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>LOHITH012008</t>
+          <t>LOGESHWARAN2008</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -3835,24 +3835,24 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/LOHITH012008/</t>
+          <t>https://leetcode.com/u/LOGESHWARAN2008/</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>922525106176</t>
+          <t>922525106175</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>LOKRAJI R</t>
+          <t>LOHITH RAJ S</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>LOKRAJI6793</t>
+          <t>LOHITH012008</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -3862,24 +3862,24 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/LOKRAJI6793/</t>
+          <t>https://leetcode.com/u/LOHITH012008/</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>922525106177</t>
+          <t>922525106176</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>MADELIN JENITA M</t>
+          <t>LOKRAJI R</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>jenita0206</t>
+          <t>LOKRAJI6793</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -3889,24 +3889,24 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/jenita0206/</t>
+          <t>https://leetcode.com/u/LOKRAJI6793/</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>922525106179</t>
+          <t>922525106177</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>MADHANKUMAR S</t>
+          <t>MADELIN JENITA M</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Madhankumar861053</t>
+          <t>jenita0206</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3916,24 +3916,24 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Madhankumar861053/</t>
+          <t>https://leetcode.com/u/jenita0206/</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>922525106180</t>
+          <t>922525106179</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>MADHUDHARA P</t>
+          <t>MADHANKUMAR S</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>madhudhara</t>
+          <t>Madhankumar861053</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -3943,24 +3943,24 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/madhudhara/</t>
+          <t>https://leetcode.com/u/Madhankumar861053/</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>922525106181</t>
+          <t>922525106180</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>MADHUMITHA B</t>
+          <t>MADHUDHARA P</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Madhumitha42</t>
+          <t>madhudhara</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -3970,24 +3970,24 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Madhumitha42/</t>
+          <t>https://leetcode.com/u/madhudhara/</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>922525106182</t>
+          <t>922525106181</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Madhup Kishor G S</t>
+          <t>MADHUMITHA B</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Madhupkishor_20</t>
+          <t>Madhumitha42</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -3997,24 +3997,24 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Madhupkishor_20/</t>
+          <t>https://leetcode.com/u/Madhumitha42/</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>922525106183</t>
+          <t>922525106182</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>MAHALAKSHMI B</t>
+          <t>Madhup Kishor G S</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>mahalakshmi182025</t>
+          <t>Madhupkishor_20</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -4024,24 +4024,24 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/mahalakshmi182025/</t>
+          <t>https://leetcode.com/u/Madhupkishor_20/</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>922525106185</t>
+          <t>922525106183</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>MAHALAKSHMI P</t>
+          <t>MAHALAKSHMI B</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>maha_lakh_20</t>
+          <t>mahalakshmi182025</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -4051,24 +4051,24 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/maha_lakh_20/</t>
+          <t>https://leetcode.com/u/mahalakshmi182025/</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>922525106186</t>
+          <t>922525106185</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>MAHIBALAN .A</t>
+          <t>MAHALAKSHMI P</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>mahi2</t>
+          <t>maha_lakh_20</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -4078,24 +4078,24 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/mahi2/</t>
+          <t>https://leetcode.com/u/maha_lakh_20/</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>922525106187</t>
+          <t>922525106186</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>MAHIN ABHISHEK VH</t>
+          <t>MAHIBALAN .A</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Mahinabhishek0411</t>
+          <t>mahi2</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -4105,24 +4105,24 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Mahinabhishek0411/</t>
+          <t>https://leetcode.com/u/mahi2/</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>922525106189</t>
+          <t>922525106187</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Manisha D</t>
+          <t>MAHIN ABHISHEK VH</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>manishaa_20</t>
+          <t>Mahinabhishek0411</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -4132,51 +4132,51 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/manishaa_20/</t>
+          <t>https://leetcode.com/u/Mahinabhishek0411/</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>922525106190</t>
+          <t>922525106189</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>MANOJ A</t>
+          <t>Manisha D</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Manoj_1319</t>
+          <t>manishaa_20</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE C</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Manoj_1319/</t>
+          <t>https://leetcode.com/u/manishaa_20/</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>922525106191</t>
+          <t>922525106190</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Manoj Kumar V</t>
+          <t>MANOJ A</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>m____a____n____o____</t>
+          <t>Manoj_1319</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -4186,24 +4186,24 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/m____a____n____o____/</t>
+          <t>https://leetcode.com/u/Manoj_1319/</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>922525106193</t>
+          <t>922525106191</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>MATHESHKUMAR S</t>
+          <t>Manoj Kumar V</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>mathesh25</t>
+          <t>m____a____n____o____</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -4213,24 +4213,24 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/mathesh25/</t>
+          <t>https://leetcode.com/u/m____a____n____o____/</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>922525106194</t>
+          <t>922525106193</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>MAYAKANNAN K</t>
+          <t>MATHESHKUMAR S</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Mayakannan129</t>
+          <t>mathesh25</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -4240,24 +4240,24 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Mayakannan129/</t>
+          <t>https://leetcode.com/u/mathesh25/</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>922525106195</t>
+          <t>922525106194</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>MAYUKA M</t>
+          <t>MAYAKANNAN K</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Mayuka_M</t>
+          <t>Mayakannan129</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -4267,24 +4267,24 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Mayuka_M/</t>
+          <t>https://leetcode.com/u/Mayakannan129/</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>922525106196</t>
+          <t>922525106195</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Milan D</t>
+          <t>MAYUKA M</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>milan190308</t>
+          <t>Mayuka_M</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -4294,24 +4294,24 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/milan190308/</t>
+          <t>https://leetcode.com/u/Mayuka_M/</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>922525106200</t>
+          <t>922525106196</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MONISHA R</t>
+          <t>Milan D</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>itsmoni</t>
+          <t>milan190308</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -4321,24 +4321,24 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itsmoni/</t>
+          <t>https://leetcode.com/u/milan190308/</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>922525106201</t>
+          <t>922525106200</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MONISHA V</t>
+          <t>MONISHA R</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Monishav2007</t>
+          <t>itsmoni</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -4348,24 +4348,24 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Monishav2007/</t>
+          <t>https://leetcode.com/u/itsmoni/</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>922525106202</t>
+          <t>922525106201</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Morrish D</t>
+          <t>MONISHA V</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>morrishd</t>
+          <t>Monishav2007</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -4375,24 +4375,24 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/morrishd/</t>
+          <t>https://leetcode.com/u/Monishav2007/</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>922525106203</t>
+          <t>922525106202</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MOULEESHWARI B</t>
+          <t>Morrish D</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Mouleeshwari2008</t>
+          <t>morrishd</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -4402,24 +4402,24 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Mouleeshwari2008/</t>
+          <t>https://leetcode.com/u/morrishd/</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>922525106204</t>
+          <t>922525106203</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>MOUSHMI P N</t>
+          <t>MOULEESHWARI B</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Moushmi_20</t>
+          <t>Mouleeshwari2008</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -4429,78 +4429,78 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Moushmi_20/</t>
+          <t>https://leetcode.com/u/Mouleeshwari2008/</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>922525106106</t>
+          <t>922525106204</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>GOWTHAMAN N</t>
+          <t>MOUSHMI P N</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>92252510610</t>
+          <t>Moushmi_20</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>ECE B</t>
+          <t>ECE D</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/92252510610/</t>
+          <t>https://leetcode.com/u/Moushmi_20/</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>922525106205</t>
+          <t>922525106106</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>MYTHILI M</t>
+          <t>GOWTHAMAN N</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>mythilimurugesan</t>
+          <t>92252510610</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE B</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/mythilimurugesan/</t>
+          <t>https://leetcode.com/u/92252510610/</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>922525106206</t>
+          <t>922525106205</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>NAFREEN J M</t>
+          <t>MYTHILI M</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>NafreenJohnbasha</t>
+          <t>mythilimurugesan</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -4510,24 +4510,24 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/NafreenJohnbasha/</t>
+          <t>https://leetcode.com/u/mythilimurugesan/</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>922525106208</t>
+          <t>922525106206</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>NANDHINI D</t>
+          <t>NAFREEN J M</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>nandhini546</t>
+          <t>NafreenJohnbasha</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -4537,24 +4537,24 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/nandhini546/</t>
+          <t>https://leetcode.com/u/NafreenJohnbasha/</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>922525106210</t>
+          <t>922525106208</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>NAVANEETHAN L</t>
+          <t>NANDHINI D</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>lnavaneethan08</t>
+          <t>nandhini546</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -4564,24 +4564,24 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/lnavaneethan08/</t>
+          <t>https://leetcode.com/u/nandhini546/</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>922525106211</t>
+          <t>922525106210</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Naveetha N</t>
+          <t>NAVANEETHAN L</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>NAVEETHAN</t>
+          <t>lnavaneethan08</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/NAVEETHAN/</t>
+          <t>https://leetcode.com/u/lnavaneethan08/</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>922525106213</t>
+          <t>922525106211</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>NIRANJANI D</t>
+          <t>Naveetha N</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>niranjani_123</t>
+          <t>NAVEETHAN</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -4618,24 +4618,24 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/niranjani_123/</t>
+          <t>https://leetcode.com/u/NAVEETHAN/</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>922525106214</t>
+          <t>922525106213</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>NITHISH C T</t>
+          <t>NIRANJANI D</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Nithishct123</t>
+          <t>niranjani_123</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -4645,24 +4645,24 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Nithishct123/</t>
+          <t>https://leetcode.com/u/niranjani_123/</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>922525106215</t>
+          <t>922525106214</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>NITHISH P</t>
+          <t>NITHISH C T</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Nithish_P_CS</t>
+          <t>Nithishct123</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -4672,24 +4672,24 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Nithish_P_CS/</t>
+          <t>https://leetcode.com/u/Nithishct123/</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>922525106216</t>
+          <t>922525106215</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Nithish R</t>
+          <t>NITHISH P</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>nithishramalingam007</t>
+          <t>Nithish_P_CS</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -4699,24 +4699,24 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/nithishramalingam007/</t>
+          <t>https://leetcode.com/u/Nithish_P_CS/</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>922525106217</t>
+          <t>922525106216</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>NITHISHWARAN D</t>
+          <t>Nithish R</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>nithishwaran25</t>
+          <t>nithishramalingam007</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -4726,24 +4726,24 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/nithishwaran25/</t>
+          <t>https://leetcode.com/u/nithishramalingam007/</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>922525106218</t>
+          <t>922525106217</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>NITHYASHREE G</t>
+          <t>NITHISHWARAN D</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>NithyashreeG10</t>
+          <t>nithishwaran25</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -4753,24 +4753,24 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/NithyashreeG10/</t>
+          <t>https://leetcode.com/u/nithishwaran25/</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>922525106219</t>
+          <t>922525106218</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>NITHYASHREE P</t>
+          <t>NITHYASHREE G</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Nithyashree273</t>
+          <t>NithyashreeG10</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -4780,24 +4780,24 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Nithyashree273/</t>
+          <t>https://leetcode.com/u/NithyashreeG10/</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>922525106220</t>
+          <t>922525106219</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>NITHYASRI M</t>
+          <t>NITHYASHREE P</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Nithyasri2008</t>
+          <t>Nithyashree273</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -4807,24 +4807,24 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Nithyasri2008/</t>
+          <t>https://leetcode.com/u/Nithyashree273/</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>922525106222</t>
+          <t>922525106220</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>PAARGAVI R</t>
+          <t>NITHYASRI M</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>paargavi2007</t>
+          <t>Nithyasri2008</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -4834,24 +4834,24 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/paargavi2007/</t>
+          <t>https://leetcode.com/u/Nithyasri2008/</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>922525106223</t>
+          <t>922525106222</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>PAVITHRA S</t>
+          <t>PAARGAVI R</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>pavithra145</t>
+          <t>paargavi2007</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -4861,24 +4861,24 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/pavithra145/</t>
+          <t>https://leetcode.com/u/paargavi2007/</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>922525106224</t>
+          <t>922525106223</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>PAVITHRAN S</t>
+          <t>PAVITHRA S</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Pavithran_S_</t>
+          <t>pavithra145</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -4888,24 +4888,24 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Pavithran_S_/</t>
+          <t>https://leetcode.com/u/pavithra145/</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>922525106225</t>
+          <t>922525106224</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>PIRAVEEN M</t>
+          <t>PAVITHRAN S</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Piraveen2025</t>
+          <t>Pavithran_S_</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -4915,24 +4915,24 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Piraveen2025/</t>
+          <t>https://leetcode.com/u/Pavithran_S_/</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>922525106226</t>
+          <t>922525106225</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>PRABHAKARAN D</t>
+          <t>PIRAVEEN M</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>_d_Prabhakaran_</t>
+          <t>Piraveen2025</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -4942,24 +4942,24 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_d_Prabhakaran_/</t>
+          <t>https://leetcode.com/u/Piraveen2025/</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>922525106227</t>
+          <t>922525106226</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>PRADHOSH T</t>
+          <t>PRABHAKARAN D</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>pradhosh</t>
+          <t>_d_Prabhakaran_</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -4969,24 +4969,24 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/pradhosh/</t>
+          <t>https://leetcode.com/u/_d_Prabhakaran_/</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>922525106228</t>
+          <t>922525106227</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>PRAGALATHAN T</t>
+          <t>PRADHOSH T</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>pragalathan070108</t>
+          <t>pradhosh</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -4996,24 +4996,24 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/pragalathan070108/</t>
+          <t>https://leetcode.com/u/pradhosh/</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>922525106229</t>
+          <t>922525106228</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>PRANESH Y</t>
+          <t>PRAGALATHAN T</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Pranesh-Y</t>
+          <t>pragalathan070108</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -5023,24 +5023,24 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Pranesh-Y/</t>
+          <t>https://leetcode.com/u/pragalathan070108/</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>922525106230</t>
+          <t>922525106229</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>PRANITHASREE SAMINATHAN</t>
+          <t>PRANESH Y</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>pranithaashree</t>
+          <t>Pranesh-Y</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -5050,24 +5050,24 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/pranithaashree/</t>
+          <t>https://leetcode.com/u/Pranesh-Y/</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>922525106231</t>
+          <t>922525106230</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>PRAVEEN D</t>
+          <t>PRANITHASREE SAMINATHAN</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>praveen1247</t>
+          <t>pranithaashree</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -5077,24 +5077,24 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/praveen1247/</t>
+          <t>https://leetcode.com/u/pranithaashree/</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>922525106232</t>
+          <t>922525106231</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>PRAVEEN G</t>
+          <t>PRAVEEN D</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>praveen_3208</t>
+          <t>praveen1247</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -5104,14 +5104,14 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/praveen_3208/</t>
+          <t>https://leetcode.com/u/praveen1247/</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>922525106233</t>
+          <t>922525106232</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5121,7 +5121,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>PRAVEENGANESAN</t>
+          <t>praveen_3208</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -5131,24 +5131,24 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/PRAVEENGANESAN/</t>
+          <t>https://leetcode.com/u/praveen_3208/</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>922525106234</t>
+          <t>922525106233</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>PRAVEENKUMAR R</t>
+          <t>PRAVEEN G</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>itz_praveen_</t>
+          <t>PRAVEENGANESAN</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -5158,24 +5158,24 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itz_praveen_/</t>
+          <t>https://leetcode.com/u/PRAVEENGANESAN/</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>922525106235</t>
+          <t>922525106234</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>PREETHY M S</t>
+          <t>PRAVEENKUMAR R</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>preethy2007</t>
+          <t>itz_praveen_</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -5185,24 +5185,24 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/preethy2007/</t>
+          <t>https://leetcode.com/u/itz_praveen_/</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>922525106236</t>
+          <t>922525106235</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>PRITHIV S</t>
+          <t>PREETHY M S</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>prithiv16</t>
+          <t>preethy2007</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -5212,24 +5212,24 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/prithiv16/</t>
+          <t>https://leetcode.com/u/preethy2007/</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>922525106237</t>
+          <t>922525106236</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>PRIYADHARSHINI V</t>
+          <t>PRITHIV S</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>priyadharshini1551</t>
+          <t>prithiv16</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -5239,24 +5239,24 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/priyadharshini1551/</t>
+          <t>https://leetcode.com/u/prithiv16/</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>922525106238</t>
+          <t>922525106237</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>PRIYANKA A</t>
+          <t>PRIYADHARSHINI V</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Priyankaashok1201</t>
+          <t>priyadharshini1551</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -5266,24 +5266,24 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Priyankaashok1201/</t>
+          <t>https://leetcode.com/u/priyadharshini1551/</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>922525106239</t>
+          <t>922525106238</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>PRIYANKA K R</t>
+          <t>PRIYANKA A</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>priyankadhanush23</t>
+          <t>Priyankaashok1201</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -5293,24 +5293,24 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/priyankadhanush23/</t>
+          <t>https://leetcode.com/u/Priyankaashok1201/</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>922525106240</t>
+          <t>922525106239</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>RAGADHARSHINI S</t>
+          <t>PRIYANKA K R</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Ragadharshini_2181</t>
+          <t>priyankadhanush23</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -5320,24 +5320,24 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Ragadharshini_2181/</t>
+          <t>https://leetcode.com/u/priyankadhanush23/</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>922525106241</t>
+          <t>922525106240</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>RAGUNATH M</t>
+          <t>RAGADHARSHINI S</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>ragunath24</t>
+          <t>Ragadharshini_2181</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -5347,24 +5347,24 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/ragunath24/</t>
+          <t>https://leetcode.com/u/Ragadharshini_2181/</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>922525106242</t>
+          <t>922525106241</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>RAHULKAJAN M</t>
+          <t>RAGUNATH M</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>rahulkajan</t>
+          <t>ragunath24</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -5374,24 +5374,24 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/rahulkajan/</t>
+          <t>https://leetcode.com/u/ragunath24/</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>922525106243</t>
+          <t>922525106242</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>RAJAPRAGADEESWARAN R</t>
+          <t>RAHULKAJAN M</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>rajaprahadeeswaran</t>
+          <t>rahulkajan</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -5401,24 +5401,24 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/rajaprahadeeswaran/</t>
+          <t>https://leetcode.com/u/rahulkajan/</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>922525106244</t>
+          <t>922525106243</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>RANJANA T</t>
+          <t>RAJAPRAGADEESWARAN R</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>RANJANA_2007</t>
+          <t>rajaprahadeeswaran</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -5428,24 +5428,24 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/RANJANA_2007/</t>
+          <t>https://leetcode.com/u/rajaprahadeeswaran/</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>922525106246</t>
+          <t>922525106244</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>RASIKA S</t>
+          <t>RANJANA T</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>RASIKA_2008</t>
+          <t>RANJANA_2007</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -5455,24 +5455,24 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/RASIKA_2008/</t>
+          <t>https://leetcode.com/u/RANJANA_2007/</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>922525106247</t>
+          <t>922525106246</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>RATHISH R</t>
+          <t>RASIKA S</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Rathish2025</t>
+          <t>RASIKA_2008</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -5482,24 +5482,24 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rathish2025/</t>
+          <t>https://leetcode.com/u/RASIKA_2008/</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>922525106248</t>
+          <t>922525106247</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>RAVIKUMAR S</t>
+          <t>RATHISH R</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Ravikumar_14</t>
+          <t>Rathish2025</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -5509,78 +5509,78 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Ravikumar_14/</t>
+          <t>https://leetcode.com/u/Rathish2025/</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>922525106173</t>
+          <t>922525106248</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>LOGESH H</t>
+          <t>RAVIKUMAR S</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>logesh2008</t>
+          <t>Ravikumar_14</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE D</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/logesh2008/</t>
+          <t>https://leetcode.com/u/Ravikumar_14/</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>922525106005</t>
+          <t>922525106173</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>ADHITHMITHRAN P</t>
+          <t>LOGESH H</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>ADHITHMITHRAN</t>
+          <t>logesh2008</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE C</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/ADHITHMITHRAN/</t>
+          <t>https://leetcode.com/u/logesh2008/</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>922525106043</t>
+          <t>922525106005</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>BHARGAVI K</t>
+          <t>ADHITHMITHRAN P</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>ADHITHMITHRAN</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -5590,24 +5590,24 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/2/</t>
+          <t>https://leetcode.com/u/ADHITHMITHRAN/</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>922525106036</t>
+          <t>922525106043</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>BALARITHISH S</t>
+          <t>BHARGAVI K</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -5617,24 +5617,24 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/3/</t>
+          <t>https://leetcode.com/u/2/</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>922525106035</t>
+          <t>922525106036</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>BALAJI C</t>
+          <t>BALARITHISH S</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -5644,24 +5644,24 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/4/</t>
+          <t>https://leetcode.com/u/3/</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>922525106058</t>
+          <t>922525106035</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>DEEKSHA K</t>
+          <t>BALAJI C</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -5671,24 +5671,24 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/5/</t>
+          <t>https://leetcode.com/u/4/</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>922525106011</t>
+          <t>922525106058</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>AJAYKRISHNA R</t>
+          <t>DEEKSHA K</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>922525106011</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -5698,24 +5698,24 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106011/</t>
+          <t>https://leetcode.com/u/5/</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>922525106049</t>
+          <t>922525106011</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>BUVNESH N</t>
+          <t>AJAYKRISHNA R</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>922525106049</t>
+          <t>922525106011</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -5725,24 +5725,24 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106049/</t>
+          <t>https://leetcode.com/u/922525106011/</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>922525106052</t>
+          <t>922525106049</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>CHINMAYASRI K</t>
+          <t>BUVNESH N</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>922525106052</t>
+          <t>922525106049</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -5752,24 +5752,24 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106052/</t>
+          <t>https://leetcode.com/u/922525106049/</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>922525106055</t>
+          <t>922525106052</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>DARSHAN C</t>
+          <t>CHINMAYASRI K</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>922525106055</t>
+          <t>922525106052</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -5779,51 +5779,51 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106055/</t>
+          <t>https://leetcode.com/u/922525106052/</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>922525106093</t>
+          <t>922525106055</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>GIRIVASH P</t>
+          <t>DARSHAN C</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>922525106093</t>
+          <t>922525106055</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>ECE B</t>
+          <t>ECE A</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106093/</t>
+          <t>https://leetcode.com/u/922525106055/</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>922525106096</t>
+          <t>922525106093</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>GOPALA KRISHNAN C</t>
+          <t>GIRIVASH P</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>922525106096</t>
+          <t>922525106093</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -5833,24 +5833,24 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106096/</t>
+          <t>https://leetcode.com/u/922525106093/</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>922525106097</t>
+          <t>922525106096</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>GOPINATH R</t>
+          <t>GOPALA KRISHNAN C</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>922525106097</t>
+          <t>922525106096</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -5860,51 +5860,51 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106097/</t>
+          <t>https://leetcode.com/u/922525106096/</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>922525106056</t>
+          <t>922525106097</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>DARSHAN MANISH A</t>
+          <t>GOPINATH R</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>2007darshan</t>
+          <t>922525106097</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE B</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/2007darshan/</t>
+          <t>https://leetcode.com/u/922525106097/</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>922525106006</t>
+          <t>922525106056</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>AFTON AJ</t>
+          <t>DARSHAN MANISH A</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>afton_2008</t>
+          <t>2007darshan</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -5914,24 +5914,24 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/afton_2008/</t>
+          <t>https://leetcode.com/u/2007darshan/</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>922525106028</t>
+          <t>922525106006</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>ARUN C</t>
+          <t>AFTON AJ</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>AGmXRQ1yTe</t>
+          <t>afton_2008</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -5941,24 +5941,24 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/AGmXRQ1yTe/</t>
+          <t>https://leetcode.com/u/afton_2008/</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>922525106013</t>
+          <t>922525106028</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>AJITH KUMAR M</t>
+          <t>ARUN C</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>ajit_kumar_23</t>
+          <t>AGmXRQ1yTe</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -5968,24 +5968,24 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/ajit_kumar_23/</t>
+          <t>https://leetcode.com/u/AGmXRQ1yTe/</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>922525106019</t>
+          <t>922525106013</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>ANBARASU S</t>
+          <t>AJITH KUMAR M</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Anbarasu28122007</t>
+          <t>ajit_kumar_23</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -5995,24 +5995,24 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Anbarasu28122007/</t>
+          <t>https://leetcode.com/u/ajit_kumar_23/</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>922525106020</t>
+          <t>922525106019</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>ANJITHAA N</t>
+          <t>ANBARASU S</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Anjithaa2006</t>
+          <t>Anbarasu28122007</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -6022,24 +6022,24 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Anjithaa2006/</t>
+          <t>https://leetcode.com/u/Anbarasu28122007/</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>922525106021</t>
+          <t>922525106020</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>ANOOP C</t>
+          <t>ANJITHAA N</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>anoop_appuz</t>
+          <t>Anjithaa2006</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -6049,24 +6049,24 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/anoop_appuz/</t>
+          <t>https://leetcode.com/u/Anjithaa2006/</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>922525106022</t>
+          <t>922525106021</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>ANUJA S</t>
+          <t>ANOOP C</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>anuja008</t>
+          <t>anoop_appuz</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -6076,24 +6076,24 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/anuja008/</t>
+          <t>https://leetcode.com/u/anoop_appuz/</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>922525106001</t>
+          <t>922525106022</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>AASHIFA SAHANAJ M</t>
+          <t>ANUJA S</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>aashifasahanaj</t>
+          <t>anuja008</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -6103,24 +6103,24 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/aashifasahanaj/</t>
+          <t>https://leetcode.com/u/anuja008/</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>922525106008</t>
+          <t>922525106027</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>AHELESH G S</t>
+          <t>Arulesh K</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>arul2008</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/B/</t>
+          <t>https://leetcode.com/u/arul2008/</t>
         </is>
       </c>
     </row>
@@ -6893,17 +6893,17 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>922525106027</t>
+          <t>922525106008</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Arulesh K</t>
+          <t>AHELESH G S</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>arul2008</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -6913,24 +6913,24 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/arul2008/</t>
+          <t>https://leetcode.com/u/B/</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>922525106002</t>
+          <t>922525106001</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>AAZHIGA N</t>
+          <t>AASHIFA SAHANAJ M</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>AAZHIGA</t>
+          <t>aashifasahanaj</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -6940,24 +6940,24 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/AAZHIGA/</t>
+          <t>https://leetcode.com/u/aashifasahanaj/</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>922525106003</t>
+          <t>922525106002</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>ABINAYA N</t>
+          <t>AAZHIGA N</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Abinaya7095</t>
+          <t>AAZHIGA</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -6967,24 +6967,24 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Abinaya7095/</t>
+          <t>https://leetcode.com/u/AAZHIGA/</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>922525106004</t>
+          <t>922525106003</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Abirami R</t>
+          <t>ABINAYA N</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>abirami8072</t>
+          <t>Abinaya7095</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -6994,24 +6994,24 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/abirami8072/</t>
+          <t>https://leetcode.com/u/Abinaya7095/</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>922525106007</t>
+          <t>922525106004</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>AGATHEESWARAN K</t>
+          <t>Abirami R</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>agatheeswarank</t>
+          <t>abirami8072</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -7021,24 +7021,24 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/agatheeswarank/</t>
+          <t>https://leetcode.com/u/abirami8072/</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>922525106009</t>
+          <t>922525106007</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>AISHWARYA G</t>
+          <t>AGATHEESWARAN K</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>codewithaish</t>
+          <t>agatheeswarank</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -7048,24 +7048,24 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/codewithaish/</t>
+          <t>https://leetcode.com/u/agatheeswarank/</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>922525106015</t>
+          <t>922525106009</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Akshara KR</t>
+          <t>AISHWARYA G</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Akshara015</t>
+          <t>codewithaish</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -7075,24 +7075,24 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Akshara015/</t>
+          <t>https://leetcode.com/u/codewithaish/</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>922525106017</t>
+          <t>922525106015</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>ALAGESHWARAN J</t>
+          <t>Akshara KR</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Alageshwaran2008</t>
+          <t>Akshara015</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -7102,24 +7102,24 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Alageshwaran2008/</t>
+          <t>https://leetcode.com/u/Akshara015/</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>922525106018</t>
+          <t>922525106017</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Amirdavarsini K S</t>
+          <t>ALAGESHWARAN J</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>amirda_varsini_2007</t>
+          <t>Alageshwaran2008</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -7129,24 +7129,24 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/amirda_varsini_2007/</t>
+          <t>https://leetcode.com/u/Alageshwaran2008/</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>922525106023</t>
+          <t>922525106018</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>ANUSRI R</t>
+          <t>Amirdavarsini K S</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Anusri_2008</t>
+          <t>amirda_varsini_2007</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -7156,24 +7156,24 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Anusri_2008/</t>
+          <t>https://leetcode.com/u/amirda_varsini_2007/</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>922525106024</t>
+          <t>922525106023</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>ANUSYA B</t>
+          <t>ANUSRI R</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>ANUSYA_30</t>
+          <t>Anusri_2008</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -7183,24 +7183,24 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/ANUSYA_30/</t>
+          <t>https://leetcode.com/u/Anusri_2008/</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>922525106029</t>
+          <t>922525106024</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>R ARUN PRASATH</t>
+          <t>ANUSYA B</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Arunravi1810</t>
+          <t>ANUSYA_30</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -7210,24 +7210,24 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Arunravi1810/</t>
+          <t>https://leetcode.com/u/ANUSYA_30/</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>922525106030</t>
+          <t>922525106029</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>ARUNKUMAR K</t>
+          <t>R ARUN PRASATH</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Arunkumar2008</t>
+          <t>Arunravi1810</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -7237,24 +7237,24 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Arunkumar2008/</t>
+          <t>https://leetcode.com/u/Arunravi1810/</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>922525106031</t>
+          <t>922525106030</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>ARUNPRASANTH T</t>
+          <t>ARUNKUMAR K</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>arunprasanth6435</t>
+          <t>Arunkumar2008</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -7264,24 +7264,24 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/arunprasanth6435/</t>
+          <t>https://leetcode.com/u/Arunkumar2008/</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>922525106032</t>
+          <t>922525106031</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>ARVIN SHANKARA</t>
+          <t>ARUNPRASANTH T</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Arvin</t>
+          <t>arunprasanth6435</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -7291,24 +7291,24 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Arvin/</t>
+          <t>https://leetcode.com/u/arunprasanth6435/</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>922525106033</t>
+          <t>922525106032</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>ASHOK KUMAR P</t>
+          <t>ARVIN SHANKARA</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>ASHOKKUMAR18</t>
+          <t>Arvin</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -7318,24 +7318,24 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/ASHOKKUMAR18/</t>
+          <t>https://leetcode.com/u/Arvin/</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>922525106034</t>
+          <t>922525106033</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Asmitha E</t>
+          <t>ASHOK KUMAR P</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>ASHOKKUMAR18</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -7345,24 +7345,24 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/1/</t>
+          <t>https://leetcode.com/u/ASHOKKUMAR18/</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>922525106042</t>
+          <t>922525106034</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>BHARATHWAJ S</t>
+          <t>Asmitha E</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>BharathwajX</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -7372,24 +7372,24 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/BharathwajX/</t>
+          <t>https://leetcode.com/u/1/</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>922525106053</t>
+          <t>922525106042</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>CHINNAPPAN S</t>
+          <t>BHARATHWAJ S</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>chinnappanrajniselvi</t>
+          <t>BharathwajX</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -7399,24 +7399,24 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/chinnappanrajniselvi/</t>
+          <t>https://leetcode.com/u/BharathwajX/</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>922525106060</t>
+          <t>922525106053</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>DESMA SHALINI K</t>
+          <t>CHINNAPPAN S</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>desmashalini</t>
+          <t>chinnappanrajniselvi</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -7426,24 +7426,24 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/desmashalini/</t>
+          <t>https://leetcode.com/u/chinnappanrajniselvi/</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>922525106061</t>
+          <t>922525106060</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>DEVA V</t>
+          <t>DESMA SHALINI K</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Devaece</t>
+          <t>desmashalini</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -7453,24 +7453,24 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Devaece/</t>
+          <t>https://leetcode.com/u/desmashalini/</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>922525106062</t>
+          <t>922525106061</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>DHAKSESH PRANAV P</t>
+          <t>DEVA V</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Dhaksesh_Pranav_P</t>
+          <t>Devaece</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -7480,24 +7480,24 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Dhaksesh_Pranav_P/</t>
+          <t>https://leetcode.com/u/Devaece/</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>922525106063</t>
+          <t>922525106062</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>DHANASRI R</t>
+          <t>DHAKSESH PRANAV P</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Dhanasri_r</t>
+          <t>Dhaksesh_Pranav_P</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -7507,51 +7507,51 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Dhanasri_r/</t>
+          <t>https://leetcode.com/u/Dhaksesh_Pranav_P/</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>922525106064</t>
+          <t>922525106063</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>DHANIKA S</t>
+          <t>DHANASRI R</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>922525106064</t>
+          <t>Dhanasri_r</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>ECE B</t>
+          <t>ECE A</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106064/</t>
+          <t>https://leetcode.com/u/Dhanasri_r/</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>922525106065</t>
+          <t>922525106064</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>DHANUSHRI D</t>
+          <t>DHANIKA S</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>922525106065</t>
+          <t>922525106064</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -7561,24 +7561,24 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106065/</t>
+          <t>https://leetcode.com/u/922525106064/</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>922525106066</t>
+          <t>922525106065</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>DHANYA K</t>
+          <t>DHANUSHRI D</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>922525106066</t>
+          <t>922525106065</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -7588,24 +7588,24 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106066/</t>
+          <t>https://leetcode.com/u/922525106065/</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>922525106067</t>
+          <t>922525106066</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>DHARAN.K</t>
+          <t>DHANYA K</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>922525106067</t>
+          <t>922525106066</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -7615,24 +7615,24 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106067/</t>
+          <t>https://leetcode.com/u/922525106066/</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>922525106068</t>
+          <t>922525106067</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>DHARANEESH K</t>
+          <t>DHARAN.K</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>dharaneeshk</t>
+          <t>922525106067</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -7642,24 +7642,24 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/dharaneeshk/</t>
+          <t>https://leetcode.com/u/922525106067/</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>922525106069</t>
+          <t>922525106068</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>DHARANESH S</t>
+          <t>DHARANEESH K</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>922525106069</t>
+          <t>dharaneeshk</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -7669,24 +7669,24 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106069/</t>
+          <t>https://leetcode.com/u/dharaneeshk/</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>922525106070</t>
+          <t>922525106069</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>DHARANI M</t>
+          <t>DHARANESH S</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>922525106070</t>
+          <t>922525106069</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -7696,24 +7696,24 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106070/</t>
+          <t>https://leetcode.com/u/922525106069/</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>922525106071</t>
+          <t>922525106070</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>DHARANI V</t>
+          <t>DHARANI M</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>922525106071</t>
+          <t>922525106070</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -7723,24 +7723,24 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106071/</t>
+          <t>https://leetcode.com/u/922525106070/</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>922525106072</t>
+          <t>922525106071</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>DAHARANESH R</t>
+          <t>DHARANI V</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>922525106072</t>
+          <t>922525106071</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -7750,24 +7750,24 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106072/</t>
+          <t>https://leetcode.com/u/922525106071/</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>922525106073</t>
+          <t>922525106072</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>DHARMENDRA M P</t>
+          <t>DAHARANESH R</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>922525106073</t>
+          <t>922525106072</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -7777,24 +7777,24 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106073/</t>
+          <t>https://leetcode.com/u/922525106072/</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>922525106074</t>
+          <t>922525106073</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>DHARSHINI P</t>
+          <t>DHARMENDRA M P</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Dharshini_74</t>
+          <t>922525106073</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -7804,24 +7804,24 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Dharshini_74/</t>
+          <t>https://leetcode.com/u/922525106073/</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>922525106075</t>
+          <t>922525106074</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>DHARSHINI S</t>
+          <t>DHARSHINI P</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>922525106075</t>
+          <t>Dharshini_74</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -7831,24 +7831,24 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106075/</t>
+          <t>https://leetcode.com/u/Dharshini_74/</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>922525106077</t>
+          <t>922525106075</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>DHARUN T</t>
+          <t>DHARSHINI S</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>922525106077</t>
+          <t>922525106075</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -7858,24 +7858,24 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106077/</t>
+          <t>https://leetcode.com/u/922525106075/</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>922525106078</t>
+          <t>922525106077</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>DHILIP P</t>
+          <t>DHARUN T</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>922525106078</t>
+          <t>922525106077</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -7885,24 +7885,24 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106078/</t>
+          <t>https://leetcode.com/u/922525106077/</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>922525106079</t>
+          <t>922525106078</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>DHINAKAR A</t>
+          <t>DHILIP P</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>922525106079</t>
+          <t>922525106078</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -7912,78 +7912,78 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106079/</t>
+          <t>https://leetcode.com/u/922525106078/</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>922525106147</t>
+          <t>922525106079</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>KATHIR E</t>
+          <t>DHINAKAR A</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>kathir__21</t>
+          <t>922525106079</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE B</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kathir__21/</t>
+          <t>https://leetcode.com/u/922525106079/</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>922525106080</t>
+          <t>922525106147</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>DHIVAKAR R</t>
+          <t>KATHIR E</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>DhivakarR</t>
+          <t>kathir__21</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>ECE B</t>
+          <t>ECE C</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/DhivakarR/</t>
+          <t>https://leetcode.com/u/kathir__21/</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>922525106081</t>
+          <t>922525106080</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>DILIPKUMAR K</t>
+          <t>DHIVAKAR R</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>922525106081</t>
+          <t>DhivakarR</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -7993,24 +7993,24 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106081/</t>
+          <t>https://leetcode.com/u/DhivakarR/</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>922525106082</t>
+          <t>922525106081</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>DINESH P</t>
+          <t>DILIPKUMAR K</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Dinesh_106082</t>
+          <t>922525106081</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -8020,24 +8020,24 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Dinesh_106082/</t>
+          <t>https://leetcode.com/u/922525106081/</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>922525106083</t>
+          <t>922525106082</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>DINESHKUMAR P</t>
+          <t>DINESH P</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>922525106083</t>
+          <t>Dinesh_106082</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -8047,24 +8047,24 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106083/</t>
+          <t>https://leetcode.com/u/Dinesh_106082/</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>922525106084</t>
+          <t>922525106083</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>DINESHKUMAR V</t>
+          <t>DINESHKUMAR P</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>922525106084</t>
+          <t>922525106083</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -8074,24 +8074,24 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106084/</t>
+          <t>https://leetcode.com/u/922525106083/</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>922525106085</t>
+          <t>922525106084</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>DIVYA ROJA R</t>
+          <t>DINESHKUMAR V</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>922525106085</t>
+          <t>922525106084</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -8101,24 +8101,24 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106085/</t>
+          <t>https://leetcode.com/u/922525106084/</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>922525106086</t>
+          <t>922525106085</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>DIVYA V</t>
+          <t>DIVYA ROJA R</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>princess-nk</t>
+          <t>922525106085</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -8128,24 +8128,24 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/princess-nk/</t>
+          <t>https://leetcode.com/u/922525106085/</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>922525106087</t>
+          <t>922525106086</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>DIVYADHARSHINI G</t>
+          <t>DIVYA V</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>922525106087</t>
+          <t>princess-nk</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -8155,24 +8155,24 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106087/</t>
+          <t>https://leetcode.com/u/princess-nk/</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>922525106088</t>
+          <t>922525106087</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>DIVYADHARSHINI S</t>
+          <t>DIVYADHARSHINI G</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>922525106088</t>
+          <t>922525106087</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -8182,24 +8182,24 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106088/</t>
+          <t>https://leetcode.com/u/922525106087/</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>922525106089</t>
+          <t>922525106088</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>DURAIMURUGAN K</t>
+          <t>DIVYADHARSHINI S</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>922525106089</t>
+          <t>922525106088</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -8209,24 +8209,24 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106089/</t>
+          <t>https://leetcode.com/u/922525106088/</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>922525106090</t>
+          <t>922525106089</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>ELAKKIYA N</t>
+          <t>DURAIMURUGAN K</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>922525106090</t>
+          <t>922525106089</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -8236,24 +8236,24 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106090/</t>
+          <t>https://leetcode.com/u/922525106089/</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>922525106091</t>
+          <t>922525106090</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>ELAVARASAN R</t>
+          <t>ELAKKIYA N</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>922525106091</t>
+          <t>922525106090</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -8263,24 +8263,24 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106091/</t>
+          <t>https://leetcode.com/u/922525106090/</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>922525106092</t>
+          <t>922525106091</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>ELAVARASU P</t>
+          <t>ELAVARASAN R</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>922525106092</t>
+          <t>922525106091</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -8290,24 +8290,24 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106092/</t>
+          <t>https://leetcode.com/u/922525106091/</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>922525106094</t>
+          <t>922525106092</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>GOKUL D</t>
+          <t>ELAVARASU P</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Gokul_tamilan_india</t>
+          <t>922525106092</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -8317,24 +8317,24 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Gokul_tamilan_india/</t>
+          <t>https://leetcode.com/u/922525106092/</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>922525106095</t>
+          <t>922525106094</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>GOMATHI R</t>
+          <t>GOKUL D</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>gomathi_0709</t>
+          <t>Gokul_tamilan_india</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -8344,24 +8344,24 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/gomathi_0709/</t>
+          <t>https://leetcode.com/u/Gokul_tamilan_india/</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>922525106098</t>
+          <t>922525106095</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>GOUTHAM R J</t>
+          <t>GOMATHI R</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>922525106098</t>
+          <t>gomathi_0709</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -8371,24 +8371,24 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106098/</t>
+          <t>https://leetcode.com/u/gomathi_0709/</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>922525106099</t>
+          <t>922525106098</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>GOVARTHAN K S</t>
+          <t>GOUTHAM R J</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>GOVARTHANKS</t>
+          <t>922525106098</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -8398,24 +8398,24 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/GOVARTHANKS/</t>
+          <t>https://leetcode.com/u/922525106098/</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>922525106100</t>
+          <t>922525106099</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>GOWRIKA K P</t>
+          <t>GOVARTHAN K S</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>922525106100</t>
+          <t>GOVARTHANKS</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -8425,24 +8425,24 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106100/</t>
+          <t>https://leetcode.com/u/GOVARTHANKS/</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>922525106101</t>
+          <t>922525106100</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>GOWRISANKAR S</t>
+          <t>GOWRIKA K P</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>922524106101</t>
+          <t>922525106100</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -8452,24 +8452,24 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922524106101/</t>
+          <t>https://leetcode.com/u/922525106100/</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>922525106102</t>
+          <t>922525106101</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>GOWSICK S</t>
+          <t>GOWRISANKAR S</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>922525106106</t>
+          <t>922524106101</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -8479,24 +8479,24 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106106/</t>
+          <t>https://leetcode.com/u/922524106101/</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>922525106103</t>
+          <t>922525106102</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>GOWTHAM M</t>
+          <t>GOWSICK S</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>922525106103</t>
+          <t>922525106106</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -8506,24 +8506,24 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106103/</t>
+          <t>https://leetcode.com/u/922525106106/</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>922525106104</t>
+          <t>922525106103</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>GOWTHAM R</t>
+          <t>GOWTHAM M</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>922525106104</t>
+          <t>922525106103</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -8533,24 +8533,24 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106104/</t>
+          <t>https://leetcode.com/u/922525106103/</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>922525106105</t>
+          <t>922525106104</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>GOWTHAM S</t>
+          <t>GOWTHAM R</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Gowtham_080</t>
+          <t>922525106104</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -8560,24 +8560,24 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Gowtham_080/</t>
+          <t>https://leetcode.com/u/922525106104/</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>922525106107</t>
+          <t>922525106105</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>GUNA SHREE V</t>
+          <t>GOWTHAM S</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Gunashree20</t>
+          <t>Gowtham_080</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -8587,24 +8587,24 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Gunashree20/</t>
+          <t>https://leetcode.com/u/Gowtham_080/</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>922525106108</t>
+          <t>922525106107</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>GURUSARAN R</t>
+          <t>GUNA SHREE V</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>922525106108</t>
+          <t>Gunashree20</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -8614,24 +8614,24 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106108/</t>
+          <t>https://leetcode.com/u/Gunashree20/</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>922525106109</t>
+          <t>922525106108</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>HANSHIKAVARSA K S</t>
+          <t>GURUSARAN R</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>922525106109</t>
+          <t>922525106108</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -8641,24 +8641,24 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106109/</t>
+          <t>https://leetcode.com/u/922525106108/</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>922525106110</t>
+          <t>922525106109</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>HARI HARAN R</t>
+          <t>HANSHIKAVARSA K S</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>922525106110</t>
+          <t>922525106109</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -8668,24 +8668,24 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106110/</t>
+          <t>https://leetcode.com/u/922525106109/</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>922525106111</t>
+          <t>922525106110</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>HARIS S</t>
+          <t>HARI HARAN R</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>922525106111</t>
+          <t>922525106110</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -8695,24 +8695,24 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106111/</t>
+          <t>https://leetcode.com/u/922525106110/</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>922525106112</t>
+          <t>922525106111</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>HARINI S</t>
+          <t>HARIS S</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>922525106112</t>
+          <t>922525106111</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -8722,24 +8722,24 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106112/</t>
+          <t>https://leetcode.com/u/922525106111/</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>922525106113</t>
+          <t>922525106112</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>HARIS M</t>
+          <t>HARINI S</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>922525106113</t>
+          <t>922525106112</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -8749,24 +8749,24 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106113/</t>
+          <t>https://leetcode.com/u/922525106112/</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>922525106114</t>
+          <t>922525106113</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>HARIS RAGAVENDAR A</t>
+          <t>HARIS M</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>922525106114</t>
+          <t>922525106113</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -8776,24 +8776,24 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106114/</t>
+          <t>https://leetcode.com/u/922525106113/</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>922525106115</t>
+          <t>922525106114</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>HARISH D</t>
+          <t>HARIS RAGAVENDAR A</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>922525106115</t>
+          <t>922525106114</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -8803,24 +8803,24 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106115/</t>
+          <t>https://leetcode.com/u/922525106114/</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>922525106116</t>
+          <t>922525106115</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>HARISH M S</t>
+          <t>HARISH D</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>922525106116</t>
+          <t>922525106115</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -8830,24 +8830,24 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106116/</t>
+          <t>https://leetcode.com/u/922525106115/</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>922525106117</t>
+          <t>922525106116</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>HARISH P</t>
+          <t>HARISH M S</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>922525106117</t>
+          <t>922525106116</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -8857,24 +8857,24 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106117/</t>
+          <t>https://leetcode.com/u/922525106116/</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>922525106118</t>
+          <t>922525106117</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>HARISHANKAR R</t>
+          <t>HARISH P</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>922525106118</t>
+          <t>922525106117</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -8884,24 +8884,24 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106118/</t>
+          <t>https://leetcode.com/u/922525106117/</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>922525106119</t>
+          <t>922525106118</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>HAVISHMATHI S</t>
+          <t>HARISHANKAR R</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>HAVISHMATHIS</t>
+          <t>922525106118</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -8911,24 +8911,24 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/HAVISHMATHIS/</t>
+          <t>https://leetcode.com/u/922525106118/</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>922525106120</t>
+          <t>922525106119</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>HEMAA SRI A</t>
+          <t>HAVISHMATHI S</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>922525106120</t>
+          <t>HAVISHMATHIS</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -8938,24 +8938,24 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106120/</t>
+          <t>https://leetcode.com/u/HAVISHMATHIS/</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>922525106121</t>
+          <t>922525106120</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>HEMAVARSHINI S</t>
+          <t>HEMAA SRI A</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>922525106121</t>
+          <t>922525106120</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -8965,24 +8965,24 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106121/</t>
+          <t>https://leetcode.com/u/922525106120/</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>922525106122</t>
+          <t>922525106121</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>HIRESH K</t>
+          <t>HEMAVARSHINI S</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>922525106122</t>
+          <t>922525106121</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -8992,24 +8992,24 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106122/</t>
+          <t>https://leetcode.com/u/922525106121/</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>922525106123</t>
+          <t>922525106122</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>INBNATHAN S</t>
+          <t>HIRESH K</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>922525106123</t>
+          <t>922525106122</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -9019,24 +9019,24 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106123/</t>
+          <t>https://leetcode.com/u/922525106122/</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>922525106124</t>
+          <t>922525106123</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>INDHIRAJITH K</t>
+          <t>INBNATHAN S</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>922525106124</t>
+          <t>922525106123</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -9046,24 +9046,24 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106124/</t>
+          <t>https://leetcode.com/u/922525106123/</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>922525106125</t>
+          <t>922525106124</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>JAI GANESH I</t>
+          <t>INDHIRAJITH K</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>922525106125</t>
+          <t>922525106124</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -9073,24 +9073,24 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106125/</t>
+          <t>https://leetcode.com/u/922525106124/</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>922525106126</t>
+          <t>922525106125</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>JANA S</t>
+          <t>JAI GANESH I</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>922525106126</t>
+          <t>922525106125</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -9100,51 +9100,51 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/922525106126/</t>
+          <t>https://leetcode.com/u/922525106125/</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>922525106127</t>
+          <t>922525106126</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>JANANI A</t>
+          <t>JANA S</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>janani_asohkan</t>
+          <t>922525106126</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE B</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/janani_asohkan/</t>
+          <t>https://leetcode.com/u/922525106126/</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>922525106128</t>
+          <t>922525106127</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>JASHVANTH J S</t>
+          <t>JANANI A</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>jashvanth2007</t>
+          <t>janani_asohkan</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -9154,24 +9154,24 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/jashvanth2007/</t>
+          <t>https://leetcode.com/u/janani_asohkan/</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>922525106130</t>
+          <t>922525106128</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>JAYASAKTHI V</t>
+          <t>JASHVANTH J S</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>jayasakthi_25</t>
+          <t>jashvanth2007</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -9181,24 +9181,24 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/jayasakthi_25/</t>
+          <t>https://leetcode.com/u/jashvanth2007/</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>922525106132</t>
+          <t>922525106130</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Jeevan bala G</t>
+          <t>JAYASAKTHI V</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>jeevanbala142008</t>
+          <t>jayasakthi_25</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -9208,24 +9208,24 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/jeevanbala142008/</t>
+          <t>https://leetcode.com/u/jayasakthi_25/</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>922525106133</t>
+          <t>922525106132</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>JEEVADHARSHAN R R</t>
+          <t>Jeevan bala G</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>dharshanjeeva</t>
+          <t>jeevanbala142008</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -9235,24 +9235,24 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/dharshanjeeva/</t>
+          <t>https://leetcode.com/u/jeevanbala142008/</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>922525106134</t>
+          <t>922525106133</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>JEEVANAA S</t>
+          <t>JEEVADHARSHAN R R</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>jeevanaa_174_</t>
+          <t>dharshanjeeva</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -9262,24 +9262,24 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/jeevanaa_174_/</t>
+          <t>https://leetcode.com/u/dharshanjeeva/</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>922525106135</t>
+          <t>922525106134</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>JERSHITH J S</t>
+          <t>JEEVANAA S</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Jerry2008</t>
+          <t>jeevanaa_174_</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -9289,24 +9289,24 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Jerry2008/</t>
+          <t>https://leetcode.com/u/jeevanaa_174_/</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>922525106136</t>
+          <t>922525106135</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>JOSHITHA KANNAN SUDHA</t>
+          <t>JERSHITH J S</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Joshi_666</t>
+          <t>Jerry2008</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -9316,24 +9316,24 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Joshi_666/</t>
+          <t>https://leetcode.com/u/Jerry2008/</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>922525106137</t>
+          <t>922525106136</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Jothi harshan D K</t>
+          <t>JOSHITHA KANNAN SUDHA</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Jothiharshan16</t>
+          <t>Joshi_666</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -9343,24 +9343,24 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Jothiharshan16/</t>
+          <t>https://leetcode.com/u/Joshi_666/</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>922525106138</t>
+          <t>922525106137</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>JOTHISHA K S</t>
+          <t>Jothi harshan D K</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Jothi-</t>
+          <t>Jothiharshan16</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -9370,24 +9370,24 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Jothi-/</t>
+          <t>https://leetcode.com/u/Jothiharshan16/</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>922525106139</t>
+          <t>922525106138</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>KAMALINI G</t>
+          <t>JOTHISHA K S</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>_kamalini_</t>
+          <t>Jothi-</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -9397,24 +9397,24 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_kamalini_/</t>
+          <t>https://leetcode.com/u/Jothi-/</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>922525106140</t>
+          <t>922525106139</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>KANISHKA A R</t>
+          <t>KAMALINI G</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>26kanishka</t>
+          <t>_kamalini_</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -9424,24 +9424,24 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/26kanishka/</t>
+          <t>https://leetcode.com/u/_kamalini_/</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>922525106142</t>
+          <t>922525106140</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>KANITHRA R</t>
+          <t>KANISHKA A R</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>kanithraakila</t>
+          <t>26kanishka</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -9451,24 +9451,24 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kanithraakila/</t>
+          <t>https://leetcode.com/u/26kanishka/</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>922525106143</t>
+          <t>922525106142</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>KARISHMA M</t>
+          <t>KANITHRA R</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Karishma_m_08</t>
+          <t>kanithraakila</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -9478,24 +9478,24 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Karishma_m_08/</t>
+          <t>https://leetcode.com/u/kanithraakila/</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>922525106144</t>
+          <t>922525106143</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>KARMUKILAN J</t>
+          <t>KARISHMA M</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>karmukilan567</t>
+          <t>Karishma_m_08</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -9505,24 +9505,24 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/karmukilan567/</t>
+          <t>https://leetcode.com/u/Karishma_m_08/</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>922525106145</t>
+          <t>922525106144</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>KARSHANA SRI V</t>
+          <t>KARMUKILAN J</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>karshana_234</t>
+          <t>karmukilan567</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -9532,24 +9532,24 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/karshana_234/</t>
+          <t>https://leetcode.com/u/karmukilan567/</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>922525106146</t>
+          <t>922525106145</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>KARTHIKA K</t>
+          <t>KARSHANA SRI V</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Karthi270827</t>
+          <t>karshana_234</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -9559,24 +9559,24 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Karthi270827/</t>
+          <t>https://leetcode.com/u/karshana_234/</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>922525106148</t>
+          <t>922525106146</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>KAVIMALAR A</t>
+          <t>KARTHIKA K</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>kavimalar08</t>
+          <t>Karthi270827</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -9586,24 +9586,24 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kavimalar08/</t>
+          <t>https://leetcode.com/u/Karthi270827/</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>922525106149</t>
+          <t>922525106148</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>KAVIN KUMAR S</t>
+          <t>KAVIMALAR A</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>KAVIN__26</t>
+          <t>kavimalar08</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -9613,78 +9613,78 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/KAVIN__26/</t>
+          <t>https://leetcode.com/u/kavimalar08/</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>922525106012</t>
+          <t>922525106149</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>AJAYKUMAR A L</t>
+          <t>KAVIN KUMAR S</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>AjaykumarAL</t>
+          <t>KAVIN__26</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE C</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/AjaykumarAL/</t>
+          <t>https://leetcode.com/u/KAVIN__26/</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>922525106150</t>
+          <t>922525106012</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>KAVINKUMAR M</t>
+          <t>AJAYKUMAR A L</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>kavinleet</t>
+          <t>AjaykumarAL</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE A</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kavinleet/</t>
+          <t>https://leetcode.com/u/AjaykumarAL/</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>922525106151</t>
+          <t>922525106150</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>KAVIPRIYA J</t>
+          <t>KAVINKUMAR M</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>_kavipriya_16</t>
+          <t>kavinleet</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -9694,24 +9694,24 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_kavipriya_16/</t>
+          <t>https://leetcode.com/u/kavinleet/</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>922525106152</t>
+          <t>922525106151</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>KAVIPRIYA R</t>
+          <t>KAVIPRIYA J</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>KAVI_RAVI</t>
+          <t>_kavipriya_16</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -9721,24 +9721,24 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/KAVI_RAVI/</t>
+          <t>https://leetcode.com/u/_kavipriya_16/</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>922525106153</t>
+          <t>922525106152</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>KAVIYARASU K</t>
+          <t>KAVIPRIYA R</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>kavi12d</t>
+          <t>KAVI_RAVI</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -9748,24 +9748,24 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kavi12d/</t>
+          <t>https://leetcode.com/u/KAVI_RAVI/</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>922525106154</t>
+          <t>922525106153</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>KAVYA A</t>
+          <t>KAVIYARASU K</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>itzz__kavya02</t>
+          <t>kavi12d</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -9775,24 +9775,24 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itzz__kavya02/</t>
+          <t>https://leetcode.com/u/kavi12d/</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>922525106155</t>
+          <t>922525106154</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>KAYALVIZHI S</t>
+          <t>KAVYA A</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>27kayalvizhi</t>
+          <t>itzz__kavya02</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -9802,24 +9802,24 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/27kayalvizhi/</t>
+          <t>https://leetcode.com/u/itzz__kavya02/</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>922525106156</t>
+          <t>922525106155</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>KEERTHANA S</t>
+          <t>KAYALVIZHI S</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>keerthana_19selvam</t>
+          <t>27kayalvizhi</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -9829,24 +9829,24 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/keerthana_19selvam/</t>
+          <t>https://leetcode.com/u/27kayalvizhi/</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>922525106157</t>
+          <t>922525106156</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>KESAVINI M</t>
+          <t>KEERTHANA S</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>KESAVINI892</t>
+          <t>keerthana_19selvam</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -9856,24 +9856,24 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/KESAVINI892/</t>
+          <t>https://leetcode.com/u/keerthana_19selvam/</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>922525106158</t>
+          <t>922525106157</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>KIRUTHIKA S</t>
+          <t>KESAVINI M</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>kiruthika_selvanathan05092007</t>
+          <t>KESAVINI892</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -9883,24 +9883,24 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kiruthika_selvanathan05092007/</t>
+          <t>https://leetcode.com/u/KESAVINI892/</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>922525106160</t>
+          <t>922525106158</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>KOHUL V</t>
+          <t>KIRUTHIKA S</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>kohul_v</t>
+          <t>kiruthika_selvanathan05092007</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -9910,24 +9910,24 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kohul_v/</t>
+          <t>https://leetcode.com/u/kiruthika_selvanathan05092007/</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>922525106161</t>
+          <t>922525106160</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>KOWSHIK M</t>
+          <t>KOHUL V</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>kowshikm23</t>
+          <t>kohul_v</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -9937,24 +9937,24 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kowshikm23/</t>
+          <t>https://leetcode.com/u/kohul_v/</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>922525106162</t>
+          <t>922525106161</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>KOWSHIK R</t>
+          <t>KOWSHIK M</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>kowshik_rk_</t>
+          <t>kowshikm23</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -9964,24 +9964,24 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kowshik_rk_/</t>
+          <t>https://leetcode.com/u/kowshikm23/</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>922525106163</t>
+          <t>922525106162</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>KOWSHIKA B</t>
+          <t>KOWSHIK R</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Kowshika08</t>
+          <t>kowshik_rk_</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -9991,24 +9991,24 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Kowshika08/</t>
+          <t>https://leetcode.com/u/kowshik_rk_/</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>922525106164</t>
+          <t>922525106163</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>KOWSHIKA M S</t>
+          <t>KOWSHIKA B</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>kowshika_moorthi</t>
+          <t>Kowshika08</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -10018,24 +10018,24 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kowshika_moorthi/</t>
+          <t>https://leetcode.com/u/Kowshika08/</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>922525106165</t>
+          <t>922525106164</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>KOWSHIKAN P</t>
+          <t>KOWSHIKA M S</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>KOWSHIKAN-PALANISAMY</t>
+          <t>kowshika_moorthi</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -10045,24 +10045,24 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/KOWSHIKAN-PALANISAMY/</t>
+          <t>https://leetcode.com/u/kowshika_moorthi/</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>922525106166</t>
+          <t>922525106165</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>KRISH R</t>
+          <t>KOWSHIKAN P</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>krish-2007</t>
+          <t>KOWSHIKAN-PALANISAMY</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -10072,24 +10072,24 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/krish-2007/</t>
+          <t>https://leetcode.com/u/KOWSHIKAN-PALANISAMY/</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>922525106167</t>
+          <t>922525106166</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>LAKSHETHA V</t>
+          <t>KRISH R</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>itz_lakshe</t>
+          <t>krish-2007</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -10099,24 +10099,24 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itz_lakshe/</t>
+          <t>https://leetcode.com/u/krish-2007/</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>922525106168</t>
+          <t>922525106167</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>LAVANYA V</t>
+          <t>LAKSHETHA V</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>lavilavanya</t>
+          <t>itz_lakshe</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -10126,12 +10126,39 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/lavilavanya/</t>
+          <t>https://leetcode.com/u/itz_lakshe/</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>922525106380</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>HARIJT VASAN S V</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Harjit_Vasan</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Harjit_Vasan/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E359"/>
+  <autoFilter ref="A1:E360"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Students.xlsx
+++ b/Students.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$360</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$361</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E360"/>
+  <dimension ref="A1:E361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -467,17 +467,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>922525106263</t>
+          <t>922525106269</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>RUBESH C</t>
+          <t>Sakthivel. M</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Rubesh_7</t>
+          <t>sakthivel23116</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -487,24 +487,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rubesh_7/</t>
+          <t>https://leetcode.com/u/sakthivel23116/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>922525106283</t>
+          <t>922525106275</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SANTHOSH S</t>
+          <t>SANJAY U</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SanthoshSathya260</t>
+          <t>SanjayUdayan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -514,24 +514,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SanthoshSathya260/</t>
+          <t>https://leetcode.com/u/SanjayUdayan/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>922525106291</t>
+          <t>922525106283</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SARVESWARAN R</t>
+          <t>SANTHOSH S</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>sarvesh312008</t>
+          <t>SanthoshSathya260</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -541,24 +541,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sarvesh312008/</t>
+          <t>https://leetcode.com/u/SanthoshSathya260/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>922525106292</t>
+          <t>922525106291</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SASHMIKA.P</t>
+          <t>SARVESWARAN R</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>sashmikaprabhu</t>
+          <t>sarvesh312008</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -568,24 +568,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sashmikaprabhu/</t>
+          <t>https://leetcode.com/u/sarvesh312008/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>922525106307</t>
+          <t>922525106292</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SHIVANI B</t>
+          <t>SASHMIKA.P</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>shivani208</t>
+          <t>sashmikaprabhu</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -595,24 +595,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shivani208/</t>
+          <t>https://leetcode.com/u/sashmikaprabhu/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>922525106272</t>
+          <t>922525106307</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SANJAY D</t>
+          <t>SHIVANI B</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>itsmesanjay007</t>
+          <t>shivani208</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -622,24 +622,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itsmesanjay007/</t>
+          <t>https://leetcode.com/u/shivani208/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>922525106309</t>
+          <t>922525106272</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SHREE CHARAN T</t>
+          <t>SANJAY D</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>shreecharan22</t>
+          <t>itsmesanjay007</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -649,24 +649,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shreecharan22/</t>
+          <t>https://leetcode.com/u/itsmesanjay007/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>922525106314</t>
+          <t>922525106309</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SIVANESH D</t>
+          <t>SHREE CHARAN T</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>sivanesh2007</t>
+          <t>shreecharan22</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -676,24 +676,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivanesh2007/</t>
+          <t>https://leetcode.com/u/shreecharan22/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>922525196293</t>
+          <t>922525106314</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SASWIN D</t>
+          <t>SIVANESH D</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>saswin_88</t>
+          <t>sivanesh2007</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -703,24 +703,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saswin_88/</t>
+          <t>https://leetcode.com/u/sivanesh2007/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>922525106253</t>
+          <t>922525196293</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>RITHANYA KN</t>
+          <t>SASWIN D</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Rithanya12-3</t>
+          <t>saswin_88</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -730,24 +730,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithanya12-3/</t>
+          <t>https://leetcode.com/u/saswin_88/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>922525106257</t>
+          <t>922525106264</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RITHIKA B</t>
+          <t>SABAREESH K</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Rithika_Balakrishnan</t>
+          <t>sabareesh_karikalan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -757,24 +757,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithika_Balakrishnan/</t>
+          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>922525106259</t>
+          <t>922525106253</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ROHITH V</t>
+          <t>RITHANYA KN</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>RohithrohiV</t>
+          <t>Rithanya12-3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -784,24 +784,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/RohithrohiV/</t>
+          <t>https://leetcode.com/u/Rithanya12-3/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>922525106260</t>
+          <t>922525106257</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ROOBAGAPRIYA R</t>
+          <t>RITHIKA B</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Roobagapriya</t>
+          <t>Rithika_Balakrishnan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Roobagapriya/</t>
+          <t>https://leetcode.com/u/Rithika_Balakrishnan/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>922525106256</t>
+          <t>922525106259</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RITHIK P</t>
+          <t>ROHITH V</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Rithik_78</t>
+          <t>RohithrohiV</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -838,24 +838,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithik_78/</t>
+          <t>https://leetcode.com/u/RohithrohiV/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>922525106258</t>
+          <t>922525106256</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RITHISH R</t>
+          <t>RITHIK P</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Rithish_</t>
+          <t>Rithik_78</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -865,24 +865,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithish_/</t>
+          <t>https://leetcode.com/u/Rithik_78/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>922525106264</t>
+          <t>922525106258</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SABAREESH K</t>
+          <t>RITHISH R</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>sabareesh_karikalan</t>
+          <t>Rithish_</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -892,24 +892,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
+          <t>https://leetcode.com/u/Rithish_/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>922525106266</t>
+          <t>922525106260</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SAHANA.V</t>
+          <t>ROOBAGAPRIYA R</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sahanavijayakumar_0033</t>
+          <t>Roobagapriya</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -919,24 +919,24 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sahanavijayakumar_0033/</t>
+          <t>https://leetcode.com/u/Roobagapriya/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>922525106269</t>
+          <t>922525106266</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sakthivel. M</t>
+          <t>SAHANA.V</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>sakthivel23116</t>
+          <t>Sahanavijayakumar_0033</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sakthivel23116/</t>
+          <t>https://leetcode.com/u/Sahanavijayakumar_0033/</t>
         </is>
       </c>
     </row>
@@ -1007,17 +1007,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>922525106275</t>
+          <t>922525106263</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SANJAY U</t>
+          <t>RUBESH C</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SanjayUdayan</t>
+          <t>Rubesh_7</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SanjayUdayan/</t>
+          <t>https://leetcode.com/u/Rubesh_7/</t>
         </is>
       </c>
     </row>
@@ -1844,17 +1844,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>922525106367</t>
+          <t>922525106365</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>VIKRAM V</t>
+          <t>VIGNESHWAR U</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>vikramvicky5678</t>
+          <t>VIGNESHWAR0221</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1864,24 +1864,24 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vikramvicky5678/</t>
+          <t>https://leetcode.com/u/VIGNESHWAR0221/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>922525106368</t>
+          <t>922525106366</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>VISHNU B</t>
+          <t>VIJAYARAGAVAN R</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>VISHNU_B_2008</t>
+          <t>vijayaragavan1216</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1891,24 +1891,24 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VISHNU_B_2008/</t>
+          <t>https://leetcode.com/u/vijayaragavan1216/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>922525106369</t>
+          <t>922525106367</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>VISHNU PRIYAN S</t>
+          <t>VIKRAM V</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>itz__priyan__</t>
+          <t>vikramvicky5678</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1918,24 +1918,24 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itz__priyan__/</t>
+          <t>https://leetcode.com/u/vikramvicky5678/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>922525106370</t>
+          <t>922525106368</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>VISHNUHARAN V S</t>
+          <t>VISHNU B</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Vishnuharan082007</t>
+          <t>VISHNU_B_2008</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1945,24 +1945,24 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vishnuharan082007/</t>
+          <t>https://leetcode.com/u/VISHNU_B_2008/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>922525106365</t>
+          <t>922525106369</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>VIGNESHWAR U</t>
+          <t>VISHNU PRIYAN S</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>VIGNESHWAR0221</t>
+          <t>itz__priyan__</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1972,24 +1972,24 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VIGNESHWAR0221/</t>
+          <t>https://leetcode.com/u/itz__priyan__/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>922525106359</t>
+          <t>922525106362</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>VASANTHKUMAR R</t>
+          <t>VELLIANGIRI R</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>VasanthKumar008</t>
+          <t>velliangiri_R</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1999,24 +1999,24 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VasanthKumar008/</t>
+          <t>https://leetcode.com/u/velliangiri_R/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>922525106360</t>
+          <t>922525106357</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>VASUDEVAN G</t>
+          <t>VASANTH S</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>GTVASU2008</t>
+          <t>_vasanth_s_</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2026,24 +2026,24 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/GTVASU2008/</t>
+          <t>https://leetcode.com/u/_vasanth_s_/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>922525106361</t>
+          <t>922525106358</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>VASUKI K</t>
+          <t>VASANTHA KUMAR D</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>vasuki</t>
+          <t>Vasanthakumar12232</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2053,24 +2053,24 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vasuki/</t>
+          <t>https://leetcode.com/u/Vasanthakumar12232/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>922525106362</t>
+          <t>922525106359</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>VELLIANGIRI R</t>
+          <t>VASANTHKUMAR R</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>velliangiri_R</t>
+          <t>VasanthKumar008</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2080,24 +2080,24 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/velliangiri_R/</t>
+          <t>https://leetcode.com/u/VasanthKumar008/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>922525106363</t>
+          <t>922525106360</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>VIGNESH M</t>
+          <t>VASUDEVAN G</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>O8bYDSRUbE</t>
+          <t>GTVASU2008</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2107,24 +2107,24 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/O8bYDSRUbE/</t>
+          <t>https://leetcode.com/u/GTVASU2008/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>922525106366</t>
+          <t>922525106361</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>VIJAYARAGAVAN R</t>
+          <t>VASUKI K</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>vijayaragavan1216</t>
+          <t>vasuki</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2134,24 +2134,24 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vijayaragavan1216/</t>
+          <t>https://leetcode.com/u/vasuki/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>922525106371</t>
+          <t>922525106363</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>VISHNUPRIYA S</t>
+          <t>VIGNESH M</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>vishnupriyamaran</t>
+          <t>O8bYDSRUbE</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2161,24 +2161,24 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vishnupriyamaran/</t>
+          <t>https://leetcode.com/u/O8bYDSRUbE/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>922525106372</t>
+          <t>922525106370</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>VISHWAJETH A M</t>
+          <t>VISHNUHARAN V S</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>vishwajeth</t>
+          <t>Vishnuharan082007</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2188,24 +2188,24 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vishwajeth/</t>
+          <t>https://leetcode.com/u/Vishnuharan082007/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>922525106373</t>
+          <t>922525106371</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>YASHNI S</t>
+          <t>VISHNUPRIYA S</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Yashnisubramaniyan</t>
+          <t>vishnupriyamaran</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2215,24 +2215,24 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Yashnisubramaniyan/</t>
+          <t>https://leetcode.com/u/vishnupriyamaran/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>922525106374</t>
+          <t>922525106372</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>YASWANTH V</t>
+          <t>VISHWAJETH A M</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>yaswanth_2008</t>
+          <t>vishwajeth</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2242,24 +2242,24 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yaswanth_2008/</t>
+          <t>https://leetcode.com/u/vishwajeth/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>922525106375</t>
+          <t>922525106373</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>YAZHINI M</t>
+          <t>YASHNI S</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>yazhini2007</t>
+          <t>Yashnisubramaniyan</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2269,24 +2269,24 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yazhini2007/</t>
+          <t>https://leetcode.com/u/Yashnisubramaniyan/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>922525106376</t>
+          <t>922525106374</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>YAZHINI S</t>
+          <t>YASWANTH V</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>yazhini__1234</t>
+          <t>yaswanth_2008</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2296,24 +2296,24 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yazhini__1234/</t>
+          <t>https://leetcode.com/u/yaswanth_2008/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>922525106316</t>
+          <t>922525106375</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SIVARANJAN M P</t>
+          <t>YAZHINI M</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SIVARANJAN_MP</t>
+          <t>yazhini2007</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2323,24 +2323,24 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SIVARANJAN_MP/</t>
+          <t>https://leetcode.com/u/yazhini2007/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>922525106317</t>
+          <t>922525106316</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SIVASANJEEV P</t>
+          <t>SIVARANJAN M P</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Sivasanjeev16</t>
+          <t>SIVARANJAN_MP</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2350,24 +2350,24 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sivasanjeev16/</t>
+          <t>https://leetcode.com/u/SIVARANJAN_MP/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>922525106318</t>
+          <t>922525106317</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SIVASUBRAMANI A</t>
+          <t>SIVASANJEEV P</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AK_Siva</t>
+          <t>Sivasanjeev16</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2377,24 +2377,24 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/AK_Siva/</t>
+          <t>https://leetcode.com/u/Sivasanjeev16/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>922525106319</t>
+          <t>922525106318</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SIVATHARUN C</t>
+          <t>SIVASUBRAMANI A</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>sivatharun22</t>
+          <t>AK_Siva</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2404,24 +2404,24 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivatharun22/</t>
+          <t>https://leetcode.com/u/AK_Siva/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>922525106320</t>
+          <t>922525106319</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SOBIKA R</t>
+          <t>SIVATHARUN C</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>_sobika_R</t>
+          <t>sivatharun22</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2431,24 +2431,24 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_sobika_R/</t>
+          <t>https://leetcode.com/u/sivatharun22/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>922525106321</t>
+          <t>922525106320</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SREE DHARANI C</t>
+          <t>SOBIKA R</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SREEDHARANI_14</t>
+          <t>_sobika_R</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2458,24 +2458,24 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SREEDHARANI_14/</t>
+          <t>https://leetcode.com/u/_sobika_R/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>922525106322</t>
+          <t>922525106321</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SRI  T</t>
+          <t>SREE DHARANI C</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Sri1540</t>
+          <t>SREEDHARANI_14</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2485,24 +2485,24 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sri1540/</t>
+          <t>https://leetcode.com/u/SREEDHARANI_14/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>922525106323</t>
+          <t>922525106322</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SRI HEERA J</t>
+          <t>SRI  T</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>sriheera03</t>
+          <t>Sri1540</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2512,24 +2512,24 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sriheera03/</t>
+          <t>https://leetcode.com/u/Sri1540/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>922525106324</t>
+          <t>922525106323</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SRI KANTH R</t>
+          <t>SRI HEERA J</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>kanth2008</t>
+          <t>sriheera03</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2539,24 +2539,24 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kanth2008/</t>
+          <t>https://leetcode.com/u/sriheera03/</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>922525106325</t>
+          <t>922525106324</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SRI SASTIKA G</t>
+          <t>SRI KANTH R</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Srisastika_1401</t>
+          <t>kanth2008</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2566,24 +2566,24 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Srisastika_1401/</t>
+          <t>https://leetcode.com/u/kanth2008/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>922525106326</t>
+          <t>922525106325</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SRI VARSHAN B P</t>
+          <t>SRI SASTIKA G</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>srivarshan_B_P</t>
+          <t>Srisastika_1401</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2593,24 +2593,24 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/srivarshan_B_P/</t>
+          <t>https://leetcode.com/u/Srisastika_1401/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>922525106327</t>
+          <t>922525106326</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SRINATH V</t>
+          <t>SRI VARSHAN B P</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>V_SRINATH</t>
+          <t>srivarshan_B_P</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2620,24 +2620,24 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/V_SRINATH/</t>
+          <t>https://leetcode.com/u/srivarshan_B_P/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>922525106328</t>
+          <t>922525106327</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SRINIRANJAN S</t>
+          <t>SRINATH V</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>SRINIRANJAN2008</t>
+          <t>V_SRINATH</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2647,24 +2647,24 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SRINIRANJAN2008/</t>
+          <t>https://leetcode.com/u/V_SRINATH/</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>922525106329</t>
+          <t>922525106328</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SRINITHE T</t>
+          <t>SRINIRANJAN S</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>srinithe_1401</t>
+          <t>SRINIRANJAN2008</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2674,24 +2674,24 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/srinithe_1401/</t>
+          <t>https://leetcode.com/u/SRINIRANJAN2008/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>922525106364</t>
+          <t>922525106329</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>VIGNESH VELAN M</t>
+          <t>SRINITHE T</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Vicky_27_Velan</t>
+          <t>srinithe_1401</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vicky_27_Velan/</t>
+          <t>https://leetcode.com/u/srinithe_1401/</t>
         </is>
       </c>
     </row>
@@ -2762,17 +2762,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>922525106378</t>
+          <t>922525106376</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>YOKESWARAN S</t>
+          <t>YAZHINI S</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>syokeswaran</t>
+          <t>yazhini__1234</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2782,24 +2782,24 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/syokeswaran/</t>
+          <t>https://leetcode.com/u/yazhini__1234/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>922525106330</t>
+          <t>922525106378</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SRINITHI S</t>
+          <t>YOKESWARAN S</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Srinithi24_</t>
+          <t>syokeswaran</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2809,24 +2809,24 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Srinithi24_/</t>
+          <t>https://leetcode.com/u/syokeswaran/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>922525106339</t>
+          <t>922525106330</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SUJITH RAJA B</t>
+          <t>SRINITHI S</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>mahi20_</t>
+          <t>Srinithi24_</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2836,24 +2836,24 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/mahi20_/</t>
+          <t>https://leetcode.com/u/Srinithi24_/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>922525106353</t>
+          <t>922525106339</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>THIRISHA C</t>
+          <t>SUJITH RAJA B</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>thirishavsb</t>
+          <t>mahi20_</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2863,24 +2863,24 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/thirishavsb/</t>
+          <t>https://leetcode.com/u/mahi20_/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>922525106331</t>
+          <t>922525106353</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SRISAMAYA R</t>
+          <t>THIRISHA C</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>mahi</t>
+          <t>thirishavsb</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2890,24 +2890,24 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/mahi/</t>
+          <t>https://leetcode.com/u/thirishavsb/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>922525106332</t>
+          <t>922525106331</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SUBARNA V</t>
+          <t>SRISAMAYA R</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Subarna_17</t>
+          <t>mahi</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2917,24 +2917,24 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Subarna_17/</t>
+          <t>https://leetcode.com/u/mahi/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>922525106334</t>
+          <t>922525106364</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>SUBIKA T</t>
+          <t>VIGNESH VELAN M</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>subika1112</t>
+          <t>Vicky_27_Velan</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2944,24 +2944,24 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/subika1112/</t>
+          <t>https://leetcode.com/u/Vicky_27_Velan/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>922525106335</t>
+          <t>922525106332</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SUDHARSAN S</t>
+          <t>SUBARNA V</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Sudharsan</t>
+          <t>Subarna_17</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2971,24 +2971,24 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sudharsan/</t>
+          <t>https://leetcode.com/u/Subarna_17/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>922525106336</t>
+          <t>922525106334</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SUGANTHAN K</t>
+          <t>SUBIKA T</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>SUGANTHKALAI</t>
+          <t>subika1112</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2998,24 +2998,24 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SUGANTHKALAI/</t>
+          <t>https://leetcode.com/u/subika1112/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>922525106337</t>
+          <t>922525106335</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SUGIDHARSHINI T</t>
+          <t>SUDHARSAN S</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Sugi_07</t>
+          <t>Sudharsan</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3025,24 +3025,24 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sugi_07/</t>
+          <t>https://leetcode.com/u/Sudharsan/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>922525106338</t>
+          <t>922525106336</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SUJEETH M</t>
+          <t>SUGANTHAN K</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>SUJEETH77</t>
+          <t>SUGANTHKALAI</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3052,24 +3052,24 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SUJEETH77/</t>
+          <t>https://leetcode.com/u/SUGANTHKALAI/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>922525106340</t>
+          <t>922525106337</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>SUMITHRA S</t>
+          <t>SUGIDHARSHINI T</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>sumithra_16</t>
+          <t>Sugi_07</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3079,24 +3079,24 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sumithra_16/</t>
+          <t>https://leetcode.com/u/Sugi_07/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>922525106341</t>
+          <t>922525106338</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>SURYA PRABHU S</t>
+          <t>SUJEETH M</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>surya001prabhu</t>
+          <t>SUJEETH77</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3106,24 +3106,24 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/surya001prabhu/</t>
+          <t>https://leetcode.com/u/SUJEETH77/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>922525106342</t>
+          <t>922525106340</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>SUSIDHARAN M</t>
+          <t>SUMITHRA S</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Susidharan147</t>
+          <t>sumithra_16</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3133,24 +3133,24 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Susidharan147/</t>
+          <t>https://leetcode.com/u/sumithra_16/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>922525106343</t>
+          <t>922525106341</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>SUTHARSHANA S</t>
+          <t>SURYA PRABHU S</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>sutharshana743</t>
+          <t>surya001prabhu</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3160,24 +3160,24 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sutharshana743/</t>
+          <t>https://leetcode.com/u/surya001prabhu/</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>922525106344</t>
+          <t>922525106342</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>SWATHI M</t>
+          <t>SUSIDHARAN M</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Swathimanivel_1234</t>
+          <t>Susidharan147</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3187,24 +3187,24 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Swathimanivel_1234/</t>
+          <t>https://leetcode.com/u/Susidharan147/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>922525106345</t>
+          <t>922525106343</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>SWATHI S</t>
+          <t>SUTHARSHANA S</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>_swathi _3366</t>
+          <t>sutharshana743</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3214,24 +3214,24 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_swathi _3366/</t>
+          <t>https://leetcode.com/u/sutharshana743/</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>922525106347</t>
+          <t>922525106344</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>TAMIL SELVAN R</t>
+          <t>SWATHI M</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Kdmif0HMNm</t>
+          <t>Swathimanivel_1234</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3241,24 +3241,24 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Kdmif0HMNm/</t>
+          <t>https://leetcode.com/u/Swathimanivel_1234/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>922525106348</t>
+          <t>922525106345</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>THAMARAI SELVI D</t>
+          <t>SWATHI S</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>thamarai_04</t>
+          <t>_swathi _3366</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3268,24 +3268,24 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/thamarai_04/</t>
+          <t>https://leetcode.com/u/_swathi _3366/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>922525106349</t>
+          <t>922525106347</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>THAMEEM FARSHITHA A</t>
+          <t>TAMIL SELVAN R</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Thameem_786</t>
+          <t>Kdmif0HMNm</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3295,24 +3295,24 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Thameem_786/</t>
+          <t>https://leetcode.com/u/Kdmif0HMNm/</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>922525106350</t>
+          <t>922525106348</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>THARANISH R</t>
+          <t>THAMARAI SELVI D</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>THARANISH2008</t>
+          <t>thamarai_04</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3322,24 +3322,24 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/THARANISH2008/</t>
+          <t>https://leetcode.com/u/thamarai_04/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>922525106351</t>
+          <t>922525106349</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>THARUNIKA P</t>
+          <t>THAMEEM FARSHITHA A</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Tharunika_12</t>
+          <t>Thameem_786</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3349,24 +3349,24 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Tharunika_12/</t>
+          <t>https://leetcode.com/u/Thameem_786/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>922525106352</t>
+          <t>922525106350</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>THIRINESH KUMAR S</t>
+          <t>THARANISH R</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>THIRINESH KUMAR.S</t>
+          <t>THARANISH2008</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3376,24 +3376,24 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/THIRINESH KUMAR.S/</t>
+          <t>https://leetcode.com/u/THARANISH2008/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>922525106354</t>
+          <t>922525106351</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>THIRUMURUGAN S</t>
+          <t>THARUNIKA P</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>thiru0211_</t>
+          <t>Tharunika_12</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3403,24 +3403,24 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/thiru0211_/</t>
+          <t>https://leetcode.com/u/Tharunika_12/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>922525106355</t>
+          <t>922525106352</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>VAISHNAVI U</t>
+          <t>THIRINESH KUMAR S</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>vaish200</t>
+          <t>THIRINESH KUMAR.S</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3430,24 +3430,24 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vaish200/</t>
+          <t>https://leetcode.com/u/THIRINESH KUMAR.S/</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>922525106356</t>
+          <t>922525106354</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>VASANTH KUMAR C</t>
+          <t>THIRUMURUGAN S</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>VASANTH2007</t>
+          <t>thiru0211_</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -3457,24 +3457,24 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VASANTH2007/</t>
+          <t>https://leetcode.com/u/thiru0211_/</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>922525106357</t>
+          <t>922525106355</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>VASANTH S</t>
+          <t>VAISHNAVI U</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>_vasanth_s_</t>
+          <t>vaish200</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3484,24 +3484,24 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_vasanth_s_/</t>
+          <t>https://leetcode.com/u/vaish200/</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>922525106358</t>
+          <t>922525106356</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>VASANTHA KUMAR D</t>
+          <t>VASANTH KUMAR C</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Vasanthakumar12232</t>
+          <t>VASANTH2007</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vasanthakumar12232/</t>
+          <t>https://leetcode.com/u/VASANTH2007/</t>
         </is>
       </c>
     </row>
@@ -6110,17 +6110,17 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>922525106027</t>
+          <t>922525106008</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Arulesh K</t>
+          <t>AHELESH G S</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>arul2008</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/arul2008/</t>
+          <t>https://leetcode.com/u/B/</t>
         </is>
       </c>
     </row>
@@ -6893,17 +6893,17 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>922525106008</t>
+          <t>922525106027</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>AHELESH G S</t>
+          <t>Arulesh K</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>arul2008</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -6913,7 +6913,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/B/</t>
+          <t>https://leetcode.com/u/arul2008/</t>
         </is>
       </c>
     </row>
@@ -10157,8 +10157,35 @@
         </is>
       </c>
     </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>922525106381</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>LOHITH T S</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>LOHITH206</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/LOHITH206/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E360"/>
+  <autoFilter ref="A1:E361"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Students.xlsx
+++ b/Students.xlsx
@@ -10170,7 +10170,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>LOHITH206</t>
+          <t>LOHITH1206</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -10180,7 +10180,7 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/LOHITH206/</t>
+          <t>https://leetcode.com/u/LOHITH1206/</t>
         </is>
       </c>
     </row>

--- a/Students.xlsx
+++ b/Students.xlsx
@@ -467,17 +467,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>922525106269</t>
+          <t>922525106266</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sakthivel. M</t>
+          <t>SAHANA.V</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>sakthivel23116</t>
+          <t>Sahanavijayakumar_0033</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -487,24 +487,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sakthivel23116/</t>
+          <t>https://leetcode.com/u/Sahanavijayakumar_0033/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>922525106275</t>
+          <t>922525106269</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SANJAY U</t>
+          <t>Sakthivel. M</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SanjayUdayan</t>
+          <t>sakthivel23116</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -514,24 +514,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SanjayUdayan/</t>
+          <t>https://leetcode.com/u/sakthivel23116/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>922525106283</t>
+          <t>922525106275</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SANTHOSH S</t>
+          <t>SANJAY U</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SanthoshSathya260</t>
+          <t>SanjayUdayan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -541,24 +541,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SanthoshSathya260/</t>
+          <t>https://leetcode.com/u/SanjayUdayan/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>922525106291</t>
+          <t>922525106283</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SARVESWARAN R</t>
+          <t>SANTHOSH S</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>sarvesh312008</t>
+          <t>SanthoshSathya260</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -568,24 +568,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sarvesh312008/</t>
+          <t>https://leetcode.com/u/SanthoshSathya260/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>922525106292</t>
+          <t>922525106291</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SASHMIKA.P</t>
+          <t>SARVESWARAN R</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>sashmikaprabhu</t>
+          <t>sarvesh312008</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -595,24 +595,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sashmikaprabhu/</t>
+          <t>https://leetcode.com/u/sarvesh312008/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>922525106307</t>
+          <t>922525106292</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SHIVANI B</t>
+          <t>SASHMIKA.P</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>shivani208</t>
+          <t>sashmikaprabhu</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shivani208/</t>
+          <t>https://leetcode.com/u/sashmikaprabhu/</t>
         </is>
       </c>
     </row>
@@ -737,17 +737,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>922525106264</t>
+          <t>922525106260</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SABAREESH K</t>
+          <t>ROOBAGAPRIYA R</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>sabareesh_karikalan</t>
+          <t>Roobagapriya</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -757,24 +757,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
+          <t>https://leetcode.com/u/Roobagapriya/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>922525106253</t>
+          <t>922525106307</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>RITHANYA KN</t>
+          <t>SHIVANI B</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Rithanya12-3</t>
+          <t>shivani208</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -784,24 +784,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithanya12-3/</t>
+          <t>https://leetcode.com/u/shivani208/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>922525106257</t>
+          <t>922525106264</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>RITHIKA B</t>
+          <t>SABAREESH K</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Rithika_Balakrishnan</t>
+          <t>sabareesh_karikalan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithika_Balakrishnan/</t>
+          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>922525106259</t>
+          <t>922525106253</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ROHITH V</t>
+          <t>RITHANYA KN</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>RohithrohiV</t>
+          <t>Rithanya12-3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -838,24 +838,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/RohithrohiV/</t>
+          <t>https://leetcode.com/u/Rithanya12-3/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>922525106256</t>
+          <t>922525106257</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RITHIK P</t>
+          <t>RITHIKA B</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Rithik_78</t>
+          <t>Rithika_Balakrishnan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -865,24 +865,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithik_78/</t>
+          <t>https://leetcode.com/u/Rithika_Balakrishnan/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>922525106258</t>
+          <t>922525106256</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>RITHISH R</t>
+          <t>RITHIK P</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Rithish_</t>
+          <t>Rithik_78</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -892,24 +892,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithish_/</t>
+          <t>https://leetcode.com/u/Rithik_78/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>922525106260</t>
+          <t>922525106258</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ROOBAGAPRIYA R</t>
+          <t>RITHISH R</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Roobagapriya</t>
+          <t>Rithish_</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -919,24 +919,24 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Roobagapriya/</t>
+          <t>https://leetcode.com/u/Rithish_/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>922525106266</t>
+          <t>922525106259</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SAHANA.V</t>
+          <t>ROHITH V</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sahanavijayakumar_0033</t>
+          <t>RohithrohiV</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sahanavijayakumar_0033/</t>
+          <t>https://leetcode.com/u/RohithrohiV/</t>
         </is>
       </c>
     </row>
@@ -2708,17 +2708,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>922525106377</t>
+          <t>922525106330</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>YAZHINI V</t>
+          <t>SRINITHI S</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>VISU_YAZHU</t>
+          <t>Srinithi24_</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2728,24 +2728,24 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VISU_YAZHU/</t>
+          <t>https://leetcode.com/u/Srinithi24_/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>922525106346</t>
+          <t>922525106377</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SWETHA E</t>
+          <t>YAZHINI V</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Swetha_20_1</t>
+          <t>VISU_YAZHU</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2755,24 +2755,24 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Swetha_20_1/</t>
+          <t>https://leetcode.com/u/VISU_YAZHU/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>922525106376</t>
+          <t>922525106346</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>YAZHINI S</t>
+          <t>SWETHA E</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>yazhini__1234</t>
+          <t>Swetha_20_1</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2782,24 +2782,24 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yazhini__1234/</t>
+          <t>https://leetcode.com/u/Swetha_20_1/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>922525106378</t>
+          <t>922525106331</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>YOKESWARAN S</t>
+          <t>SRISAMAYA R</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>syokeswaran</t>
+          <t>mahi</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2809,24 +2809,24 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/syokeswaran/</t>
+          <t>https://leetcode.com/u/mahi/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>922525106330</t>
+          <t>922525106376</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SRINITHI S</t>
+          <t>YAZHINI S</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Srinithi24_</t>
+          <t>yazhini__1234</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2836,24 +2836,24 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Srinithi24_/</t>
+          <t>https://leetcode.com/u/yazhini__1234/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>922525106339</t>
+          <t>922525106378</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SUJITH RAJA B</t>
+          <t>YOKESWARAN S</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>mahi20_</t>
+          <t>syokeswaran</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2863,24 +2863,24 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/mahi20_/</t>
+          <t>https://leetcode.com/u/syokeswaran/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>922525106353</t>
+          <t>922525106332</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>THIRISHA C</t>
+          <t>SUBARNA V</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>thirishavsb</t>
+          <t>Subarna_17</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2890,24 +2890,24 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/thirishavsb/</t>
+          <t>https://leetcode.com/u/Subarna_17/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>922525106331</t>
+          <t>922525106339</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SRISAMAYA R</t>
+          <t>SUJITH RAJA B</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>mahi</t>
+          <t>mahi20_</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2917,24 +2917,24 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/mahi/</t>
+          <t>https://leetcode.com/u/mahi20_/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>922525106364</t>
+          <t>922525106353</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>VIGNESH VELAN M</t>
+          <t>THIRISHA C</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Vicky_27_Velan</t>
+          <t>thirishavsb</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2944,24 +2944,24 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vicky_27_Velan/</t>
+          <t>https://leetcode.com/u/thirishavsb/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>922525106332</t>
+          <t>922525106334</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SUBARNA V</t>
+          <t>SUBIKA T</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Subarna_17</t>
+          <t>subika1112</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2971,24 +2971,24 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Subarna_17/</t>
+          <t>https://leetcode.com/u/subika1112/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>922525106334</t>
+          <t>922525106364</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SUBIKA T</t>
+          <t>VIGNESH VELAN M</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>subika1112</t>
+          <t>Vicky_27_Velan</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/subika1112/</t>
+          <t>https://leetcode.com/u/Vicky_27_Velan/</t>
         </is>
       </c>
     </row>
@@ -6083,17 +6083,17 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>922525106022</t>
+          <t>922525106027</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>ANUJA S</t>
+          <t>Arulesh K</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>anuja008</t>
+          <t>arul2008</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -6103,7 +6103,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/anuja008/</t>
+          <t>https://leetcode.com/u/arul2008/</t>
         </is>
       </c>
     </row>
@@ -6893,17 +6893,17 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>922525106027</t>
+          <t>922525106022</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Arulesh K</t>
+          <t>ANUJA S</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>arul2008</t>
+          <t>anuja008</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -6913,7 +6913,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/arul2008/</t>
+          <t>https://leetcode.com/u/anuja008/</t>
         </is>
       </c>
     </row>

--- a/Students.xlsx
+++ b/Students.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$361</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$362</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E361"/>
+  <dimension ref="A1:E362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -467,17 +467,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>922525106266</t>
+          <t>922525106253</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SAHANA.V</t>
+          <t>RITHANYA KN</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sahanavijayakumar_0033</t>
+          <t>Rithanya12-3</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -487,24 +487,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sahanavijayakumar_0033/</t>
+          <t>https://leetcode.com/u/Rithanya12-3/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>922525106269</t>
+          <t>922525106266</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sakthivel. M</t>
+          <t>SAHANA.V</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>sakthivel23116</t>
+          <t>Sahanavijayakumar_0033</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -514,24 +514,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sakthivel23116/</t>
+          <t>https://leetcode.com/u/Sahanavijayakumar_0033/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>922525106275</t>
+          <t>922525106269</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SANJAY U</t>
+          <t>Sakthivel. M</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SanjayUdayan</t>
+          <t>sakthivel23116</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -541,24 +541,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SanjayUdayan/</t>
+          <t>https://leetcode.com/u/sakthivel23116/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>922525106283</t>
+          <t>922525106275</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SANTHOSH S</t>
+          <t>SANJAY U</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SanthoshSathya260</t>
+          <t>SanjayUdayan</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -568,24 +568,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SanthoshSathya260/</t>
+          <t>https://leetcode.com/u/SanjayUdayan/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>922525106291</t>
+          <t>922525106283</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SARVESWARAN R</t>
+          <t>SANTHOSH S</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>sarvesh312008</t>
+          <t>SanthoshSathya260</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -595,24 +595,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sarvesh312008/</t>
+          <t>https://leetcode.com/u/SanthoshSathya260/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>922525106292</t>
+          <t>922525106291</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SASHMIKA.P</t>
+          <t>SARVESWARAN R</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>sashmikaprabhu</t>
+          <t>sarvesh312008</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -622,24 +622,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sashmikaprabhu/</t>
+          <t>https://leetcode.com/u/sarvesh312008/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>922525106272</t>
+          <t>922525106292</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SANJAY D</t>
+          <t>SASHMIKA.P</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>itsmesanjay007</t>
+          <t>sashmikaprabhu</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -649,24 +649,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itsmesanjay007/</t>
+          <t>https://leetcode.com/u/sashmikaprabhu/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>922525106309</t>
+          <t>922525106272</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SHREE CHARAN T</t>
+          <t>SANJAY D</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>shreecharan22</t>
+          <t>itsmesanjay007</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -676,24 +676,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shreecharan22/</t>
+          <t>https://leetcode.com/u/itsmesanjay007/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>922525106314</t>
+          <t>922525106309</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SIVANESH D</t>
+          <t>SHREE CHARAN T</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>sivanesh2007</t>
+          <t>shreecharan22</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -703,24 +703,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivanesh2007/</t>
+          <t>https://leetcode.com/u/shreecharan22/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>922525196293</t>
+          <t>922525106314</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SASWIN D</t>
+          <t>SIVANESH D</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>saswin_88</t>
+          <t>sivanesh2007</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -730,24 +730,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saswin_88/</t>
+          <t>https://leetcode.com/u/sivanesh2007/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>922525106260</t>
+          <t>922525196293</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ROOBAGAPRIYA R</t>
+          <t>SASWIN D</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Roobagapriya</t>
+          <t>saswin_88</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -757,24 +757,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Roobagapriya/</t>
+          <t>https://leetcode.com/u/saswin_88/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>922525106307</t>
+          <t>922525106257</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SHIVANI B</t>
+          <t>RITHIKA B</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>shivani208</t>
+          <t>Rithika_Balakrishnan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -784,24 +784,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shivani208/</t>
+          <t>https://leetcode.com/u/Rithika_Balakrishnan/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>922525106264</t>
+          <t>922525106259</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SABAREESH K</t>
+          <t>ROHITH V</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>sabareesh_karikalan</t>
+          <t>RohithrohiV</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
+          <t>https://leetcode.com/u/RohithrohiV/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>922525106253</t>
+          <t>922525106260</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RITHANYA KN</t>
+          <t>ROOBAGAPRIYA R</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Rithanya12-3</t>
+          <t>Roobagapriya</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -838,24 +838,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithanya12-3/</t>
+          <t>https://leetcode.com/u/Roobagapriya/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>922525106257</t>
+          <t>922525106307</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RITHIKA B</t>
+          <t>SHIVANI B</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Rithika_Balakrishnan</t>
+          <t>shivani208</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -865,24 +865,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithika_Balakrishnan/</t>
+          <t>https://leetcode.com/u/shivani208/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>922525106256</t>
+          <t>922525106264</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>RITHIK P</t>
+          <t>SABAREESH K</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Rithik_78</t>
+          <t>sabareesh_karikalan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -892,24 +892,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithik_78/</t>
+          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>922525106258</t>
+          <t>922525106256</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>RITHISH R</t>
+          <t>RITHIK P</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Rithish_</t>
+          <t>Rithik_78</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -919,24 +919,24 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithish_/</t>
+          <t>https://leetcode.com/u/Rithik_78/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>922525106259</t>
+          <t>922525106258</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ROHITH V</t>
+          <t>RITHISH R</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>RohithrohiV</t>
+          <t>Rithish_</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/RohithrohiV/</t>
+          <t>https://leetcode.com/u/Rithish_/</t>
         </is>
       </c>
     </row>
@@ -1844,17 +1844,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>922525106365</t>
+          <t>922525106362</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>VIGNESHWAR U</t>
+          <t>VELLIANGIRI R</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>VIGNESHWAR0221</t>
+          <t>velliangiri_R</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1864,24 +1864,24 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VIGNESHWAR0221/</t>
+          <t>https://leetcode.com/u/velliangiri_R/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>922525106366</t>
+          <t>922525106363</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>VIJAYARAGAVAN R</t>
+          <t>VIGNESH M</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>vijayaragavan1216</t>
+          <t>O8bYDSRUbE</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1891,24 +1891,24 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vijayaragavan1216/</t>
+          <t>https://leetcode.com/u/O8bYDSRUbE/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>922525106367</t>
+          <t>922525106365</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>VIKRAM V</t>
+          <t>VIGNESHWAR U</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>vikramvicky5678</t>
+          <t>VIGNESHWAR0221</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1918,24 +1918,24 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vikramvicky5678/</t>
+          <t>https://leetcode.com/u/VIGNESHWAR0221/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>922525106368</t>
+          <t>922525106366</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>VISHNU B</t>
+          <t>VIJAYARAGAVAN R</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>VISHNU_B_2008</t>
+          <t>vijayaragavan1216</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1945,24 +1945,24 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VISHNU_B_2008/</t>
+          <t>https://leetcode.com/u/vijayaragavan1216/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>922525106369</t>
+          <t>922525106367</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>VISHNU PRIYAN S</t>
+          <t>VIKRAM V</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>itz__priyan__</t>
+          <t>vikramvicky5678</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1972,24 +1972,24 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itz__priyan__/</t>
+          <t>https://leetcode.com/u/vikramvicky5678/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>922525106362</t>
+          <t>922525106368</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>VELLIANGIRI R</t>
+          <t>VISHNU B</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>velliangiri_R</t>
+          <t>VISHNU_B_2008</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1999,24 +1999,24 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/velliangiri_R/</t>
+          <t>https://leetcode.com/u/VISHNU_B_2008/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>922525106357</t>
+          <t>922525106360</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>VASANTH S</t>
+          <t>VASUDEVAN G</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>_vasanth_s_</t>
+          <t>GTVASU2008</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2026,24 +2026,24 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_vasanth_s_/</t>
+          <t>https://leetcode.com/u/GTVASU2008/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>922525106358</t>
+          <t>922525106355</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>VASANTHA KUMAR D</t>
+          <t>VAISHNAVI U</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Vasanthakumar12232</t>
+          <t>vaish200</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2053,24 +2053,24 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vasanthakumar12232/</t>
+          <t>https://leetcode.com/u/vaish200/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>922525106359</t>
+          <t>922525106356</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>VASANTHKUMAR R</t>
+          <t>VASANTH KUMAR C</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>VasanthKumar008</t>
+          <t>VASANTH2007</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2080,24 +2080,24 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VasanthKumar008/</t>
+          <t>https://leetcode.com/u/VASANTH2007/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>922525106360</t>
+          <t>922525106357</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>VASUDEVAN G</t>
+          <t>VASANTH S</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>GTVASU2008</t>
+          <t>_vasanth_s_</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2107,24 +2107,24 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/GTVASU2008/</t>
+          <t>https://leetcode.com/u/_vasanth_s_/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>922525106361</t>
+          <t>922525106358</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>VASUKI K</t>
+          <t>VASANTHA KUMAR D</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>vasuki</t>
+          <t>Vasanthakumar12232</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2134,24 +2134,24 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vasuki/</t>
+          <t>https://leetcode.com/u/Vasanthakumar12232/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>922525106363</t>
+          <t>922525106359</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>VIGNESH M</t>
+          <t>VASANTHKUMAR R</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>O8bYDSRUbE</t>
+          <t>VasanthKumar008</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2161,24 +2161,24 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/O8bYDSRUbE/</t>
+          <t>https://leetcode.com/u/VasanthKumar008/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>922525106370</t>
+          <t>922525106361</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>VISHNUHARAN V S</t>
+          <t>VASUKI K</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Vishnuharan082007</t>
+          <t>vasuki</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2188,24 +2188,24 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vishnuharan082007/</t>
+          <t>https://leetcode.com/u/vasuki/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>922525106371</t>
+          <t>922525106369</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>VISHNUPRIYA S</t>
+          <t>VISHNU PRIYAN S</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>vishnupriyamaran</t>
+          <t>itz__priyan__</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2215,24 +2215,24 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vishnupriyamaran/</t>
+          <t>https://leetcode.com/u/itz__priyan__/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>922525106372</t>
+          <t>922525106370</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>VISHWAJETH A M</t>
+          <t>VISHNUHARAN V S</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>vishwajeth</t>
+          <t>Vishnuharan082007</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2242,24 +2242,24 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vishwajeth/</t>
+          <t>https://leetcode.com/u/Vishnuharan082007/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>922525106373</t>
+          <t>922525106371</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>YASHNI S</t>
+          <t>VISHNUPRIYA S</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Yashnisubramaniyan</t>
+          <t>vishnupriyamaran</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2269,24 +2269,24 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Yashnisubramaniyan/</t>
+          <t>https://leetcode.com/u/vishnupriyamaran/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>922525106374</t>
+          <t>922525106372</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>YASWANTH V</t>
+          <t>VISHWAJETH A M</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>yaswanth_2008</t>
+          <t>vishwajeth</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2296,24 +2296,24 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yaswanth_2008/</t>
+          <t>https://leetcode.com/u/vishwajeth/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>922525106375</t>
+          <t>922525106373</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>YAZHINI M</t>
+          <t>YASHNI S</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>yazhini2007</t>
+          <t>Yashnisubramaniyan</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2323,24 +2323,24 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yazhini2007/</t>
+          <t>https://leetcode.com/u/Yashnisubramaniyan/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>922525106316</t>
+          <t>922525106374</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SIVARANJAN M P</t>
+          <t>YASWANTH V</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SIVARANJAN_MP</t>
+          <t>yaswanth_2008</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2350,24 +2350,24 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SIVARANJAN_MP/</t>
+          <t>https://leetcode.com/u/yaswanth_2008/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>922525106317</t>
+          <t>922525106316</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SIVASANJEEV P</t>
+          <t>SIVARANJAN M P</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Sivasanjeev16</t>
+          <t>SIVARANJAN_MP</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2377,24 +2377,24 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sivasanjeev16/</t>
+          <t>https://leetcode.com/u/SIVARANJAN_MP/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>922525106318</t>
+          <t>922525106317</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SIVASUBRAMANI A</t>
+          <t>SIVASANJEEV P</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AK_Siva</t>
+          <t>Sivasanjeev16</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2404,24 +2404,24 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/AK_Siva/</t>
+          <t>https://leetcode.com/u/Sivasanjeev16/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>922525106319</t>
+          <t>922525106318</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SIVATHARUN C</t>
+          <t>SIVASUBRAMANI A</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>sivatharun22</t>
+          <t>AK_Siva</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2431,24 +2431,24 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivatharun22/</t>
+          <t>https://leetcode.com/u/AK_Siva/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>922525106320</t>
+          <t>922525106319</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SOBIKA R</t>
+          <t>SIVATHARUN C</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>_sobika_R</t>
+          <t>sivatharun22</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2458,24 +2458,24 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_sobika_R/</t>
+          <t>https://leetcode.com/u/sivatharun22/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>922525106321</t>
+          <t>922525106320</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SREE DHARANI C</t>
+          <t>SOBIKA R</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>SREEDHARANI_14</t>
+          <t>_sobika_R</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2485,24 +2485,24 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SREEDHARANI_14/</t>
+          <t>https://leetcode.com/u/_sobika_R/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>922525106322</t>
+          <t>922525106321</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SRI  T</t>
+          <t>SREE DHARANI C</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Sri1540</t>
+          <t>SREEDHARANI_14</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2512,24 +2512,24 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sri1540/</t>
+          <t>https://leetcode.com/u/SREEDHARANI_14/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>922525106323</t>
+          <t>922525106322</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SRI HEERA J</t>
+          <t>SRI  T</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>sriheera03</t>
+          <t>Sri1540</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2539,24 +2539,24 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sriheera03/</t>
+          <t>https://leetcode.com/u/Sri1540/</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>922525106324</t>
+          <t>922525106323</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SRI KANTH R</t>
+          <t>SRI HEERA J</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>kanth2008</t>
+          <t>sriheera03</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2566,24 +2566,24 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kanth2008/</t>
+          <t>https://leetcode.com/u/sriheera03/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>922525106325</t>
+          <t>922525106324</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SRI SASTIKA G</t>
+          <t>SRI KANTH R</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Srisastika_1401</t>
+          <t>kanth2008</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2593,24 +2593,24 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Srisastika_1401/</t>
+          <t>https://leetcode.com/u/kanth2008/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>922525106326</t>
+          <t>922525106325</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SRI VARSHAN B P</t>
+          <t>SRI SASTIKA G</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>srivarshan_B_P</t>
+          <t>Srisastika_1401</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2620,24 +2620,24 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/srivarshan_B_P/</t>
+          <t>https://leetcode.com/u/Srisastika_1401/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>922525106327</t>
+          <t>922525106326</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SRINATH V</t>
+          <t>SRI VARSHAN B P</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>V_SRINATH</t>
+          <t>srivarshan_B_P</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2647,24 +2647,24 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/V_SRINATH/</t>
+          <t>https://leetcode.com/u/srivarshan_B_P/</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>922525106328</t>
+          <t>922525106327</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SRINIRANJAN S</t>
+          <t>SRINATH V</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>SRINIRANJAN2008</t>
+          <t>V_SRINATH</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2674,24 +2674,24 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SRINIRANJAN2008/</t>
+          <t>https://leetcode.com/u/V_SRINATH/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>922525106329</t>
+          <t>922525106328</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SRINITHE T</t>
+          <t>SRINIRANJAN S</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>srinithe_1401</t>
+          <t>SRINIRANJAN2008</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/srinithe_1401/</t>
+          <t>https://leetcode.com/u/SRINIRANJAN2008/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>922525106330</t>
+          <t>922525106329</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SRINITHI S</t>
+          <t>SRINITHE T</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Srinithi24_</t>
+          <t>srinithe_1401</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2728,24 +2728,24 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Srinithi24_/</t>
+          <t>https://leetcode.com/u/srinithe_1401/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>922525106377</t>
+          <t>922525106330</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>YAZHINI V</t>
+          <t>SRINITHI S</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>VISU_YAZHU</t>
+          <t>Srinithi24_</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2755,24 +2755,24 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VISU_YAZHU/</t>
+          <t>https://leetcode.com/u/Srinithi24_/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>922525106346</t>
+          <t>922525106331</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SWETHA E</t>
+          <t>SRISAMAYA R</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Swetha_20_1</t>
+          <t>mahi</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2782,24 +2782,24 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Swetha_20_1/</t>
+          <t>https://leetcode.com/u/mahi/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>922525106331</t>
+          <t>922525106332</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SRISAMAYA R</t>
+          <t>SUBARNA V</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>mahi</t>
+          <t>Subarna_17</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/mahi/</t>
+          <t>https://leetcode.com/u/Subarna_17/</t>
         </is>
       </c>
     </row>
@@ -2843,17 +2843,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>922525106378</t>
+          <t>922525106364</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>YOKESWARAN S</t>
+          <t>VIGNESH VELAN M</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>syokeswaran</t>
+          <t>Vicky_27_Velan</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2863,24 +2863,24 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/syokeswaran/</t>
+          <t>https://leetcode.com/u/Vicky_27_Velan/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>922525106332</t>
+          <t>922525106334</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SUBARNA V</t>
+          <t>SUBIKA T</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Subarna_17</t>
+          <t>subika1112</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2890,24 +2890,24 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Subarna_17/</t>
+          <t>https://leetcode.com/u/subika1112/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>922525106339</t>
+          <t>922525106375</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SUJITH RAJA B</t>
+          <t>YAZHINI M</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>mahi20_</t>
+          <t>yazhini2007</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2917,24 +2917,24 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/mahi20_/</t>
+          <t>https://leetcode.com/u/yazhini2007/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>922525106353</t>
+          <t>922525106377</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>THIRISHA C</t>
+          <t>YAZHINI V</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>thirishavsb</t>
+          <t>VISU_YAZHU</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2944,24 +2944,24 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/thirishavsb/</t>
+          <t>https://leetcode.com/u/VISU_YAZHU/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>922525106334</t>
+          <t>922525106335</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SUBIKA T</t>
+          <t>SUDHARSAN S</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>subika1112</t>
+          <t>Sudharsan</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2971,24 +2971,24 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/subika1112/</t>
+          <t>https://leetcode.com/u/Sudharsan/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>922525106364</t>
+          <t>922525106339</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>VIGNESH VELAN M</t>
+          <t>SUJITH RAJA B</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Vicky_27_Velan</t>
+          <t>mahi20_</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2998,24 +2998,24 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vicky_27_Velan/</t>
+          <t>https://leetcode.com/u/mahi20_/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>922525106335</t>
+          <t>922525106353</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SUDHARSAN S</t>
+          <t>THIRISHA C</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Sudharsan</t>
+          <t>thirishavsb</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3025,24 +3025,24 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sudharsan/</t>
+          <t>https://leetcode.com/u/thirishavsb/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>922525106336</t>
+          <t>922525106346</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SUGANTHAN K</t>
+          <t>SWETHA E</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>SUGANTHKALAI</t>
+          <t>Swetha_20_1</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3052,24 +3052,24 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SUGANTHKALAI/</t>
+          <t>https://leetcode.com/u/Swetha_20_1/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>922525106337</t>
+          <t>922525106336</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>SUGIDHARSHINI T</t>
+          <t>SUGANTHAN K</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Sugi_07</t>
+          <t>SUGANTHKALAI</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3079,24 +3079,24 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sugi_07/</t>
+          <t>https://leetcode.com/u/SUGANTHKALAI/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>922525106338</t>
+          <t>922525106378</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>SUJEETH M</t>
+          <t>YOKESWARAN S</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>SUJEETH77</t>
+          <t>syokeswaran</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3106,24 +3106,24 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SUJEETH77/</t>
+          <t>https://leetcode.com/u/syokeswaran/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>922525106340</t>
+          <t>922525106337</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>SUMITHRA S</t>
+          <t>SUGIDHARSHINI T</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>sumithra_16</t>
+          <t>Sugi_07</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3133,24 +3133,24 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sumithra_16/</t>
+          <t>https://leetcode.com/u/Sugi_07/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>922525106341</t>
+          <t>922525106338</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>SURYA PRABHU S</t>
+          <t>SUJEETH M</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>surya001prabhu</t>
+          <t>SUJEETH77</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3160,24 +3160,24 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/surya001prabhu/</t>
+          <t>https://leetcode.com/u/SUJEETH77/</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>922525106342</t>
+          <t>922525106340</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>SUSIDHARAN M</t>
+          <t>SUMITHRA S</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Susidharan147</t>
+          <t>sumithra_16</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3187,24 +3187,24 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Susidharan147/</t>
+          <t>https://leetcode.com/u/sumithra_16/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>922525106343</t>
+          <t>922525106341</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>SUTHARSHANA S</t>
+          <t>SURYA PRABHU S</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>sutharshana743</t>
+          <t>surya001prabhu</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3214,24 +3214,24 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sutharshana743/</t>
+          <t>https://leetcode.com/u/surya001prabhu/</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>922525106344</t>
+          <t>922525106342</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>SWATHI M</t>
+          <t>SUSIDHARAN M</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Swathimanivel_1234</t>
+          <t>Susidharan147</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3241,24 +3241,24 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Swathimanivel_1234/</t>
+          <t>https://leetcode.com/u/Susidharan147/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>922525106345</t>
+          <t>922525106343</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>SWATHI S</t>
+          <t>SUTHARSHANA S</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>_swathi _3366</t>
+          <t>sutharshana743</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3268,24 +3268,24 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_swathi _3366/</t>
+          <t>https://leetcode.com/u/sutharshana743/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>922525106347</t>
+          <t>922525106344</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>TAMIL SELVAN R</t>
+          <t>SWATHI M</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Kdmif0HMNm</t>
+          <t>Swathimanivel_1234</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3295,24 +3295,24 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Kdmif0HMNm/</t>
+          <t>https://leetcode.com/u/Swathimanivel_1234/</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>922525106348</t>
+          <t>922525106345</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>THAMARAI SELVI D</t>
+          <t>SWATHI S</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>thamarai_04</t>
+          <t>_swathi _3366</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3322,24 +3322,24 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/thamarai_04/</t>
+          <t>https://leetcode.com/u/_swathi _3366/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>922525106349</t>
+          <t>922525106347</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>THAMEEM FARSHITHA A</t>
+          <t>TAMIL SELVAN R</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Thameem_786</t>
+          <t>Kdmif0HMNm</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3349,24 +3349,24 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Thameem_786/</t>
+          <t>https://leetcode.com/u/Kdmif0HMNm/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>922525106350</t>
+          <t>922525106348</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>THARANISH R</t>
+          <t>THAMARAI SELVI D</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>THARANISH2008</t>
+          <t>thamarai_04</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3376,24 +3376,24 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/THARANISH2008/</t>
+          <t>https://leetcode.com/u/thamarai_04/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>922525106351</t>
+          <t>922525106349</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>THARUNIKA P</t>
+          <t>THAMEEM FARSHITHA A</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Tharunika_12</t>
+          <t>Thameem_786</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3403,24 +3403,24 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Tharunika_12/</t>
+          <t>https://leetcode.com/u/Thameem_786/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>922525106352</t>
+          <t>922525106350</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>THIRINESH KUMAR S</t>
+          <t>THARANISH R</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>THIRINESH KUMAR.S</t>
+          <t>THARANISH2008</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3430,24 +3430,24 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/THIRINESH KUMAR.S/</t>
+          <t>https://leetcode.com/u/THARANISH2008/</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>922525106354</t>
+          <t>922525106351</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>THIRUMURUGAN S</t>
+          <t>THARUNIKA P</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>thiru0211_</t>
+          <t>Tharunika_12</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -3457,24 +3457,24 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/thiru0211_/</t>
+          <t>https://leetcode.com/u/Tharunika_12/</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>922525106355</t>
+          <t>922525106352</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>VAISHNAVI U</t>
+          <t>THIRINESH KUMAR S</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>vaish200</t>
+          <t>THIRINESH KUMAR.S</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3484,24 +3484,24 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vaish200/</t>
+          <t>https://leetcode.com/u/THIRINESH KUMAR.S/</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>922525106356</t>
+          <t>922525106354</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>VASANTH KUMAR C</t>
+          <t>THIRUMURUGAN S</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>VASANTH2007</t>
+          <t>thiru0211_</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VASANTH2007/</t>
+          <t>https://leetcode.com/u/thiru0211_/</t>
         </is>
       </c>
     </row>
@@ -10184,8 +10184,35 @@
         </is>
       </c>
     </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>922525106274</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>SANJAY P</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>Sanjay_Sakthivel-2</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Sanjay_Sakthivel-2/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E361"/>
+  <autoFilter ref="A1:E362"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Students.xlsx
+++ b/Students.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$362</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$363</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E362"/>
+  <dimension ref="A1:E363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -467,17 +467,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>922525106253</t>
+          <t>922525106296</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>RITHANYA KN</t>
+          <t>SELVAKUMAR K</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Rithanya12-3</t>
+          <t>Selvakumarsk-32</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -487,24 +487,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithanya12-3/</t>
+          <t>https://leetcode.com/u/Selvakumarsk-32/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>922525106266</t>
+          <t>922525106298</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SAHANA.V</t>
+          <t>SELVA RAGAVAN</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sahanavijayakumar_0033</t>
+          <t>Selvax07</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -514,24 +514,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sahanavijayakumar_0033/</t>
+          <t>https://leetcode.com/u/Selvax07/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>922525106269</t>
+          <t>922525106299</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sakthivel. M</t>
+          <t>SENTHAMIZHSELVAN K</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>sakthivel23116</t>
+          <t>Senthamizh08</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -541,24 +541,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sakthivel23116/</t>
+          <t>https://leetcode.com/u/Senthamizh08/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>922525106275</t>
+          <t>922525106300</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SANJAY U</t>
+          <t>Senthil.S</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SanjayUdayan</t>
+          <t>Jna76WrjNd</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -568,24 +568,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SanjayUdayan/</t>
+          <t>https://leetcode.com/u/Jna76WrjNd/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>922525106283</t>
+          <t>922525106297</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SANTHOSH S</t>
+          <t>SELVAPRAGADEESH S</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SanthoshSathya260</t>
+          <t>Selvapragadeesh</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -595,24 +595,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SanthoshSathya260/</t>
+          <t>https://leetcode.com/u/Selvapragadeesh/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>922525106291</t>
+          <t>922525106302</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SARVESWARAN R</t>
+          <t>SHAHANA S</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>sarvesh312008</t>
+          <t>shahana_pandiraj04</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -622,24 +622,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sarvesh312008/</t>
+          <t>https://leetcode.com/u/shahana_pandiraj04/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>922525106292</t>
+          <t>922525106303</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SASHMIKA.P</t>
+          <t>SHANTHINI C</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>sashmikaprabhu</t>
+          <t>ShanthiniChelladurai</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -649,24 +649,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sashmikaprabhu/</t>
+          <t>https://leetcode.com/u/ShanthiniChelladurai/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>922525106272</t>
+          <t>922525106305</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SANJAY D</t>
+          <t>SHARATH P</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>itsmesanjay007</t>
+          <t>sharath_1010</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -676,24 +676,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itsmesanjay007/</t>
+          <t>https://leetcode.com/u/sharath_1010/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>922525106309</t>
+          <t>922525106310</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SHREE CHARAN T</t>
+          <t>SIVA MANIKANDAN K</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>shreecharan22</t>
+          <t>9043374912</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -703,24 +703,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shreecharan22/</t>
+          <t>https://leetcode.com/u/9043374912/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>922525106314</t>
+          <t>922525106308</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SIVANESH D</t>
+          <t>SHREE HARINI L</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>sivanesh2007</t>
+          <t>Shree_Harini478</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -730,24 +730,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivanesh2007/</t>
+          <t>https://leetcode.com/u/Shree_Harini478/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>922525196293</t>
+          <t>922525106314</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SASWIN D</t>
+          <t>SIVANESH D</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>saswin_88</t>
+          <t>sivanesh2007</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -757,24 +757,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saswin_88/</t>
+          <t>https://leetcode.com/u/sivanesh2007/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>922525106257</t>
+          <t>922525196293</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>RITHIKA B</t>
+          <t>SASWIN D</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Rithika_Balakrishnan</t>
+          <t>saswin_88</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -784,24 +784,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithika_Balakrishnan/</t>
+          <t>https://leetcode.com/u/saswin_88/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>922525106259</t>
+          <t>922525106253</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ROHITH V</t>
+          <t>RITHANYA KN</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>RohithrohiV</t>
+          <t>Rithanya12-3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/RohithrohiV/</t>
+          <t>https://leetcode.com/u/Rithanya12-3/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>922525106260</t>
+          <t>922525106257</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ROOBAGAPRIYA R</t>
+          <t>RITHIKA B</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Roobagapriya</t>
+          <t>Rithika_Balakrishnan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -838,24 +838,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Roobagapriya/</t>
+          <t>https://leetcode.com/u/Rithika_Balakrishnan/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>922525106307</t>
+          <t>922525106259</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SHIVANI B</t>
+          <t>ROHITH V</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>shivani208</t>
+          <t>RohithrohiV</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -865,24 +865,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shivani208/</t>
+          <t>https://leetcode.com/u/RohithrohiV/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>922525106264</t>
+          <t>922525106260</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SABAREESH K</t>
+          <t>ROOBAGAPRIYA R</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>sabareesh_karikalan</t>
+          <t>Roobagapriya</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -892,24 +892,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
+          <t>https://leetcode.com/u/Roobagapriya/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>922525106256</t>
+          <t>922525106266</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>RITHIK P</t>
+          <t>SAHANA.V</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Rithik_78</t>
+          <t>Sahanavijayakumar_0033</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -919,24 +919,24 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithik_78/</t>
+          <t>https://leetcode.com/u/Sahanavijayakumar_0033/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>922525106258</t>
+          <t>922525106269</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>RITHISH R</t>
+          <t>Sakthivel. M</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Rithish_</t>
+          <t>sakthivel23116</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -946,24 +946,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithish_/</t>
+          <t>https://leetcode.com/u/sakthivel23116/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>922525106261</t>
+          <t>922525106275</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Roshan M</t>
+          <t>SANJAY U</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>roshan2403</t>
+          <t>SanjayUdayan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -973,24 +973,24 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/roshan2403/</t>
+          <t>https://leetcode.com/u/SanjayUdayan/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>922525106262</t>
+          <t>922525106307</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ROSHIKA V</t>
+          <t>SHIVANI B</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>roshikaveeramalai</t>
+          <t>shivani208</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1000,24 +1000,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/roshikaveeramalai/</t>
+          <t>https://leetcode.com/u/shivani208/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>922525106263</t>
+          <t>922525106264</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>RUBESH C</t>
+          <t>SABAREESH K</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Rubesh_7</t>
+          <t>sabareesh_karikalan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1027,24 +1027,24 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rubesh_7/</t>
+          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>922525106265</t>
+          <t>922525106283</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SABARIVASAN P</t>
+          <t>SANTHOSH S</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SabarivasanP</t>
+          <t>SanthoshSathya260</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1054,24 +1054,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SabarivasanP/</t>
+          <t>https://leetcode.com/u/SanthoshSathya260/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>922525106268</t>
+          <t>922525106291</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SAKTHI S</t>
+          <t>SARVESWARAN R</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sakthisaro08</t>
+          <t>sarvesh312008</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1081,24 +1081,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sakthisaro08/</t>
+          <t>https://leetcode.com/u/sarvesh312008/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>922525106271</t>
+          <t>922525106292</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SANDHOSH KUMAR R</t>
+          <t>SASHMIKA.P</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>sandhosh_30_R</t>
+          <t>sashmikaprabhu</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1108,24 +1108,24 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sandhosh_30_R/</t>
+          <t>https://leetcode.com/u/sashmikaprabhu/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>922525106273</t>
+          <t>922525106272</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SANJAY P</t>
+          <t>SANJAY D</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>sanjay00675</t>
+          <t>itsmesanjay007</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1135,24 +1135,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sanjay00675/</t>
+          <t>https://leetcode.com/u/itsmesanjay007/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>922525106278</t>
+          <t>922525106258</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SANMATHI R</t>
+          <t>RITHISH R</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>sanmathi06</t>
+          <t>Rithish_</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1162,24 +1162,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sanmathi06/</t>
+          <t>https://leetcode.com/u/Rithish_/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>922525106279</t>
+          <t>922525106315</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SANTHIYA T</t>
+          <t>SIVANESH G</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>santhiya0202</t>
+          <t>GSIVANESH</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1189,24 +1189,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhiya0202/</t>
+          <t>https://leetcode.com/u/GSIVANESH/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>922525106280</t>
+          <t>922525106313</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SANTHOSH D</t>
+          <t>SIVAGNANAM M</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>santhosh7811</t>
+          <t>sivagnanam3344</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1216,24 +1216,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh7811/</t>
+          <t>https://leetcode.com/u/sivagnanam3344/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>922525106282</t>
+          <t>922525106309</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SANTHOSH PRIYAN S</t>
+          <t>SHREE CHARAN T</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SANTHOSH PRIYAN S</t>
+          <t>shreecharan22</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1243,24 +1243,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SANTHOSH PRIYAN S/</t>
+          <t>https://leetcode.com/u/shreecharan22/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>922525106284</t>
+          <t>922525106256</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Santhosh S</t>
+          <t>RITHIK P</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>santhosh2407</t>
+          <t>Rithik_78</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1270,24 +1270,24 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh2407/</t>
+          <t>https://leetcode.com/u/Rithik_78/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>922525106285</t>
+          <t>922525106261</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SANTHOSH V</t>
+          <t>Roshan M</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>santhosh8760</t>
+          <t>roshan2403</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1297,24 +1297,24 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh8760/</t>
+          <t>https://leetcode.com/u/roshan2403/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>922525106286</t>
+          <t>922525106262</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SARAN K</t>
+          <t>ROSHIKA V</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>saran32</t>
+          <t>roshikaveeramalai</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1324,24 +1324,24 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saran32/</t>
+          <t>https://leetcode.com/u/roshikaveeramalai/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>922525106287</t>
+          <t>922525106263</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SARAVANAN K</t>
+          <t>RUBESH C</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>saravanan .k</t>
+          <t>Rubesh_7</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1351,24 +1351,24 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saravanan .k/</t>
+          <t>https://leetcode.com/u/Rubesh_7/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>922525106288</t>
+          <t>922525106265</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SARAVANAN K</t>
+          <t>SABARIVASAN P</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>saravanan__k__</t>
+          <t>SabarivasanP</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1378,24 +1378,24 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saravanan__k__/</t>
+          <t>https://leetcode.com/u/SabarivasanP/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>922525106289</t>
+          <t>922525106312</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SARAVANAN S</t>
+          <t>SIVADHARSHINI D</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Saravanan_7525</t>
+          <t>dharshinideivsigamani</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1405,24 +1405,24 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Saravanan_7525/</t>
+          <t>https://leetcode.com/u/dharshinideivsigamani/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>922525106290</t>
+          <t>922525106268</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SARIKA M P</t>
+          <t>SAKTHI S</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>sarika_5408</t>
+          <t>Sakthisaro08</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1432,24 +1432,24 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sarika_5408/</t>
+          <t>https://leetcode.com/u/Sakthisaro08/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>922525106296</t>
+          <t>922525106311</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SELVAKUMAR K</t>
+          <t>SIVA PRAKASH M</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Selvakumarsk-32</t>
+          <t>sivaprakash_0406</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1459,24 +1459,24 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvakumarsk-32/</t>
+          <t>https://leetcode.com/u/sivaprakash_0406/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>922525106297</t>
+          <t>922525106271</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SELVAPRAGADEESH S</t>
+          <t>SANDHOSH KUMAR R</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Selvapragadeesh</t>
+          <t>sandhosh_30_R</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1486,24 +1486,24 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvapragadeesh/</t>
+          <t>https://leetcode.com/u/sandhosh_30_R/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>922525106298</t>
+          <t>922525106273</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SELVA RAGAVAN</t>
+          <t>SANJAY P</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Selvax07</t>
+          <t>sanjay00675</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1513,24 +1513,24 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvax07/</t>
+          <t>https://leetcode.com/u/sanjay00675/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>922525106299</t>
+          <t>922525106278</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SENTHAMIZHSELVAN K</t>
+          <t>SANMATHI R</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Senthamizh08</t>
+          <t>sanmathi06</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1540,24 +1540,24 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Senthamizh08/</t>
+          <t>https://leetcode.com/u/sanmathi06/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>922525106300</t>
+          <t>922525106279</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Senthil.S</t>
+          <t>SANTHIYA T</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Jna76WrjNd</t>
+          <t>santhiya0202</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1567,24 +1567,24 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Jna76WrjNd/</t>
+          <t>https://leetcode.com/u/santhiya0202/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>922525106302</t>
+          <t>922525106280</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SHAHANA S</t>
+          <t>SANTHOSH D</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>shahana_pandiraj04</t>
+          <t>santhosh7811</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1594,24 +1594,24 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shahana_pandiraj04/</t>
+          <t>https://leetcode.com/u/santhosh7811/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>922525106303</t>
+          <t>922525106282</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SHANTHINI C</t>
+          <t>SANTHOSH PRIYAN S</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ShanthiniChelladurai</t>
+          <t>SANTHOSH PRIYAN S</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1621,24 +1621,24 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/ShanthiniChelladurai/</t>
+          <t>https://leetcode.com/u/SANTHOSH PRIYAN S/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>922525106305</t>
+          <t>922525106284</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SHARATH P</t>
+          <t>Santhosh S</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>sharath_1010</t>
+          <t>santhosh2407</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1648,24 +1648,24 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sharath_1010/</t>
+          <t>https://leetcode.com/u/santhosh2407/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>922525106308</t>
+          <t>922525106285</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SHREE HARINI L</t>
+          <t>SANTHOSH V</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Shree_Harini478</t>
+          <t>santhosh8760</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1675,24 +1675,24 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Shree_Harini478/</t>
+          <t>https://leetcode.com/u/santhosh8760/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>922525106310</t>
+          <t>922525106286</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SIVA MANIKANDAN K</t>
+          <t>SARAN K</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>9043374912</t>
+          <t>saran32</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1702,24 +1702,24 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/9043374912/</t>
+          <t>https://leetcode.com/u/saran32/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>922525106311</t>
+          <t>922525106287</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SIVA PRAKASH M</t>
+          <t>SARAVANAN K</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>sivaprakash_0406</t>
+          <t>saravanan .k</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1729,24 +1729,24 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivaprakash_0406/</t>
+          <t>https://leetcode.com/u/saravanan .k/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>922525106312</t>
+          <t>922525106288</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SIVADHARSHINI D</t>
+          <t>SARAVANAN K</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>dharshinideivsigamani</t>
+          <t>saravanan__k__</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/dharshinideivsigamani/</t>
+          <t>https://leetcode.com/u/saravanan__k__/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>922525106313</t>
+          <t>922525106289</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SIVAGNANAM M</t>
+          <t>SARAVANAN S</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>sivagnanam3344</t>
+          <t>Saravanan_7525</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1783,24 +1783,24 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivagnanam3344/</t>
+          <t>https://leetcode.com/u/Saravanan_7525/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>922525106315</t>
+          <t>922525106290</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SIVANESH G</t>
+          <t>SARIKA M P</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>GSIVANESH</t>
+          <t>sarika_5408</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/GSIVANESH/</t>
+          <t>https://leetcode.com/u/sarika_5408/</t>
         </is>
       </c>
     </row>
@@ -1844,17 +1844,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>922525106362</t>
+          <t>922525106373</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>VELLIANGIRI R</t>
+          <t>YASHNI S</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>velliangiri_R</t>
+          <t>Yashnisubramaniyan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1864,24 +1864,24 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/velliangiri_R/</t>
+          <t>https://leetcode.com/u/Yashnisubramaniyan/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>922525106363</t>
+          <t>922525106339</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>VIGNESH M</t>
+          <t>SUJITH RAJA B</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>O8bYDSRUbE</t>
+          <t>mahi20_</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1891,24 +1891,24 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/O8bYDSRUbE/</t>
+          <t>https://leetcode.com/u/mahi20_/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>922525106365</t>
+          <t>922525106353</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>VIGNESHWAR U</t>
+          <t>THIRISHA C</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>VIGNESHWAR0221</t>
+          <t>thirishavsb</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1918,24 +1918,24 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VIGNESHWAR0221/</t>
+          <t>https://leetcode.com/u/thirishavsb/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>922525106366</t>
+          <t>922525106374</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>VIJAYARAGAVAN R</t>
+          <t>YASWANTH V</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>vijayaragavan1216</t>
+          <t>yaswanth_2008</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1945,24 +1945,24 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vijayaragavan1216/</t>
+          <t>https://leetcode.com/u/yaswanth_2008/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>922525106367</t>
+          <t>922525106376</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>VIKRAM V</t>
+          <t>YAZHINI S</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>vikramvicky5678</t>
+          <t>yazhini__1234</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1972,24 +1972,24 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vikramvicky5678/</t>
+          <t>https://leetcode.com/u/yazhini__1234/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>922525106368</t>
+          <t>922525106375</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>VISHNU B</t>
+          <t>YAZHINI M</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>VISHNU_B_2008</t>
+          <t>yazhini2007</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1999,24 +1999,24 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VISHNU_B_2008/</t>
+          <t>https://leetcode.com/u/yazhini2007/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>922525106360</t>
+          <t>922525106364</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>VASUDEVAN G</t>
+          <t>VIGNESH VELAN M</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>GTVASU2008</t>
+          <t>Vicky_27_Velan</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2026,24 +2026,24 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/GTVASU2008/</t>
+          <t>https://leetcode.com/u/Vicky_27_Velan/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>922525106355</t>
+          <t>922525106377</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>VAISHNAVI U</t>
+          <t>YAZHINI V</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>vaish200</t>
+          <t>VISU_YAZHU</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2053,24 +2053,24 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vaish200/</t>
+          <t>https://leetcode.com/u/VISU_YAZHU/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>922525106356</t>
+          <t>922525106346</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>VASANTH KUMAR C</t>
+          <t>SWETHA E</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>VASANTH2007</t>
+          <t>Swetha_20_1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2080,24 +2080,24 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VASANTH2007/</t>
+          <t>https://leetcode.com/u/Swetha_20_1/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>922525106357</t>
+          <t>922525106378</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>VASANTH S</t>
+          <t>YOKESWARAN S</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>_vasanth_s_</t>
+          <t>syokeswaran</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2107,24 +2107,24 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_vasanth_s_/</t>
+          <t>https://leetcode.com/u/syokeswaran/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>922525106358</t>
+          <t>922525106367</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>VASANTHA KUMAR D</t>
+          <t>VIKRAM V</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Vasanthakumar12232</t>
+          <t>vikramvicky5678</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2134,24 +2134,24 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vasanthakumar12232/</t>
+          <t>https://leetcode.com/u/vikramvicky5678/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>922525106359</t>
+          <t>922525106368</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>VASANTHKUMAR R</t>
+          <t>VISHNU B</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>VasanthKumar008</t>
+          <t>VISHNU_B_2008</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2161,24 +2161,24 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VasanthKumar008/</t>
+          <t>https://leetcode.com/u/VISHNU_B_2008/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>922525106361</t>
+          <t>922525106369</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>VASUKI K</t>
+          <t>VISHNU PRIYAN S</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>vasuki</t>
+          <t>itz__priyan__</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2188,24 +2188,24 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vasuki/</t>
+          <t>https://leetcode.com/u/itz__priyan__/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>922525106369</t>
+          <t>922525106370</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>VISHNU PRIYAN S</t>
+          <t>VISHNUHARAN V S</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>itz__priyan__</t>
+          <t>Vishnuharan082007</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2215,24 +2215,24 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itz__priyan__/</t>
+          <t>https://leetcode.com/u/Vishnuharan082007/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>922525106370</t>
+          <t>922525106371</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>VISHNUHARAN V S</t>
+          <t>VISHNUPRIYA S</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Vishnuharan082007</t>
+          <t>vishnupriyamaran</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2242,24 +2242,24 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vishnuharan082007/</t>
+          <t>https://leetcode.com/u/vishnupriyamaran/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>922525106371</t>
+          <t>922525106372</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>VISHNUPRIYA S</t>
+          <t>VISHWAJETH A M</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>vishnupriyamaran</t>
+          <t>vishwajeth</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2269,24 +2269,24 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vishnupriyamaran/</t>
+          <t>https://leetcode.com/u/vishwajeth/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>922525106372</t>
+          <t>922525106316</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>VISHWAJETH A M</t>
+          <t>SIVARANJAN M P</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>vishwajeth</t>
+          <t>SIVARANJAN_MP</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2296,24 +2296,24 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vishwajeth/</t>
+          <t>https://leetcode.com/u/SIVARANJAN_MP/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>922525106373</t>
+          <t>922525106317</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>YASHNI S</t>
+          <t>SIVASANJEEV P</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Yashnisubramaniyan</t>
+          <t>Sivasanjeev16</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2323,24 +2323,24 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Yashnisubramaniyan/</t>
+          <t>https://leetcode.com/u/Sivasanjeev16/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>922525106374</t>
+          <t>922525106318</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>YASWANTH V</t>
+          <t>SIVASUBRAMANI A</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>yaswanth_2008</t>
+          <t>AK_Siva</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2350,24 +2350,24 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yaswanth_2008/</t>
+          <t>https://leetcode.com/u/AK_Siva/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>922525106316</t>
+          <t>922525106319</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SIVARANJAN M P</t>
+          <t>SIVATHARUN C</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>SIVARANJAN_MP</t>
+          <t>sivatharun22</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2377,24 +2377,24 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SIVARANJAN_MP/</t>
+          <t>https://leetcode.com/u/sivatharun22/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>922525106317</t>
+          <t>922525106320</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SIVASANJEEV P</t>
+          <t>SOBIKA R</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Sivasanjeev16</t>
+          <t>_sobika_R</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2404,24 +2404,24 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sivasanjeev16/</t>
+          <t>https://leetcode.com/u/_sobika_R/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>922525106318</t>
+          <t>922525106321</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SIVASUBRAMANI A</t>
+          <t>SREE DHARANI C</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AK_Siva</t>
+          <t>SREEDHARANI_14</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2431,24 +2431,24 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/AK_Siva/</t>
+          <t>https://leetcode.com/u/SREEDHARANI_14/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>922525106319</t>
+          <t>922525106322</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SIVATHARUN C</t>
+          <t>SRI  T</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>sivatharun22</t>
+          <t>Sri1540</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2458,24 +2458,24 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivatharun22/</t>
+          <t>https://leetcode.com/u/Sri1540/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>922525106320</t>
+          <t>922525106323</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SOBIKA R</t>
+          <t>SRI HEERA J</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>_sobika_R</t>
+          <t>sriheera03</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2485,24 +2485,24 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_sobika_R/</t>
+          <t>https://leetcode.com/u/sriheera03/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>922525106321</t>
+          <t>922525106324</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SREE DHARANI C</t>
+          <t>SRI KANTH R</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SREEDHARANI_14</t>
+          <t>kanth2008</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2512,24 +2512,24 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SREEDHARANI_14/</t>
+          <t>https://leetcode.com/u/kanth2008/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>922525106322</t>
+          <t>922525106325</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SRI  T</t>
+          <t>SRI SASTIKA G</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Sri1540</t>
+          <t>Srisastika_1401</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2539,24 +2539,24 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sri1540/</t>
+          <t>https://leetcode.com/u/Srisastika_1401/</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>922525106323</t>
+          <t>922525106326</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SRI HEERA J</t>
+          <t>SRI VARSHAN B P</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>sriheera03</t>
+          <t>srivarshan_B_P</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2566,24 +2566,24 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sriheera03/</t>
+          <t>https://leetcode.com/u/srivarshan_B_P/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>922525106324</t>
+          <t>922525106327</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SRI KANTH R</t>
+          <t>SRINATH V</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>kanth2008</t>
+          <t>V_SRINATH</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2593,24 +2593,24 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kanth2008/</t>
+          <t>https://leetcode.com/u/V_SRINATH/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>922525106325</t>
+          <t>922525106328</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SRI SASTIKA G</t>
+          <t>SRINIRANJAN S</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Srisastika_1401</t>
+          <t>SRINIRANJAN2008</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2620,24 +2620,24 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Srisastika_1401/</t>
+          <t>https://leetcode.com/u/SRINIRANJAN2008/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>922525106326</t>
+          <t>922525106329</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SRI VARSHAN B P</t>
+          <t>SRINITHE T</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>srivarshan_B_P</t>
+          <t>srinithe_1401</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2647,24 +2647,24 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/srivarshan_B_P/</t>
+          <t>https://leetcode.com/u/srinithe_1401/</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>922525106327</t>
+          <t>922525106330</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SRINATH V</t>
+          <t>SRINITHI S</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>V_SRINATH</t>
+          <t>Srinithi24_</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2674,24 +2674,24 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/V_SRINATH/</t>
+          <t>https://leetcode.com/u/Srinithi24_/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>922525106328</t>
+          <t>922525106331</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SRINIRANJAN S</t>
+          <t>SRISAMAYA R</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>SRINIRANJAN2008</t>
+          <t>mahi</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SRINIRANJAN2008/</t>
+          <t>https://leetcode.com/u/mahi/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>922525106329</t>
+          <t>922525106332</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SRINITHE T</t>
+          <t>SUBARNA V</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>srinithe_1401</t>
+          <t>Subarna_17</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2728,24 +2728,24 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/srinithe_1401/</t>
+          <t>https://leetcode.com/u/Subarna_17/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>922525106330</t>
+          <t>922525106334</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SRINITHI S</t>
+          <t>SUBIKA T</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Srinithi24_</t>
+          <t>subika1112</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2755,24 +2755,24 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Srinithi24_/</t>
+          <t>https://leetcode.com/u/subika1112/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>922525106331</t>
+          <t>922525106335</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SRISAMAYA R</t>
+          <t>SUDHARSAN S</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>mahi</t>
+          <t>Sudharsan</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2782,24 +2782,24 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/mahi/</t>
+          <t>https://leetcode.com/u/Sudharsan/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>922525106332</t>
+          <t>922525106336</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SUBARNA V</t>
+          <t>SUGANTHAN K</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Subarna_17</t>
+          <t>SUGANTHKALAI</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2809,24 +2809,24 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Subarna_17/</t>
+          <t>https://leetcode.com/u/SUGANTHKALAI/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>922525106376</t>
+          <t>922525106337</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>YAZHINI S</t>
+          <t>SUGIDHARSHINI T</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>yazhini__1234</t>
+          <t>Sugi_07</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2836,24 +2836,24 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yazhini__1234/</t>
+          <t>https://leetcode.com/u/Sugi_07/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>922525106364</t>
+          <t>922525106338</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>VIGNESH VELAN M</t>
+          <t>SUJEETH M</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Vicky_27_Velan</t>
+          <t>SUJEETH77</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2863,24 +2863,24 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vicky_27_Velan/</t>
+          <t>https://leetcode.com/u/SUJEETH77/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>922525106334</t>
+          <t>922525106340</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SUBIKA T</t>
+          <t>SUMITHRA S</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>subika1112</t>
+          <t>sumithra_16</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2890,24 +2890,24 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/subika1112/</t>
+          <t>https://leetcode.com/u/sumithra_16/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>922525106375</t>
+          <t>922525106341</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>YAZHINI M</t>
+          <t>SURYA PRABHU S</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>yazhini2007</t>
+          <t>surya001prabhu</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2917,24 +2917,24 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yazhini2007/</t>
+          <t>https://leetcode.com/u/surya001prabhu/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>922525106377</t>
+          <t>922525106342</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>YAZHINI V</t>
+          <t>SUSIDHARAN M</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>VISU_YAZHU</t>
+          <t>Susidharan147</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2944,24 +2944,24 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VISU_YAZHU/</t>
+          <t>https://leetcode.com/u/Susidharan147/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>922525106335</t>
+          <t>922525106343</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SUDHARSAN S</t>
+          <t>SUTHARSHANA S</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Sudharsan</t>
+          <t>sutharshana743</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2971,24 +2971,24 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sudharsan/</t>
+          <t>https://leetcode.com/u/sutharshana743/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>922525106339</t>
+          <t>922525106344</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SUJITH RAJA B</t>
+          <t>SWATHI M</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>mahi20_</t>
+          <t>Swathimanivel_1234</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2998,24 +2998,24 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/mahi20_/</t>
+          <t>https://leetcode.com/u/Swathimanivel_1234/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>922525106353</t>
+          <t>922525106345</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>THIRISHA C</t>
+          <t>SWATHI S</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>thirishavsb</t>
+          <t>_swathi _3366</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3025,24 +3025,24 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/thirishavsb/</t>
+          <t>https://leetcode.com/u/_swathi _3366/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>922525106346</t>
+          <t>922525106347</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SWETHA E</t>
+          <t>TAMIL SELVAN R</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Swetha_20_1</t>
+          <t>Kdmif0HMNm</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3052,24 +3052,24 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Swetha_20_1/</t>
+          <t>https://leetcode.com/u/Kdmif0HMNm/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>922525106336</t>
+          <t>922525106348</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>SUGANTHAN K</t>
+          <t>THAMARAI SELVI D</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>SUGANTHKALAI</t>
+          <t>thamarai_04</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3079,24 +3079,24 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SUGANTHKALAI/</t>
+          <t>https://leetcode.com/u/thamarai_04/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>922525106378</t>
+          <t>922525106349</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>YOKESWARAN S</t>
+          <t>THAMEEM FARSHITHA A</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>syokeswaran</t>
+          <t>Thameem_786</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3106,24 +3106,24 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/syokeswaran/</t>
+          <t>https://leetcode.com/u/Thameem_786/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>922525106337</t>
+          <t>922525106350</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>SUGIDHARSHINI T</t>
+          <t>THARANISH R</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Sugi_07</t>
+          <t>THARANISH2008</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3133,24 +3133,24 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sugi_07/</t>
+          <t>https://leetcode.com/u/THARANISH2008/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>922525106338</t>
+          <t>922525106351</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>SUJEETH M</t>
+          <t>THARUNIKA P</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>SUJEETH77</t>
+          <t>Tharunika_12</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3160,24 +3160,24 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SUJEETH77/</t>
+          <t>https://leetcode.com/u/Tharunika_12/</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>922525106340</t>
+          <t>922525106352</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>SUMITHRA S</t>
+          <t>THIRINESH KUMAR S</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>sumithra_16</t>
+          <t>THIRINESH KUMAR.S</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3187,24 +3187,24 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sumithra_16/</t>
+          <t>https://leetcode.com/u/THIRINESH KUMAR.S/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>922525106341</t>
+          <t>922525106354</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>SURYA PRABHU S</t>
+          <t>THIRUMURUGAN S</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>surya001prabhu</t>
+          <t>thiru0211_</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3214,24 +3214,24 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/surya001prabhu/</t>
+          <t>https://leetcode.com/u/thiru0211_/</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>922525106342</t>
+          <t>922525106355</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>SUSIDHARAN M</t>
+          <t>VAISHNAVI U</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Susidharan147</t>
+          <t>vaish200</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3241,24 +3241,24 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Susidharan147/</t>
+          <t>https://leetcode.com/u/vaish200/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>922525106343</t>
+          <t>922525106356</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>SUTHARSHANA S</t>
+          <t>VASANTH KUMAR C</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>sutharshana743</t>
+          <t>VASANTH2007</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3268,24 +3268,24 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sutharshana743/</t>
+          <t>https://leetcode.com/u/VASANTH2007/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>922525106344</t>
+          <t>922525106357</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>SWATHI M</t>
+          <t>VASANTH S</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Swathimanivel_1234</t>
+          <t>_vasanth_s_</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3295,24 +3295,24 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Swathimanivel_1234/</t>
+          <t>https://leetcode.com/u/_vasanth_s_/</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>922525106345</t>
+          <t>922525106358</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SWATHI S</t>
+          <t>VASANTHA KUMAR D</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>_swathi _3366</t>
+          <t>Vasanthakumar12232</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3322,24 +3322,24 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_swathi _3366/</t>
+          <t>https://leetcode.com/u/Vasanthakumar12232/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>922525106347</t>
+          <t>922525106359</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>TAMIL SELVAN R</t>
+          <t>VASANTHKUMAR R</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Kdmif0HMNm</t>
+          <t>VasanthKumar008</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3349,24 +3349,24 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Kdmif0HMNm/</t>
+          <t>https://leetcode.com/u/VasanthKumar008/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>922525106348</t>
+          <t>922525106360</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>THAMARAI SELVI D</t>
+          <t>VASUDEVAN G</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>thamarai_04</t>
+          <t>GTVASU2008</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3376,24 +3376,24 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/thamarai_04/</t>
+          <t>https://leetcode.com/u/GTVASU2008/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>922525106349</t>
+          <t>922525106361</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>THAMEEM FARSHITHA A</t>
+          <t>VASUKI K</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Thameem_786</t>
+          <t>vasuki</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3403,24 +3403,24 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Thameem_786/</t>
+          <t>https://leetcode.com/u/vasuki/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>922525106350</t>
+          <t>922525106362</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>THARANISH R</t>
+          <t>VELLIANGIRI R</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>THARANISH2008</t>
+          <t>velliangiri_R</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3430,24 +3430,24 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/THARANISH2008/</t>
+          <t>https://leetcode.com/u/velliangiri_R/</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>922525106351</t>
+          <t>922525106363</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>THARUNIKA P</t>
+          <t>VIGNESH M</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Tharunika_12</t>
+          <t>O8bYDSRUbE</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -3457,24 +3457,24 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Tharunika_12/</t>
+          <t>https://leetcode.com/u/O8bYDSRUbE/</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>922525106352</t>
+          <t>922525106365</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>THIRINESH KUMAR S</t>
+          <t>VIGNESHWAR U</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>THIRINESH KUMAR.S</t>
+          <t>VIGNESHWAR0221</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3484,24 +3484,24 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/THIRINESH KUMAR.S/</t>
+          <t>https://leetcode.com/u/VIGNESHWAR0221/</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>922525106354</t>
+          <t>922525106366</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>THIRUMURUGAN S</t>
+          <t>VIJAYARAGAVAN R</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>thiru0211_</t>
+          <t>vijayaragavan1216</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/thiru0211_/</t>
+          <t>https://leetcode.com/u/vijayaragavan1216/</t>
         </is>
       </c>
     </row>
@@ -6056,17 +6056,17 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>922525106021</t>
+          <t>922525106022</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>ANOOP C</t>
+          <t>ANUJA S</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>anoop_appuz</t>
+          <t>anuja008</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -6076,7 +6076,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/anoop_appuz/</t>
+          <t>https://leetcode.com/u/anuja008/</t>
         </is>
       </c>
     </row>
@@ -6893,17 +6893,17 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>922525106022</t>
+          <t>922525106021</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>ANUJA S</t>
+          <t>ANOOP C</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>anuja008</t>
+          <t>anoop_appuz</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -6913,7 +6913,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/anuja008/</t>
+          <t>https://leetcode.com/u/anoop_appuz/</t>
         </is>
       </c>
     </row>
@@ -10211,8 +10211,35 @@
         </is>
       </c>
     </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>922525106295</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>SATHYA PRAKASAM KANNAN</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>SATHYAPRAKASAM__7</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/SATHYAPRAKASAM__7/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E362"/>
+  <autoFilter ref="A1:E363"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Students.xlsx
+++ b/Students.xlsx
@@ -737,17 +737,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>922525106314</t>
+          <t>922525106309</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SIVANESH D</t>
+          <t>SHREE CHARAN T</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>sivanesh2007</t>
+          <t>shreecharan22</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -757,24 +757,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivanesh2007/</t>
+          <t>https://leetcode.com/u/shreecharan22/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>922525196293</t>
+          <t>922525106314</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SASWIN D</t>
+          <t>SIVANESH D</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>saswin_88</t>
+          <t>sivanesh2007</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -784,24 +784,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saswin_88/</t>
+          <t>https://leetcode.com/u/sivanesh2007/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>922525106253</t>
+          <t>922525196293</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>RITHANYA KN</t>
+          <t>SASWIN D</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Rithanya12-3</t>
+          <t>saswin_88</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithanya12-3/</t>
+          <t>https://leetcode.com/u/saswin_88/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>922525106257</t>
+          <t>922525106287</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RITHIKA B</t>
+          <t>SARAVANAN K</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Rithika_Balakrishnan</t>
+          <t>X01u2FNNX4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -838,24 +838,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithika_Balakrishnan/</t>
+          <t>https://leetcode.com/u/X01u2FNNX4/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>922525106259</t>
+          <t>922525106258</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ROHITH V</t>
+          <t>RITHISH R</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>RohithrohiV</t>
+          <t>Rithish_</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -865,24 +865,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/RohithrohiV/</t>
+          <t>https://leetcode.com/u/Rithish_/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>922525106260</t>
+          <t>922525106264</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ROOBAGAPRIYA R</t>
+          <t>SABAREESH K</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Roobagapriya</t>
+          <t>sabareesh_karikalan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -892,24 +892,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Roobagapriya/</t>
+          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>922525106266</t>
+          <t>922525106253</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SAHANA.V</t>
+          <t>RITHANYA KN</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sahanavijayakumar_0033</t>
+          <t>Rithanya12-3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -919,24 +919,24 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sahanavijayakumar_0033/</t>
+          <t>https://leetcode.com/u/Rithanya12-3/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>922525106269</t>
+          <t>922525106257</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sakthivel. M</t>
+          <t>RITHIKA B</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>sakthivel23116</t>
+          <t>Rithika_Balakrishnan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -946,24 +946,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sakthivel23116/</t>
+          <t>https://leetcode.com/u/Rithika_Balakrishnan/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>922525106275</t>
+          <t>922525106259</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SANJAY U</t>
+          <t>ROHITH V</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SanjayUdayan</t>
+          <t>RohithrohiV</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -973,24 +973,24 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SanjayUdayan/</t>
+          <t>https://leetcode.com/u/RohithrohiV/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>922525106307</t>
+          <t>922525106256</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SHIVANI B</t>
+          <t>RITHIK P</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>shivani208</t>
+          <t>Rithik_78</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1000,24 +1000,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shivani208/</t>
+          <t>https://leetcode.com/u/Rithik_78/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>922525106264</t>
+          <t>922525106260</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SABAREESH K</t>
+          <t>ROOBAGAPRIYA R</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>sabareesh_karikalan</t>
+          <t>Roobagapriya</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1027,24 +1027,24 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
+          <t>https://leetcode.com/u/Roobagapriya/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>922525106283</t>
+          <t>922525106266</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SANTHOSH S</t>
+          <t>SAHANA.V</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SanthoshSathya260</t>
+          <t>Sahanavijayakumar_0033</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1054,24 +1054,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SanthoshSathya260/</t>
+          <t>https://leetcode.com/u/Sahanavijayakumar_0033/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>922525106291</t>
+          <t>922525106269</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SARVESWARAN R</t>
+          <t>Sakthivel. M</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>sarvesh312008</t>
+          <t>sakthivel23116</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1081,24 +1081,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sarvesh312008/</t>
+          <t>https://leetcode.com/u/sakthivel23116/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>922525106292</t>
+          <t>922525106307</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SASHMIKA.P</t>
+          <t>SHIVANI B</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>sashmikaprabhu</t>
+          <t>shivani208</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1108,24 +1108,24 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sashmikaprabhu/</t>
+          <t>https://leetcode.com/u/shivani208/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>922525106272</t>
+          <t>922525106275</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SANJAY D</t>
+          <t>SANJAY U</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>itsmesanjay007</t>
+          <t>SanjayUdayan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1135,24 +1135,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itsmesanjay007/</t>
+          <t>https://leetcode.com/u/SanjayUdayan/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>922525106258</t>
+          <t>922525106283</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>RITHISH R</t>
+          <t>SANTHOSH S</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Rithish_</t>
+          <t>SanthoshSathya260</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1162,24 +1162,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithish_/</t>
+          <t>https://leetcode.com/u/SanthoshSathya260/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>922525106315</t>
+          <t>922525106291</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SIVANESH G</t>
+          <t>SARVESWARAN R</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>GSIVANESH</t>
+          <t>sarvesh312008</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1189,24 +1189,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/GSIVANESH/</t>
+          <t>https://leetcode.com/u/sarvesh312008/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>922525106313</t>
+          <t>922525106292</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SIVAGNANAM M</t>
+          <t>SASHMIKA.P</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>sivagnanam3344</t>
+          <t>sashmikaprabhu</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1216,24 +1216,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivagnanam3344/</t>
+          <t>https://leetcode.com/u/sashmikaprabhu/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>922525106309</t>
+          <t>922525106272</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SHREE CHARAN T</t>
+          <t>SANJAY D</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>shreecharan22</t>
+          <t>itsmesanjay007</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1243,24 +1243,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shreecharan22/</t>
+          <t>https://leetcode.com/u/itsmesanjay007/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>922525106256</t>
+          <t>922525106315</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>RITHIK P</t>
+          <t>SIVANESH G</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Rithik_78</t>
+          <t>GSIVANESH</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1270,24 +1270,24 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithik_78/</t>
+          <t>https://leetcode.com/u/GSIVANESH/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>922525106261</t>
+          <t>922525106313</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Roshan M</t>
+          <t>SIVAGNANAM M</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>roshan2403</t>
+          <t>sivagnanam3344</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1297,24 +1297,24 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/roshan2403/</t>
+          <t>https://leetcode.com/u/sivagnanam3344/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>922525106262</t>
+          <t>922525106261</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ROSHIKA V</t>
+          <t>Roshan M</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>roshikaveeramalai</t>
+          <t>roshan2403</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1324,24 +1324,24 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/roshikaveeramalai/</t>
+          <t>https://leetcode.com/u/roshan2403/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>922525106263</t>
+          <t>922525106262</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>RUBESH C</t>
+          <t>ROSHIKA V</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Rubesh_7</t>
+          <t>roshikaveeramalai</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1351,24 +1351,24 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rubesh_7/</t>
+          <t>https://leetcode.com/u/roshikaveeramalai/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>922525106265</t>
+          <t>922525106263</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SABARIVASAN P</t>
+          <t>RUBESH C</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SabarivasanP</t>
+          <t>Rubesh_7</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1378,24 +1378,24 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SabarivasanP/</t>
+          <t>https://leetcode.com/u/Rubesh_7/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>922525106312</t>
+          <t>922525106265</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SIVADHARSHINI D</t>
+          <t>SABARIVASAN P</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>dharshinideivsigamani</t>
+          <t>SabarivasanP</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1405,24 +1405,24 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/dharshinideivsigamani/</t>
+          <t>https://leetcode.com/u/SabarivasanP/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>922525106268</t>
+          <t>922525106312</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SAKTHI S</t>
+          <t>SIVADHARSHINI D</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sakthisaro08</t>
+          <t>dharshinideivsigamani</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1432,24 +1432,24 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sakthisaro08/</t>
+          <t>https://leetcode.com/u/dharshinideivsigamani/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>922525106311</t>
+          <t>922525106268</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SIVA PRAKASH M</t>
+          <t>SAKTHI S</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>sivaprakash_0406</t>
+          <t>Sakthisaro08</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1459,24 +1459,24 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivaprakash_0406/</t>
+          <t>https://leetcode.com/u/Sakthisaro08/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>922525106271</t>
+          <t>922525106311</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SANDHOSH KUMAR R</t>
+          <t>SIVA PRAKASH M</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>sandhosh_30_R</t>
+          <t>sivaprakash_0406</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1486,24 +1486,24 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sandhosh_30_R/</t>
+          <t>https://leetcode.com/u/sivaprakash_0406/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>922525106273</t>
+          <t>922525106271</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SANJAY P</t>
+          <t>SANDHOSH KUMAR R</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>sanjay00675</t>
+          <t>sandhosh_30_R</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1513,24 +1513,24 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sanjay00675/</t>
+          <t>https://leetcode.com/u/sandhosh_30_R/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>922525106278</t>
+          <t>922525106273</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SANMATHI R</t>
+          <t>SANJAY P</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>sanmathi06</t>
+          <t>sanjay00675</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1540,24 +1540,24 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sanmathi06/</t>
+          <t>https://leetcode.com/u/sanjay00675/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>922525106279</t>
+          <t>922525106278</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SANTHIYA T</t>
+          <t>SANMATHI R</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>santhiya0202</t>
+          <t>sanmathi06</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1567,24 +1567,24 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhiya0202/</t>
+          <t>https://leetcode.com/u/sanmathi06/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>922525106280</t>
+          <t>922525106279</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SANTHOSH D</t>
+          <t>SANTHIYA T</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>santhosh7811</t>
+          <t>santhiya0202</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1594,24 +1594,24 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh7811/</t>
+          <t>https://leetcode.com/u/santhiya0202/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>922525106282</t>
+          <t>922525106280</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SANTHOSH PRIYAN S</t>
+          <t>SANTHOSH D</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SANTHOSH PRIYAN S</t>
+          <t>santhosh7811</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1621,24 +1621,24 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SANTHOSH PRIYAN S/</t>
+          <t>https://leetcode.com/u/santhosh7811/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>922525106284</t>
+          <t>922525106282</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Santhosh S</t>
+          <t>SANTHOSH PRIYAN S</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>santhosh2407</t>
+          <t>SANTHOSH PRIYAN S</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1648,24 +1648,24 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh2407/</t>
+          <t>https://leetcode.com/u/SANTHOSH PRIYAN S/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>922525106285</t>
+          <t>922525106284</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SANTHOSH V</t>
+          <t>Santhosh S</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>santhosh8760</t>
+          <t>santhosh2407</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1675,24 +1675,24 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh8760/</t>
+          <t>https://leetcode.com/u/santhosh2407/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>922525106286</t>
+          <t>922525106285</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SARAN K</t>
+          <t>SANTHOSH V</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>saran32</t>
+          <t>santhosh8760</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1702,24 +1702,24 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saran32/</t>
+          <t>https://leetcode.com/u/santhosh8760/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>922525106287</t>
+          <t>922525106286</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SARAVANAN K</t>
+          <t>SARAN K</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>saravanan .k</t>
+          <t>saran32</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saravanan .k/</t>
+          <t>https://leetcode.com/u/saran32/</t>
         </is>
       </c>
     </row>
@@ -1871,17 +1871,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>922525106339</t>
+          <t>922525106376</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SUJITH RAJA B</t>
+          <t>YAZHINI S</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>mahi20_</t>
+          <t>yazhini__1234</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1891,24 +1891,24 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/mahi20_/</t>
+          <t>https://leetcode.com/u/yazhini__1234/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>922525106353</t>
+          <t>922525106374</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>THIRISHA C</t>
+          <t>YASWANTH V</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>thirishavsb</t>
+          <t>yaswanth_2008</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1918,24 +1918,24 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/thirishavsb/</t>
+          <t>https://leetcode.com/u/yaswanth_2008/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>922525106374</t>
+          <t>922525106375</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>YASWANTH V</t>
+          <t>YAZHINI M</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>yaswanth_2008</t>
+          <t>yazhini2007</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1945,24 +1945,24 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yaswanth_2008/</t>
+          <t>https://leetcode.com/u/yazhini2007/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>922525106376</t>
+          <t>922525106378</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>YAZHINI S</t>
+          <t>YOKESWARAN S</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>yazhini__1234</t>
+          <t>syokeswaran</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1972,24 +1972,24 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yazhini__1234/</t>
+          <t>https://leetcode.com/u/syokeswaran/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>922525106375</t>
+          <t>922525106364</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>YAZHINI M</t>
+          <t>VIGNESH VELAN M</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>yazhini2007</t>
+          <t>Vicky_27_Velan</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1999,24 +1999,24 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yazhini2007/</t>
+          <t>https://leetcode.com/u/Vicky_27_Velan/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>922525106364</t>
+          <t>922525106377</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>VIGNESH VELAN M</t>
+          <t>YAZHINI V</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Vicky_27_Velan</t>
+          <t>VISU_YAZHU</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2026,24 +2026,24 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vicky_27_Velan/</t>
+          <t>https://leetcode.com/u/VISU_YAZHU/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>922525106377</t>
+          <t>922525106346</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>YAZHINI V</t>
+          <t>SWETHA E</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>VISU_YAZHU</t>
+          <t>Swetha_20_1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2053,24 +2053,24 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VISU_YAZHU/</t>
+          <t>https://leetcode.com/u/Swetha_20_1/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>922525106346</t>
+          <t>922525106339</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SWETHA E</t>
+          <t>SUJITH RAJA B</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Swetha_20_1</t>
+          <t>mahi20_</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2080,24 +2080,24 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Swetha_20_1/</t>
+          <t>https://leetcode.com/u/mahi20_/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>922525106378</t>
+          <t>922525106353</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>YOKESWARAN S</t>
+          <t>THIRISHA C</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>syokeswaran</t>
+          <t>thirishavsb</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/syokeswaran/</t>
+          <t>https://leetcode.com/u/thirishavsb/</t>
         </is>
       </c>
     </row>
@@ -6029,17 +6029,17 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>922525106020</t>
+          <t>922525106021</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>ANJITHAA N</t>
+          <t>ANOOP C</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Anjithaa2006</t>
+          <t>anoop_appuz</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -6049,7 +6049,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Anjithaa2006/</t>
+          <t>https://leetcode.com/u/anoop_appuz/</t>
         </is>
       </c>
     </row>
@@ -6893,17 +6893,17 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>922525106021</t>
+          <t>922525106020</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>ANOOP C</t>
+          <t>ANJITHAA N</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>anoop_appuz</t>
+          <t>Anjithaa2006</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -6913,7 +6913,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/anoop_appuz/</t>
+          <t>https://leetcode.com/u/Anjithaa2006/</t>
         </is>
       </c>
     </row>

--- a/Students.xlsx
+++ b/Students.xlsx
@@ -467,17 +467,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>922525106296</t>
+          <t>922525106256</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SELVAKUMAR K</t>
+          <t>RITHIK P</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Selvakumarsk-32</t>
+          <t>Rithik_78</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -487,24 +487,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvakumarsk-32/</t>
+          <t>https://leetcode.com/u/Rithik_78/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>922525106298</t>
+          <t>922525106258</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SELVA RAGAVAN</t>
+          <t>RITHISH R</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Selvax07</t>
+          <t>Rithish_</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -514,24 +514,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvax07/</t>
+          <t>https://leetcode.com/u/Rithish_/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>922525106299</t>
+          <t>922525106266</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SENTHAMIZHSELVAN K</t>
+          <t>SAHANA.V</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Senthamizh08</t>
+          <t>Sahanavijayakumar_0033</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -541,24 +541,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Senthamizh08/</t>
+          <t>https://leetcode.com/u/Sahanavijayakumar_0033/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>922525106300</t>
+          <t>922525106269</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Senthil.S</t>
+          <t>Sakthivel. M</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jna76WrjNd</t>
+          <t>sakthivel23116</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -568,24 +568,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Jna76WrjNd/</t>
+          <t>https://leetcode.com/u/sakthivel23116/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>922525106297</t>
+          <t>922525106275</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SELVAPRAGADEESH S</t>
+          <t>SANJAY U</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Selvapragadeesh</t>
+          <t>SanjayUdayan</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -595,24 +595,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvapragadeesh/</t>
+          <t>https://leetcode.com/u/SanjayUdayan/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>922525106302</t>
+          <t>922525106283</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SHAHANA S</t>
+          <t>SANTHOSH S</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>shahana_pandiraj04</t>
+          <t>SanthoshSathya260</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -622,24 +622,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shahana_pandiraj04/</t>
+          <t>https://leetcode.com/u/SanthoshSathya260/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>922525106303</t>
+          <t>922525106291</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SHANTHINI C</t>
+          <t>SARVESWARAN R</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ShanthiniChelladurai</t>
+          <t>sarvesh312008</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -649,24 +649,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/ShanthiniChelladurai/</t>
+          <t>https://leetcode.com/u/sarvesh312008/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>922525106305</t>
+          <t>922525106292</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SHARATH P</t>
+          <t>SASHMIKA.P</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>sharath_1010</t>
+          <t>sashmikaprabhu</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -676,24 +676,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sharath_1010/</t>
+          <t>https://leetcode.com/u/sashmikaprabhu/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>922525106310</t>
+          <t>922525106272</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SIVA MANIKANDAN K</t>
+          <t>SANJAY D</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>9043374912</t>
+          <t>itsmesanjay007</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -703,24 +703,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/9043374912/</t>
+          <t>https://leetcode.com/u/itsmesanjay007/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>922525106308</t>
+          <t>922525106309</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SHREE HARINI L</t>
+          <t>SHREE CHARAN T</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Shree_Harini478</t>
+          <t>shreecharan22</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -730,24 +730,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Shree_Harini478/</t>
+          <t>https://leetcode.com/u/shreecharan22/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>922525106309</t>
+          <t>922525106314</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SHREE CHARAN T</t>
+          <t>SIVANESH D</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>shreecharan22</t>
+          <t>sivanesh2007</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -757,24 +757,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shreecharan22/</t>
+          <t>https://leetcode.com/u/sivanesh2007/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>922525106314</t>
+          <t>922525196293</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SIVANESH D</t>
+          <t>SASWIN D</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>sivanesh2007</t>
+          <t>saswin_88</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -784,24 +784,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivanesh2007/</t>
+          <t>https://leetcode.com/u/saswin_88/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>922525196293</t>
+          <t>922525106287</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SASWIN D</t>
+          <t>SARAVANAN K</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>saswin_88</t>
+          <t>X01u2FNNX4</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saswin_88/</t>
+          <t>https://leetcode.com/u/X01u2FNNX4/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>922525106287</t>
+          <t>922525106264</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SARAVANAN K</t>
+          <t>SABAREESH K</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>X01u2FNNX4</t>
+          <t>sabareesh_karikalan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -838,24 +838,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/X01u2FNNX4/</t>
+          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>922525106258</t>
+          <t>922525106253</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RITHISH R</t>
+          <t>RITHANYA KN</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Rithish_</t>
+          <t>Rithanya12-3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -865,24 +865,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithish_/</t>
+          <t>https://leetcode.com/u/Rithanya12-3/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>922525106264</t>
+          <t>922525106257</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SABAREESH K</t>
+          <t>RITHIKA B</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>sabareesh_karikalan</t>
+          <t>Rithika_Balakrishnan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -892,24 +892,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
+          <t>https://leetcode.com/u/Rithika_Balakrishnan/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>922525106253</t>
+          <t>922525106259</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>RITHANYA KN</t>
+          <t>ROHITH V</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Rithanya12-3</t>
+          <t>RohithrohiV</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -919,24 +919,24 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithanya12-3/</t>
+          <t>https://leetcode.com/u/RohithrohiV/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>922525106257</t>
+          <t>922525106260</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>RITHIKA B</t>
+          <t>ROOBAGAPRIYA R</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Rithika_Balakrishnan</t>
+          <t>Roobagapriya</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -946,24 +946,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithika_Balakrishnan/</t>
+          <t>https://leetcode.com/u/Roobagapriya/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>922525106259</t>
+          <t>922525106307</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ROHITH V</t>
+          <t>SHIVANI B</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>RohithrohiV</t>
+          <t>shivani208</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -973,24 +973,24 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/RohithrohiV/</t>
+          <t>https://leetcode.com/u/shivani208/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>922525106256</t>
+          <t>922525106261</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>RITHIK P</t>
+          <t>Roshan M</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rithik_78</t>
+          <t>roshan2403</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1000,24 +1000,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithik_78/</t>
+          <t>https://leetcode.com/u/roshan2403/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>922525106260</t>
+          <t>922525106262</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ROOBAGAPRIYA R</t>
+          <t>ROSHIKA V</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Roobagapriya</t>
+          <t>roshikaveeramalai</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1027,24 +1027,24 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Roobagapriya/</t>
+          <t>https://leetcode.com/u/roshikaveeramalai/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>922525106266</t>
+          <t>922525106263</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SAHANA.V</t>
+          <t>RUBESH C</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sahanavijayakumar_0033</t>
+          <t>Rubesh_7</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1054,24 +1054,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sahanavijayakumar_0033/</t>
+          <t>https://leetcode.com/u/Rubesh_7/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>922525106269</t>
+          <t>922525106265</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Sakthivel. M</t>
+          <t>SABARIVASAN P</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>sakthivel23116</t>
+          <t>SabarivasanP</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1081,24 +1081,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sakthivel23116/</t>
+          <t>https://leetcode.com/u/SabarivasanP/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>922525106307</t>
+          <t>922525106268</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SHIVANI B</t>
+          <t>SAKTHI S</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>shivani208</t>
+          <t>Sakthisaro08</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1108,24 +1108,24 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shivani208/</t>
+          <t>https://leetcode.com/u/Sakthisaro08/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>922525106275</t>
+          <t>922525106271</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SANJAY U</t>
+          <t>SANDHOSH KUMAR R</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SanjayUdayan</t>
+          <t>sandhosh_30_R</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1135,24 +1135,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SanjayUdayan/</t>
+          <t>https://leetcode.com/u/sandhosh_30_R/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>922525106283</t>
+          <t>922525106273</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SANTHOSH S</t>
+          <t>SANJAY P</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SanthoshSathya260</t>
+          <t>sanjay00675</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1162,24 +1162,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SanthoshSathya260/</t>
+          <t>https://leetcode.com/u/sanjay00675/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>922525106291</t>
+          <t>922525106278</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SARVESWARAN R</t>
+          <t>SANMATHI R</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>sarvesh312008</t>
+          <t>sanmathi06</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1189,24 +1189,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sarvesh312008/</t>
+          <t>https://leetcode.com/u/sanmathi06/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>922525106292</t>
+          <t>922525106279</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SASHMIKA.P</t>
+          <t>SANTHIYA T</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>sashmikaprabhu</t>
+          <t>santhiya0202</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1216,24 +1216,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sashmikaprabhu/</t>
+          <t>https://leetcode.com/u/santhiya0202/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>922525106272</t>
+          <t>922525106280</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SANJAY D</t>
+          <t>SANTHOSH D</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>itsmesanjay007</t>
+          <t>santhosh7811</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1243,24 +1243,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itsmesanjay007/</t>
+          <t>https://leetcode.com/u/santhosh7811/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>922525106315</t>
+          <t>922525106284</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SIVANESH G</t>
+          <t>Santhosh S</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>GSIVANESH</t>
+          <t>santhosh2407</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1270,24 +1270,24 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/GSIVANESH/</t>
+          <t>https://leetcode.com/u/santhosh2407/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>922525106313</t>
+          <t>922525106285</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SIVAGNANAM M</t>
+          <t>SANTHOSH V</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>sivagnanam3344</t>
+          <t>santhosh8760</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1297,24 +1297,24 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivagnanam3344/</t>
+          <t>https://leetcode.com/u/santhosh8760/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>922525106261</t>
+          <t>922525106286</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Roshan M</t>
+          <t>SARAN K</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>roshan2403</t>
+          <t>saran32</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1324,24 +1324,24 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/roshan2403/</t>
+          <t>https://leetcode.com/u/saran32/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>922525106262</t>
+          <t>922525106288</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ROSHIKA V</t>
+          <t>SARAVANAN K</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>roshikaveeramalai</t>
+          <t>saravanan__k__</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1351,24 +1351,24 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/roshikaveeramalai/</t>
+          <t>https://leetcode.com/u/saravanan__k__/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>922525106263</t>
+          <t>922525106289</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>RUBESH C</t>
+          <t>SARAVANAN S</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Rubesh_7</t>
+          <t>Saravanan_7525</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1378,24 +1378,24 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rubesh_7/</t>
+          <t>https://leetcode.com/u/Saravanan_7525/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>922525106265</t>
+          <t>922525106290</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SABARIVASAN P</t>
+          <t>SARIKA M P</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SabarivasanP</t>
+          <t>sarika_5408</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1405,24 +1405,24 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SabarivasanP/</t>
+          <t>https://leetcode.com/u/sarika_5408/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>922525106312</t>
+          <t>922525106296</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SIVADHARSHINI D</t>
+          <t>SELVAKUMAR K</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>dharshinideivsigamani</t>
+          <t>Selvakumarsk-32</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1432,24 +1432,24 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/dharshinideivsigamani/</t>
+          <t>https://leetcode.com/u/Selvakumarsk-32/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>922525106268</t>
+          <t>922525106297</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SAKTHI S</t>
+          <t>SELVAPRAGADEESH S</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sakthisaro08</t>
+          <t>Selvapragadeesh</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1459,24 +1459,24 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sakthisaro08/</t>
+          <t>https://leetcode.com/u/Selvapragadeesh/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>922525106311</t>
+          <t>922525106298</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SIVA PRAKASH M</t>
+          <t>SELVA RAGAVAN</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>sivaprakash_0406</t>
+          <t>Selvax07</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1486,24 +1486,24 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivaprakash_0406/</t>
+          <t>https://leetcode.com/u/Selvax07/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>922525106271</t>
+          <t>922525106299</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SANDHOSH KUMAR R</t>
+          <t>SENTHAMIZHSELVAN K</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>sandhosh_30_R</t>
+          <t>Senthamizh08</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1513,24 +1513,24 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sandhosh_30_R/</t>
+          <t>https://leetcode.com/u/Senthamizh08/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>922525106273</t>
+          <t>922525106300</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SANJAY P</t>
+          <t>Senthil.S</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>sanjay00675</t>
+          <t>Jna76WrjNd</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1540,24 +1540,24 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sanjay00675/</t>
+          <t>https://leetcode.com/u/Jna76WrjNd/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>922525106278</t>
+          <t>922525106302</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SANMATHI R</t>
+          <t>SHAHANA S</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>sanmathi06</t>
+          <t>shahana_pandiraj04</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1567,24 +1567,24 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sanmathi06/</t>
+          <t>https://leetcode.com/u/shahana_pandiraj04/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>922525106279</t>
+          <t>922525106303</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SANTHIYA T</t>
+          <t>SHANTHINI C</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>santhiya0202</t>
+          <t>ShanthiniChelladurai</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1594,24 +1594,24 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhiya0202/</t>
+          <t>https://leetcode.com/u/ShanthiniChelladurai/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>922525106280</t>
+          <t>922525106305</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SANTHOSH D</t>
+          <t>SHARATH P</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>santhosh7811</t>
+          <t>sharath_1010</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1621,24 +1621,24 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh7811/</t>
+          <t>https://leetcode.com/u/sharath_1010/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>922525106282</t>
+          <t>922525106308</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SANTHOSH PRIYAN S</t>
+          <t>SHREE HARINI L</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SANTHOSH PRIYAN S</t>
+          <t>Shree_Harini478</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1648,24 +1648,24 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SANTHOSH PRIYAN S/</t>
+          <t>https://leetcode.com/u/Shree_Harini478/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>922525106284</t>
+          <t>922525106310</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Santhosh S</t>
+          <t>SIVA MANIKANDAN K</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>santhosh2407</t>
+          <t>9043374912</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1675,24 +1675,24 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh2407/</t>
+          <t>https://leetcode.com/u/9043374912/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>922525106285</t>
+          <t>922525106311</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SANTHOSH V</t>
+          <t>SIVA PRAKASH M</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>santhosh8760</t>
+          <t>sivaprakash_0406</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1702,24 +1702,24 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh8760/</t>
+          <t>https://leetcode.com/u/sivaprakash_0406/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>922525106286</t>
+          <t>922525106312</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SARAN K</t>
+          <t>SIVADHARSHINI D</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>saran32</t>
+          <t>dharshinideivsigamani</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1729,24 +1729,24 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saran32/</t>
+          <t>https://leetcode.com/u/dharshinideivsigamani/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>922525106288</t>
+          <t>922525106313</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SARAVANAN K</t>
+          <t>SIVAGNANAM M</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>saravanan__k__</t>
+          <t>sivagnanam3344</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saravanan__k__/</t>
+          <t>https://leetcode.com/u/sivagnanam3344/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>922525106289</t>
+          <t>922525106315</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SARAVANAN S</t>
+          <t>SIVANESH G</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Saravanan_7525</t>
+          <t>GSIVANESH</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1783,24 +1783,24 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Saravanan_7525/</t>
+          <t>https://leetcode.com/u/GSIVANESH/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>922525106290</t>
+          <t>922525106282</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SARIKA M P</t>
+          <t>SANTHOSH PRIYAN S</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>sarika_5408</t>
+          <t>8925787430</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sarika_5408/</t>
+          <t>https://leetcode.com/u/8925787430/</t>
         </is>
       </c>
     </row>
@@ -1844,17 +1844,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>922525106373</t>
+          <t>922525106360</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>YASHNI S</t>
+          <t>VASUDEVAN G</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Yashnisubramaniyan</t>
+          <t>GTVASU2008</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1864,24 +1864,24 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Yashnisubramaniyan/</t>
+          <t>https://leetcode.com/u/GTVASU2008/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>922525106376</t>
+          <t>922525106361</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>YAZHINI S</t>
+          <t>VASUKI K</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>yazhini__1234</t>
+          <t>vasuki</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1891,24 +1891,24 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yazhini__1234/</t>
+          <t>https://leetcode.com/u/vasuki/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>922525106374</t>
+          <t>922525106362</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>YASWANTH V</t>
+          <t>VELLIANGIRI R</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>yaswanth_2008</t>
+          <t>velliangiri_R</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1918,24 +1918,24 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yaswanth_2008/</t>
+          <t>https://leetcode.com/u/velliangiri_R/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>922525106375</t>
+          <t>922525106363</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>YAZHINI M</t>
+          <t>VIGNESH M</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>yazhini2007</t>
+          <t>O8bYDSRUbE</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1945,24 +1945,24 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yazhini2007/</t>
+          <t>https://leetcode.com/u/O8bYDSRUbE/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>922525106378</t>
+          <t>922525106365</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>YOKESWARAN S</t>
+          <t>VIGNESHWAR U</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>syokeswaran</t>
+          <t>VIGNESHWAR0221</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1972,24 +1972,24 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/syokeswaran/</t>
+          <t>https://leetcode.com/u/VIGNESHWAR0221/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>922525106364</t>
+          <t>922525106366</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>VIGNESH VELAN M</t>
+          <t>VIJAYARAGAVAN R</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Vicky_27_Velan</t>
+          <t>vijayaragavan1216</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1999,24 +1999,24 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vicky_27_Velan/</t>
+          <t>https://leetcode.com/u/vijayaragavan1216/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>922525106377</t>
+          <t>922525106358</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>YAZHINI V</t>
+          <t>VASANTHA KUMAR D</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>VISU_YAZHU</t>
+          <t>Vasanthakumar12232</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2026,24 +2026,24 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VISU_YAZHU/</t>
+          <t>https://leetcode.com/u/Vasanthakumar12232/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>922525106346</t>
+          <t>922525106352</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SWETHA E</t>
+          <t>THIRINESH KUMAR S</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Swetha_20_1</t>
+          <t>THIRINESH KUMAR.S</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2053,24 +2053,24 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Swetha_20_1/</t>
+          <t>https://leetcode.com/u/THIRINESH KUMAR.S/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>922525106339</t>
+          <t>922525106354</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SUJITH RAJA B</t>
+          <t>THIRUMURUGAN S</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>mahi20_</t>
+          <t>thiru0211_</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2080,24 +2080,24 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/mahi20_/</t>
+          <t>https://leetcode.com/u/thiru0211_/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>922525106353</t>
+          <t>922525106355</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>THIRISHA C</t>
+          <t>VAISHNAVI U</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>thirishavsb</t>
+          <t>vaish200</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2107,24 +2107,24 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/thirishavsb/</t>
+          <t>https://leetcode.com/u/vaish200/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>922525106367</t>
+          <t>922525106356</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>VIKRAM V</t>
+          <t>VASANTH KUMAR C</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>vikramvicky5678</t>
+          <t>VASANTH2007</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2134,24 +2134,24 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vikramvicky5678/</t>
+          <t>https://leetcode.com/u/VASANTH2007/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>922525106368</t>
+          <t>922525106357</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>VISHNU B</t>
+          <t>VASANTH S</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>VISHNU_B_2008</t>
+          <t>_vasanth_s_</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2161,24 +2161,24 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VISHNU_B_2008/</t>
+          <t>https://leetcode.com/u/_vasanth_s_/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>922525106369</t>
+          <t>922525106359</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>VISHNU PRIYAN S</t>
+          <t>VASANTHKUMAR R</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>itz__priyan__</t>
+          <t>VasanthKumar008</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2188,24 +2188,24 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itz__priyan__/</t>
+          <t>https://leetcode.com/u/VasanthKumar008/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>922525106370</t>
+          <t>922525106367</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>VISHNUHARAN V S</t>
+          <t>VIKRAM V</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Vishnuharan082007</t>
+          <t>vikramvicky5678</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2215,24 +2215,24 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vishnuharan082007/</t>
+          <t>https://leetcode.com/u/vikramvicky5678/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>922525106371</t>
+          <t>922525106368</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>VISHNUPRIYA S</t>
+          <t>VISHNU B</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>vishnupriyamaran</t>
+          <t>VISHNU_B_2008</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2242,24 +2242,24 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vishnupriyamaran/</t>
+          <t>https://leetcode.com/u/VISHNU_B_2008/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>922525106372</t>
+          <t>922525106369</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>VISHWAJETH A M</t>
+          <t>VISHNU PRIYAN S</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>vishwajeth</t>
+          <t>itz__priyan__</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2269,24 +2269,24 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vishwajeth/</t>
+          <t>https://leetcode.com/u/itz__priyan__/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>922525106316</t>
+          <t>922525106370</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SIVARANJAN M P</t>
+          <t>VISHNUHARAN V S</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SIVARANJAN_MP</t>
+          <t>Vishnuharan082007</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2296,24 +2296,24 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SIVARANJAN_MP/</t>
+          <t>https://leetcode.com/u/Vishnuharan082007/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>922525106317</t>
+          <t>922525106371</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SIVASANJEEV P</t>
+          <t>VISHNUPRIYA S</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Sivasanjeev16</t>
+          <t>vishnupriyamaran</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2323,24 +2323,24 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sivasanjeev16/</t>
+          <t>https://leetcode.com/u/vishnupriyamaran/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>922525106318</t>
+          <t>922525106372</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SIVASUBRAMANI A</t>
+          <t>VISHWAJETH A M</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>AK_Siva</t>
+          <t>vishwajeth</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2350,24 +2350,24 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/AK_Siva/</t>
+          <t>https://leetcode.com/u/vishwajeth/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>922525106319</t>
+          <t>922525106316</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SIVATHARUN C</t>
+          <t>SIVARANJAN M P</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>sivatharun22</t>
+          <t>SIVARANJAN_MP</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2377,24 +2377,24 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivatharun22/</t>
+          <t>https://leetcode.com/u/SIVARANJAN_MP/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>922525106320</t>
+          <t>922525106317</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SOBIKA R</t>
+          <t>SIVASANJEEV P</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>_sobika_R</t>
+          <t>Sivasanjeev16</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2404,24 +2404,24 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_sobika_R/</t>
+          <t>https://leetcode.com/u/Sivasanjeev16/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>922525106321</t>
+          <t>922525106318</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SREE DHARANI C</t>
+          <t>SIVASUBRAMANI A</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>SREEDHARANI_14</t>
+          <t>AK_Siva</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2431,24 +2431,24 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SREEDHARANI_14/</t>
+          <t>https://leetcode.com/u/AK_Siva/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>922525106322</t>
+          <t>922525106319</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SRI  T</t>
+          <t>SIVATHARUN C</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Sri1540</t>
+          <t>sivatharun22</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2458,24 +2458,24 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sri1540/</t>
+          <t>https://leetcode.com/u/sivatharun22/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>922525106323</t>
+          <t>922525106320</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SRI HEERA J</t>
+          <t>SOBIKA R</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>sriheera03</t>
+          <t>_sobika_R</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2485,24 +2485,24 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sriheera03/</t>
+          <t>https://leetcode.com/u/_sobika_R/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>922525106324</t>
+          <t>922525106321</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SRI KANTH R</t>
+          <t>SREE DHARANI C</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>kanth2008</t>
+          <t>SREEDHARANI_14</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2512,24 +2512,24 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/kanth2008/</t>
+          <t>https://leetcode.com/u/SREEDHARANI_14/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>922525106325</t>
+          <t>922525106373</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SRI SASTIKA G</t>
+          <t>YASHNI S</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Srisastika_1401</t>
+          <t>Yashnisubramaniyan</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2539,24 +2539,24 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Srisastika_1401/</t>
+          <t>https://leetcode.com/u/Yashnisubramaniyan/</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>922525106326</t>
+          <t>922525106322</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SRI VARSHAN B P</t>
+          <t>SRI  T</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>srivarshan_B_P</t>
+          <t>Sri1540</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2566,24 +2566,24 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/srivarshan_B_P/</t>
+          <t>https://leetcode.com/u/Sri1540/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>922525106327</t>
+          <t>922525106323</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SRINATH V</t>
+          <t>SRI HEERA J</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>V_SRINATH</t>
+          <t>sriheera03</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2593,24 +2593,24 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/V_SRINATH/</t>
+          <t>https://leetcode.com/u/sriheera03/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>922525106328</t>
+          <t>922525106324</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SRINIRANJAN S</t>
+          <t>SRI KANTH R</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>SRINIRANJAN2008</t>
+          <t>kanth2008</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2620,24 +2620,24 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SRINIRANJAN2008/</t>
+          <t>https://leetcode.com/u/kanth2008/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>922525106329</t>
+          <t>922525106325</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SRINITHE T</t>
+          <t>SRI SASTIKA G</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>srinithe_1401</t>
+          <t>Srisastika_1401</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2647,24 +2647,24 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/srinithe_1401/</t>
+          <t>https://leetcode.com/u/Srisastika_1401/</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>922525106330</t>
+          <t>922525106326</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SRINITHI S</t>
+          <t>SRI VARSHAN B P</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Srinithi24_</t>
+          <t>srivarshan_B_P</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2674,24 +2674,24 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Srinithi24_/</t>
+          <t>https://leetcode.com/u/srivarshan_B_P/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>922525106331</t>
+          <t>922525106327</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SRISAMAYA R</t>
+          <t>SRINATH V</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>mahi</t>
+          <t>V_SRINATH</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/mahi/</t>
+          <t>https://leetcode.com/u/V_SRINATH/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>922525106332</t>
+          <t>922525106328</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SUBARNA V</t>
+          <t>SRINIRANJAN S</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Subarna_17</t>
+          <t>SRINIRANJAN2008</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2728,24 +2728,24 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Subarna_17/</t>
+          <t>https://leetcode.com/u/SRINIRANJAN2008/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>922525106334</t>
+          <t>922525106329</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SUBIKA T</t>
+          <t>SRINITHE T</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>subika1112</t>
+          <t>srinithe_1401</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2755,24 +2755,24 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/subika1112/</t>
+          <t>https://leetcode.com/u/srinithe_1401/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>922525106335</t>
+          <t>922525106330</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SUDHARSAN S</t>
+          <t>SRINITHI S</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Sudharsan</t>
+          <t>Srinithi24_</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2782,24 +2782,24 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sudharsan/</t>
+          <t>https://leetcode.com/u/Srinithi24_/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>922525106336</t>
+          <t>922525106376</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SUGANTHAN K</t>
+          <t>YAZHINI S</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>SUGANTHKALAI</t>
+          <t>yazhini__1234</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2809,24 +2809,24 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SUGANTHKALAI/</t>
+          <t>https://leetcode.com/u/yazhini__1234/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>922525106337</t>
+          <t>922525106331</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SUGIDHARSHINI T</t>
+          <t>SRISAMAYA R</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Sugi_07</t>
+          <t>mahi</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2836,24 +2836,24 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sugi_07/</t>
+          <t>https://leetcode.com/u/mahi/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>922525106338</t>
+          <t>922525106332</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SUJEETH M</t>
+          <t>SUBARNA V</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>SUJEETH77</t>
+          <t>Subarna_17</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2863,24 +2863,24 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SUJEETH77/</t>
+          <t>https://leetcode.com/u/Subarna_17/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>922525106340</t>
+          <t>922525106334</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SUMITHRA S</t>
+          <t>SUBIKA T</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>sumithra_16</t>
+          <t>subika1112</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2890,24 +2890,24 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sumithra_16/</t>
+          <t>https://leetcode.com/u/subika1112/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>922525106341</t>
+          <t>922525106335</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SURYA PRABHU S</t>
+          <t>SUDHARSAN S</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>surya001prabhu</t>
+          <t>Sudharsan</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2917,24 +2917,24 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/surya001prabhu/</t>
+          <t>https://leetcode.com/u/Sudharsan/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>922525106342</t>
+          <t>922525106374</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>SUSIDHARAN M</t>
+          <t>YASWANTH V</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Susidharan147</t>
+          <t>yaswanth_2008</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2944,24 +2944,24 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Susidharan147/</t>
+          <t>https://leetcode.com/u/yaswanth_2008/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>922525106343</t>
+          <t>922525106336</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SUTHARSHANA S</t>
+          <t>SUGANTHAN K</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>sutharshana743</t>
+          <t>SUGANTHKALAI</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2971,24 +2971,24 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sutharshana743/</t>
+          <t>https://leetcode.com/u/SUGANTHKALAI/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>922525106344</t>
+          <t>922525106375</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SWATHI M</t>
+          <t>YAZHINI M</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Swathimanivel_1234</t>
+          <t>yazhini2007</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2998,24 +2998,24 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Swathimanivel_1234/</t>
+          <t>https://leetcode.com/u/yazhini2007/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>922525106345</t>
+          <t>922525106378</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SWATHI S</t>
+          <t>YOKESWARAN S</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>_swathi _3366</t>
+          <t>syokeswaran</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3025,24 +3025,24 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_swathi _3366/</t>
+          <t>https://leetcode.com/u/syokeswaran/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>922525106347</t>
+          <t>922525106337</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>TAMIL SELVAN R</t>
+          <t>SUGIDHARSHINI T</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Kdmif0HMNm</t>
+          <t>Sugi_07</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3052,24 +3052,24 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Kdmif0HMNm/</t>
+          <t>https://leetcode.com/u/Sugi_07/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>922525106348</t>
+          <t>922525106364</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>THAMARAI SELVI D</t>
+          <t>VIGNESH VELAN M</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>thamarai_04</t>
+          <t>Vicky_27_Velan</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3079,24 +3079,24 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/thamarai_04/</t>
+          <t>https://leetcode.com/u/Vicky_27_Velan/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>922525106349</t>
+          <t>922525106377</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>THAMEEM FARSHITHA A</t>
+          <t>YAZHINI V</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Thameem_786</t>
+          <t>VISU_YAZHU</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3106,24 +3106,24 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Thameem_786/</t>
+          <t>https://leetcode.com/u/VISU_YAZHU/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>922525106350</t>
+          <t>922525106346</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>THARANISH R</t>
+          <t>SWETHA E</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>THARANISH2008</t>
+          <t>Swetha_20_1</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3133,24 +3133,24 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/THARANISH2008/</t>
+          <t>https://leetcode.com/u/Swetha_20_1/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>922525106351</t>
+          <t>922525106338</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>THARUNIKA P</t>
+          <t>SUJEETH M</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Tharunika_12</t>
+          <t>SUJEETH77</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3160,24 +3160,24 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Tharunika_12/</t>
+          <t>https://leetcode.com/u/SUJEETH77/</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>922525106352</t>
+          <t>922525106339</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>THIRINESH KUMAR S</t>
+          <t>SUJITH RAJA B</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>THIRINESH KUMAR.S</t>
+          <t>mahi20_</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3187,24 +3187,24 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/THIRINESH KUMAR.S/</t>
+          <t>https://leetcode.com/u/mahi20_/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>922525106354</t>
+          <t>922525106353</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>THIRUMURUGAN S</t>
+          <t>THIRISHA C</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>thiru0211_</t>
+          <t>thirishavsb</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3214,24 +3214,24 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/thiru0211_/</t>
+          <t>https://leetcode.com/u/thirishavsb/</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>922525106355</t>
+          <t>922525106340</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>VAISHNAVI U</t>
+          <t>SUMITHRA S</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>vaish200</t>
+          <t>sumithra_16</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3241,24 +3241,24 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vaish200/</t>
+          <t>https://leetcode.com/u/sumithra_16/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>922525106356</t>
+          <t>922525106341</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>VASANTH KUMAR C</t>
+          <t>SURYA PRABHU S</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>VASANTH2007</t>
+          <t>surya001prabhu</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3268,24 +3268,24 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VASANTH2007/</t>
+          <t>https://leetcode.com/u/surya001prabhu/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>922525106357</t>
+          <t>922525106342</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>VASANTH S</t>
+          <t>SUSIDHARAN M</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>_vasanth_s_</t>
+          <t>Susidharan147</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3295,24 +3295,24 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_vasanth_s_/</t>
+          <t>https://leetcode.com/u/Susidharan147/</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>922525106358</t>
+          <t>922525106343</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>VASANTHA KUMAR D</t>
+          <t>SUTHARSHANA S</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Vasanthakumar12232</t>
+          <t>sutharshana743</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3322,24 +3322,24 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vasanthakumar12232/</t>
+          <t>https://leetcode.com/u/sutharshana743/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>922525106359</t>
+          <t>922525106344</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>VASANTHKUMAR R</t>
+          <t>SWATHI M</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>VasanthKumar008</t>
+          <t>Swathimanivel_1234</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3349,24 +3349,24 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VasanthKumar008/</t>
+          <t>https://leetcode.com/u/Swathimanivel_1234/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>922525106360</t>
+          <t>922525106345</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>VASUDEVAN G</t>
+          <t>SWATHI S</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>GTVASU2008</t>
+          <t>_swathi _3366</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3376,24 +3376,24 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/GTVASU2008/</t>
+          <t>https://leetcode.com/u/_swathi _3366/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>922525106361</t>
+          <t>922525106347</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>VASUKI K</t>
+          <t>TAMIL SELVAN R</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>vasuki</t>
+          <t>Kdmif0HMNm</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3403,24 +3403,24 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vasuki/</t>
+          <t>https://leetcode.com/u/Kdmif0HMNm/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>922525106362</t>
+          <t>922525106348</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>VELLIANGIRI R</t>
+          <t>THAMARAI SELVI D</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>velliangiri_R</t>
+          <t>thamarai_04</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3430,24 +3430,24 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/velliangiri_R/</t>
+          <t>https://leetcode.com/u/thamarai_04/</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>922525106363</t>
+          <t>922525106349</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>VIGNESH M</t>
+          <t>THAMEEM FARSHITHA A</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>O8bYDSRUbE</t>
+          <t>Thameem_786</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -3457,24 +3457,24 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/O8bYDSRUbE/</t>
+          <t>https://leetcode.com/u/Thameem_786/</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>922525106365</t>
+          <t>922525106350</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>VIGNESHWAR U</t>
+          <t>THARANISH R</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>VIGNESHWAR0221</t>
+          <t>THARANISH2008</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3484,24 +3484,24 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VIGNESHWAR0221/</t>
+          <t>https://leetcode.com/u/THARANISH2008/</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>922525106366</t>
+          <t>922525106351</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>VIJAYARAGAVAN R</t>
+          <t>THARUNIKA P</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>vijayaragavan1216</t>
+          <t>Tharunika_12</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vijayaragavan1216/</t>
+          <t>https://leetcode.com/u/Tharunika_12/</t>
         </is>
       </c>
     </row>

--- a/Students.xlsx
+++ b/Students.xlsx
@@ -1223,17 +1223,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>922525106280</t>
+          <t>922525106284</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SANTHOSH D</t>
+          <t>Santhosh S</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>santhosh7811</t>
+          <t>santhosh2407</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1243,24 +1243,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh7811/</t>
+          <t>https://leetcode.com/u/santhosh2407/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>922525106284</t>
+          <t>922525106285</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Santhosh S</t>
+          <t>SANTHOSH V</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>santhosh2407</t>
+          <t>santhosh8760</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1270,24 +1270,24 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh2407/</t>
+          <t>https://leetcode.com/u/santhosh8760/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>922525106285</t>
+          <t>922525106286</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SANTHOSH V</t>
+          <t>SARAN K</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>santhosh8760</t>
+          <t>saran32</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1297,24 +1297,24 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh8760/</t>
+          <t>https://leetcode.com/u/saran32/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>922525106286</t>
+          <t>922525106288</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SARAN K</t>
+          <t>SARAVANAN K</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>saran32</t>
+          <t>saravanan__k__</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1324,24 +1324,24 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saran32/</t>
+          <t>https://leetcode.com/u/saravanan__k__/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>922525106288</t>
+          <t>922525106289</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SARAVANAN K</t>
+          <t>SARAVANAN S</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>saravanan__k__</t>
+          <t>Saravanan_7525</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1351,24 +1351,24 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saravanan__k__/</t>
+          <t>https://leetcode.com/u/Saravanan_7525/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>922525106289</t>
+          <t>922525106290</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SARAVANAN S</t>
+          <t>SARIKA M P</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Saravanan_7525</t>
+          <t>sarika_5408</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1378,24 +1378,24 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Saravanan_7525/</t>
+          <t>https://leetcode.com/u/sarika_5408/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>922525106290</t>
+          <t>922525106296</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SARIKA M P</t>
+          <t>SELVAKUMAR K</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>sarika_5408</t>
+          <t>Selvakumarsk-32</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1405,24 +1405,24 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sarika_5408/</t>
+          <t>https://leetcode.com/u/Selvakumarsk-32/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>922525106296</t>
+          <t>922525106297</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SELVAKUMAR K</t>
+          <t>SELVAPRAGADEESH S</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Selvakumarsk-32</t>
+          <t>Selvapragadeesh</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1432,24 +1432,24 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvakumarsk-32/</t>
+          <t>https://leetcode.com/u/Selvapragadeesh/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>922525106297</t>
+          <t>922525106298</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SELVAPRAGADEESH S</t>
+          <t>SELVA RAGAVAN</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Selvapragadeesh</t>
+          <t>Selvax07</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1459,24 +1459,24 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvapragadeesh/</t>
+          <t>https://leetcode.com/u/Selvax07/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>922525106298</t>
+          <t>922525106299</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SELVA RAGAVAN</t>
+          <t>SENTHAMIZHSELVAN K</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Selvax07</t>
+          <t>Senthamizh08</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1486,24 +1486,24 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvax07/</t>
+          <t>https://leetcode.com/u/Senthamizh08/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>922525106299</t>
+          <t>922525106300</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SENTHAMIZHSELVAN K</t>
+          <t>Senthil.S</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Senthamizh08</t>
+          <t>Jna76WrjNd</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1513,24 +1513,24 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Senthamizh08/</t>
+          <t>https://leetcode.com/u/Jna76WrjNd/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>922525106300</t>
+          <t>922525106302</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Senthil.S</t>
+          <t>SHAHANA S</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Jna76WrjNd</t>
+          <t>shahana_pandiraj04</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1540,24 +1540,24 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Jna76WrjNd/</t>
+          <t>https://leetcode.com/u/shahana_pandiraj04/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>922525106302</t>
+          <t>922525106303</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SHAHANA S</t>
+          <t>SHANTHINI C</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>shahana_pandiraj04</t>
+          <t>ShanthiniChelladurai</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1567,24 +1567,24 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shahana_pandiraj04/</t>
+          <t>https://leetcode.com/u/ShanthiniChelladurai/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>922525106303</t>
+          <t>922525106305</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SHANTHINI C</t>
+          <t>SHARATH P</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ShanthiniChelladurai</t>
+          <t>sharath_1010</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1594,24 +1594,24 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/ShanthiniChelladurai/</t>
+          <t>https://leetcode.com/u/sharath_1010/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>922525106305</t>
+          <t>922525106308</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SHARATH P</t>
+          <t>SHREE HARINI L</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>sharath_1010</t>
+          <t>Shree_Harini478</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1621,24 +1621,24 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sharath_1010/</t>
+          <t>https://leetcode.com/u/Shree_Harini478/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>922525106308</t>
+          <t>922525106310</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SHREE HARINI L</t>
+          <t>SIVA MANIKANDAN K</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Shree_Harini478</t>
+          <t>9043374912</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1648,24 +1648,24 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Shree_Harini478/</t>
+          <t>https://leetcode.com/u/9043374912/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>922525106310</t>
+          <t>922525106311</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SIVA MANIKANDAN K</t>
+          <t>SIVA PRAKASH M</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>9043374912</t>
+          <t>sivaprakash_0406</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1675,24 +1675,24 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/9043374912/</t>
+          <t>https://leetcode.com/u/sivaprakash_0406/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>922525106311</t>
+          <t>922525106312</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SIVA PRAKASH M</t>
+          <t>SIVADHARSHINI D</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>sivaprakash_0406</t>
+          <t>dharshinideivsigamani</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1702,24 +1702,24 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivaprakash_0406/</t>
+          <t>https://leetcode.com/u/dharshinideivsigamani/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>922525106312</t>
+          <t>922525106313</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SIVADHARSHINI D</t>
+          <t>SIVAGNANAM M</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>dharshinideivsigamani</t>
+          <t>sivagnanam3344</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1729,24 +1729,24 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/dharshinideivsigamani/</t>
+          <t>https://leetcode.com/u/sivagnanam3344/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>922525106313</t>
+          <t>922525106315</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SIVAGNANAM M</t>
+          <t>SIVANESH G</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>sivagnanam3344</t>
+          <t>GSIVANESH</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivagnanam3344/</t>
+          <t>https://leetcode.com/u/GSIVANESH/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>922525106315</t>
+          <t>922525106282</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SIVANESH G</t>
+          <t>SANTHOSH PRIYAN S</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>GSIVANESH</t>
+          <t>8925787430</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1783,24 +1783,24 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/GSIVANESH/</t>
+          <t>https://leetcode.com/u/8925787430/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>922525106282</t>
+          <t>922525106280</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SANTHOSH PRIYAN S</t>
+          <t>SANTHOSH D</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>8925787430</t>
+          <t>santhosh7811</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/8925787430/</t>
+          <t>https://leetcode.com/u/santhosh7811/</t>
         </is>
       </c>
     </row>
@@ -1979,17 +1979,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>922525106366</t>
+          <t>922525106358</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>VIJAYARAGAVAN R</t>
+          <t>VASANTHA KUMAR D</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>vijayaragavan1216</t>
+          <t>Vasanthakumar12232</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1999,24 +1999,24 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vijayaragavan1216/</t>
+          <t>https://leetcode.com/u/Vasanthakumar12232/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>922525106358</t>
+          <t>922525106352</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>VASANTHA KUMAR D</t>
+          <t>THIRINESH KUMAR S</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Vasanthakumar12232</t>
+          <t>THIRINESH KUMAR.S</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2026,24 +2026,24 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Vasanthakumar12232/</t>
+          <t>https://leetcode.com/u/THIRINESH KUMAR.S/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>922525106352</t>
+          <t>922525106354</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>THIRINESH KUMAR S</t>
+          <t>THIRUMURUGAN S</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>THIRINESH KUMAR.S</t>
+          <t>thiru0211_</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2053,24 +2053,24 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/THIRINESH KUMAR.S/</t>
+          <t>https://leetcode.com/u/thiru0211_/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>922525106354</t>
+          <t>922525106355</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>THIRUMURUGAN S</t>
+          <t>VAISHNAVI U</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>thiru0211_</t>
+          <t>vaish200</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2080,24 +2080,24 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/thiru0211_/</t>
+          <t>https://leetcode.com/u/vaish200/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>922525106355</t>
+          <t>922525106356</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>VAISHNAVI U</t>
+          <t>VASANTH KUMAR C</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>vaish200</t>
+          <t>VASANTH2007</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2107,24 +2107,24 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vaish200/</t>
+          <t>https://leetcode.com/u/VASANTH2007/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>922525106356</t>
+          <t>922525106357</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>VASANTH KUMAR C</t>
+          <t>VASANTH S</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>VASANTH2007</t>
+          <t>_vasanth_s_</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2134,24 +2134,24 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VASANTH2007/</t>
+          <t>https://leetcode.com/u/_vasanth_s_/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>922525106357</t>
+          <t>922525106359</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>VASANTH S</t>
+          <t>VASANTHKUMAR R</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>_vasanth_s_</t>
+          <t>VasanthKumar008</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2161,24 +2161,24 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_vasanth_s_/</t>
+          <t>https://leetcode.com/u/VasanthKumar008/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>922525106359</t>
+          <t>922525106366</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>VASANTHKUMAR R</t>
+          <t>VIJAYARAGAVAN R</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>VasanthKumar008</t>
+          <t>vijayaragavan1216</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/VasanthKumar008/</t>
+          <t>https://leetcode.com/u/vijayaragavan1216/</t>
         </is>
       </c>
     </row>
@@ -2330,17 +2330,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>922525106372</t>
+          <t>922525106316</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>VISHWAJETH A M</t>
+          <t>SIVARANJAN M P</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>vishwajeth</t>
+          <t>SIVARANJAN_MP</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2350,24 +2350,24 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/vishwajeth/</t>
+          <t>https://leetcode.com/u/SIVARANJAN_MP/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>922525106316</t>
+          <t>922525106317</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SIVARANJAN M P</t>
+          <t>SIVASANJEEV P</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>SIVARANJAN_MP</t>
+          <t>Sivasanjeev16</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2377,24 +2377,24 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SIVARANJAN_MP/</t>
+          <t>https://leetcode.com/u/Sivasanjeev16/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>922525106317</t>
+          <t>922525106318</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SIVASANJEEV P</t>
+          <t>SIVASUBRAMANI A</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Sivasanjeev16</t>
+          <t>AK_Siva</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2404,24 +2404,24 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sivasanjeev16/</t>
+          <t>https://leetcode.com/u/AK_Siva/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>922525106318</t>
+          <t>922525106319</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SIVASUBRAMANI A</t>
+          <t>SIVATHARUN C</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AK_Siva</t>
+          <t>sivatharun22</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2431,24 +2431,24 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/AK_Siva/</t>
+          <t>https://leetcode.com/u/sivatharun22/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>922525106319</t>
+          <t>922525106320</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SIVATHARUN C</t>
+          <t>SOBIKA R</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>sivatharun22</t>
+          <t>_sobika_R</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2458,24 +2458,24 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivatharun22/</t>
+          <t>https://leetcode.com/u/_sobika_R/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>922525106320</t>
+          <t>922525106321</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SOBIKA R</t>
+          <t>SREE DHARANI C</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>_sobika_R</t>
+          <t>SREEDHARANI_14</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2485,24 +2485,24 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/_sobika_R/</t>
+          <t>https://leetcode.com/u/SREEDHARANI_14/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>922525106321</t>
+          <t>922525106372</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SREE DHARANI C</t>
+          <t>VISHWAJETH A M</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SREEDHARANI_14</t>
+          <t>vishwajeth</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SREEDHARANI_14/</t>
+          <t>https://leetcode.com/u/vishwajeth/</t>
         </is>
       </c>
     </row>
